--- a/gisaid_batch_uploader_mira_batch_01.xlsx
+++ b/gisaid_batch_uploader_mira_batch_01.xlsx
@@ -680,7 +680,6 @@
           <t>H5N1</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>Original</t>
@@ -701,7 +700,6 @@
           <t>La_Milina</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>Sula variegata</t>
@@ -712,20 +710,11 @@
           <t>Piquero peruano</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
           <t>Flu-0008|A_NS</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr">
         <is>
           <t>Flu-0008</t>
@@ -761,28 +750,11 @@
           <t>2023-05-10</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="inlineStr"/>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="inlineStr"/>
       <c r="AS2" t="inlineStr">
         <is>
           <t>Confirmed segments: NS; source institution: MAATE; originating lab: MAATE; partial segments only where applicable.</t>
         </is>
       </c>
-      <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -805,7 +777,6 @@
           <t>H5N1</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>Original</t>
@@ -821,8 +792,6 @@
           <t>Morona Santiago</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>Gallus gallus domesticus</t>
@@ -833,15 +802,11 @@
           <t>Aves de corral</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>Flu-0009|A_NA</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
           <t>Flu-0009|A_MP</t>
@@ -857,8 +822,6 @@
           <t>Flu-0009|A_NP</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr">
         <is>
           <t>Flu-0009</t>
@@ -894,28 +857,11 @@
           <t>2023-04-13</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr"/>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="inlineStr"/>
-      <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr"/>
-      <c r="AM3" t="inlineStr"/>
-      <c r="AN3" t="inlineStr"/>
-      <c r="AO3" t="inlineStr"/>
-      <c r="AP3" t="inlineStr"/>
-      <c r="AQ3" t="inlineStr"/>
-      <c r="AR3" t="inlineStr"/>
       <c r="AS3" t="inlineStr">
         <is>
           <t>Confirmed segments: NP,NA,MP,NS; source institution: Agrocalidad; originating lab: AGROCALIDAD; partial segments only where applicable.</t>
         </is>
       </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AU3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -938,7 +884,6 @@
           <t>H5N1</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>Original</t>
@@ -954,8 +899,6 @@
           <t>Napo</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>Gallus gallus domesticus</t>
@@ -966,11 +909,6 @@
           <t>Aves de corral</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
           <t>Flu-0011|A_MP</t>
@@ -981,9 +919,6 @@
           <t>Flu-0011|A_NS</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr">
         <is>
           <t>Flu-0011</t>
@@ -1019,28 +954,11 @@
           <t>2023-04-02</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr"/>
-      <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr"/>
-      <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr"/>
-      <c r="AM4" t="inlineStr"/>
-      <c r="AN4" t="inlineStr"/>
-      <c r="AO4" t="inlineStr"/>
-      <c r="AP4" t="inlineStr"/>
-      <c r="AQ4" t="inlineStr"/>
-      <c r="AR4" t="inlineStr"/>
       <c r="AS4" t="inlineStr">
         <is>
           <t>Confirmed segments: MP,NS; source institution: Agrocalidad; originating lab: AGROCALIDAD; partial segments only where applicable.</t>
         </is>
       </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AU4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1063,7 +981,6 @@
           <t>H5N1</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>Original</t>
@@ -1079,8 +996,6 @@
           <t>Tungurahua</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>Gallus gallus domesticus</t>
@@ -1101,9 +1016,6 @@
           <t>Flu-0013|A_NA</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
           <t>Flu-0013|A_MP</t>
@@ -1119,8 +1031,6 @@
           <t>Flu-0013|A_NP</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr">
         <is>
           <t>Flu-0013</t>
@@ -1156,28 +1066,11 @@
           <t>2023-01-20</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr"/>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="inlineStr"/>
-      <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr"/>
-      <c r="AJ5" t="inlineStr"/>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr"/>
-      <c r="AM5" t="inlineStr"/>
-      <c r="AN5" t="inlineStr"/>
-      <c r="AO5" t="inlineStr"/>
-      <c r="AP5" t="inlineStr"/>
-      <c r="AQ5" t="inlineStr"/>
-      <c r="AR5" t="inlineStr"/>
       <c r="AS5" t="inlineStr">
         <is>
           <t>Confirmed segments: HA,NP,NA,MP,NS; source institution: Agrocalidad; originating lab: AGROCALIDAD; partial segments only where applicable.</t>
         </is>
       </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AU5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1200,7 +1093,6 @@
           <t>H5N1</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>Original</t>
@@ -1221,27 +1113,16 @@
           <t>Salinas</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>Sula nebouxii</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
           <t>Flu-0014|A_NS</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr">
         <is>
           <t>Flu-0014</t>
@@ -1277,28 +1158,11 @@
           <t>2023-05-27</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr"/>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="inlineStr"/>
-      <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr"/>
-      <c r="AJ6" t="inlineStr"/>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr"/>
-      <c r="AM6" t="inlineStr"/>
-      <c r="AN6" t="inlineStr"/>
-      <c r="AO6" t="inlineStr"/>
-      <c r="AP6" t="inlineStr"/>
-      <c r="AQ6" t="inlineStr"/>
-      <c r="AR6" t="inlineStr"/>
       <c r="AS6" t="inlineStr">
         <is>
           <t>Confirmed segments: NS; source institution: MAATE; originating lab: MAATE; partial segments only where applicable.</t>
         </is>
       </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AU6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1321,7 +1185,6 @@
           <t>H5N1</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>Original</t>
@@ -1342,7 +1205,6 @@
           <t>Montañita</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>avian</t>
@@ -1353,20 +1215,11 @@
           <t>unknown bird species</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
           <t>Flu-0018|A_NS</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr">
         <is>
           <t>Flu-0018</t>
@@ -1402,28 +1255,11 @@
           <t>2023-06-01</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr"/>
-      <c r="AE7" t="inlineStr"/>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="inlineStr"/>
-      <c r="AH7" t="inlineStr"/>
-      <c r="AI7" t="inlineStr"/>
-      <c r="AJ7" t="inlineStr"/>
-      <c r="AK7" t="inlineStr"/>
-      <c r="AL7" t="inlineStr"/>
-      <c r="AM7" t="inlineStr"/>
-      <c r="AN7" t="inlineStr"/>
-      <c r="AO7" t="inlineStr"/>
-      <c r="AP7" t="inlineStr"/>
-      <c r="AQ7" t="inlineStr"/>
-      <c r="AR7" t="inlineStr"/>
       <c r="AS7" t="inlineStr">
         <is>
           <t>Confirmed segments: NS; source institution: MAATE; originating lab: MAATE; partial segments only where applicable.</t>
         </is>
       </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AU7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1446,7 +1282,6 @@
           <t>H5N1</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>Original</t>
@@ -1467,7 +1302,6 @@
           <t>San Lorenzo</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>Ardenna grisea</t>
@@ -1488,9 +1322,6 @@
           <t>Flu-0023|A_NA</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
           <t>Flu-0023|A_MP</t>
@@ -1506,8 +1337,6 @@
           <t>Flu-0023|A_NP</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr">
         <is>
           <t>Flu-0023</t>
@@ -1543,28 +1372,11 @@
           <t>2023-06-02</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr"/>
-      <c r="AE8" t="inlineStr"/>
-      <c r="AF8" t="inlineStr"/>
-      <c r="AG8" t="inlineStr"/>
-      <c r="AH8" t="inlineStr"/>
-      <c r="AI8" t="inlineStr"/>
-      <c r="AJ8" t="inlineStr"/>
-      <c r="AK8" t="inlineStr"/>
-      <c r="AL8" t="inlineStr"/>
-      <c r="AM8" t="inlineStr"/>
-      <c r="AN8" t="inlineStr"/>
-      <c r="AO8" t="inlineStr"/>
-      <c r="AP8" t="inlineStr"/>
-      <c r="AQ8" t="inlineStr"/>
-      <c r="AR8" t="inlineStr"/>
       <c r="AS8" t="inlineStr">
         <is>
           <t>Confirmed segments: HA,NP,NA,MP,NS; source institution: MAATE; originating lab: MAATE; partial segments only where applicable.</t>
         </is>
       </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AU8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1587,7 +1399,6 @@
           <t>H5N1</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>Original</t>
@@ -1608,18 +1419,11 @@
           <t>Ayangue</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>Puffinus sp.</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
           <t>Flu-0027|A_MP</t>
@@ -1630,9 +1434,6 @@
           <t>Flu-0027|A_NS</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr">
         <is>
           <t>Flu-0027</t>
@@ -1648,7 +1449,6 @@
           <t>3761</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr">
         <is>
           <t>05</t>
@@ -1664,28 +1464,11 @@
           <t>2023-05-30</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr"/>
-      <c r="AE9" t="inlineStr"/>
-      <c r="AF9" t="inlineStr"/>
-      <c r="AG9" t="inlineStr"/>
-      <c r="AH9" t="inlineStr"/>
-      <c r="AI9" t="inlineStr"/>
-      <c r="AJ9" t="inlineStr"/>
-      <c r="AK9" t="inlineStr"/>
-      <c r="AL9" t="inlineStr"/>
-      <c r="AM9" t="inlineStr"/>
-      <c r="AN9" t="inlineStr"/>
-      <c r="AO9" t="inlineStr"/>
-      <c r="AP9" t="inlineStr"/>
-      <c r="AQ9" t="inlineStr"/>
-      <c r="AR9" t="inlineStr"/>
       <c r="AS9" t="inlineStr">
         <is>
           <t>Confirmed segments: MP,NS; source institution: MAATE; originating lab: MAATE; partial segments only where applicable.</t>
         </is>
       </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AU9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1708,7 +1491,6 @@
           <t>H5N1</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>Original</t>
@@ -1729,18 +1511,11 @@
           <t>Muisne</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>Thalasseus elegans</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
           <t>Flu-0035|A_MP</t>
@@ -1756,8 +1531,6 @@
           <t>Flu-0035|A_NP</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr">
         <is>
           <t>Flu-0035</t>
@@ -1793,28 +1566,11 @@
           <t>2023-05-31</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr"/>
-      <c r="AE10" t="inlineStr"/>
-      <c r="AF10" t="inlineStr"/>
-      <c r="AG10" t="inlineStr"/>
-      <c r="AH10" t="inlineStr"/>
-      <c r="AI10" t="inlineStr"/>
-      <c r="AJ10" t="inlineStr"/>
-      <c r="AK10" t="inlineStr"/>
-      <c r="AL10" t="inlineStr"/>
-      <c r="AM10" t="inlineStr"/>
-      <c r="AN10" t="inlineStr"/>
-      <c r="AO10" t="inlineStr"/>
-      <c r="AP10" t="inlineStr"/>
-      <c r="AQ10" t="inlineStr"/>
-      <c r="AR10" t="inlineStr"/>
       <c r="AS10" t="inlineStr">
         <is>
           <t>Confirmed segments: NP,MP,NS; source institution: MAATE; originating lab: MAATE; partial segments only where applicable.</t>
         </is>
       </c>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AU10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1837,7 +1593,6 @@
           <t>H5N1</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>Original</t>
@@ -1858,7 +1613,6 @@
           <t>Manta</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>Ardenna grisea</t>
@@ -1869,20 +1623,11 @@
           <t>Pardela gris</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
           <t>Flu-0055|A_MP</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr">
         <is>
           <t>Flu-0055</t>
@@ -1918,28 +1663,11 @@
           <t>2023-06-06</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr"/>
-      <c r="AE11" t="inlineStr"/>
-      <c r="AF11" t="inlineStr"/>
-      <c r="AG11" t="inlineStr"/>
-      <c r="AH11" t="inlineStr"/>
-      <c r="AI11" t="inlineStr"/>
-      <c r="AJ11" t="inlineStr"/>
-      <c r="AK11" t="inlineStr"/>
-      <c r="AL11" t="inlineStr"/>
-      <c r="AM11" t="inlineStr"/>
-      <c r="AN11" t="inlineStr"/>
-      <c r="AO11" t="inlineStr"/>
-      <c r="AP11" t="inlineStr"/>
-      <c r="AQ11" t="inlineStr"/>
-      <c r="AR11" t="inlineStr"/>
       <c r="AS11" t="inlineStr">
         <is>
           <t>Confirmed segments: MP; source institution: MAATE; originating lab: MAATE; partial segments only where applicable.</t>
         </is>
       </c>
-      <c r="AT11" t="inlineStr"/>
-      <c r="AU11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1962,7 +1690,6 @@
           <t>H5N1</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>Original</t>
@@ -1983,27 +1710,16 @@
           <t>Puerto Engabao</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>Ardenna grisea</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
           <t>Flu-0205|A_MP</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr">
         <is>
           <t>Flu-0205</t>
@@ -2039,20 +1755,6 @@
           <t>2023-07-11</t>
         </is>
       </c>
-      <c r="AD12" t="inlineStr"/>
-      <c r="AE12" t="inlineStr"/>
-      <c r="AF12" t="inlineStr"/>
-      <c r="AG12" t="inlineStr"/>
-      <c r="AH12" t="inlineStr"/>
-      <c r="AI12" t="inlineStr"/>
-      <c r="AJ12" t="inlineStr"/>
-      <c r="AK12" t="inlineStr"/>
-      <c r="AL12" t="inlineStr"/>
-      <c r="AM12" t="inlineStr"/>
-      <c r="AN12" t="inlineStr"/>
-      <c r="AO12" t="inlineStr"/>
-      <c r="AP12" t="inlineStr"/>
-      <c r="AQ12" t="inlineStr"/>
       <c r="AR12" t="inlineStr">
         <is>
           <t>Dead</t>
@@ -2063,8 +1765,6 @@
           <t>Confirmed segments: MP; source institution: USFQ; originating lab: MAATE; partial segments only where applicable.</t>
         </is>
       </c>
-      <c r="AT12" t="inlineStr"/>
-      <c r="AU12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2087,7 +1787,6 @@
           <t>H5N1</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>Original</t>
@@ -2108,18 +1807,11 @@
           <t>Puerto Engabao</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>Ardenna grisea</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
         <is>
           <t>Flu-0206|A_MP</t>
@@ -2130,9 +1822,6 @@
           <t>Flu-0206|A_NS</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr">
         <is>
           <t>Flu-0206</t>
@@ -2168,20 +1857,6 @@
           <t>2023-07-11</t>
         </is>
       </c>
-      <c r="AD13" t="inlineStr"/>
-      <c r="AE13" t="inlineStr"/>
-      <c r="AF13" t="inlineStr"/>
-      <c r="AG13" t="inlineStr"/>
-      <c r="AH13" t="inlineStr"/>
-      <c r="AI13" t="inlineStr"/>
-      <c r="AJ13" t="inlineStr"/>
-      <c r="AK13" t="inlineStr"/>
-      <c r="AL13" t="inlineStr"/>
-      <c r="AM13" t="inlineStr"/>
-      <c r="AN13" t="inlineStr"/>
-      <c r="AO13" t="inlineStr"/>
-      <c r="AP13" t="inlineStr"/>
-      <c r="AQ13" t="inlineStr"/>
       <c r="AR13" t="inlineStr">
         <is>
           <t>Dead</t>
@@ -2192,8 +1867,6 @@
           <t>Confirmed segments: MP,NS; source institution: USFQ; originating lab: MAATE; partial segments only where applicable.</t>
         </is>
       </c>
-      <c r="AT13" t="inlineStr"/>
-      <c r="AU13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2216,7 +1889,6 @@
           <t>H5N1</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>Original</t>
@@ -2237,7 +1909,6 @@
           <t>Ambato</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>duck</t>
@@ -2248,15 +1919,11 @@
           <t>Patos</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
           <t>Flu-0314|A_NA</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
         <is>
           <t>Flu-0314|A_MP</t>
@@ -2267,9 +1934,6 @@
           <t>Flu-0314|A_NS</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr">
         <is>
           <t>Flu-0314</t>
@@ -2305,28 +1969,11 @@
           <t>2023-07-24</t>
         </is>
       </c>
-      <c r="AD14" t="inlineStr"/>
-      <c r="AE14" t="inlineStr"/>
-      <c r="AF14" t="inlineStr"/>
-      <c r="AG14" t="inlineStr"/>
-      <c r="AH14" t="inlineStr"/>
-      <c r="AI14" t="inlineStr"/>
-      <c r="AJ14" t="inlineStr"/>
-      <c r="AK14" t="inlineStr"/>
-      <c r="AL14" t="inlineStr"/>
-      <c r="AM14" t="inlineStr"/>
-      <c r="AN14" t="inlineStr"/>
-      <c r="AO14" t="inlineStr"/>
-      <c r="AP14" t="inlineStr"/>
-      <c r="AQ14" t="inlineStr"/>
-      <c r="AR14" t="inlineStr"/>
       <c r="AS14" t="inlineStr">
         <is>
           <t>Confirmed segments: NA,MP,NS; source institution: Agrocalidad; originating lab: AGROCALIDAD; partial segments only where applicable.</t>
         </is>
       </c>
-      <c r="AT14" t="inlineStr"/>
-      <c r="AU14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2349,7 +1996,6 @@
           <t>H5N1</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>Original</t>
@@ -2370,7 +2016,6 @@
           <t>Salcedo</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>Gallus gallus domesticus</t>
@@ -2421,8 +2066,6 @@
           <t>Flu-0316|A_NP</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr">
         <is>
           <t>Flu-0316</t>
@@ -2458,28 +2101,11 @@
           <t>2023-07-28</t>
         </is>
       </c>
-      <c r="AD15" t="inlineStr"/>
-      <c r="AE15" t="inlineStr"/>
-      <c r="AF15" t="inlineStr"/>
-      <c r="AG15" t="inlineStr"/>
-      <c r="AH15" t="inlineStr"/>
-      <c r="AI15" t="inlineStr"/>
-      <c r="AJ15" t="inlineStr"/>
-      <c r="AK15" t="inlineStr"/>
-      <c r="AL15" t="inlineStr"/>
-      <c r="AM15" t="inlineStr"/>
-      <c r="AN15" t="inlineStr"/>
-      <c r="AO15" t="inlineStr"/>
-      <c r="AP15" t="inlineStr"/>
-      <c r="AQ15" t="inlineStr"/>
-      <c r="AR15" t="inlineStr"/>
       <c r="AS15" t="inlineStr">
         <is>
           <t>Confirmed segments: PB2,PB1,PA,HA,NP,NA,MP,NS; source institution: Agrocalidad; originating lab: AGROCALIDAD; partial segments only where applicable.</t>
         </is>
       </c>
-      <c r="AT15" t="inlineStr"/>
-      <c r="AU15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2502,7 +2128,6 @@
           <t>H5N1</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>Original</t>
@@ -2523,7 +2148,6 @@
           <t>Salcedo</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>Gallus gallus domesticus</t>
@@ -2574,8 +2198,6 @@
           <t>Flu-0317|A_NP</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr">
         <is>
           <t>Flu-0317</t>
@@ -2611,28 +2233,11 @@
           <t>2023-07-28</t>
         </is>
       </c>
-      <c r="AD16" t="inlineStr"/>
-      <c r="AE16" t="inlineStr"/>
-      <c r="AF16" t="inlineStr"/>
-      <c r="AG16" t="inlineStr"/>
-      <c r="AH16" t="inlineStr"/>
-      <c r="AI16" t="inlineStr"/>
-      <c r="AJ16" t="inlineStr"/>
-      <c r="AK16" t="inlineStr"/>
-      <c r="AL16" t="inlineStr"/>
-      <c r="AM16" t="inlineStr"/>
-      <c r="AN16" t="inlineStr"/>
-      <c r="AO16" t="inlineStr"/>
-      <c r="AP16" t="inlineStr"/>
-      <c r="AQ16" t="inlineStr"/>
-      <c r="AR16" t="inlineStr"/>
       <c r="AS16" t="inlineStr">
         <is>
           <t>Confirmed segments: PB2,PB1,PA,HA,NP,NA,MP,NS; source institution: Agrocalidad; originating lab: AGROCALIDAD; partial segments only where applicable.</t>
         </is>
       </c>
-      <c r="AT16" t="inlineStr"/>
-      <c r="AU16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2655,7 +2260,6 @@
           <t>H5N1</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>Original</t>
@@ -2671,8 +2275,6 @@
           <t>Tungurahua</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>Gallus gallus domesticus</t>
@@ -2683,7 +2285,6 @@
           <t>Aves de corral</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
           <t>Flu-0318|A_NA</t>
@@ -2719,8 +2320,6 @@
           <t>Flu-0318|A_NP</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr">
         <is>
           <t>Flu-0318</t>
@@ -2756,28 +2355,11 @@
           <t>2023-07-24</t>
         </is>
       </c>
-      <c r="AD17" t="inlineStr"/>
-      <c r="AE17" t="inlineStr"/>
-      <c r="AF17" t="inlineStr"/>
-      <c r="AG17" t="inlineStr"/>
-      <c r="AH17" t="inlineStr"/>
-      <c r="AI17" t="inlineStr"/>
-      <c r="AJ17" t="inlineStr"/>
-      <c r="AK17" t="inlineStr"/>
-      <c r="AL17" t="inlineStr"/>
-      <c r="AM17" t="inlineStr"/>
-      <c r="AN17" t="inlineStr"/>
-      <c r="AO17" t="inlineStr"/>
-      <c r="AP17" t="inlineStr"/>
-      <c r="AQ17" t="inlineStr"/>
-      <c r="AR17" t="inlineStr"/>
       <c r="AS17" t="inlineStr">
         <is>
           <t>Confirmed segments: PB2,PB1,PA,NP,NA,MP,NS; source institution: Agrocalidad; originating lab: AGROCALIDAD; partial segments only where applicable.</t>
         </is>
       </c>
-      <c r="AT17" t="inlineStr"/>
-      <c r="AU17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2800,7 +2382,6 @@
           <t>H5N1</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
           <t>Original</t>
@@ -2816,8 +2397,6 @@
           <t>Cotopaxi</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>Gallus gallus domesticus</t>
@@ -2828,15 +2407,11 @@
           <t>Aves de corral</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
           <t>Flu-0321|A_NA</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
         <is>
           <t>Flu-0321|A_MP</t>
@@ -2847,9 +2422,6 @@
           <t>Flu-0321|A_NS</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr">
         <is>
           <t>Flu-0321</t>
@@ -2885,28 +2457,11 @@
           <t>2023-07-28</t>
         </is>
       </c>
-      <c r="AD18" t="inlineStr"/>
-      <c r="AE18" t="inlineStr"/>
-      <c r="AF18" t="inlineStr"/>
-      <c r="AG18" t="inlineStr"/>
-      <c r="AH18" t="inlineStr"/>
-      <c r="AI18" t="inlineStr"/>
-      <c r="AJ18" t="inlineStr"/>
-      <c r="AK18" t="inlineStr"/>
-      <c r="AL18" t="inlineStr"/>
-      <c r="AM18" t="inlineStr"/>
-      <c r="AN18" t="inlineStr"/>
-      <c r="AO18" t="inlineStr"/>
-      <c r="AP18" t="inlineStr"/>
-      <c r="AQ18" t="inlineStr"/>
-      <c r="AR18" t="inlineStr"/>
       <c r="AS18" t="inlineStr">
         <is>
           <t>Confirmed segments: NA,MP,NS; source institution: Agrocalidad; originating lab: AGROCALIDAD; partial segments only where applicable.</t>
         </is>
       </c>
-      <c r="AT18" t="inlineStr"/>
-      <c r="AU18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2929,7 +2484,6 @@
           <t>H5N1</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>Original</t>
@@ -2945,8 +2499,6 @@
           <t>Pichincha</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>Gallus gallus domesticus</t>
@@ -2957,11 +2509,6 @@
           <t>Aves de corral</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
         <is>
           <t>Flu-0323|A_MP</t>
@@ -2972,9 +2519,6 @@
           <t>Flu-0323|A_NS</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr">
         <is>
           <t>Flu-0323</t>
@@ -3010,28 +2554,11 @@
           <t>2023-08-03</t>
         </is>
       </c>
-      <c r="AD19" t="inlineStr"/>
-      <c r="AE19" t="inlineStr"/>
-      <c r="AF19" t="inlineStr"/>
-      <c r="AG19" t="inlineStr"/>
-      <c r="AH19" t="inlineStr"/>
-      <c r="AI19" t="inlineStr"/>
-      <c r="AJ19" t="inlineStr"/>
-      <c r="AK19" t="inlineStr"/>
-      <c r="AL19" t="inlineStr"/>
-      <c r="AM19" t="inlineStr"/>
-      <c r="AN19" t="inlineStr"/>
-      <c r="AO19" t="inlineStr"/>
-      <c r="AP19" t="inlineStr"/>
-      <c r="AQ19" t="inlineStr"/>
-      <c r="AR19" t="inlineStr"/>
       <c r="AS19" t="inlineStr">
         <is>
           <t>Confirmed segments: MP,NS; source institution: Agrocalidad; originating lab: AGROCALIDAD; partial segments only where applicable.</t>
         </is>
       </c>
-      <c r="AT19" t="inlineStr"/>
-      <c r="AU19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3054,7 +2581,6 @@
           <t>H5N1</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>Original</t>
@@ -3070,8 +2596,6 @@
           <t>Pichincha</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>Gallus gallus domesticus</t>
@@ -3082,11 +2606,6 @@
           <t>Aves de corral</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
         <is>
           <t>Flu-0325|A_MP</t>
@@ -3102,8 +2621,6 @@
           <t>Flu-0325|A_NP</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr">
         <is>
           <t>Flu-0325</t>
@@ -3139,28 +2656,11 @@
           <t>2023-08-03</t>
         </is>
       </c>
-      <c r="AD20" t="inlineStr"/>
-      <c r="AE20" t="inlineStr"/>
-      <c r="AF20" t="inlineStr"/>
-      <c r="AG20" t="inlineStr"/>
-      <c r="AH20" t="inlineStr"/>
-      <c r="AI20" t="inlineStr"/>
-      <c r="AJ20" t="inlineStr"/>
-      <c r="AK20" t="inlineStr"/>
-      <c r="AL20" t="inlineStr"/>
-      <c r="AM20" t="inlineStr"/>
-      <c r="AN20" t="inlineStr"/>
-      <c r="AO20" t="inlineStr"/>
-      <c r="AP20" t="inlineStr"/>
-      <c r="AQ20" t="inlineStr"/>
-      <c r="AR20" t="inlineStr"/>
       <c r="AS20" t="inlineStr">
         <is>
           <t>Confirmed segments: NP,MP,NS; source institution: Agrocalidad; originating lab: AGROCALIDAD; partial segments only where applicable.</t>
         </is>
       </c>
-      <c r="AT20" t="inlineStr"/>
-      <c r="AU20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3183,7 +2683,6 @@
           <t>H5N1</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>Original</t>
@@ -3199,8 +2698,6 @@
           <t>Pichincha</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>Gallus gallus domesticus</t>
@@ -3211,11 +2708,6 @@
           <t>Aves de corral</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
         <is>
           <t>Flu-0326|A_MP</t>
@@ -3231,8 +2723,6 @@
           <t>Flu-0326|A_NP</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr">
         <is>
           <t>Flu-0326</t>
@@ -3268,28 +2758,11 @@
           <t>2023-08-03</t>
         </is>
       </c>
-      <c r="AD21" t="inlineStr"/>
-      <c r="AE21" t="inlineStr"/>
-      <c r="AF21" t="inlineStr"/>
-      <c r="AG21" t="inlineStr"/>
-      <c r="AH21" t="inlineStr"/>
-      <c r="AI21" t="inlineStr"/>
-      <c r="AJ21" t="inlineStr"/>
-      <c r="AK21" t="inlineStr"/>
-      <c r="AL21" t="inlineStr"/>
-      <c r="AM21" t="inlineStr"/>
-      <c r="AN21" t="inlineStr"/>
-      <c r="AO21" t="inlineStr"/>
-      <c r="AP21" t="inlineStr"/>
-      <c r="AQ21" t="inlineStr"/>
-      <c r="AR21" t="inlineStr"/>
       <c r="AS21" t="inlineStr">
         <is>
           <t>Confirmed segments: NP,MP,NS; source institution: Agrocalidad; originating lab: AGROCALIDAD; partial segments only where applicable.</t>
         </is>
       </c>
-      <c r="AT21" t="inlineStr"/>
-      <c r="AU21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3312,7 +2785,6 @@
           <t>H5N1</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
           <t>Original</t>
@@ -3328,8 +2800,6 @@
           <t>Guayas</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
           <t>Gallus gallus domesticus</t>
@@ -3340,11 +2810,6 @@
           <t>Aves de corral</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
         <is>
           <t>Flu-0330|A_MP</t>
@@ -3360,8 +2825,6 @@
           <t>Flu-0330|A_NP</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr">
         <is>
           <t>Flu-0330</t>
@@ -3397,28 +2860,11 @@
           <t>2023-08-17</t>
         </is>
       </c>
-      <c r="AD22" t="inlineStr"/>
-      <c r="AE22" t="inlineStr"/>
-      <c r="AF22" t="inlineStr"/>
-      <c r="AG22" t="inlineStr"/>
-      <c r="AH22" t="inlineStr"/>
-      <c r="AI22" t="inlineStr"/>
-      <c r="AJ22" t="inlineStr"/>
-      <c r="AK22" t="inlineStr"/>
-      <c r="AL22" t="inlineStr"/>
-      <c r="AM22" t="inlineStr"/>
-      <c r="AN22" t="inlineStr"/>
-      <c r="AO22" t="inlineStr"/>
-      <c r="AP22" t="inlineStr"/>
-      <c r="AQ22" t="inlineStr"/>
-      <c r="AR22" t="inlineStr"/>
       <c r="AS22" t="inlineStr">
         <is>
           <t>Confirmed segments: NP,MP,NS; source institution: Agrocalidad; originating lab: AGROCALIDAD; partial segments only where applicable.</t>
         </is>
       </c>
-      <c r="AT22" t="inlineStr"/>
-      <c r="AU22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3441,7 +2887,6 @@
           <t>H5N1</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>Original</t>
@@ -3462,7 +2907,6 @@
           <t>Guayaquil</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>Fregata magnificens</t>
@@ -3508,9 +2952,6 @@
           <t>Flu-0402|A_NS</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr">
         <is>
           <t>Flu-0402</t>
@@ -3546,32 +2987,16 @@
           <t>2023-10-31</t>
         </is>
       </c>
-      <c r="AD23" t="inlineStr"/>
-      <c r="AE23" t="inlineStr"/>
-      <c r="AF23" t="inlineStr"/>
-      <c r="AG23" t="inlineStr"/>
-      <c r="AH23" t="inlineStr"/>
-      <c r="AI23" t="inlineStr"/>
-      <c r="AJ23" t="inlineStr"/>
-      <c r="AK23" t="inlineStr"/>
-      <c r="AL23" t="inlineStr"/>
-      <c r="AM23" t="inlineStr"/>
-      <c r="AN23" t="inlineStr"/>
       <c r="AO23" t="inlineStr">
         <is>
           <t>Juvenil</t>
         </is>
       </c>
-      <c r="AP23" t="inlineStr"/>
-      <c r="AQ23" t="inlineStr"/>
-      <c r="AR23" t="inlineStr"/>
       <c r="AS23" t="inlineStr">
         <is>
           <t>Confirmed segments: PB2,PB1,PA,HA,NA,MP,NS; source institution: MAATE; originating lab: MAATE; partial segments only where applicable.</t>
         </is>
       </c>
-      <c r="AT23" t="inlineStr"/>
-      <c r="AU23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3594,7 +3019,6 @@
           <t>H5N1</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>Original</t>
@@ -3615,7 +3039,6 @@
           <t>Guayaquil</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
           <t>Fregata magnificens</t>
@@ -3626,20 +3049,11 @@
           <t>Fragata</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
         <is>
           <t>Flu-0403|A_MP</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr">
         <is>
           <t>Flu-0403</t>
@@ -3675,32 +3089,16 @@
           <t>2023-10-31</t>
         </is>
       </c>
-      <c r="AD24" t="inlineStr"/>
-      <c r="AE24" t="inlineStr"/>
-      <c r="AF24" t="inlineStr"/>
-      <c r="AG24" t="inlineStr"/>
-      <c r="AH24" t="inlineStr"/>
-      <c r="AI24" t="inlineStr"/>
-      <c r="AJ24" t="inlineStr"/>
-      <c r="AK24" t="inlineStr"/>
-      <c r="AL24" t="inlineStr"/>
-      <c r="AM24" t="inlineStr"/>
-      <c r="AN24" t="inlineStr"/>
       <c r="AO24" t="inlineStr">
         <is>
           <t>Juvenil</t>
         </is>
       </c>
-      <c r="AP24" t="inlineStr"/>
-      <c r="AQ24" t="inlineStr"/>
-      <c r="AR24" t="inlineStr"/>
       <c r="AS24" t="inlineStr">
         <is>
           <t>Confirmed segments: MP; source institution: MAATE; originating lab: MAATE; partial segments only where applicable.</t>
         </is>
       </c>
-      <c r="AT24" t="inlineStr"/>
-      <c r="AU24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3723,7 +3121,6 @@
           <t>H5N1</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>Original</t>
@@ -3744,7 +3141,6 @@
           <t>Guayaquil</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
           <t>Fregata magnificens</t>
@@ -3795,8 +3191,6 @@
           <t>Flu-0406|A_NP</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr"/>
       <c r="W25" t="inlineStr">
         <is>
           <t>Flu-0406</t>
@@ -3832,36 +3226,21 @@
           <t>2023-10-31</t>
         </is>
       </c>
-      <c r="AD25" t="inlineStr"/>
-      <c r="AE25" t="inlineStr"/>
-      <c r="AF25" t="inlineStr"/>
-      <c r="AG25" t="inlineStr"/>
-      <c r="AH25" t="inlineStr"/>
-      <c r="AI25" t="inlineStr"/>
-      <c r="AJ25" t="inlineStr"/>
-      <c r="AK25" t="inlineStr"/>
-      <c r="AL25" t="inlineStr"/>
-      <c r="AM25" t="inlineStr"/>
-      <c r="AN25" t="inlineStr"/>
       <c r="AO25" t="inlineStr">
         <is>
           <t>Adulto</t>
         </is>
       </c>
-      <c r="AP25" t="inlineStr"/>
       <c r="AQ25" t="inlineStr">
         <is>
           <t>Hembra</t>
         </is>
       </c>
-      <c r="AR25" t="inlineStr"/>
       <c r="AS25" t="inlineStr">
         <is>
           <t>Confirmed segments: PB2,PB1,PA,HA,NP,NA,MP,NS; source institution: MAATE; originating lab: MAATE; partial segments only where applicable.</t>
         </is>
       </c>
-      <c r="AT25" t="inlineStr"/>
-      <c r="AU25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4188,1024 +3567,846 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B85"/>
+  <dimension ref="A1:FL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Seq_Id</t>
+          <t>&gt;Flu-0008|A_NS</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Sequence</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Flu-0008|A_NS</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
           <t>NNGGATTCCAACACTGTGTCAAGCTTNCAGGTAGACTGCTTTCTTTGGCATGTCCGCAAACGATTTGCAGACCAAGAACTGGGTGATGCCCCATTCCTTGACCGGCTNCGCCGAGACCAGAAGTCTCTNAGAGGAAGAGGCAGCACTCTTGGTCTGGACATCGAGACGGCCACTCGTGCTGGAAAGCAGATAGTGGAGAGGATTCTGGAGGAAGAATCCGACGAGGCACTCAAAATGACTATTGCCTCTGTGCCTGCTCCACGCTACCTAACTGACATGACTCTTGAAGAGATGTCAAGAGACTGGTTCATGCTCATGCCCAAGCAAAAAGTGGCAGGCTCCCTCTGTATCAGAATGGACCAGGCGATTATGGATAAGAACATCATACTGAAGGCAAACTTCAGTGTGATCTTCAATCGGCTGGAGACACTAATACTACTCAGAGCTTTCACTGAAGAGGGAGCAATTGTNGGCGAAATTTCACCATTGCCTTCTCTTCCAGGACATACTGATGAGGATGTCAAAAATGCAATTGGGGTCCTCATCGGAGGACTTGAATGGAATGATAACACAGTTCGAGTCTCTGAAATTTTACAGAGATTCGCTTGGAGAAGCAGTAATGAGGATGGGAGACCTCCACTCCCTCCAAAGCAGAAACGGAAAATGGAGAGAACAATTGAGTCAGAAGTTTGAAGAAATAAGGTGGCTGATTGAAGAGGTGCGACACAGANTAAAGATCACAGAAAATAGTTTTGAACAAATAACATTTATGCAAGCCTTACAACTACTGCTTGAAGTGGAGCAAGAGATACGAACTTTCTCGTTTCAGCTTATTTAA</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Flu-0009|A_NP</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0009|A_NP</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
         <is>
           <t>ATGGCGTCTCAAGGCACCAAACGATCCTATGAACAAATGGAAACTGGTGGGGAACGCCAGAATGCCACTGAAATCAGAGCATCTGTTGGAAGAATGGTTGGCGGAATAGGAAGATTCTACATACAGATGTGCACTGAGCTCAAACTCAGTGATTACGAAGGGAGGCTGATCCAAAACAGCATAACCATAGAAAGGATGGTTCTCTCGGCATTTGATGAGAGGAGGAACAAGTACCTGGAGGAACATCCCAGTGCCGGGAAGGATCCCAAGAAGACTGGAGGTCCAATCTACAGGAGGAGAGATGGCAAATGGGTGAGAGAGTTGATCCTCTACGACAAAGAAGAGATCAGAAGAATTTGGCGTCAAGCTAATAATGGAGAGGATGCAACTGCTGGTCTCACTCATTTGATGATTTGGCATTCCAATCTGAATGATGCAACATACCAGAGAACAAGGGCACTTGTGCGTACTGGAATGGACCCTAGRATGTGCTCTCTGATGCAAGGCTCAACCCTCCCTAGGAGATCCGGGGCTGCTGGAGCAGCAGTGAAAGGAGTTGGAACAATGGTGATGGAACTAATTCGAATGATCAAACGAGGGATCAATGATCGGAATTTCTGGAGAGGCGAAAACGGTCGGAGAACCAGGATTGCCTACGAGAGAATGTGCAACATCCTCAAGGGAAAGTTCCAAACAGCAGCACAACGGGCAATGATGGACCAAGTGAGAGAAAGCCGGAATCCTGGGAATGCTGAAATTGAAGATCTCATCTTTCTCGCACSATCTGCTCTCATCCTGAGGGGATCAGTGGCTCATAAGTCCTGTCTGCCTGCTTGCGTATATGGACTTGCTGTAGCCAGTGGATATGACTTTGAAAGAGAGGGATATTCTCTAGTCGGAATTGATCCTTTCCGTCTGCTCCAAAACAGCCAAGTCTTCAGTCTCATCAGACCGAACGAAAATCCAGCTCATAAAAGTCAGCTGGTATGGATGGCATGCCACTCTGCGGCATTTGAGGATCTGAGAGTTTCAAGCTTCATCAGAGGGACAAGAGTAGTCCCAAGAGGACAACTGTCCACCAGAGGAGTTCAGATTGCTTCAAATGAAAACATGGAGACAATGGACTCCAGTACTCTTGAACTGAGGAGCAGRTACTGGGCTATAAGAACAAGAAGTGGAGGAAACACTAACCAACAGAGAGCATCTGCAGGACAAATCAGCGTACAGCCCACATTCTCTGTGCAAAGAAACCTCCCATTCGAGAGAGCAACCATCATGGCAGCATTTACGGGAAACACTGAAGGCAGAACTTCAGACATGAGAACTGAGATCATAAGGATGATGGAAAATGCCAGACCTGAAGATGTGTCTTTCCAGGGGCGGGGAGTCTTCGAGCTCTCGGACGAAAAGGCAACGAACCCGATCGTGCCTTCCTTTGACATGAGTAATGAAGGATCTTATTTCTTCGGAGACAATGCAGAGGAGTATGACAATTAA</t>
         </is>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Flu-0009|A_NA</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0009|A_NA</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
         <is>
           <t>ATGAATCCAAATCAAAAGATAACAACCATTGGATCAATCTGTATGGTAATTGGGACAGTCAGCTTGATGCTGCAAATTGGGAACATAATCTCAATATGGGTTAGCCATTCAATCCAAACAGGGAATCAATACCAGCCTGAACCATGCAATCAAAGCGTAATTACCTATGAGAACAACACCTGGGTAAATCAGACGTATGTCAACATTAGCAATACCAATTTTCTTGCTGAGCAGGCTGTTACTTCGGTAACATTAGCGGGCAATTCATCTCTTTGCCCTATTAGTGGGTGGGCAATATACAGTAAGGACAACGGTATAAGAATTGGGTCCAAGGGGGATGTGTTTGTTATAAGAGAACCGTTCATCTCATGCTCCCACTTGGAATGCAGAACCTTTTTCCTGACCCAGGGAGCTCTGCTGAATGACAAACATTCTAATGGGACAGTTAAGGATAGAAGCCCTTATAGAACTTTGATGAGTTGTCCCGTGGGTGAGGCTCCTTCCCCGTACAATTCAAGATTTGAGTCTGTTGCTTGGTCGGCAAGTGCTTGTCATGATGGCATCAGTTGGTTGACAATCGGTATTTCTGGTCCAGACAATGGAGCTGTGGCTGTATTGAAGTACAATGGCATAATAACGGATACTATCAAGAGTTGGAGAAACAACATTTTGAGAACTCAAGAATCTGAATGTGCTTGTGTAAATGGCTCTTGCTTCACCGTAATGACTGATGGACCAAGCAATGGGCAGGCCTCATATAAAATCTTCAAGATAGAGAAAGGGAAAGTTGTCAAATCAGTTGAATTGAATGCCCCTAATTACCACTACGAGGAATGTTCCTGTTATCCTGATGCGGGTGATATTATATGTGTGTGCAGGGACAATTGGCATGGCTCAAACCGGCCGTGGGTATCTTTTAATCAAAATCTGGAGTATCAAATAGGATATATATGCAGTGGGGTTTTCGGGGACAATCCCCGCCCCAATGATGGAACAGGCAGTTGCAGTCCAATGTCCTCTAATGGGGCATATGGGGTAAAAGGGTTCTCATTTAAGTACGGTAATGGGGTTTGGATCGGAAGAACAAAAGGCACTAGTTCCAGAAGCGGCTTTGAGATGATTTGGGACCCGAATGGGTGGACTGAGACGGACAGTAGTTTCTCAGTGAAGCAAGACATTGTAGAAATAACTGACTGGTCAGGATATAGTGGGAGTTTTGTCCAGCATCCAGAACTGACAGGATTAGATTGCATGAGGCCTTGTTTCTGGGTTGAGCTAATTAGAGGGAGGCCCAAAGAGAACACAATTTGGACTAGCGGGAGCAGCATATCCTTTTGTGGTGTAAATAGTGACACTGTGGGTTGGTCTTGGCCAGACGGTGCTGAGTTGCCATTCACCATTGACAAGTAG</t>
         </is>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Flu-0009|A_MP</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0009|A_MP</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
         <is>
           <t>ATGAGTCTTCTAACCGAGGTCGAAACGTACGTTCTCTCTATCGTCCCGTCGGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTTGAAGATGTTTTTGCAGGGAAGAACACCGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATACTGTCACCTCTGACTAAGGGGATTTTGGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCTCTAAGTGGAAATGGAGACCCAAACAACATGGACAGGGCAGTCAAGTTGTACAGGAAATTGAAGAGAGAAATAACATTTCATGGGGCTAAAGAAGTTGCACTCAGTTACTCAACCGGTGCACTTGCCAGTTGTATGGGTCTCATATACAACAGGATGGGGACGGTGACCGCAGAAGTGGCATTGGGCCTAGTGTGTGCCACCTGTGAGCAGATTGCTGATTCACAGCATCGGTCTCACAGACAGATAGCTACCACCACCAACCCACTAATCAGACATGAAAACAGAATGGTTTTGGCCAGTACTACAGCTAAGGCTATGGAGCAGATGGCTGGATCGAGTGAGCAAGCAGTGGAAGCCATGGAGGTTGCTAGTCAGGCTAGGCAAATGGTGCAGGCGATGAGGACCATTGGAACTCATCCTAGCTCCAGTGCCGGTCTGAGAGATGATCTCCTTGAAAATTTGCAGGCCTACCAAAAACGAATGGGAGTGCAACTGCAGCGATTCAAGTGATCCTCTCGTTATTGCCGCAAGTATCATTGGGATCTTGCACTTGATATTGTGGATTCTTGATCGCCTTTTCTTCAAATGCGTTTATCGTCGCCTTAAATACGGTTTGAAAGGAGGGCCTTCTACGGAAGGAGTACCTGAGTCCATGAGGGAAGAGTACCGGCAGGAACAGCAGAGTGCTGTGGATGTTGACGATGGTCATTTTGTCAACATAGAGATGGAGTAA</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Flu-0009|A_NS</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0009|A_NS</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
         <is>
           <t>ATGGATTCCAACACTGTGTCAAGCTTTCAGGTAGACTGCTTTCTTTGGCATGTCCGCAAACGATTTGCAGACCAAGAACTGGGTGATGCCCCATTCCTTGACCGGCTCCGCCGAGACCAGAAGTCTCTAAGAGGAAGAGGCAGCACTCTTGGTCTGGACATCGAGACGGCCACTCGTGCTGGAAAGCAGATAGTGGAGAGGATTCTGGAGGAAGAATCCGACGAGGCACTCAAAATGACTATTGCCTCTGTGCCTGCTCCACGCTACCTAACTGACATGACTCTTGAAGAGATGTCAAGAGATTGGTTCATGCTCATGCCCAAGCAAAAAGTGGCAGGCTCCCTCTGTATCAGAATGGACCAGGCGATTATGGATAAGAACATCATACTGAAGGCAAACTTCAGTGTGATCTTCAATCGGCTGGAGACACTAATACTACTCAGAGCTTTCACTGAAGAGGGAGCAATTGTCGGCGAAATTTCACCATTGCCTTCTCTTCCAGGACATACTGATGAGGATGTCAAAAATGCAATTGGGGTCCTCATCGGAGGACTTGAATGGAATGATAACACAGTTCGAGTCTCTGAAATTTTACAGAGATTCGCTTGGAGAAGCAGTAATGAGGATGGGAGACCTCCACTCCCTCCAAAGCAGAAACGGAAAATGGAGAGAACAATTGAGTCAGAAGTTTGAAGAAATAAGGTGGCTGATTGAAGAGGTGCGACACAGATTAAAGATCACAGAAAATAGTTTTGAACAAATAACATTTATGCAAGCCTTACAACTACTGCTTGAAGTGGAGCAAGAGATACGAACTTTCTCGTTTCAGCTTATTTAA</t>
         </is>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Flu-0011|A_MP</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0011|A_MP</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
         <is>
           <t>ATGAGTCTTCTAACCGAGGTCGAAACGTACGTTCTCTCTATCGTCCCGTCGGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTTGAAGATGTCTTTGCAGGGAAGAACACCGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATACTGTCACCTCTGACTAAGGGGATTTTGGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCTCTAAGTGGAAATGGAGACCCAAACAACATGGACAGGGCAGTCAAGTTGTACAGGAAACTGAAGAGAGAAATAACATTCCATGGGGCTAAAGAAGTTGCACTCAGTTACTCAACCGGTGCACTTGCCAGTTGTATGGGTCTCATATACAACAGGATGGGGACGGTGACCGCAGAAGTGGCATTGGGCCTAGTGTGTGCCACCTGTGAGCAGATTGCTGATTCACAGCATCGGTCTCACAGACAGATAGCTACCACCACCAACCCACTAATCAGACATGAAAACAGAATGGTTTTGGCCAGTACTACAGCTAAGGCTATGGAGCAGATGGCTGGATCGAGTGAGCAAGCAGCGGAAGCCATGGAGGTTGCTAGTCAGGCTAGGCAAATGGTGCAGGCGATGAGGACCATTGGAACTCATCCTAGCTCCAGTGCCGGTCTGAGAGATGATCTCCTTGAAAATTTGCAGGCCTACCAAAAACGAATGGGAGTGCAACTGCAGCGATTCAAGTGATCCTCTCGTTATTGCCGCAAGTATCATTGGGATCTTGCACTTGATATTGTGGATTCTTGATCGCCTTTTCTTCAAATGCGTTTATCGTCGCCTTAAATACGGTTTGAAAGGAGGGCCTTCTACGGAAGGAGTACCTGAGTCCATGAGGGAAGAGTACCGGCAGGAACAGCAGAGTGCTGTGGATGTTGACGATGGTCATTTTGTCAACATAGAGATGGAGTAA</t>
         </is>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Flu-0011|A_NS</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0011|A_NS</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
         <is>
           <t>ATGGATTCCAACACTGTGTCAAGCTTTCAGGTAGACTGCTTTCTTTGGCATGTCCGCAAACGATTTGCAGACCAAGAACTGGGTGATGCCCCATTCCTTGACCGGCTCCGCCGAGACCAGAAGTCTCTAAGAGGAAGAGGCAGCACTCTTGGTCTGGACATCGAGACGGCCACTCGTGCTGGAAAGCAGATAGTGGAGAGGATTCTGGAGGAAGAATCCGACGAGGCACTCAAAATGACTATTGCCTCTGTGCCTGCTCCACGCTACCTAACTGACATGACTCTTGAAGAGATGTCAAGAGACTGGTTCATGCTCATGCCCAAGCAAAAAGTGGCAGGCTCCCTCTGTATCAGAATGGACCAGGCGATTATGGATAAGAACATCATACTGAAGGCAAACTTCAGTGTGATCTTCAATCGGCTGGAGACACTAATACTACTCAGAGCTTTCACTGAAGAGGGAGCAATTGTCGGCGAAATTTCACCATTGCCTTCTCTTCCAGGACATACTGATGAGGATGTCAAAAATGCAATTGGGGTCCTCATCGGAGGACTTGAATGGAATGATAACACAGTTCGAGTCTCTGAAATTTTACAGAGATTCGCTTGGAGAAGCAGTAATGAGGATGGGAGACCTCCACTCCCTCCAAAGCAGAAACGGAAAATGGAGAGAACAATTGAGTCAGAAGTTTGAAGAAATAAGGTGGCTGATTGAAGAGGTGCGACACAGACTAAAGATCACAGAAAATAGTTTTGAACAAATAACATTTATGCAAGCCTTACAACTACTGCTTGAAGTGGAGCAAGAGATACGAACTTTCTCGTTTCAGCTTATTTAA</t>
         </is>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Flu-0013|A_HA</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0013|A_HA</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
         <is>
           <t>ATGGAGAACATAGTACTACTTCTTGCAATAGTTAGCCTTGTTAAAAGTGACCAGATTTGCATTGGTTACCATGCAAACAATTCGACAGAGCAAGTTGACACGATAATGGAAAAGAACGTCACTGTTACACATGCCCAAGACATACTGGAAAAAACACACAACGGGAAGCTCTGTGATTTAAATGGGGTGAAGCCACTGATTTTAAAGGATTGTAGTGTAGCTGGATGGCTCCTCGGGAACCCAATGTGCGACGAATTCATCAGAGTGCCGGAATGGTCCTACATAGTGGAGCGAGCTAACCCAGCTAATGACCTCTGTTACCCAGGGAGCCTCAATGACTATGAAGAACTGAAACACATGTTGAGCAGAATAAATCATTTTGAGAAGATTCAGATCATTCCCAAGAGTTCCTGGCCAAATCATGAAACATCACTAGGGGTGAGCGCAGCTTGTCCATACCAGGGAGCGCCCTCCTTTTTCAGAAATGTGGTGTGGCTTATCAAAAAGAACGATGCATACCCAACAATAAAGATAAGCTACAATAATACTAATCGGGAAGATCTCTTGATACTGTGGGGGATTCATCATTCCAACARTGCAGAAGAGCAGACAAATCTCTACAAAAACCCAACCACCTACATTTCAGTTGGAACATCAACTTTAAACCAGAGGTTGGCACCAAAAATAGCTACTAGATCCCAAGTAAACGGGCAACGTGGAAGAATGGACTTCTTTTGGACAATCTTAAAACCAGATGATGCAATCCATTTCGAGAGTAACGGAAATTTCATTGCTCCAGAATATGCATACAAAATTGTCAAGAAAGGGGACTCAACAATTATGAAAAGTGGAGTGGAATATGGCCACTGCAACACCAAATGTCAAACCCCAGTAGGTGCTATAAATTCTAGTATGCCATTCCACAACATACATCCTCTCACCATTGGGGAATGCCCCAAATACGTGAAGTCAAACAAGTTGGTCCTTGCGACTGGGCTCAGAAATAGTCCTCTAAGAGAAAAGAGAAGAAAAAGAGGTCTGTTTGGGGCGATAGCAGGGTTTATAGAGGGAGGATGGCAGGGAATGGTTGATGGTTGGTATGGGTACCATCATAGCAATGAGCAGGGGAGTGGGTACGCTGCGGACAAAGAATCCACCCAAAAGGCAATAGATGGAGTTACCAATAAGGTCAACTCAATCATTGACAAAATGAACACTCAATTTGAGGCAGTTGGAAGGGAGTTTAATAACTTAGAAAGGAGGATAGAGAATTTGAACAAGAAAATGGAAGACGGATTCCTAGATGTCTGGACCTATAATGCTGAACTTCTAGTTCTCATGGAAAACGAGAGGACTCTAGATTTCCATGATTCAAATGTCAAGAACCTTTACGACAAAGTCAGATTACAGCTTAGGGATAATGCAAAGGAGCTGGGTAACGGCTGTTTCGAATTCTATCACAAATGTGATAATGAATGTATGGAAAGTGTGAGAAATGGGACGTATGACTACCCTCAGTATTCAGAAGAAGCAAGATTAAAAAGAGAAGAAATAAGCGGAGTGAAATTAGAATCAGTAGGAACTTACCAGATACTGTCAATTTATTCAACAGCGGCAAGTTCCCTAGCACTGGCAATCATGATGGCTGGTCTATCTTTATGGATGTGCTCCAATGGGTCGTTACAATGCAGAATTTGCATTTAG</t>
         </is>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Flu-0013|A_NP</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0013|A_NP</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
         <is>
           <t>ATGGCGTCTCAAGGCACCAAACGATCCTATGAACAAATGGAAACTGGTGGGGAACGCCAGAATGCCACTGAAATCAGAGCATCCGTTGGAAGAATGGTTGGCGGAATAGGAAGATTCTACATACAGATGTGCACTGAGCTCAAACTCAGTGATTACGAAGGGAGGCTGATCCAAAACAGCATAACCATAGAAAGGATGGTTCTCTCGGCATTTGATGAGAGGAGGAACAAGTACCTGGAGGAACATCCCAGTGCCGGGAAGGATCCCAAGAAGACTGGAGGTCCAATCTACAGGAGGAGAGATGGCAAATGGGTGAGAGAGTTGATCCTCTACGACAAAGAAGAGATCAGAAGAATTTGGCGTCAAGCTAATAATGGAGAGGATGCAACTGCTGGTCTCACTCATTTGATGATTTGGCATTCCAATCTGAATGATGCAACATACCAGAGAACAAGGGCACTTGTGCGTACTGGAATGGACCCTAGGATGTGCTCTCTGATGCAAGGCTCAACCCTCCCTAGGAGATCCGGGGCTGCTGGAGCAGCAGTGAAAGGAGTTGGAACAATGGTGATGGAACTAATTCGAATGATCAAACGAGGGATCAATGATCGGAATTTCTGGAGAGGCGAAAACGGTCGGAGAACCAGGATTGCCTACGAGAGAATGTGCAACATCCTCAAGGGAAAGTTCCAAACAGCAGCACAACGGGCAATGATGGACCAAGTGAGAGAAAGCCGGAATCCTGGGAATGCTGAAATTGAAGATCTCATCTTTCTCGCACSATCTGCTCTCATCCTGAGGGGATCAGTGGCTCATAAGTCCTGTCTGCCTGCTTGCGTATATGGACTTGCTGTAGCCAGTGGATATGACTTTGAAAGAGAGGGATATTCTCTAGTCGGAATTGATCCTTTCCGTCTGCTCCAAAACAGCCAAGTCTTCAGTCTCATCAGACCGAACGAAAATCCAGCTCATAAAAGTCAGCTGGTATGGATGGCATGCCACTCTGCGGCATTTGAGGATCTGAGAGTTTCAAGCTTCATCAGAGGGACAAGAGTAGTCCCAAGAGGACAACTGTCCACCAGAGGAGTTCAGATTGCTTCAAATGAAAACATGGAGACAATGGACTCCAGTACTCTTGAACTGAGGAGCAGATACTGGGCTATAAGAACAAGAAGTGGAGGAAACACTAACCAACAGAGAGCATCTGCAGGACAAATCAGCGTACAGCCCACATTCTCTGTGCAAAGAAACCTCCCATTCGAGAGAGCAACCATCATGGCAGCATTTACGGGAAACACTGAAGGCAGAACTTCAGACATGAGAACTGAGATCATAAGGATGATGGAAAATGCCAGACCTGAAGATGTGTCTTTCCAGGGGCGGGGAGTCTTCGAGCTCTCGGACGAAAAGGCAACGAACCCGATCGTGCCTTCCTTTGACATGAGTAATGAAGGATCTTATTTCTTCGGAGACAATGCAGAGGAGTATGACAATTAA</t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Flu-0013|A_NA</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0013|A_NA</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
         <is>
           <t>ATGAATCCAAATCAAAAGATAACAACCATTGGATCAATCTGTATGGTAATTGGGACAGTCAGCTTGATGCTGCAAATTGGGAACATAATCTCAATATGGGTTAGCCATTCAATCCAAACAGGGAATCAATACCAGCCTGAACCATGCAATCAAAGCATCATTACCTATGAGAACAACACCTGGGTAAATCAGACGTATGTCAACATCAGCAATACCAATTTTCTTGCTGAGCAGGCTGTTACTTCGGTAACATTAGCGGGCAATTCATCTCTTTGCCCTATTAGTGGGTGGGCAATATACAGTAAGGACAACGGTATAAGAATTGGGTCCAAGGGGGATGTGTTTGTTATAAGAGAACCGTTCATCTCATGCTCCCACTTGGAATGCAGAACCTTTTTCCTGACCCAGGGAGCTCTGCTGAATGACAAACATTCTAATGGGACAGTTAAGGATAGAAGCCCTTATAGAACTTTGATGAGTTGTCCCGTGGGTGAGGCTCCTTCCCCGTACAATTCAAGATTTGAGTCTGTTGCTTGGTCGGCAAGTGCTTGTCATGATGGCATCAGTTGGTTGACAATCGGTATTTCTGGTCCAGACAATGGAGCTGTGGCTGTATTGAAGTACAATGGCATAATAACGGATACTATCAAGAGTTGGAGAAACAACATTTTGAGAACTCAAGAATCTGAATGTGCTTGCGTAAATGGCTCTTGCTTCACCGTAATGACTGATGGACCAAGCAATGGGCAGGCCTCATATAAAATCTTCAAGATAGAGAAAGGGAAAGTTGTCAAATCAGTTGAATTGAATGCCCCTAATTACCACTACGAGGAATGTTCCTGTTATCCTGATGCGGGTGATATTATATGTGTGTGCAGGGACAATTGGCATGGCTCAAACCGGCCGTGGGTATCTTTTAATCAAAATCTGGAGTATCAAATAGGATATATATGCAGTGGGGTTTTCGGGGACAATCCCCGCCCCAATGATGGAACAGGCAGTTGCAGTCCAATGTCCTCTAATGGGGCATATGGGGTAAAAGGGTTTTCATTTAAGTACGGTAATGGGGTTTGGATCGGAAGAACAAAAGGCACTAGTTCCAGAAGCGGCTTTGAGATGATTTGGGACCCGAATGGGTGGACTGAGACGGACAGTAGTTTCTCAGTGAAGCAAGACATTGTAAAAATAACTGACTGGTCAGGATATAGTGGGAGTTTTGTCCAGCATCCAGAACTGACAGGATTAGATTGCATGAGGCCTTGTTTCTGGGTTGAGCTAATTAGAGGGAGGCCCAAAGAGAACACAATTTGGACTAGCGGGAGCAGCATATCCTTTTGTGGTGTAAATAGTGACACTGTGGGTTGGTCTTGGCCAGACGGTGCTGAGTTGCCATTCACCATTGACAAGTAG</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Flu-0013|A_MP</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0013|A_MP</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
         <is>
           <t>ATGAGTCTTCTAACCGAGGTCGAAACGTACGTTCTCTCTATCGTCCCGTCGGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTTGAAGATGTCTTTGCAGGGAAGAACACCGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATACTGTCACCTCTGACTAAGGGGATTTTGGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCTCTAAGTGGAAATGGAGACCCAAACAACATGGACAGGGCAGTCAAGTTGTACAGGAAATTGAAGAGAGAAATAACATTCCATGGGGCTAAAGAAGTTGCACTCAGTTACTCAACCGGTGCACTTGCCAGTTGTATGGGTCTCATATACAACAGGATGGGGACGGTGACCGCAGAAGTGGCATTGGGCCTAGTGTGTGCCACCTGTGAGCAGATTGCTGATTCACAGCATCGGTCTCACAGACAGATAGCTACCACCACCAACCCACTAATCAGACATGAAAACAGAATGGTTTTGGCCAGTACTACAGCTAAGGCTATGGAGCAGATGGCTGGATCGAGTGAGCAAGCAGTGGAAGCCATGGAGGTTGCTAGTCAGGCTAGGCAAATGGTGCAGGCGATGAGGACCATTGGAACTCATCCTAGCTCCAGTGCCGGTCTGAGAGATGATCTCCTTGAAAATTTGCAGGCCTACCAAAAACGAATGGGAGTGCAACTGCAGCGATTCAAGTGATCCTCTCGTTATTGCCGCAAGTATCATTGGGATCTTGCACTTGATATTGTGGATTCTTGATCGCCTTTTCTTCAAATGCGTTTATCGTCGCCTTAAATACGGTTTGAAAGGAGGGCCTTCTACGGAAGGAGTACCTGAGTCCATGAGGGAAGAGTACCGGCAGGAACAGCAGAGTGCTGTGGATGTTGACGATGGTCATTTTGTCAACATAGAGATGGAGTAA</t>
         </is>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Flu-0013|A_NS</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0013|A_NS</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
         <is>
           <t>ATGGATTCCAACACTGTGTCAAGCTTCCAGGTAGACTGCTTTCTTTGGCATGTCCGCAAACGATTTGCAGACCAAGAACTGGGTGATGCCCCATTCCTTGACCGGCTCCGCCGAGACCAGAAGTCTCTAAGAGGAAGAGGCAGCACTCTTGGTCTGGACATCGAGACGGCCACTCGTGCTGGAAAGCAGATAGTGGAGAGGATTCTGGAGGAAGAATCCGACGAGGCACTCAAAATGACTATTGCCTCTGTGCCTGCTCCACGCTACCTAACTGACATGACTCTTGAAGAGATGTCAAGAGACTGGTTCATGCTCATGCCCAAGCAAAAAGTGGCAGGCTCCCTCTGTATCAGAATGGACCAGGCGATTATGGATAAGAACATCATACTGAAGGCAAACTTCAGTGTGATCTTCAATCGGCTGGAGACACTAATACTACTCAGAGCTTTCACTGAAGAGGGAGCAATTGTCGGCGAAATTTCACCATTGCCTTCTCTTCCAGGACATACTGATGAGGATGTCAAAAATGCAATTGGGGTCCTCATCGGAGGACTTGAATGGAATGATAACACAGTTCGAGTCTCTGAAATTTTACAGAGATTCGCTTGGAGAAGCAGTAATGAGGATGGGAGACCTCCACTCCCTCCAAAGCAGAAACGGAAAATGGAGAGAACAATTGAGTCAGAAGTTTGAAGAAATAAGGTGGCTGATTGAAGAGGTGCGACACAGACTAAAGATCACAGAAAATAGTTTTGAACAAATAACATTTATGCAAGCCTTACAACTACTGCTTGAAGTGGAGCAAGAGATACGAACTTTCTCGTTTCAGCTTATTTAA</t>
         </is>
       </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Flu-0014|A_NS</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0014|A_NS</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
         <is>
           <t>ATGGATTCCAACACTGTGTCAAGCTTTCAGGTAGACTGCTTTCTTTGGCATGTCCGCAAACGATTTGCAGACCAAGAACTGGGTGATGCCCCATTCCTTGACCGGCTCCGCCGAGACCAGAAGTCTCTAAGAGGAAGAGGCAGCACTCTTGGTCTGGACATCGAGACGGCCACTCGTGCTGGAAAGCAGATAGTGGAGAGGATTCTGGAGGAAGAATCCGACGAGGCACTCAAAATGACTATTGCCTCTGTGCCTGCTCCACGCTACCTAACTGACATGACTCTTGAAGAGATGTCAAGAGANTGGTTCATGCTCATGCCCAAGCAAAAAGTGGCAGGCTCCCTCNGTATCAGAATGGACCAGGCGATTATGGATAAGAACATCATACTGAAGGCAAACTTCAGTGTGATCTTCAATCGGCTGGAGACACTAATACTACTCAGAGCTTTCACTGAAGAGGGAGCAATTGTCGGCGAAATTTCACCATTGCCTTCTCTTCCAGGACATACTGATGAGGATGTCAAAAATGCAATTGGGGTCCTCATCGGAGGACTTGAATGGAATGATAACACAGTTCGAGTCTCTGAAANTTTACAGAGATTCGCTTGGAGAAGCAGTAATGAGGATGGGAGACCTCCACTCCCTCCAAAGCAGAAACGGAAAATGGAGAGAACAATTGAGTCAGAAGTTTGAAGAAATAAGGTGGCTGATTGAAGANGTNCGACACAGANTAAAGATCACAGAAAATAGTTTTGAACAAATAACATTTATGCAAGCCTTACAACTACTGCTTGAAGTGGAGCAAGAGATANGAACTTTCTCGTTTCAGCTTATTTAA</t>
         </is>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Flu-0018|A_NS</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0018|A_NS</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
         <is>
           <t>ATGGATTCCAACACTGTGTCAAGCTTTCAGGTAGACTGCTTTCTTTGGCATGTCCGCAAACGATTTGCAGACCAAGAACTGGGTGATGCCCCATTCCTTGACCGGCTCCGCCGAGACCAGAAGTCTCTAAGAGGAAGAGGCAGCACTCTTGGTCTGGACATCGAGACGGCCACTCGTGCTGGAAAGCAGATAGTGGAGAGGATTCTGGAGGAAGAATCCGACGAGGCACTCAAAATGACTATTGCCTCTGTGCCTGCTCCACGCTACCTAACTGACATGACTCTTGAAGAGATGTCAAGAGAYTGGTTCATGCTCATGCCCAAGCAAAAAGTGGCAGGCTCCCTCWGTATCAGAATGGACCAGGCGATTATGGATAAGAACATCATACTGAAGGCAAACTTCAGTGTGATCTTCAATCGGCTGGAGACACTAATACTACTCAGAGCTTTCACTGAAGAGGGAGCAATTGTCGGCGAAATTTCACCATTGCCTTCTCTTCCAGGACATACTGATGAGGATGTCAAAAATGCAATTGGGGTCCTCATCGGAGGACTTGAATGGAATGATAACACAGTTCGAGTCTCTGAAAYTTTACAGAGATTCGCTTGGAGAAGCAGTAATGAGGATGGGAGACCTCCACTCCCTCCAAAGCAGAAACGGAAAATGGAGAGAACAATTGAGTCAGAAGTTTGAAGAAATAAGGTGGCTGATTGAAGARGTKCGACACAGAYTAAAGATCACAGAAAATAGTTTTGAACAAATAACATTTATGCAAGCCTTACAACTACTGCTTGAAGTGGAGCAAGAGATAMGAACTTTCTCGTTTCAGCTTATTTAA</t>
         </is>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Flu-0023|A_HA</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0023|A_HA</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
         <is>
           <t>ATGGAGGACATAGTACTACTTCTTGCAATAGTTAGCCTTGTTAAAAGTGATCAGATTTGCATTGGTTACCATGCAAACAATTCGACAGAGCAAGTTGACACGATAATGGAAAAGAACGTCACTGTTACACATGCCCAAGACATACTGGAAAAAACACACAACGGGAAACTCTGTGATTTAAATGGGGTGAAGCCACTGATTTTAAAGGATTGTAGTGTAGCTGGATGGCTCCTCGGAAACCCAATGTGCGACGAATTCATCAGAGTGCCGGAATGGTCCTACATAGTGGAGCGGGCTAACCCAGCTAATGACCTCTGTTACCCAGGGAGCCTCAATGACTATGAAGAACTGAAACACATGTTGAGCAGAATAAATCATTTTGAGAAGATTCAGATCATTCCCAAGAGTTCCTGGCCAAATCATGAAACATCACTAGGAGTGAGCGCAGCTTGTCCATACCAGGGAGCGCCCTCCNTTTTCAGAAATGTGGTGTGGCTTATCAAAAAGAACGATGCATACCCAACAATAAAGATAAGCTACAATAATACTAATCGGGAAGATCTCTTGATACTGTGGGGGATTCATCATTCCAACAATGCAAAAGAACAGACAAATCTCTACAAAAACCCAACCACCTACATTTCAGTTGGAACATCAACTTTAAACCAGAGGTTGGCACCAAAAATAGCTACTAGATCCCAAGTAAACGGGCAACGTGGAAGAATGGACTTCTTCTGGACAATCTTAAAACCAGATGATGCAATCCATTTCGAGAGTAACGGAAATTTCATTGCTCCAGAATATGCATACAAAATTGTCAAGAAAGGGGACTCAACAATTATGAAAAGTGGAGTGGAATATGGCCACTGCAACACCAAATGTCAAACCCCAGTAGGTGCGATAAATTCTAGTATGCCATTCCACAACATACATCCTCTCACCATTGGGGAATGCCCCAAATACGTGAAGTCAAACAAGTTGGTCCTTGCGACTGGGCTCAGAAATAGTCCTCTAAGAGAAAAGAGAAGNNNAAAAAGAGGTCTGTTTGGRGCRAWAGCAGGGTTTATAGAGGGAGGATGGCAGGGAATGGTTGATGGTTGGTATGGATACCATCATAGCAATRAGCAGGGGAGTGGGTACGCTGCGGACAAAGAATCCACCCAAAAGGCAATAGATGGAGTTACCAATAAGGTCAACTCAATCATTGACAAAATGAACACTCAATTTGAGGCAGTTGGAAGGGAGTTTAATAACTTAGAAAGGAGGATAGAGAATTTGAACAAGAAAATGGAAGACGGATTCCTAGATGTCTGGACCTATAATGCTGAACTTCTAGTTCTCATGGAAAACGAGAGGACTCTAGATTTCCATGATTCAAATGTCAAGAACCTTTACGACAAAGTCAGATTACAGCTTAGGGATAATGCAAAGGAGCTGGGTAACGGCTGTTTCGAATTCTATCACAAATGTGATAATGAATGTATGGAAAGTGTGAGAAATGGGACGTATGACTACCCTCAGTATTCAGAAGAAGCAAGATTAAAAAGAGAAGAAATAAGCGGAGTGAAATTAGAATCAGTAGGAACTTACCAGATACTGTCAATTTATTCAACAGCGGCAAGTTCCCTAGCACTGGCAATCATGATGGCTGGTCTATCTTTATGGATGTGCTCCAATGGGTCGTTACAATGCAGAATTTGCATTTAG</t>
         </is>
       </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Flu-0023|A_NP</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0023|A_NP</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
         <is>
           <t>ATGGCGTCTCAAGGCACCAAACGATCCTATGAACAAATGGAAACTGGTGGGGAACGCCAGAATGCCACTGAAATCAGAGCTTCTGTTGGAAGAATGGTTGGCGGAATCGGGAGATTCTACATACAGATGTGCACTGAACTCAAACTCAGTGATTACGAAGGGAGGCTGATCCAAAACAGCATAACCATAGAAAGGATGGTTCTCTCGGCATTTGATGAGAGGAGGAACAAGTACCTGGAGGAACATCCCAGTGCCGGGAAGGATCCCAAGAAGACTGGAGGTCCAATCTACAGGAGGAGAGATGGCAAATGGGTGAGAGAGTTGATCCTCTACGACAAAGAAGAGATCAGAAGAATTTGGCGTCAAGCTAATAATGGAGAGGATGCAACTGCTGGTCTCACTCACTTGATGATTTGGCATTCCAATCTGAATGATGCCACATACCAGAGAACAAGGGCACTTGTGCGTACTGGAATGGACCCTAGAATGTGCTCTCTGATGCAAGGCTCAACCCTCCCTAGGAGATCAGGGGCTGCTGGAGCAGCAGTGAAAGGAGTTGGAACAATGGCGATGGAACTAATTCGAATGATCAAACGAGGGATCAATGATCGGAATTTCTGGAGAGGCGAAAACGGTCGGAGAACCAGGATTGCCTACGAGAGAATGTGCAACATTCTCAAGGGAAAGCTCCAAACAGCAGCACAACGGGCAATGATGGACCAAGTGAGAGAAAGCCGGAATCCTGGGAATGCTGAAATCGAAGATCTCATCTTTCTCGCACSATCTGCTCTCATCCTGAGGGGATCAGTGGCTCATAAGTCCTGTCTGCCTGCTTGCGTATATGGACTTGCTGTAGCCAGTGGATATGACTTTGAAAGAGAGGGATATTCTCTAGTCGGAATTGATCCTTTCCGTCTGCTCCAAAACAGCCAAGTCTTCAGTCTCATCAGACCGAACGAAAATCCAGCTCATAAAAGTCAGCTGGTATGGATGGCATGCCACTCTGCGGCATTTGAGGATCTGAGAGTGTCAAGCTTCATCAGAGGGACAAGAGTAGTCCCAAGAGGACAACTGTCCACCAGAGGAGTTCAGATTGCTTCAAATGAAAACATGGAGACAATGGACTCCAGTACTCTTGAACTGAGGAGCAGATATTGGGCTATAAGAACAAGAAGTGGAGGAAACACTAACCAACAGAGAGCATCTGCAGGACAAATCAGCGTACAGCCCACATTCTCTGTACAAAGAAACCTCCCATTCGAGAGAGCAACCATCATGGCAGCATTTACGGGAAACACTGAAGGCAGAACTTCAGATATGAGAACTGAGATCATAAGGATGATGGAAAATGCCAGACCTGAAGATGTGTCTTTCCAGGGGCGGGGAGTCTTCGAGCTCTCGGACGAAAAGGCAACGAACCCGATCGTGCCTTCCTTTGACATGAGTAATGAAGGATCTTATTTCTTCGGAGACAATGCAGAGGAGTATGACAATTAA</t>
         </is>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Flu-0023|A_NA</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0023|A_NA</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
         <is>
           <t>ATGAATCCAAATCAAAAGATAACAACCATTGGAACAATCTGTATGGTAATTGGGATAGTCAGCTTGATGCTGCAAATTGGGAACATAATCTCAATATGGGTTAGCCATTCAATCCAAACAGGGAATCAATACCAGCCTGAACCATGCAATCAAAGCATCATTACCTATGAGAACAACACCTGGGTAAATCAGACGTATGTCAAAATCAGCAATACCAATTTTCTTGCTGAGCAGGCTGTTACTTCGGTAACATTAGCGGGCAATTCATCTCTTTGCCCTATTAGTGGGTGGGCAATATACAGTAAGGACAACGGTATAAGAATTGGGTCCAAGGGGGATGTGTTTGTTATAAGAGAACCGTTCATCTCATGCTCCCACTTGGAATGCAGAACCTTTTTCCTGACCCAGGGAGCTCTGCTGAATGACAAACATTCTAATGGGACAGTTAAGGATAGAAGCCCTTATAGAACTTTGATGAGTTGTCCCGTGGGTGAGGCTCCTTCCCCGTATAATTCAAGATTTGAGTCTGTTGCTTGGTCGGCAAGTGCTTGTCATGATGGCATCAGTTGGTTGACAATCGGTATTTCTGGTCCAGACAATGGAGCTGTGGCTGTATTGAAGTACAATGGCATAATAACGGATACTATCAAGAGTTGGAGAAACAACATTTTGAGAACTCAAGAATCTGAATGTGCTTGCGTAAATGGCTCTTGCTTCACCGTAATGACTGATGGACCAAGCAATGGGCAGGCCTCATATAAAATCTTCAAGATAGAGAAAGGGAAAGTTGTCAAATCAGTTGAAATGAATGCCCCTAATTACCACTACGAGGAATGCTCCTGTTATCCTGATGCGGGTGATATTATGTGTGTGTGCAGGGACAATTGGCATGGCTCAAACCGGCCGTGGGTATCTTTTAATCAAAATCTGGAGTATCAAATAGGATATATATGCAGTGGGGTTTTCGGGGACAATCCCCGCCCCAATGATGGAACAGGCAGTTGCAGTCCAATGCCCTCTAATGGGGCATATGGGGTAAAAGGGTTTTCATTTAAGTACGGTAATGGGGTTTGGATCGGAAGAACAAAAAGCACTAGTTCCAGAAGCGGCTTTGAGATGATTTGGGATCCGAATGGGTGGACTGAGACGGACAGTAGTTTCTCAGTGAAGCAAGACATTGTAGAAATAACTGACTGGTCAGGATATAGTGGGAGTTTTGTCCAGCATCCAGAACTGACGGGATTAGATTGCATGAGGCCTTGTTTCTGGGTTGAGCTAATCAGAGGGAGGCCCAAAGAGAACACAATTTGGACTAGCGGGAGCAGCATATCCTTTTGTGGTGTAAATAGTGACACTGTGGGTTGGTCTTGGCCAGACGGTGCTGAGTTGCCATTCACCATTGACAAGTAG</t>
         </is>
       </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Flu-0023|A_MP</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0023|A_MP</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>ATGAGTCTTCTAACCGAGGTCGAAACGTACGTTCTCTCTATCGTCCCGTCGGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTTGAAGATGTCTTTGCAGGGAAGAACACCGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATCCTGTCACCTCTGACTAAGGGGATTTTGGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCTCTAAGTGGAACTGGAGACCCAAACAACATGGACAGGGCAGTCAAGTTGTACAGGAAACTGAAGAGAGAGATAACATTCCATGGTGCTAAAGAAGTTGCACTCAGTTACTCAACCGGTGCACTTGCCAGTTGTATGGGTCTCATATACAACAGGATGGGGACGGTGACCGCAGAAGTGGCATTGGGCCTAGTGTGTGCCACCTGTGAGCAGATTGCTGATTCACAGCATCGGTCTCACAGACAGATAGCTACCACCACCAACCCACTAATCAGACATGAAAACAGAATGGTTTTGGCCAGTACTACAGCTAAGGCTATGGAGCAGATGGCTGGATCGAGTGAACAAGCAGTGGAAGCCATGGAGGTTGCTAGTCAGGCTAGGCAGATGGTGCAGGCAATGAGGACCATTGGAACTCATCCTAGCTCCAGTGCCGGTCTGAGAGATGATCTCCTTGAAAATTTGCAGGCCTACCAAAAACGGATGGGAGTGCAACTGCAGCGATTCAAGTGATCCTCTCGTTATTGCCGCAAGTATCATTGGGATCTTGCACTTGATATTGTGGATTCTTGATCGCCTTTTCTTCAAATGCGTTTATCGTCGCCTTAAATACGGTTTGAAAGGAGGGCCTTCTACGGAAGGAGTACCTGAGTCCATGAGGGAAGAGTACCGGCAGGAACAGCAGAGTGCTGTGGATGTTGACGATGGTCATTTTGTCAACATAGAGCTGGAGTAA</t>
         </is>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Flu-0023|A_NS</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0023|A_NS</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
         <is>
           <t>ATGGATTCCAACACTGTGTCAAGCTTTCAGGTAGACTGCTTTCTTTGGCATGTCCGCAAACGATTTGCAGACCAAGAACTGGGTGATGCCCCATTCCTTGACCGGCTCCGCCGAGACCAGAAGTCTCTAAGAGGAAGAGGCAGCACTCTTGGTCTGGACATCGAGACGGCCACTCGTGCTGGAAAGCAGATAGTGGAGAGGATTCTGGAGGAAGAATCCGACGAGGCACTCAAAATGACTATTGCCTCTGTGCCTGCTCCACGCTACCTAACTGACATGACTCTTGAAGAGATGTCAAGAGACTGGTTCATGCTCATGCCCAAGCAAAAAGTGGCAGGCTCCCTCAGTATCAGAATGGACCAGGCGATTATGGATAAGAACATCATACTGAAGGCAAACTTCAGTGTGATCTTCAATCGGCTGGAGACACTAATACTACTCAGAGCTTTCACTGAAGAGGGAGCAATTGTCGGCGAAATTTCACCATTGCCTTCTCTTCCAGGACATACTGATGAGGATGTCAAAAATGCAATTGGGGTCCTCATCGGAGGACTTGAATGGAATGATAACACAGTTCGAGTCTCTGAAACTTTACAGAGATTCGCTTGGAGAAGCAGTAATGAGGATGGGAGACCTCCACTCCCTCCAAAGCAGAAACGGAAAATGGAGAGAACAATTGAGTCAGAAGTTTGAAGAAATAAGGTGGCTGATTGAAGAAGTTCGACACAGACTAAAGATCACAGAAAATAGTTTTGAACAAATAACATTTATGCAAGCCTTACAACTACTGCTTGAAGTGGAGCAAGAGATAAGAACTTTCTCGTTTCAGCTTATTTAA</t>
         </is>
       </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Flu-0027|A_MP</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0027|A_MP</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
         <is>
           <t>ATGAGTCTTCTAACCGAGGTCGAAACGTACGTTCTCTCTATCGTCCCGTCGGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTTGAAGATGTCTTTGCAGGGAAGAACACCGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATACTGTCACCTCTGACTAAGGGGATTTTGGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCTCTAAGTGGAAATGGAGACCCAAACAACATGGACAGGGCAGTCAAGTTGTACAGGAAATTGAAGAGAGAAATAACATTCCATGGGGCTAAAGAAGTTGCACTCAGTTACTCAACCGGTGCACTTGCCAGTTGTATGGGTCTCATATACAACAGGATGGGGACGGTGACCGCAGAAGTGGCATTGGGCCTAGTGTGTGCCACCTGTGAGCAGATTGCTGATTCACAGCATCGGTCTCACAGACAGATAGCTACCACCACCAACCCACTAATCAGACATGAAAACAGAATGGTTTTGGCCAGTACTACAGCTAAGGCTATGGAGCAGATGGCTGGATCGAGTGAGCAAGCAGTGGAAGCCATGGAGGTTGCTAGTCAGGCTAGGCAAATGGTGCAGGCGATGAGGACCATTGGAACTCATCCTAGCTCCAGTGCCGGTCTGAGAGATGATCTCCTTGAAAATTTGCAGGCCTACCAAAAACGAATGGGAGTGCAACTGCAGCGATTCAAGTGATCCTCTCGTTATTGCCGCAAGTATCATTGGGATCTTGCACTTGATATTGTGGATTCTTGATCGCCTTTTCTTCAAATGCGTTTATCGTCGCCTTAAATACGGTTTGAAAGGAGGGCCTTCTACGGAAGGAGTACCTGAGTCCATGAGGGAAGAGTACCGGCAGGAACAGCAGAGTGCTGTGGATGTTGACGATGGTCATTTTGTCAACATAGAGATGGAGTAA</t>
         </is>
       </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Flu-0027|A_NS</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0027|A_NS</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
         <is>
           <t>ATGGATTCCAACACTGTGTCAAGCTTCCAGGTAGACTGCTTTCTTTGGCATGTCCGCAAACGATTTGCAGACCAAGAACTGGGTGATGCCCCATTCCTTGACCGGCTCCGCCGAGACCAGAAGTCTCTAAGAGGAAGAGGCAGCACTCTTGGTCTGGACATCGAGACGGCCACTCGTGCTGGAAAGCAGATAGTGGAGAGGATTCTGGAGGAAGAATCCGACGAGGCACTCAAAATGACTATTGCCTCTGTGCCTGCTCCACGCTACCTAACTGACATGACTCTTGAAGAGATGTCAAGAGACTGGTTCATGCTCATGCCCAAGCAAAAAGTGGCAGGCTCCCTCTGTATCAGAATGGACCAGGCGATTATGGATAAGAACATCATACTGAAGGCAAACTTCAGTGTGATCTTCAATCGGCTGGAGACACTAATACTACTCAGAGCTTTCACTGAAGAGGGAGCAATTGTCGGCGAAATTTCACCATTGCCTTCTCTTCCAGGACATACTGATGAGGATGTCAAAAATGCAATTGGGGTCCTCATCGGAGGACTTGAATGGAATGATAACACAGTTCGAGTCTCTGAAATTTTACAGAGATTCGCTTGGAGAAGCAGTAATGAGGATGGGAGACCTCCACTCCCTCCAAAGCAGAAACGGAAAATGGAGAGAACAATTGAGTCAGAAGTTTGAAGAAATAAGGTGGCTGATTGAAGAGGTGCGACACAGACTAAAGATCACAGAAAATAGTTTTGAACAAATAACATTTATGCAAGCCTTACAACTACTGCTTGAAGTGGAGCAAGAGATACGAACTTTCTCGTTTCAGCTTATTTAA</t>
         </is>
       </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Flu-0035|A_NP</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0035|A_NP</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
         <is>
           <t>ATGGCGTCTCAAGGCACCAAACGATCCTATGAACAAATGGAAACTGGTGGGGAACGCCAGAATGCCACTGAAATCAGAGCATCTGTTGGAAGAATGGTTGGCGGAATAGGAAGATTCTACATACAGATGTGCACTGAGCTCAAACTCAGTGATTACGAAGGGAGGCTGATCCAAAACAGCATAACCATAGAAAGGATGGTTCTCTCGGCATTTGATGAGAGGAGGAACAAGTACCTGGAGGAACATCCCAGTGCCGGGAAGGATCCCAAGAAGACTGGAGGTCCAATCTACAGGAGGAGAGATGGCAAATGGGTGAGAGAGTTGATCCTCTACGACAAAGAAGAGATCAGAAGAATTTGGCGTCAAGCTAATAATGGAGAGGATGCAACTGCTGGTCTCACTCATTTGATGATTTGGCATTCCAATCTGAATGATGCAACATACCAGAGAACAAGGGCACTTGTGCGTACTGGAATGGACCCTAGAATGTGCTCTCTGATGCAAGGCTCAACCCTCCCTAGGAGATCCGGGGCTGCTGGAGCAGCAGTGAAAGGAGTTGGAACAATGGTGATGGAACTAATTCGAATGATCAAACGAGGGATCAATGATCGGAATTTCTGGAGAGGCGAAAACGGTCGGAGAACCAGGATTGCCTACGAGAGAATGTGCAACATCCTCAAGGGAAAGTTCCAAACAGCAGCACAACGGGCAATGATGGACCAAGTGAGAGAAAGCCGGAATCCTGGGAATGCTGAAATTGAAGATCTCATCTTTCTCGCACGATCTGCTCTCATCCTGAGGGGATCAGTGGCTCATAAGTCCTGTCTGCCTGCTTGCGTATATGGACTTGCTGTAGCCAGTGGATATGACTTTGAAAGAGAGGGATATTCTCTAGTCGGAATTGATCCTTTCCGTCTGCTCCAAAACAGCCAAGTCTTCAGTCTCATCAGACCGAACGAAAATCCAGCTCATAAAAGTCAGCTGGTATGGATGGCATGCCACTCTGCGGCATTTGAGGATCTGAGAGTTTCAAGCTTCATCAGAGGGACAAGAGTAGTCCCAAGAGGACAACTGTCCACCAGAGGAGTTCAGATTGCTTCAAATGAAAACATGGAGACAATGGACTCCAGTACTCTTGAACTGAGGAGCAGGTACTGGGCTATAAGAACAAGAAGTGGAGGAAACACTAACCAACAGAGAGCATCTGCAGGACAAATCAGCGTACAGCCCACATTCTCTGTGCAAAGAAACCTCCCATTCGAGAGAGCAACCATCATGGCAGCATTTACGGGAAACACTGAAGGCAGAACTTCAGACATGAGAACTGAGATCATAAGGATGATGGAAAATGCCAGACCTGAAGATGTGTCTTTCCAGGGGCGGGGAGTCTTCGAGCTCTCGGACGAAAAGGCAACGAACCCGATCGTGCCTTCCTTTGACATGAGTAATGAAGGATCTTATTTCTTCGGAGACAATGCAGAGGAGTATGACAATTAA</t>
         </is>
       </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Flu-0035|A_MP</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0035|A_MP</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
         <is>
           <t>ATGAGTCTTCTAACCGAGGTCGAAACGTACGTTCTCTCTATCGTCCCGTCGGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTTGAAGATGTTTTTGCAGGGAAGAACACCGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATACTGTCACCTCTGACTAAGGGGATTTTGGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCTCTAAGTGGAAATGGAGACCCAAACAACATGGACAGGGCAGTCAAGTTGTACAGGAAATTGAAGAGAGAAATAACATTTCATGGGGCTAAAGAAGTTGCACTCAGTTACTCAACCGGTGCACTTGCCAGTTGTATGGGTCTCATATACAACAGGATGGGGACGGTGACCGCAGAAGTGGCATTGGGCCTAGTGTGTGCCACCTGTGAGCAGATTGCTGATTCACAGCATCGGTCTCACAGACAGATAGCTACCACCACCAACCCACTAATCAGACATGAAAACAGAATGGTTTTGGCCAGTACTACAGCTAAGGCTATGGAGCAGATGGCTGGATCGAGTGAGCAAGCAGTGGAAGCCATGGAGGTTGCTAGTCAGGCTAGGCAAATGGTGCAGGCGATGAGGACCATTGGAACTCATCCTAGCTCCAGTGCCGGTCTGAGAGATGATCTCCTTGAAAATTTGCAGGCCTACCAAAAACGAATGGGAGTGCAACTGCAGCGATTCAAGTGATCCTCTCGTTATTGCCGCAAGTATCATTGGGATCTTGCACTTGATATTGTGGATTCTTGATCGCCTTTTCTTCAAATGCGTTTATCGTCGCCTTAAATACGGTTTGAAAGGAGGGCCTTCTACGGAAGGAGTACCTGAGTCCATGAGGGAAGAGTACCGGCAGGAACAGCAGAGTGCTGTGGATGTTGACGATGGTCATTTTGTCAACATAGAGATGGAGTAA</t>
         </is>
       </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Flu-0035|A_NS</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0035|A_NS</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
         <is>
           <t>ATGGATTCCAACACTGTGTCAAGCTTTCAGGTAGACTGCTTTCTTTGGCATGTCCGCAAACGATTTGCAGACCAAGAACTGGGTGATGCCCCATTCCTTGACCGGCTCCGCCGAGACCAGAAGTCTCTAAGAGGAAGAGGCAGCACTCTTGGTCTGGACATCGAGACGGCCACTCGTGCTGGAAAGCAGATAGTGGAGAGGATTCTGGAGGAAGAATCCGACGAGGCACTCAAAATGACTATTGCCTCTGTGCCTGCTCCACGCTACCTAACTGACATGACTCTTGAAGAGATGTCAAGAGATTGGTTCATGCTCATGCCCAAGCAAAAAGTGGCAGGCTCCCTCTGTATCAGAATGGACCAGGCGATTATGGATAAGAACATCATACTGAAGGCAAACTTCAGTGTGATCTTCAATCGGCTGGAGACACTAATACTACTCAGAGCTTTCACTGAAGAGGGAGCAATTGTCGGCGAAATTTCACCATTGCCTTCTCTTCCAGGACATACTGATGAGGATGTCAAAAATGCAATTGGGGTCCTCATCGGAGGACTTGAATGGAATGATAACACAGTTCGAGTCTCTGAAATTTTACAGAGATTCGCTTGGAGAAGCAGTAATGAGGATGGGAGACCTCCACTCCCTCCAAAGCAGAAACGGAAAATGGAGAGAACAATTGAGTCAGAAGTTTGAAGAAATAAGGTGGCTGATTGAAGAGGTGCGACACAGATTAAAGATCACAGAAAATAGTTTTGAACAAATAACATTTATGCAAGCCTTACAACTACTGCTTGAAGTGGAGCAAGAGATACGAACTTTCTCGTTTCAGCTTATTTAA</t>
         </is>
       </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Flu-0055|A_MP</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0055|A_MP</t>
+        </is>
+      </c>
+      <c r="AX1" t="inlineStr">
         <is>
           <t>ATGAGTCTTCTAACCGAGGTCGAAACGTACGTTCTCTCTATCGTCCCGTCGGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTTGAAGATGTCTTTGCAGGGAAGAACACCGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATCCTGTCACCTCTGACTAAGGGGATTTTGGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCTCTAAGTGGAACTGGAGACCCAAACAACATGGACAGGGCAGTCAAGTTGTACAGGAAACTGAAGAGAGAGATAACATTCCATGGTGCTAAAGAAGTTGCACTCAGTTACTCAACCGGTGCACTTGCCAGTTGTATGGGTCTCATATACAACAGGATGGGGACGGTGACCGCAGAAGTGGCATTGGGCCTAGTGTGTGCCACCTGTGAGCAGATTGCTGATTCACAGCATCGGTCTCACAGACAGATAGCTACCACCACCAACCCACTAATCAGACATGAAAACAGAATGGTTTTGGCCAGTACTACAGCTAAGGCTATGGAGCAGATGGCTGGATCGAGTGARCAAGCAGTGGAAGCCATGGAGGTTGCTAGTCAGGCTAGGCARATGGTGCAGGCRATGAGGACCATTGGAACTCATCCTAGCTCCAGTGCCGGTCTGAGAGATGATCTCCTTGAAAATTTGCAGGCCTACCAAAAACGRATGGGAGTGCAACTGCAGCGATTCAAGTGATCCTCTCGTTATTGCCGCAAGTATCATTGGGATCTTGCACTTGATATTGTGGATTCTTGATCGCCTTTTCTTCAAATGCGTTTATCGTCGCCTTAAATACGGTTTGAAAGGAGGGCCTTCTACGGAAGGAGTACCTGAGTCCATGAGGGAAGAGTACCGGCAGGAACAGCAGAGTGCTGTGGATGTTGACGATGGTCATTTTGTCAACATAGAGMTGGAGTAA</t>
         </is>
       </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Flu-0205|A_MP</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
+      <c r="AY1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0205|A_MP</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>NNNNGTCTTCTAACCGAGGTCGAAACGTACGTTCTCTCTATCGTCCCGTCGGGNCCCCTCAAAGCCGAGATCGCGCAGAGACTTGAAGATGTCTTTGCANGGAAGAACACCGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATCCTGTCACCTCTGACTAAGGGGATTTTGGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCTCTAAGTGGAACTGGAGACCCAAACAACATGGACAGGGCAGTCAAGTTGTACAGGAAACTAAAGAGAGAGATAACATTCCATGGTGCTAAAGAAGTTGCACTCAGTTACTCAACCGGTGCACTTGCCAGTTGTATGGGTCTCATATACAACAGGATGGGGACNGTGACCGCAGAAGTGGCATTGGGCCTAGTGTGTGCCACCTGTGAGCAGATTGCTGATTCACAGCATCGGTCTCACAGACAGATAGCTACCACCACCAACCCACTAATCAGACATGAAAACAGAATGGTTTTGGCCAGTACTACAGCTAAGGCTATGGAGCAGATGGCTGGATCGAGTGAGCAAGCAGTGGAAGCCATGGAGGTTGCTAGTCAGGCTAGGCAGATGGTGCAGGCGATGAGGACCATTGGAACTCATCCTAGCTCCAGTGCCGGTCTAAGAGATGATCTCCTTGAAAATTTGCAGGCCTACCAAAAACGGATGGGAGTGCAACTGCAGCGATTCAAGTGATCCTCTCGTTATTGCCGCAAGTATCATTGGGATCTTGCACTTGATATTGTGGATTCTTGATCGCCTTTTCTTCAAATGCGTTTATCGTCGCCTTAAATACGGTTTGAAAGGAGGGCCTTCTACGGAAGGAGTACCTGAGTCCATGAGGGAAGAGTACCGGCAGGAACAGCAGAGTGCTGTGGATGTTGACGATGGTCATTTTGTCAACATAGANNNNNNNNNN</t>
         </is>
       </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Flu-0206|A_MP</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
+      <c r="BA1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0206|A_MP</t>
+        </is>
+      </c>
+      <c r="BB1" t="inlineStr">
         <is>
           <t>ATGAGTCTTCTAACCGAGGTCGAAACGTACGTTCTCTCTATCGTCCCGTCGGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTTGAAGATGTCTTTGCAGGGAAGAACACCGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATCCTGTCACCTCTGACTAAGGGGATTTTGGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCTCTAAGTGGAACTGGAGACCCAAACAACATGGACAGGGCAGTCAAGTTGTACAGGAAACTAAAGAGAGAGATAACATTCCATGGTGCTAAAGAAGTTGCACTCAGTTACTCAACCGGTGCACTTGCCAGTTGTATGGGTCTCATATACAACAGGATGGGGACGGTGACCGCAGAAGTGGCATTGGGCCTAGTGTGTGCCACCTGTGAGCAGATTGCTGATTCACAGCATCGGTCTCACAGACAGATAGCTACCACCACCAACCCACTAATCAGACATGAAAACAGAATGGTTTTGGCCAGTACTACAGCTAAGGCTATGGAGCAGATGGCTGGATCGAGTGAGCAAGCAGTGGAAGCCATGGAGGTTGCTAGTCAGGCTAGGCAGATGGTGCAGGCGATGAGGACCATTGGAACTCATCCTAGCTCCAGTGCCGGTCTAAGAGATGATCTCCTTGAAAATTTGCAGGCCTACCAAAAACGGATGGGAGTGCAACTGCAGCGATTCAAGTGATCCTCTCGTTATTGCCGCAAGTATCATTGGGATCTTGCACTTGATATTGTGGATTCTTGATCGCCTTTTCTTCAAATGCGTTTATCGTCGCCTTAAATACGGTTTGAAAGGAGGGCCTTCTACGGAAGGAGTACCTGAGTCCATGAGGGAAGAGTACCGGCAGGAACAGCAGAGTGCTGTGGATGTTGACGATGGTCATTTTGTCAACATAGAGCTGGAGTAA</t>
         </is>
       </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Flu-0206|A_NS</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
+      <c r="BC1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0206|A_NS</t>
+        </is>
+      </c>
+      <c r="BD1" t="inlineStr">
         <is>
           <t>NNNGATTCCAACACTGTGTCAAGCTTTCAGGTAGACTGCTTTCTTTGGCATGTCCGCAAACGATTTGCAGACCAAGAACTGGGTGATGCCCCATTCCTTGACNGGCTCCGCCGAGACCAGAAGTCTCTAAGAGGAAGAGGCAGCACTCTTGGTCTGAACATCGAGACGGCCACTCGTGCTGGAAAGCAGATAGTGGAGAGGATTCTGGAGGAAGAATCCGACGAAGCACTCAAAATGACTATTGCCTCTGTGCCTGCTCCACGCTACCTAACTGACATGACTCTTGAAGAGATGTCAAGAGACTGGTTCATGCTCATGCCCAAGCNAAAAGTGGCAGGCTCCCTCAGTATCAGAATGGACCAGGCGATTATGGATAAGAACATCATACTGAAGGCAAACTTCAGTGTGATCTTCAATCGGCTGGAGACACTAATACTACTCAGAGCTTTCACTGAAGAAGGAGCAATTGTCGGCGAAATTTCACCATTGCCTTCTCTTCCAGGACATACTGATGAGGATGTCAAAAATGCAATTGGGGTCCTCATCGGAGGATTTGAATGGAATGATAACACAGTTCGAGTCTCTGAAACTTTACAGAGGTTCGCTTGGAGAAGCAGTAATGAGGATGGGAGACCTCCACTCCCTCCAAAGCAGAAACGGAAAATGGAGAGAACAATTGAGTCAGAAGTTTGAAGAAATAAGGTGGCTGATTGAAGAAGTTCGACACAGACTAAAGATCACAGAAAATAGTTTTGAACAAATAACATTTATGCAAGCCTTACAACTACTGCTTGAAGTGGAGCAAGAGATAAGAACTTTCTCGTTTCAGCTTATTNNN</t>
         </is>
       </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Flu-0314|A_NA</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
+      <c r="BE1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0314|A_NA</t>
+        </is>
+      </c>
+      <c r="BF1" t="inlineStr">
         <is>
           <t>ATGAATCCAAATCAAAAGATAACAACCATTGGATCAATCTGTATGGTAATTGGGACAGTCAGCTTGATGCTGCAAATTGGGAACATAATCTCAATATGGGTTAGCCATTCAATCCAAACAGGGAATCAATACCAGCCTGAACCATGCAATCAAAGCATCATTACCTATGAGAACAACACCTGGGTAAATCAGACGTATGTCAACATCAGCAATAACAATTTTCTTGCTGAGCAGGCTGTTACTTCGGTAACATTAGCGGGCAATTCATCTCTTTGCCCTATTAGTGGGTGGGCAATATACAGTAAGGACAACGGTATAAGAATTGGGTCCAAGGGGGATGTGTTTGTCATAAGAGAACCGTTCATCTCATGCTCCCACTTGGAATGCAGAACCTTTTTCCTGACTCAGGGAGCTCTGCTGAATGACAAACATTCTAATGGGACAGTTAAGGATAGAAGCCCTTATAGAACTTTGATGAGTTGTCCCGTGGGTGAGGCTCCTTCCCCGTACAATTCAAGATTTGAGTCTGTTGCTTGGTCGGCAAGTGCTTGTCATGATGGCATCAGTTGGTTGACAATCGGTATTTCTGGTCCAGACAATGGAGCTGTGGCTGTATTGAAGTACAATGGCATAATAACGGATACTATCAAGAGTTGGAGAAACAACATTTTGAGAACTCAAGAATCTGAATGTGCTTGCGTAAATGGCTCTTGCTTCACCGTAATGACTGATGGACCAAGCAATGGGCAGGCCTCGTATAAAATCTTCAAGATAGAGAAAGGGAAAGTTGTCAAATCAGTTGAATTGAATGCCCCTAATTACCACTACGAGGAATGTTCCTGTTATCCTGATGCGGGTGATATTATATGTGTGTGCAGGGACAATTGGCACGGCTCAAACCGGCCGTGGATATCTTTTAATCAAAATCTGGAGTATCAAATAGGATATATATGCAGTGGGGTTTTCGGGGACAATCCCCGCCCCAATGATGGAACAGGCAGTTGCAGTCCAATGTCCTCTAATGGGGCATATGGGGTRAAAGGGTTTTCATTTAAGTACGGTAATGGGGTTTGGATCGGAAGAACAAAAGGCACTAGTTCCAGAAGCGGCTTTGAGATGATTTGGGACCCGAATGGGTGGACTGAGACGGACAGTAGTTTCTCAGTGAAGCAAGACATTGTAGAAATAACTGACTGGTCAGGATATAGTGGGAGTTTTGTCCAGCATCCAGAACTGACAGGATTAGATTGCATGAGGCCTTGTTTCTGGGTTGAGCTAATTAGAGGGAGGCCCAAAGAGAACACAATTTGGACTAGCGGGAGCAGCATATCCTTTTGTGGTGTAAATAGTGACACTGTGGGTTGGTCTTGGCCAGACGGTGCTGAGTTGCCATTCACCATTGACAAGTAG</t>
         </is>
       </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Flu-0314|A_MP</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
+      <c r="BG1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0314|A_MP</t>
+        </is>
+      </c>
+      <c r="BH1" t="inlineStr">
         <is>
           <t>ATGAGTCTTCTAACCGAGGTCGAAACGTACGTTCTCTCTATCGTCCCGTCGGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTTGAAGATGTCTTTGCAGGGAAGAACACCGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATACTGTCACCTCTGACTAAGGGGATTTTGGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCTCTAAGTGGAAATGGAGACCCAAACAACATGGACAGGGCAGTCAAGTTGTACAGGAAACTGAAGAGAGAAATAACATTCCATGGGGCTAAAGAAGTTGCACTTAGTTACTCAACCGGTGCACTTGCCAGTTGTATGGGTCTCATATACAACAGGATGGGGACGGTGACCGCAGAAGTGGCATTGGGCCTAGTGTGTGCCACCTGTGAGCAGATTGCTGATTCACAGCATCGGTCTCACAGACAGATAGCTACCACCACCAACCCACTAATCAGACATGAAAACAGAATGGTTTTGGCCAGTACTACAGCTAAGGCTATGGAGCAGATGGCTGGATCGAGTGAGCAAGCAGTGGAAGCCATGGAGGTTGCTAGTCAGGCTAGGCAAATGGTGCAGGCGATGAGGACCATTGGAACTCATCCTAGCTCCAGTGCCGGTCTGAGAGATGATCTCCTTGAAAATTTGCAGGCCTACCAAAAACGAATGGGAGTGCAACTGCAGCGATTCAAGTGATCCTCTCGTTATTGCAGCAAGTATCATTGGGATCTTGCACTTGATATTGTGGATTCTTGATCGCCTTTTCTTCAAATGCGTTTATCGTCGCCTTAAATACGGTTTGAAAGGAGGGCCTTCTACGGAAGGAGTACCTGAGTCCATGAGGGAAGAGTACCGGCAGGAACAGCAGAGTGCTGTGGATGTTGACGATGGTCATTTTGTCAACATAGAGATGGAGTAA</t>
         </is>
       </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Flu-0314|A_NS</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
+      <c r="BI1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0314|A_NS</t>
+        </is>
+      </c>
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>ATGGATTCCAACACTGTGTCAAGCTTTCAGGTAGACTGCTTTCTTTGGCATGTCCGCAAACAATTTGCAGACCAAGAACTGGGTGATGCCCCATTCCTTGACCGGCTCCGCCGAGACCAGAAGTCTCTAAGAGGAAGAGGCAGCACTCTTGGTCTGGACATCGAGACGGCCACTCGTGCTGGAAAGCAGATAGTGGAGAGGATTCTGGAGGAAGAATCCGACGAGGCACTCAAAATGACTATTGCCTCTGTGCCTGCTCCACGCTACCTAACTGACATGACTCTTGAAGAGATGTCAAGAGACTGGTTCATGCTCATGCCCAAGCAAAAAGTGGCAGGCTCCCTCTGTATCAGAATGGACCAGGCGATTATGGATAAGAACATCATACTGAAGGCAAACTTCAGTGTGATCTTCAATCGGCTGGAGACACTAATACTACTCAGAGCTTTCACTGAAGAGGGAGCAATTGTCGGCGAAATTTCACCATTGCCTTCTCTTCCAGGACATACTGATGAGGATGTCAAAAATGCAATTGGGGTCCTCATCGGAGGACTTGAATGGAATGATAACACAGTTCGAGTCTCTGAAATTTTACAGAGATTCGCTTGGAGAAGCAGTAATGAGGATGGGAGACCTCCACTCCCTCCAAAGCAGAAACGGAAAATGGAGAGAACAATTGAGTCAGAAGTTTGAAGAAATAAGGTGGCTGATTGAAGAGGTGCGACACAGACTAAAGATCACAGAAAATAGTTTTGAACAAATAACATTTATGCAAGCCTTACAACTACTGCTTGAAGTGGAGCAAGAGATACGAACTTTCTCGTTTCAGCTTATTTAA</t>
         </is>
       </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Flu-0316|A_PB2</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
+      <c r="BK1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0316|A_PB2</t>
+        </is>
+      </c>
+      <c r="BL1" t="inlineStr">
         <is>
           <t>ATGGAGAGAATAAAAGAACTAAGAGATCTAATGTCACAGTCTCGCACTCGCGAGATACTGACCAAAACCACTGTTGACCACATGGCCATAATCAAAAAGTACACATCGGGAAGGCAAGAGAAGAACCCCGCACTCAGAATGAAATGGATGATGGCAATGAAATATCCAATTACAGCAGATAAGCGAATAATGGAAATGATCCCTGAGAGGAATGAACAAGGGCAAACTCTCTGGAGCAAAACAAACGATGCCGGATCAGACCGAGTGATGGTATCACCCCTGGCTGTGACATGGTGGAACAGGAACGGACCAACAACAAGTACAGTTCACTACCCAAAGGTATATAAAACTTATTTCGAAAAAGTTAAAAGGTTGAAACACGGGACCTTTGGCCCTGTGCACTTCAGAAACCAAGTTAAGATAAGACGGAGGGTCGATATAAACCCGGGCCATGCTGACCTTAGTGCCAAAGAGGCACAGGATGTAATCATGGAAGTCGTCTTCCCAAATGAAGTGGGAGCTAGGATATTGACGTCGGAGTCACAACTGACGATAACAAAGGAGAAAAAGGAAGAACTCCAGGACTGCAAAATCGCTCCTCTGATGGTTGCATACATGCTAGAACGAGAGTTGGTTCGCAAGACGAGGTTTCTCCCAGTTGCTGGTGGGACAAGCAGTGTCTACATTGAGGTGCTGCATTTGACCCAGGGGACATGCTGGGAGCAGATGTACACTCCGGGAGGAGAAGTGAGGAACGATGATGTAGACCAAAGCTTGATCATTGCTGCCAGGAATATAGTAAGAAGAGCAACAGTATCAGCAGATCCGTTAGCATCTCTATTGGAGATGTGTCACAGCACACAAATTGGGGGAATAAGGATGGTAGACATCCTTCGGCAAAACCCAACAGAGGAACAAGCCGTGGATATATGCAAGGCAGCAATGGGCTTGAGGATTAGCTCATCTTTCAGCTTTGGTGGATTCACTTTTAAAAGAACAAGTGGATCGTCAGTCAAAAAAGAAGAAGAAGTGCTAACAGGCAACCTTCAAACATTGAAAATAAGAGTACATGAGGGGTATGAAGAGTTCACAATGGTTGGGAGAAGAGCAACGGCCATTCTCAGGAAAGCAACCAGAAGGCTGATCCAGCTAATAGTAAGTGGGAGAGACGAGCAGTCAATTGCTGAAGCAATAATTGTGGCCATGGTATTCTCACAAGAGGACTGCATGATTAAAGCAGTTAGAGGTGACCTGAATTTTGTCAATAGGGCGAACCAGCGACTAAACCCAATGCATCAACTCTTGAGGCATTTCCAAAAGGATGCAAAAGTGCTTTTCCAAAATTGGGGAATTGAACCCATTGACAATGTGATGGGAATGATCGGGGTAATGCCTGACATGACCCCAAGTACTGAGATGTCGCTGAGGGGAATAAGAGTCAGCAAGATGGGAGTAGATGAATACTCAAGCACAGAGCGAGTAGTAGTAAGCATCGACCGGTTTTTAAGAGTTCGAGACCAACGGGGGAACGTACTATTATCACCCGAAGAGGTCAGTGAGACACAAGGAACGGAGAAACTGACAATCACTTATTCGTCATCAATGATGTGGGAGATCAATGGTCCTGAGTCGGTGTTGGTCAATACTTATCAGTGGATAATTAGAAACTGGGAAACTGTAAAAATTCAATGGTCACAGGATCCCACAATGCTGTATAATAAGATGGAATTCGAGCCATTCCAGTCTCTAGTCCCTAAGGCAGCCAGAGGTCAATACAGTGGGTTTGTGAGAACACTATTCCAGCAAATGCGAGATGTGCTTGGAACATTTGACACTGTTCAGATAGTAAAACTCCTCCCCTTTGCTGCCGCCCCACCGGAACAAAGTAGGATGCAGTTCTCCTCCCTGACTGTGAATGTAAGAGGATCAGGAATGAGGATACTGGTAAGAGGCAATTCACCAGTGTTCAATTACAACAAGGCCACCAAGAGGCTCACAGTTCTCGGGAAAGATGCAGGTGCATTGACCGAAGATCCAGATGAAGGCACAGCTGGAGTGGAGTCTGCTGTTTTAAGAGGATTCCTCATTTTGGGCAAAGAAGACAAGAGATATGGCCCAGCATTGAGCATCAATGAGCTGAGCAATCTTGCAAAGGGAGAGAAGGCTAATGTGCTAATTGGGCAAGGAGACGTAGTGTTGGTGATGAAACGGAAACGGGACTCTAGCATACTTACTGACAGCCAGACAGCGACCAAAAGAATTCGGATGGCCATCAATTAG</t>
         </is>
       </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Flu-0316|A_PB1</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
+      <c r="BM1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0316|A_PB1</t>
+        </is>
+      </c>
+      <c r="BN1" t="inlineStr">
         <is>
           <t>ATGGATGTCAATCCGACTTTACTTTTCTTGAAAGTTCCAGCGCAAAATGCCATAAGCACCACATTCCCGTATACTGGAGATCCTCCATACAGCCATGGAACAGGAACAGGATATACCATGGACACAGTTAACAGAACACATCAGTATTCAGAAAAAGGGAAATGGACAACAAACTCAGAAACTGGAGCACCTCAACTCAATCCAATTGATGGACCATTGCCTGAGGGCAATGAACCAAGTGGGTATGCACAAACGGACTGTGTCCTTGAAGCAATGGCTTTCCTTGAAGAGTCCCACCCAGGAATCTTTGAAAACTCGTGTCTTGAAACGATGGAAGTTGTTCAACAAACAAGAGTGGACAAGTTGACCCAAGGCCGTCAGACCTATGATTGGACGTTAAACAGGAATCAGCCGGCTGCAACTGCATTAGCTAATACTATAGAGGTCTTCAGATCTAACGGCCTCACAGCCAATGAATCAGGAAGGCTAATAGATTTTCTCAAGGATGTGATGGAATCAATGGATAAGGAGGAAATGGAAATAACAACGCATTTCCAAAGGAAAAGAAGAGTGAGAGACAACATGACCAAGAAAATGGTCACACAAAGGACAATAGGAAAGAAGAAACAGAGGCTAAATAAAAAGAGCTATCTAATAAGAGCATTGACACTGAACACGATGACAAAAGACGCCGAAAGAGGCAAATTAAAAAGAAGGGCAATTGCAACACCTGGAATGCAAATCAGAGGGTTTGTGTACTTTGTTGAGACATTAGCGAGGAGCATTTGTGATAAGCTTGAACAATCTGGACTCCCAGTTGGGGGCAATGAAAAGAAGGCTAAACTGGCAAATGTTGTGAGAAAAATGATGACTAATTCGCAGGACACAGAGCTCTCTTTCACAATCACTGGAGACAACACCAAATGGAATGAAAATCAGAACCCTAGGATGTTTCTGGCAATGATAACATATATAACAAGGAACCAACCTGAATGGTTCAGGAATGTCTTAAGCATTGCACCTATAATGTTCTCAAATAAAATGGCAAGACTAGGGAAAGGGTACATGTTCGAAAGTAAGAGCATGAAGCTCCGAACACAAATACCAGCAGAAATGCTAGCAAGCATTGATCTGAAGTACTTCAATGAGTCAACAAGAAAGAAAATAGAGAAGATAAGACCTCTTCTAATAGATGGTACAGCCTCATTAAGCCCAGGAATGATGATGGGCATGTTCAATATGCTGAGTACAGTTTTGGGAGTTTCGATTCTAAATCTAGGACAAAGGAGGTACACCAAAACAACATACTGGTGGGACGGACTCCAATCCTCTGATGACTTTGCTCTCATAGTGAATGCTCCGAATCATGAGGGAATACAAGCAGGGGTAGACAGATTCTATAGAACCTGCAAGCTGGTCGGAATCAACATGAGCAAAAAGAAGTCCTACATAAACAGGACAGGAACATTTGAATTCACAAGTTTTTTCTACCGCTATGGATTTGTAGCCAACTTCAGTATGGAGTTGCCCAGCTTTGGAGTGTCTGGGATCAATGAATCTGCAGACATGAGCATTGGAGTAACAGTAATAAAGAACAACATGATCAACAATGATCTTGGACCAGCAACAGCTCAAATGGCTCTTCAGCTATTCATCAAGGATTACAGATACACATACCGGTGTCACAGAGGAGACACACAAATTCAGACAAGGAGGTCATTCGAGCTGAAGAAGTTGTGGGAACAGACCCGTTCAAAAGCAGGACTGCTGGTCTCAGATGGAGGACCAAATCTATACAATATTCGGAATCTTCACATTCCAGAAGTCTGCTTGAAATGGGAGCTAATGGACGAAGACTATCAGGGAAGGCTTTGTAATCCCCTGAACCCGTTTGTCAGCCACAAGGAAATAGAGTCTGTGAACAACGCAGTGGTGATGCCAGCTCATGGCCCGGCCAAGAGCATGGAATATGATGCTGTTGCCACCACTCACTCCTGGATACCGAAGAGGAACCGCTCCATTCTCAATACAAGCCAAAGGGGAATCCTTGAAGACGAACAGATGTATCAAAAGTGCTGCAACCTGTTCGAAAAATTCTTCCCTAGCAGTTCATACAGGAGGCCAGTTGGAATTTCCAGCATGGTGGAGGCCATGGTTTCTAGGGCCCGAATTGACGCACGAATTGACTTCGAATCTGGACGGATTAAGAAGGAGGAGTTTGCTAAGATCATGAAGATCTGTTCCACCATTGAAGAGCTCAGACGGCAGAAATAG</t>
         </is>
       </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Flu-0316|A_PA</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
+      <c r="BO1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0316|A_PA</t>
+        </is>
+      </c>
+      <c r="BP1" t="inlineStr">
         <is>
           <t>ATGGAAGACTTTGTGCGACAATGCTTCAATCCAATGATTGTCGAGCTTGCGGAAAAAGCAATGAAAGAATATGGGGAAGATCCGAAAATCGAGACAAACAAATTTGCCGCAATATGCACACACTTAGAAGTCTGTTTCATGTATTCGGATTTCCATTTTATTAATGAACGAGGCGAATCAATGATTGTAGAATCTGGCGATCCAAATGCATTATTGAAACACCGATTTGAGATAATAGAAGGGAGAGACCGGGCAATGGCCTGGACAGTGGTGAATAGTATCTGCAACACCACAGGGGTCGAAAAGCCCAAATTCCTCCCTGATTTGTATGACTACAAAGAGAACCGATTCATTGAAATTGGAGTAACGCGAAGGGAAGTTCACATATACTATTTAGAAAAAGCCAACAAGATAAAGTCAGAGAAAACACATATTCACATATTCTCATTCACTGGAGAGGAAATGGCCACCAAGGCGGACTACACCCTTGATGAAGAGAGCAGAGCAAGAATAAAAACCAGACTGTTCACTATAAGACAAGAAATGGCCAGTAGAGGTCTATGGGATTCCTTTCGTCAATCCGAGAGAGGCGAAGAGACAATTGAAGAAAGATTTGAAATCGCAGGAACCATGCGCAGGCTTGCCAACCAAAGTCTTCCACCGAACTTCTCCAGCCTTGAAAACTTTAGAGCCTATGTGGATGGATTCGAACCGAACGGCTGCATTGAGGGCAAACTTTCTCAAATGTCAAAAGAAGTGAACGCCAGGATTGAGCCATTTCTGAAGACAACACCACGCCCTCTCAGATTACCTGATGGGCCTCCCTGTTCTCAGCGGTCGAAGTTCTTGCTGATGGATGCCCTTAAGTTGAGCATCGAAGACCCTAGCCATGAGGGGGAGGGCATACCGCTGTATGATGCAATCAAATGCATGAAGACATTTTTTGGCTGGAAAGAGCCCAACATCGTAAAGCCGCATGAGAAAGGCATAAACCCTAATTACCTCCTGACTTGGAAGCAGGTGCTGGCAGAACTTCAAGACATTGAAAATGAGGAGAAAATTCCAAAGACAAAGAACATGAAGAAAACAAGCCAATTGAAGTGGGCACTTGGTGAGAACATGGCTCCAGAGAAAGTGGACTTTGAGGACTGCAAAGATGTTAGCGATCTAAGACAGTACGACAGTAACGAACCAGAGTCTAGAACACTAGCAAGCTGGATTCAGAGTGAATTCAACAAGGCATGCGAACTGACAGATTCGAGTTGGATTGAACTTGATGAGATAGGGGAAGACGTTGCTCCAATCGAACACATTGCGAGTGTGAGGAGGAACTATTTCACAGCGGAGGTATCCCATTGCAGGGCCACTGAATACATAATGAAGGGAGTATACATAAACACAGCCCTATTGAATGCATCCTGTGCAGCCATGGATGACTTCCAATTGATTCCAATGATAAGTAAGTGCAGAACTAAAGAAGGAAGACGGAAGACAAATCTGTATGGATTCATTATAAAAGGAAGATCCCATTTGAGGAATGACACCGATGTGGTAAACTTTGTGAGCATGGAATTCTCTCTAACTGACCCGAGGCTGGAGCCACACAAATGGGAGAAGTACTGTGTTCTTGAGATAGGAGACATGCTCCTACGGACTGCAATAGGCCAAGTGTCGAGGCCCATGTTCCTGTATGTGAGAACCAATGGGACTTCCAAGATCAAAATGAAATGGGGCATGGAGATGAGGCGATGCCTTCTTCAGTCCCTTCAACAAATTGAGAGCATGATTGAGGCCGAATCTTCTGTCAAAGAGAAGGACATGTCCAAGGAATTCTTTGAAAACAAATCAGAAACATGGCCAATTGGAGAATCACCCAAAGGGGTGGAGGAAGGCTCTATTGGGAAAGTATGCAGAACATTGCTAGCAAAGTCTGTGTTCAACAGCCTATATGCATCTCCACAACTCGAGGGGTTTTCAGCTGAATCAAGAAAATTGCTTCTCATTGTTCAGGCACTTAGGGACAACCTGGAACCTGGAACCTTCGATCTTGGGGGGCTATATGAAGCAATTGAGGAGTGCCTGATTAACGATCCCTGGGTTTTGCTTAATGCATCTTGGTTCAACTCCTTCCTCACACATGCACTGAAATAG</t>
         </is>
       </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Flu-0316|A_HA</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
+      <c r="BQ1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0316|A_HA</t>
+        </is>
+      </c>
+      <c r="BR1" t="inlineStr">
         <is>
           <t>ATGGAGAACATAGTACTACTTCTTGCAATAGTTAGCCTTGTTAAAAGTGACCAGATTTGCATTGGTTACCATGCAAACAATTCGACAGAGCAAGTTGACACGATAATGGAAAAGAACGTCACTGTTACACATGCCCAAGACATACTGGAAAAAACACACAACGGGAAGCTCTGTGATTTAAATGGGGTGAAGCCACTGATTTTAAAGGATTGTAGTGTAGCTGGATGGCTCCTCGGGAACCCAATGTGCGACGAATTCATCAGAGTGCCGGAATGGTCCTACATAGTGGAGCGAGCTAACCCAGCTAATGACCTCTGTTACCCAGGGAGCCTCAATGACTATGAAGAACTGAAACACATGTTGAGCAGAATAAATCATTTTGAGAAGATTCAGATCATTCCCAARAGTTCCTGGCCAAATCATGAAACATCACTAGGGGTGAGCGCAGCTTGTCCATACCAGGGAGCGCCCTCCTTTTTCAGAAATGTGGTGTGGCTTATCAAAAAGAACGATGCATACCCAACAATAAAGATAAGCTACAATAATACTAATCGGGAAGATCTCTTGATACTGTGGGGGATTCATCATCCCAACAATGCAGAAGAGCAGACAAATCTCTACAAAAACCCAACCACCTACATTTCAGTTGGAACATCAACTTTAAACCAGAGATTGGCACCAAAAATAGCTACTAGATCCCAAGTAAACGGGCAACGTGGAAGAATGGACTTCTTTTGGACAATCTTAAAACCAGATGATGCAATCCATTTCGAGAGTAACGGAAATTTCATTGCTCCAGAATATGCATACAAAATTGTCAAGAAAGGGGACTCAACAATTATGAAAAGTGGAGTGGAATATGGCCACTGCAACACCAAATGTCAAACCCCAGTAGGTGCTATAAATTCTAGTATGCCATTCCACAACATACATCCTCTCACCATTGGGGAATGCCCCAAATACGTGAAATCAAACAAGTTGGTCCTTGCGACTGGGCTCAGAAATAGTCCTCTAAGAGAAAAGAGAAGAAAAAGAGGTCTGTTTGGGGCGATAGCAGGGTTTATAGAGGGAGGATGGCAGGGAATGGTTGATGGTTGGTATGGGTACCATCATAGCAATGAGCAGGGGAGTGGGTACGCTGCGGACAAAGAATCCACCCAAAAGGCAATAGATGGAGTTACCAATAAGGTCAACTCAATCATTGACAAAATGAACACTCAATTTGAGGCAGTTGGAAGGGAGTTTAATAACTTAGAAAGGAGGATAGAGAATTTGAACAAGAAAATGGAAGACGGATTCCTAGATGTCTGGACCTATAATGCTGAACTTCTAGTTCTTATGGAAAACGAGAGGACTCTAGATTTCCATGATTCAAATGTCAAGAACCTTTACGACAAAGTCAGATTACAGCTTAGGGATAATGCAAAGGAGCTGGGTAACGGCTGTTTCGAATTCTATCACAAATGTGATAATGAATGTATGGAAAGTGTGAGAAATGGGACGTATGACTACCCTCAGTATTCAGAAGAAGCAAGATTAAAAAGAGAAGAAATAAGCGGAGTGAAATTAGAATCAGTAGGAACTTACCAGATACTGTCAATTTATTCAACAGCGGCAAGTTCCCTAGCACTGGCAATCATGATGGCTGGTCTATCTTTATGGATGTGCTCCAATGGGTCGTTACAATGCAGAATTTGCATTTAG</t>
         </is>
       </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Flu-0316|A_NP</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
+      <c r="BS1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0316|A_NP</t>
+        </is>
+      </c>
+      <c r="BT1" t="inlineStr">
         <is>
           <t>ATGGCGTCTCAAGGCACCAAACGATCCTATGAACAAATGGAAACTGGTGGGGAACGCCAGAATGCCACTGAAATCAGAGCATCTGTTGGAAGAATGGTTGGCGGAATAGGAAGATTCTACATACAGATGTGCACTGAGCTCAAACTCAGTGATTATGAAGGGAGGCTGATCCAAAACAGCATAACCATAGAAAGGATGGTTCTCTCGGCATTTGATGAGAGGAGGAACAAGTACCTGGAGGAACATCCCAGTGCCGGGAAGGATCCCAAGAAGACTGGAGGTCCAATCTACAGGAGGAGAGATGGCAAATGGGTGAGAGAGTTGATCCTCTACGACAAAGAAGAGATCAGAAGAATTTGGCGTCAAGCTAATAATGGAGAGGATGCAACTGCTGGTCTCACTCATTTGATGATTTGGCATTCCAATCTGAATGATGCAACATACCAGAGAACAAGGGCACTTGTGCGTACTGGAATGGACCCTAGAATGTGCTCTCTGATGCAAGGATCAACCCTCCCTAGGAGATCCGGGGCTGCTGGAGCAGCAGTGAAAGGAGTTGGAACAATGGTGATGGAACTAATTCGAATGATCAAGCGAGGGATCAATGATCGGAATTTCTGGAGAGGCGAAAACGGTCGGAGAACCAGGATTGCCTACGAGAGAATGTGCAACATCCTCAAGGGAAAGTTCCAAACAGCAGCACAACGGGCAATGATGGACCAAGTGAGAGAAAGCCGGAATCCTGGGAATGCTGAAATTGAAGATCTCATCTTTCTCGCACGATCTGCTCTCATCCTGAGGGGATCAGTGGCTCATAAGTCCTGTCTGCCTGCTTGCGTATATGGACTTGCTGTAGCCAGTGGATATGACTTTGAAAGAGAGGGATATTCTCTAGTCGGAATTGATCCTTTCCGTCTGCTCCAAAACAGCCAAGTCTTCAGTCTCATCAGACCGAACGAAAATCCAGCTCATAAGAGTCAGCTGGTATGGATGGCATGCCACTCTGCGGCATTTGAGGATCTGAGAGTTTCAAGCTTCATCAGAGGGACAAGAGTAGTCCCAAGAGGACAACTGTCCACCAGAGGAGTTCAGATTGCTTCAAATGAAAACATGGAGACAATGGACTCCAGTACTCTTGAACTGAGGAGCAGATACTGGGCTATAAGAACAAGAAGTGGAGGAAACACTAACCAACAGAGAGCATCTGCAGGACAAATCAGCGTGCAGCCCACATTCTCTGTGCAAAGAAACCTCCCATTCGAGAGAGCAACCATCATGGCAGCATTTACGGGAAACACTGAAGGCAGAACTTCAGACATGAGAACGGAGATCATAAGGATGATGGAAAATGCCAGACCTGAAGATGTGTCTTTCCAGGGGCGGGGAGTCTTCGAGCTCTCGGACGAAAAGGCAACGAACCCGATCGTGCCTTCCTTTGACATGAGTAATGAAGGATCTTATTTCTTCGGAGACAATGCAGAGGAGTATGACAATTAA</t>
         </is>
       </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Flu-0316|A_NA</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
+      <c r="BU1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0316|A_NA</t>
+        </is>
+      </c>
+      <c r="BV1" t="inlineStr">
         <is>
           <t>ATGAATCCAAATCAAAAGATAACAACCATTGGATCAATCTGTATGGTAATTGGGACAGTCAGCTTGATGCTGCAAATTGGGAACATAATCTCAATATGGGTTAGCCATTCAATCCAAACAGGGAATCAATACCAGCCTGAACCATGCAATCAAAGCATCATTACCTATGAGAACAACACCTGGGTAAATCAGACGTATGTCAACATCAGCAATAACAATTTTCTTGCTGAGCAGGCTGTTACTTCGGTAACATTAGCGGGCAATTCATCTCTTTGCCCTATTAGTGGGTGGGCAATATACAGTAAGGACAACGGTATAAGAATTGGGTCCAAGGGGGATGTGTTTGTCATAAGAGAACCGTTCATCTCATGCTCCCACTTGGAATGCAGAACCTTTTTCCTGACTCAGGGAGCTCTGCTGAATGACAAACATTCTAATGGGACAGTTAAGGATAGAAGCCCTTATAGAACTTTGATGAGTTGTCCCGTGGGTGAGGCTCCTTCCCCGTACAATTCAAGATTTGAGTCTGTTGCTTGGTCGGCAAGTGCTTGTCATGATGGCATCAGTTGGTTGACAATCGGTATTTCTGGTCCAGACAATGGAGCTGTGGCTGTATTGAAGTACAATGGCATAATAACGGATACTATCAAGAGTTGGAGAAACAACATTTTGAGAACTCAAGAATCTGAATGTGCTTGCGTAAATGGCTCTTGCTTCACCGTAATGACTGATGGACCAAGCAATGGGCAGGCCTCGTATAAAATCTTCAAGATAGAGAAAGGGAAAGTTGTCAAATCAGTTGAATTGAATGCCCCTAATTACCACTACGAGGAATGTTCCTGTTATCCTGATGCGGGTGATATTATATGTGTGTGCAGGGACAATTGGCACGGCTCAAACCGGCCGTGGATATCTTTTAATCAAAATCTGGAGTATCAAATAGGATATATATGCAGTGGGGTTTTCGGGGACAATCCCCGCCCCAATGATGGAACAGGCAGTTGCAGTCCAATGTCCTCTAATGGGGCATATGGGGTAAAAGGGTTTTCATTTAAGTACGGTAATGGGGTTTGGATCGGAAGAACAAAAGGCACTAGTTCCAGAAGCGGCTTTGAGATGATTTGGGACCCGAATGGGTGGACTGAGACGGACAGTAGTTTCTCAGTGAAGCAAGACATTGTAGAAATAACTGACTGGTCAGGATATAGTGGGAGTTTTGTCCAGCATCCAGAACTGACAGGATTAGATTGCATGAGGCCTTGTTTCTGGGTTGAGCTAATTAGAGGGAGGCCCAAAGAGAACACAATTTGGACTAGCGGGAGCAGCATATCCTTTTGTGGTGTAAATAGTGACACTGTGGGTTGGTCTTGGCCAGACGGTGCTGAGTTGCCATTCACCATTGACAAGTAG</t>
         </is>
       </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Flu-0316|A_MP</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
+      <c r="BW1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0316|A_MP</t>
+        </is>
+      </c>
+      <c r="BX1" t="inlineStr">
         <is>
           <t>ATGAGTCTTCTAACCGAGGTCGAAACGTACGTTCTCTCTATCGTCCCGTCGGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTTGAAGATGTCTTTGCAGGGAAGAACACCGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATACTGTCACCTCTGACTAAGGGGATTTTGGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCTCTAAGTGGAAATGGAGACCCAAACAACATGGACAGGGCAGTCAAGTTGTACAGGAAACTGAAGAGAGAAATAACATTCCATGGGGCTAAAGAAGTTGCACTTAGTTACTCAACCGGTGCACTTGCCAGTTGTATGGGTCTCATATACAACAGGATGGGGACGGTGACCGCAGAAGTGGCATTGGGCCTAGTGTGTGCCACCTGTGAGCAGATTGCTGATTCACAGCATCGGTCTCACAGACAGATAGCTACCACCACCAACCCACTAATCAGACATGAAAACAGAATGGTTTTGGCCAGTACTACAGCTAAGGCTATGGAGCAGATGGCTGGATCGAGTGAGCAAGCAGTGGAAGCCATGGAGGTTGCTAGTCAGGCTAGGCAAATGGTGCAGGCGATGAGGACCATTGGAACTCATCCTAGCTCCAGTGCCGGTCTGAGAGATGATCTCCTTGAAAATTTGCAGGCCTACCAAAAACGAATGGGAGTGCAACTGCAGCGATTCAAGTGATCCTCTCGTTATTGCAGCAAGTATCATTGGGATCTTGCACTTGATATTGTGGATTCTTGATCGCCTTTTCTTCAAATGCGTTTATCGTCGCCTTAAATACGGTTTGAAAGGAGGGCCTTCTACGGAAGGAGTACCTGAGTCCATGAGGGAAGAGTACCGGCAGGAACAGCAGAGTGCTGTGGATGTTGACGATGGTCATTTTGTCAACATAGAGATGGAGTAA</t>
         </is>
       </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Flu-0316|A_NS</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
+      <c r="BY1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0316|A_NS</t>
+        </is>
+      </c>
+      <c r="BZ1" t="inlineStr">
         <is>
           <t>ATGGATTCCAACACTGTGTCAAGCTTTCAGGTAGACTGCTTTCTTTGGCATGTCCGCAAACAATTTGCAGACCAAGAACTGGGTGATGCCCCATTCCTTGACCGGCTCCGCCGAGACCAGAAGTCTCTAAGAGGAAGAGGCAGCACTCTTGGTCTGGACATCGAGACGGCCACTCGTGCTGGAAAGCAGATAGTGGAGAGGATTCTGGAGGAAGAATCCGACGAGGCACTCAAAATGACTATTGCCTCTGTGCCTGCTCCACGCTACCTAACTGACATGACTCTTGAAGAGATGTCAAGAGACTGGTTCATGCTCATGCCCAAGCAAAAAGTGGCAGGCTCCCTCTGTATCAGAATGGACCAGGCGATTATGGATAAGAACATCATACTGAAGGCAAACTTCAGTGTGATCTTCAATCGGCTGGAGACACTAATACTACTCAGAGCTTTCACTGAAGAGGGAGCAATTGTCGGCGAAATTTCACCATTGCCTTCTCTTCCAGGACATACTGATGAGGATGTCAAAAATGCAATTGGGGTCCTCATCGGAGGACTTGAATGGAATGATAACACAGTTCGAGTCTCTGAAATTTTACAGAGATTCGCTTGGAGAAGCAGTAATGAGGATGGGAGACCTCCACTCCCTCCAAAGCAGAAACGGAAAATGGAGAGAACAATTGAGTCAGAAGTTTGAAGAAATAAGGTGGCTGATTGAAGAGGTGCGACACAGACTAAAGATCACAGAAAATAGTTTTGAACAAATAACATTTATGCAAGCCTTACAACTACTGCTTGAAGTGGAGCAAGAGATACGAACTTTCTCGTTTCAGCTTATTTAA</t>
         </is>
       </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Flu-0317|A_PB2</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
+      <c r="CA1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0317|A_PB2</t>
+        </is>
+      </c>
+      <c r="CB1" t="inlineStr">
         <is>
           <t>ATGGAGAGAATAAAAGAACTAAGAGATCTAATGTCACAGTCTCGCACTCGCGAGATACTGACCAAAACCACTGTTGACCACATGGCCATAATCAAAAAGTACACATCGGGAAGGCAAGAGAAGAACCCCGCACTCAGAATGAAATGGATGATGGCAATGAAATATCCAATTACAGCAGATAAGCGAATAATGGAAATGATCCCTGAGAGGAATGAACAAGGGCAAACTCTCTGGAGCAAAACAAACGATGCCGGATCAGACCGAGTGATGGTATCACCCCTGGCTGTGACATGGTGGAACAGGAACGGACCAACAACAAGTACAGTTCACTACCCAAAGGTATATAAAACTTATTTCGAAAAAGTTAAAAGGTTGAAACACGGGACCTTTGGCCCTGTGCACTTCAGAAACCAAGTTAAGATAAGACGGAGGGTCGATATAAACCCGGGCCATGCTGACCTTAGTGCCAAAGAGGCACAGGATGTAATCATGGAAGTCGTCTTCCCAAATGAAGTGGGAGCTAGGATATTGACGTCGGAGTCACAACTGACGATAACAAAGGAGAAAAAGGAAGAACTCCAGGACTGCAAAATCGCTCCTCTGATGGTTGCATACATGCTAGAACGAGAGTTGGTTCGCAAGACGAGGTTTCTCCCAGTTGCTGGTGGGACAAGCAGTGTCTACATTGAGGTGCTGCATTTGACCCAGGGGACATGCTGGGAGCAGATGTACACTCCGGGAGGAGAAGTGAGGAACGATGATGTAGACCAAAGCTTGATCATTGCTGCCAGGAATATAGTAAGAAGAGCAACAGTATCAGCAGATCCGTTAGCATCTCTATTGGAGATGTGTCACAGCACACAAATTGGGGGAATAAGGATGGTAGACATCCTTCGGCAAAACCCAACAGAGGAACAAGCCGTGGATATATGCAAGGCAGCAATGGGCTTGAGGATTAGCTCATCTTTCAGCTTTGGTGGATTCACTTTTAAAAGAACAAGTGGATCGTCAGTCAAAAAAGAAGAAGAAGTGCTAACAGGCAACCTTCAAACATTGAAAATAAGAGTACATGAGGGGTATGAAGAGTTCACAATGGTTGGGAGAAGAGCAACGGCCATTCTCAGGAAAGCAACCAGAAGGCTGATCCAGCTAATAGTAAGTGGGAGAGACGAGCAGTCAATTGCTGAAGCAATAATTGTGGCCATGGTATTCTCACAAGAGGACTGCATGATTAAAGCAGTTAGAGGTGACCTGAATTTTGTCAATAGGGCGAACCAGCGACTAAACCCAATGCATCAACTCTTGAGGCATTTCCAAAAGGATGCAAAAGTGCTTTTCCAAAATTGGGGAATTGAACCCATTGACAATGTGATGGGAATGATCGGGGTAATGCCTGACATGACCCCAAGTACTGAGATGTCGCTGAGGGGAATAAGAGTCAGCAAGATGGGAGTAGATGAATACTCAAGCACAGAGCGAGTAGTAGTAAGCATCGACCGGTTTTTAAGAGTTCGAGACCAACGGGGGAACGTACTATTATCACCCGAAGAGGTCAGTGAGACACAAGGAACGGAGAAACTGACAATCACTTATTCGTCATCAATGATGTGGGAGATCAATGGTCCTGAGTCGGTGTTGGTCAATACTTATCAGTGGATAATTAGAAACTGGGAAACTGTAAAAATTCAATGGTCACAGGATCCCACAATGCTGTATAATAAGATGGAATTCGAGCCATTCCAGTCTCTAGTCCCTAAGGCAGCCAGAGGTCAATACAGTGGGTTTGTGAGAACACTATTCCAGCAAATGCGAGATGTGCTTGGAACATTTGACACTGTTCAGATAGTAAAACTCCTCCCCTTTGCTGCCGCCCCACCGGAACAAAGTAGGATGCAGTTCTCCTCCCTGACTGTGAATGTAAGAGGATCAGGAATGAGGATACTGGTAAGAGGCAATTCACCAGTGTTCAATTACAACAAGGCCACCAAGAGGCTCACAGTTCTCGGGAAAGATGCAGGTGCATTGACCGAAGATCCAGATGAAGGCACAGCTGGAGTGGAGTCTGCTGTTTTAAGAGGATTCCTCATTTTGGGCAAAGAAGACAAGAGATATGGCCCAGCATTGAGCATCAATGAGCTGAGCAATCTTGCAAAGGGAGAGAAGGCTAATGTGCTAATTGGGCAAGGAGACGTAGTGTTGGTGATGAAACGGAAACGGGACTCTAGCATACTTACTGACAGCCAGACAGCGACCAAAAGAATTCGGATGGCCATCAATTAG</t>
         </is>
       </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Flu-0317|A_PB1</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
+      <c r="CC1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0317|A_PB1</t>
+        </is>
+      </c>
+      <c r="CD1" t="inlineStr">
         <is>
           <t>ATGGATGTCAATCCGACTTTACTTTTCTTGAAAGTTCCAGCGCAAAATGCCATAAGCACCACATTCCCGTATACTGGAGATCCTCCATACAGCCATGGAACAGGAACAGGATATACCATGGACACAGTTAACAGAACACATCAGTATTCAGAAAAAGGGAAATGGACAACAAACTCAGAAACTGGAGCACCTCAACTCAATCCAATTGATGGACCATTGCCTGAGGGCAATGAACCAAGTGGGTATGCACAAACGGACTGTGTCCTTGAAGCAATGGCTTTCCTTGAAGAGTCCCACCCAGGAATCTTTGAAAACTCGTGTCTTGAAACGATGGAAGTTGTTCAACAAACAAGAGTGGACAAGTTGACCCAAGGCCGTCAGACCTATGATTGGACGTTAAACAGGAATCAGCCGGCTGCAACTGCATTAGCTAATACTATAGAGGTCTTCAGATCTAACGGCCTCACAGCCAATGAATCAGGAAGGCTAATAGATTTTCTCAAGGATGTGATGGAATCAATGGATAAGGAGGAAATGGAAATAACAACGCATTTCCAAAGGAAAAGAAGAGTGAGAGACAACATGACCAAGAAAATGGTCACACAAAGGACAATAGGAAAGAAGAAACAGAGGCTAAATAAAAAGAGCTATCTAATAAGAGCATTGACACTGAACACGATGACAAAAGACGCCGAAAGAGGCAAATTAAAAAGAAGGGCAATTGCAACACCTGGAATGCAAATCAGAGGGTTTGTGTACTTTGTTGAGACATTAGCGAGGAGCATTTGTGATAAGCTTGAACAATCTGGACTCCCAGTTGGGGGCAATGAAAAGAAGGCTAAACTGGCAAATGTTGTGAGAAAAATGATGACTAATTCGCAGGACACAGAGCTCTCTTTCACAATCACTGGAGACAACACCAAATGGAATGAAAATCAGAACCCTAGGATGTTTCTGGCAATGATAACATATATAACAAGGAACCAACCTGAATGGTTCAGGAATGTCTTAAGCATTGCACCTATAATGTTCTCAAATAAAATGGCAAGACTAGGGAAAGGGTACATGTTCGAAAGTAAGAGCATGAAGCTCCGAACACAAATACCAGCAGAAATGCTAGCAAGCATTGATCTGAAGTACTTCAATGAGTCAACAAGAAAGAAAATAGAGAAGATAAGACCTCTTCTAATAGATGGTACAGCCTCATTAAGCCCAGGAATGATGATGGGCATGTTCAATATGCTGAGTACAGTTTTGGGAGTTTCGATTCTAAATCTAGGACAAAGGAGGTACACCAAAACAACATACTGGTGGGACGGACTCCAATCCTCTGATGACTTTGCTCTCATAGTGAATGCTCCGAATCATGAGGGAATACAAGCAGGGGTAGACAGATTCTATAGAACCTGCAAGCTGGTCGGAATCAACATGAGCAAAAAGAAGTCCTACATAAACAGGACAGGAACATTTGAATTCACAAGTTTTTTCTACCGCTATGGATTTGTAGCCAACTTCAGTATGGAGTTGCCCAGCTTTGGAGTGTCTGGGATCAATGAATCTGCAGACATGAGCATTGGAGTAACAGTAATAAAGAACAACATGATCAACAATGATCTTGGACCAGCAACAGCTCAAATGGCTCTTCAGCTATTCATCAAGGATTACAGATACACATACCGGTGTCACAGAGGAGACACACAAATTCAGACAAGGAGGTCATTCGAGCTGAAGAAGTTGTGGGAACAGACCCGTTCAAAAGCAGGACTGCTGGTCTCAGATGGAGGACCAAATCTATACAATATTCGGAATCTTCACATTCCAGAAGTCTGCTTGAAATGGGAGCTAATGGACGAAGACTATCAGGGAAGGCTTTGTAATCCCCTGAACCCGTTTGTCAGCCACAAGGAAATAGAGTCTGTGAACAACGCAGTGGTGATGCCAGCTCATGGCCCGGCCAAGAGCATGGAATATGATGCTGTTGCCACCACTCACTCCTGGATACCGAAGAGGAACCGCTCCATTCTCAATACAAGCCAAAGGGGAATCCTTGAAGACGAACAGATGTATCAAAAGTGCTGCAACCTGTTCGAAAAATTCTTCCCTAGCAGTTCATACAGGAGGCCAGTTGGAATTTCCAGCATGGTGGAGGCCATGGTTTCTAGGGCCCGAATTGACGCACGAATTGACTTCGAATCTGGACGGATTAAGAAGGAGGAGTTTGCTAAGATCATGAAGATCTGTTCCACCATTGAAGAGCTCAGACGGCAGAAATAG</t>
         </is>
       </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Flu-0317|A_PA</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
+      <c r="CE1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0317|A_PA</t>
+        </is>
+      </c>
+      <c r="CF1" t="inlineStr">
         <is>
           <t>ATGGAAGACTTTGTGCGACAATGCTTCAATCCAATGATTGTCGAGCTTGCGGAAAAAGCAATGAAAGAATATGGGGAAGATCCGAAAATCGAGACAAACAAATTTGCCGCAATATGCACACACTTAGAAGTCTGTTTCATGTATTCGGATTTCCATTTTATTAATGAACGAGGCGAATCAATGATTGTAGAATCTGGCGATCCAAATGCATTATTGAAACACCGATTTGAGATAATAGAAGGGAGAGACCGGGCAATGGCCTGGACAGTGGTGAATAGTATCTGCAACACCACAGGGGTCGAAAAGCCCAAATTCCTCCCTGATTTGTATGACTACAAAGAGAACCGATTCATTGAAATTGGAGTAACGCGAAGGGAAGTTCACATATACTATTTAGAAAAAGCCAACAAGATAAAGTCAGAGAAAACACATATTCACATATTCTCATTCACTGGAGAGGAAATGGCCACCAAGGCGGACTACACCCTTGATGAAGAGAGCAGAGCAAGAATAAAAACCAGACTGTTCACTATAAGACAAGAAATGGCCAGTAGAGGTCTATGGGATTCCTTTCGTCAATCCGAGAGAGGCGAAGAGACAATTGAAGAAAGATTTGAAATCGCAGGAACCATGCGCAGGCTTGCCAACCAAAGTCTTCCACCGAACTTCTCCAGCCTTGAAAACTTTAGAGCCTATGTGGATGGATTCGAACCGAACGGCTGCATTGAGGGCAAACTTTCTCAAATGTCAAAAGAAGTGAACGCCAGGATTGAGCCATTTCTGAAGACAACACCACGCCCTCTCAGATTACCTGATGGGCCTCCCTGTTCTCAGCGGTCGAAGTTCTTGCTGATGGATGCCCTTAAGTTGAGCATCGAAGACCCTAGCCATGAGGGGGAGGGCATACCGCTGTATGATGCAATCAAATGCATGAAGACATTTTTTGGCTGGAAAGAGCCCAACATCGTAAAGCCGCATGAGAAAGGCATAAACCCTAATTACCTCCTGACTTGGAAGCAGGTGCTGGCAGAACTTCAAGACATTGAAAATGAGGAGAAAATTCCAAAGACAAAGAACATGAAGAAAACAAGCCAATTGAAGTGGGCACTTGGTGAGAACATGGCTCCAGAGAAAGTGGACTTTGAGGACTGCAAAGATGTTAGCGATCTAAGACAGTACGACAGTAACGAACCAGAGTCTAGAACACTAGCAAGCTGGATTCAGAGTGAATTCAACAAGGCATGCGAACTGACAGATTCGAGTTGGATTGAACTTGATGAGATAGGGGAAGACGTTGCTCCAATCGAACACATTGCGAGTGTGAGGAGGAACTATTTCACAGCGGAGGTATCCCATTGCAGGGCCACTGAATACATAATGAAGGGAGTATACATAAACACAGCCCTATTGAATGCATCCTGTGCAGCCATGGATGACTTCCAATTGATTCCAATGATAAGTAAGTGCAGAACTAAAGAAGGAAGACGGAAGACAAATCTGTATGGATTCATTATAAAAGGAAGATCCCATTTGAGGAATGACACCGATGTGGTAAACTTTGTGAGCATGGAATTCTCTCTAACTGACCCGAGGCTGGAGCCACACAAATGGGAGAAGTACTGTGTTCTTGAGATAGGAGACATGCTCCTACGGACTGCAATAGGCCAAGTGTCGAGGCCCATGTTCCTGTATGTGAGAACCAATGGGACTTCCAAGATCAAAATGAAATGGGGCATGGAGATGAGGCGATGCCTTCTTCAGTCCCTTCAACAAATTGAGAGCATGATTGAGGCCGAATCTTCTGTCAAAGAGAAGGACATGTCCAAGGAATTCTTTGAAAACAAATCAGAAACATGGCCAATTGGAGAATCACCCAAAGGGGTGGAGGAAGGCTCTATTGGGAAAGTATGCAGAACATTGCTAGCAAAGTCTGTGTTCAACAGCCTATATGCATCTCCACAACTCGAGGGGTTTTCAGCTGAATCAAGAAAATTGCTTCTCATTGTTCAGGCACTTAGGGACAACCTGGAACCTGGAACCTTCGATCTTGGGGGGCTATATGAAGCAATTGAGGAGTGCCTGATTAACGATCCCTGGGTTTTGCTTAATGCATCTTGGTTCAACTCCTTCCTCACACATGCACTGAAATAG</t>
         </is>
       </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Flu-0317|A_HA</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
+      <c r="CG1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0317|A_HA</t>
+        </is>
+      </c>
+      <c r="CH1" t="inlineStr">
         <is>
           <t>ATGGAGAACATAGTACTACTTCTTGCAATAGTTAGCCTTGTTAAAAGTGACCAGATTTGCATTGGTTACCATGCAAACAATTCGACAGAGCAAGTTGACACGATAATGGAAAAGAACGTCACTGTTACACATGCCCAAGACATACTGGAAAAAACACACAACGGGAAGCTCTGTGATTTAAATGGGGTGAAGCCACTGATTTTAAAGGATTGTAGTGTAGCTGGATGGCTCCTCGGGAACCCAATGTGCGACGAATTCATCAGAGTGCCGGAATGGTCCTACATAGTGGAGCGAGCTAACCCAGCTAATGACCTCTGTTACCCAGGGAGCCTCAATGACTATGAAGAACTGAAACACATGTTGAGCAGAATAAATCATTTTGAGAAGATTCAGATCATTCCCAAGAGTTCCTGGCCAAATCATGAAACATCACTAGGGGTGAGCGCAGCTTGTCCATACCAGGGAGCGCCCTCCTTTTTCAGAAATGTGGTGTGGCTTATCAAAAAGAACGATGCATACCCAACAATAAAGATAAGCTACAATAATACTAATCGGGAAGATCTCTTGATACTGTGGGGGATTCATCATCCCAACAATGCAGAAGAGCAGACAAATCTCTACAAAAACCCAACCACCTACATTTCAGTTGGAACATCAACTTTAAACCAGAGATTGGCACCAAAAATAGCTACTAGATCCCAAGTAAACGGGCAACGTGGAAGAATGGACTTCTTTTGGACAATCTTAAAACCAGATGATGCAATCCATTTCGAGAGTAACGGAAATTTCATTGCTCCAGAATATGCATACAAAATTGTCAAGAAAGGGGACTCAACAATTATGAAAAGTGGAGTGGAATATGGCCACTGCAACACCAAATGTCAAACCCCAGTAGGTGCTATAAATTCTAGTATGCCATTCCACAACATACATCCTCTCACCATTGGGGAATGCCCCAAATACGTGAAATCAAACAAGTTGGTCCTTGCGACTGGGCTCAGAAATAGTCCTCTAAGAGAAAAGAGAAGAAAAAGAGGTCTGTTTGGGGCGATAGCAGGGTTTATAGAGGGAGGATGGCAGGGAATGGTTGATGGTTGGTATGGGTACCATCATAGCAATGAGCAGGGGAGTGGGTACGCTGCGGACAAAGAATCCACCCAAAAGGCAATAGATGGAGTTACCAATAAGGTCAACTCAATCATTGACAAAATGAACACTCAATTTGAGGCAGTTGGAAGGGAGTTTAATAACTTAGAAAGGAGGATAGAGAATTTGAACAAGAAAATGGAAGACGGATTCCTAGATGTCTGGACCTATAATGCTGAACTTCTAGTTCTTATGGAAAACGAGAGGACTCTAGATTTCCATGATTCAAATGTCAAGAACCTTTACGACAAAGTCAGATTACAGCTTAGGGATAATGCAAAGGAGCTGGGTAACGGCTGTTTCGAATTCTATCACAAATGTGATAATGAATGTATGGAAAGTGTGAGAAATGGGACGTATGACTACCCTCAGTATTCAGAAGAAGCAAGATTAAAAAGAGAAGAAATAAGCGGAGTGAAATTAGAATCAGTAGGAACTTACCAGATACTGTCAATTTATTCAACAGCGGCAAGTTCCCTAGCACTGGCAATCATGATGGCTGGTCTATCTTTATGGATGTGCTCCAATGGGTCGTTACAATGCAGAATTTGCATTTAG</t>
         </is>
       </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Flu-0317|A_NP</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
+      <c r="CI1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0317|A_NP</t>
+        </is>
+      </c>
+      <c r="CJ1" t="inlineStr">
         <is>
           <t>ATGGCGTCTCAAGGCACCAAACGATCCTATGAACAAATGGAAACTGGTGGGGAACGCCAGAATGCCACTGAAATCAGAGCATCTGTTGGAAGAATGGTTGGCGGAATAGGAAGATTCTACATACAGATGTGCACTGAGCTCAAACTCAGTGATTATGAAGGGAGGCTGATCCAAAACAGCATAACCATAGAAAGGATGGTTCTCTCGGCATTTGATGAGAGGAGGAACAAGTACCTGGAGGAACATCCCAGTGCCGGGAAGGATCCCAAGAAGACTGGAGGTCCAATCTACAGGAGGAGAGATGGCAAATGGGTGAGAGAGTTGATCCTCTACGACAAAGAAGAGATCAGAAGAATTTGGCGTCAAGCTAATAATGGAGAGGATGCAACTGCTGGTCTCACTCATTTGATGATTTGGCATTCCAATCTGAATGATGCAACATACCAGAGAACAAGGGCACTTGTGCGTACTGGAATGGACCCTAGAATGTGCTCTCTGATGCAAGGATCAACCCTCCCTAGGAGATCCGGGGCTGCTGGAGCAGCAGTGAAAGGAGTTGGAACAATGGTGATGGAACTAATTCGAATGATCAAGCGAGGGATCAATGATCGGAATTTCTGGAGAGGCGAAAACGGTCGGAGAACCAGGATTGCCTACGAGAGAATGTGCAACATCCTCAAGGGAAAGTTCCAAACAGCAGCACAACGGGCAATGATGGACCAAGTGAGAGAAAGCCGGAATCCTGGGAATGCTGAAATTGAAGATCTCATCTTTCTCGCACGATCTGCTCTCATCCTGAGGGGATCAGTGGCTCATAAGTCCTGTCTGCCTGCTTGCGTATATGGACTTGCTGTAGCCAGTGGATATGACTTTGAAAGAGAGGGATATTCTCTAGTCGGAATTGATCCTTTCCGTCTGCTCCAAAACAGCCAAGTCTTCAGTCTCATCAGACCGAACGAAAATCCAGCTCATAAGAGTCAGCTGGTATGGATGGCATGCCACTCTGCGGCATTTGAGGATCTGAGAGTTTCAAGCTTCATCAGAGGGACAAGAGTAGTCCCAAGAGGACAACTGTCCACCAGAGGAGTTCAGATTGCTTCAAATGAAAACATGGAGACAATGGACTCCAGTACTCTTGAACTGAGGAGCAGATACTGGGCTATAAGAACAAGAAGTGGAGGAAACACTAACCAACAGAGAGCATCTGCAGGACAAATCAGCGTGCAGCCCACATTCTCTGTGCAAAGAAACCTCCCATTCGAGAGAGCAACCATCATGGCAGCATTTACGGGAAACACTGAAGGCAGAACTTCAGACATGAGAACGGAGATCATAAGGATGATGGAAAATGCCAGACCTGAAGATGTGTCTTTCCAGGGGCGGGGAGTCTTCGAGCTCTCGGACGAAAAGGCAACGAACCCGATCGTGCCTTCCTTTGACATGAGTAATGAAGGATCTTATTTCTTCGGAGACAATGCAGAGGAGTATGACAATTAA</t>
         </is>
       </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Flu-0317|A_NA</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
+      <c r="CK1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0317|A_NA</t>
+        </is>
+      </c>
+      <c r="CL1" t="inlineStr">
         <is>
           <t>ATGAATCCAAATCAAAAGATAACAACCATTGGATCAATCTGTATGGTAATTGGGACAGTCAGCTTGATGCTGCAAATTGGGAACATAATCTCAATATGGGTTAGCCATTCAATCCAAACAGGGAATCAATACCAGCCTGAACCATGCAATCAAAGCATCATTACCTATGAGAACAACACCTGGGTAAATCAGACGTATGTCAACATCAGCAATAACAATTTTCTTGCTGAGCAGGCTGTTACTTCGGTAACATTAGCGGGCAATTCATCTCTTTGCCCTATTAGTGGGTGGGCAATATACAGTAAGGACAACGGTATAAGAATTGGGTCCAAGGGGGATGTGTTTGTCATAAGAGAACCGTTCATCTCATGCTCCCACTTGGAATGCAGAACCTTTTTCCTGACTCAGGGAGCTCTGCTGAATGACAAACATTCTAATGGGACAGTTAAGGATAGAAGCCCTTATAGAACTTTGATGAGTTGTCCCGTGGGTGAGGCTCCTTCCCCGTACAATTCAAGATTTGAGTCTGTTGCTTGGTCGGCAAGTGCTTGTCATGATGGCATCAGTTGGTTGACAATCGGTATTTCTGGTCCAGACAATGGAGCTGTGGCTGTATTGAAGTACAATGGCATAATAACGGATACTATCAAGAGTTGGAGAAACAACATTTTGAGAACTCAAGAATCTGAATGTGCTTGCGTAAATGGCTCTTGCTTCACCGTAATGACTGATGGACCAAGCAATGGGCAGGCCTCGTATAAAATCTTCAAGATAGAGAAAGGGAAAGTTGTCAAATCAGTTGAATTGAATGCCCCTAATTACCACTACGAGGAATGTTCCTGTTATCCTGATGCGGGTGATATTATATGTGTGTGCAGGGACAATTGGCACGGCTCAAACCGGCCGTGGATATCTTTTAATCAAAATCTGGAGTATCAAATAGGATATATATGCAGTGGGGTTTTCGGGGACAATCCCCGCCCCAATGATGGAACAGGCAGTTGCAGTCCAATGTCCTCTAATGGGGCATATGGGGTAAAAGGGTTTTCATTTAAGTACGGTAATGGGGTTTGGATCGGAAGAACAAAAGGCACTAGTTCCAGAAGCGGCTTTGAGATGATTTGGGACCCGAATGGGTGGACTGAGACGGACAGTAGTTTCTCAGTGAAGCAAGACATTGTAGAAATAACTGACTGGTCAGGATATAGTGGGAGTTTTGTCCAGCATCCAGAACTGACAGGATTAGATTGCATGAGGCCTTGTTTCTGGGTTGAGCTAATTAGAGGGAGGCCCAAAGAGAACACAATTTGGACTAGCGGGAGCAGCATATCCTTTTGTGGTGTAAATAGTGACACTGTGGGTTGGTCTTGGCCAGACGGTGCTGAGTTGCCATTCACCATTGACAAGTAG</t>
         </is>
       </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Flu-0317|A_MP</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
+      <c r="CM1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0317|A_MP</t>
+        </is>
+      </c>
+      <c r="CN1" t="inlineStr">
         <is>
           <t>ATGAGTCTTCTAACCGAGGTCGAAACGTACGTTCTCTCTATCGTCCCGTCGGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTTGAAGATGTCTTTGCAGGGAAGAACACCGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATACTGTCACCTCTGACTAAGGGGATTTTGGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCTCTAAGTGGAAATGGAGACCCAAACAACATGGACAGGGCAGTCAAGTTGTACAGGAAACTGAAGAGAGAAATAACATTCCATGGGGCTAAAGAAGTTGCACTTAGTTACTCAACCGGTGCACTTGCCAGTTGTATGGGTCTCATATACAACAGGATGGGGACGGTGACCGCAGAAGTGGCATTGGGCCTAGTGTGTGCCACCTGTGAGCAGATTGCTGATTCACAGCATCGGTCTCACAGACAGATAGCTACCACCACCAACCCACTAATCAGACATGAAAACAGAATGGTTTTGGCCAGTACTACAGCTAAGGCTATGGAGCAGATGGCTGGATCGAGTGAGCAAGCAGTGGAAGCCATGGAGGTTGCTAGTCAGGCTAGGCAAATGGTGCAGGCGATGAGGACCATTGGAACTCATCCTAGCTCCAGTGCCGGTCTGAGAGATGATCTCCTTGAAAATTTGCAGGCCTACCAAAAACGAATGGGAGTGCAACTGCAGCGATTCAAGTGATCCTCTCGTTATTGCAGCAAGTATCATTGGGATCTTGCACTTGATATTGTGGATTCTTGATCGCCTTTTCTTCAAATGCGTTTATCGTCGCCTTAAATACGGTTTGAAAGGAGGGCCTTCTACGGAAGGAGTACCTGAGTCCATGAGGGAAGAGTACCGGCAGGAACAGCAGAGTGCTGTGGATGTTGACGATGGTCATTTTGTCAACATAGAGATGGAGTAA</t>
         </is>
       </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Flu-0317|A_NS</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
+      <c r="CO1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0317|A_NS</t>
+        </is>
+      </c>
+      <c r="CP1" t="inlineStr">
         <is>
           <t>ATGGATTCCAACACTGTGTCAAGCTTTCAGGTAGACTGCTTTCTTTGGCATGTCCGCAAACAATTTGCAGACCAAGAACTGGGTGATGCCCCATTCCTTGACCGGCTCCGCCGAGACCAGAAGTCTCTAAGAGGAAGAGGCAGCACTCTTGGTCTGGACATCGAGACGGCCACTCGTGCTGGAAAGCAGATAGTGGAGAGGATTCTGGAGGAAGAATCCGACGAGGCACTCAAAATGACTATTGCCTCTGTGCCTGCTCCACGCTACCTAACTGACATGACTCTTGAAGAGATGTCAAGAGACTGGTTCATGCTCATGCCCAAGCAAAAAGTGGCAGGCTCCCTCTGTATCAGAATGGACCAGGCGATTATGGATAAGAACATCATACTGAAGGCAAACTTCAGTGTGATCTTCAATCGGCTGGAGACACTAATACTACTCAGAGCTTTCACTGAAGAGGGAGCAATTGTCGGCGAAATTTCACCATTGCCTTCTCTTCCAGGACATACTGATGAGGATGTCAAAAATGCAATTGGGGTCCTCATCGGAGGACTTGAATGGAATGATAACACAGTTCGAGTCTCTGAAATTTTACAGAGATTCGCTTGGAGAAGCAGTAATGAGGATGGGAGACCTCCACTCCCTCCAAAGCAGAAACGGAAAATGGAGAGAACAATTGAGTCAGAAGTTTGAAGAAATAAGGTGGCTGATTGAAGAGGTGCGACACAGACTAAAGATCACAGAAAATAGTTTTGAACAAATAACATTTATGCAAGCCTTACAACTACTGCTTGAAGTGGAGCAAGAGATACGAACTTTCTCGTTTCAGCTTATTTAA</t>
         </is>
       </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Flu-0318|A_PB2</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
+      <c r="CQ1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0318|A_PB2</t>
+        </is>
+      </c>
+      <c r="CR1" t="inlineStr">
         <is>
           <t>ATGGAGAGAATAAAAGAACTAAGAGATCTAATGTCACAGTCTCGCACTCGCGAGATACTGACCAAAACCACTGTTGACCACATGGCCATAATCAAAAAGTACACATCGGGAAGGCAAGAGAAGAACCCCGCACTCAGAATGAAATGGATGATGGCAATGAAATATCCAATTACAGCAGATAAGCGAATAATGGAAATGATCCCTGAGAGGAATGAACAAGGGCAAACTCTCTGGAGCAAAACAAACGATGCCGGATCAGACCGAGTGATGGTATCACCCCTGGCTGTGACATGGTGGAACAGGAACGGACCAACAACAAGTACAGTTCACTACCCAAAGGTATATAAAACTTATTTCGAAAAAGTTAAAAGGTTGAAACACGGGACCTTTGGCCCTGTGCACTTCAGAAACCAAGTTAAGATAAGACGGAGGGTCGATATAAACCCGGGCCATGCTGACCTTAGTGCCAAAGAGGCACAGGATGTAATCATGGAAGTCGTCTTCCCAAATGAAGTGGGAGCTAGGATATTGACGTCGGAGTCACAACTGACGATAACAAATGAGAAAAAGGAAGAACTCCAGGACTGCAAAATCGCTCCTCTGATGGTTGCATACATGCTAGAACGAGAGTTGGTTCGCAAGACGAGGTTTCTCCCAGTTGCTGGTGGGACAAGCAGTGTCTACATTGAGGTGCTGCATTTGACCCAGGGGACATGCTGGGAGCAGATGTACACTCCGGGAGGAGAAGTGAGGAACGATGATGTAGACCAAAGCTTGATCATTGCTGCCAGGAATATAGTAAGAAGAGCAACAGTATCAGCAGATCCGTTAGCATCTCTATTGGAGATGTGTCACAGCACACAAATTGGGGGAATAAGGATGGTAGACATCCTTCGGCAAAACCCAACAGAGGAACAAGCCGTGGATATATGCAAGGCAGCAATGGGCTTGAGGATTAGTTCATCTTTCAGCTTTGGTGGATTCACTTTTAAAAGAACAAGTGGATCGTCAGTCAAAAAAGAAGAAGAAGTGCTAACAGGCAACCTTCAAACATTGAAAATAAGAGTACATGAGGGGTATGAAGAGTTCACAATGGTTGGGAGAAGAGCAACGGCCATTCTCAGGAAAGCAACCAGAAGGCTGATCCAGCTAATAGTAAGTGGGAGAGACGAGCAGTCAATTGCTGAAGCAATAATTGTGGCCATGGTATTCTCACAAGAGGACTGCATGATTAAAGCAGTTAGAGGTGACCTGAATTTTGTCAATAGGGCGAACCAGCGACTAAACCCAATGCATCAACTCTTGAGGCATTTCCAAAAGGATGCAAAAGTGCTTTTCCAAAATTGGGGAATTGAACCCATTGACAATGTGATGGGAATGATCGGGGTAATGCCTGACATGACCCCAAGTACTGAGATGTCGCTGAGGGGAATAAGAGTCAGCAAGATGGGAGTAGATGAATACTCAAGCACAGAGCGAGTAGTAGTAAGCATCGACCGGTTTTTAAGAGTTCGAGACCAACGGGGGAACGTACTATTATCACCCGAAGAGGTCAGTGAGACACAAGGAACGGAGAAACTGACAATCACTTATTCGTCATCAATGATGTGGGAGATCAATGGTCCTGAGTCGGTGTTGGTCAATACTTATCAGTGGATAATTAGAAACTGGGAAACTGTAAAAATTCAATGGTCACAGGATCCCACAATGCTGTATAATAAGATGGAATTCGAGCCATTCCAGTCTCTAGTCCCTAAGGCAGCCAGAGGTCAATACAGTGGGTTTGTGAGAACACTATTCCAGCAAATGCGAGATGTGCTTGGAACATTTGACACTGTTCAGATAGTAAAACTCCTCCCCTTTGCTGCCGCCCCACCGGAACAAAGTAGGATGCAGTTCTCCTCCCTGACTGTGAATGTAAGAGGATCAGGAATGAGGATACTGGTAAGAGGCAATTCACCAGTGTTCAATTACAACAAGGCCACCAAGAGGCTCACAGTTCTCGGGAAAGATGCAGGTGCATTGACCGAAGATCCAGATGAAGGCACAGCTGGAGTGGAGTCTGCTGTTTTAAGAGGATTCCTCATTTTGGGCAAAGAAGACAAGAGATATGGCCCAGCATTGAGCATCAATGAGCTGAGCAATCTTGCAAAGGGAGAGAAGGCTAATGTGCTAATTGGGCAAGGAGACGTAGTGTTGGTGATGAAACGGAAACGGGACTCTAGCATACTTACTGACAGCCAGACAGCGACCAAAAGAATTCGGATGGCCATCAATTAG</t>
         </is>
       </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Flu-0318|A_PB1</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
+      <c r="CS1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0318|A_PB1</t>
+        </is>
+      </c>
+      <c r="CT1" t="inlineStr">
         <is>
           <t>ATGGATGTCAATCCGACTTTACTTTTCTTGAAAGTTCCAGCGCAAAATGCCATAAGCACCACATTCCCGTATACTGGAGATCCTCCATACAGCCATGGAACAGGAACAGGATATACCATGGACACAGTTAACAGAACACATCAGTATTCAGAAAAAGGGAAATGGACAACAAACTCAGAAACTGGAGCACCTCAACTCAATCCAATTGATGGACCATTGCCTGAGGGCAATGAACCAAGTGGGTATGCACAAACGGACTGTGTCCTTGAAGCAATGGCTTTCCTTGAAGAGTCCCACCCAGGAATCTTTGAAAACTCGTGTCTTGAAACGATGGAAGTTGTTCAACAAACAAGAGTGGACAAGTTGACCCAAGGCCGTCAGACCTATGATTGGACGTTAAACAGGAATCAGCCGGCTGCAACTGCATTAGCTAATACTATAGAGGTCTTCAGATCTAACGGCCTCACAGCCAATGAATCAGGAAGGCTAATAGATTTTCTCAAGGATGTGATGGAATCAATGGATAAGGAGGAAATGGAAATAACAACGCATTTCCAAAGGAAAAGAAGAGTGAGAGACAACATGACCAAGAAAATGGTCACACAAAGGACAATAGGAAAGAAGAAACAGAGGCTAAATAAAAAGAGCTATCTAATAAGAGCATTGACACTGAACACGATGACAAAAGACGCCGAAAGAGGCAAATTAAAAAGAAGGGCAATTGCAACACCTGGAATGCAAATCAGAGGGTTTGTGTACTTTGTTGAGACATTAGCGAGGAGCATTTGTGATAAGCTTGAACAATCTGGACTCCCAGTTGGGGGCAATGAAAAGAAGGCTAAACTGGCAAATGTTGTGAGAAAAATGATGACTAATTCGCAGGACACAGAGCTCTCTTTCACAATCACTGGAGACAACACCAAATGGAATGAAAATCAGAACCCTAGGATGTTTCTGGCAATGATAACATATATAACAAGGAACCAACCTGAATGGTTCAGGAATGTCTTAAGCATTGCACCTATAATGTTCTCAAATAAAATGGCAAGACTAGGGAAAGGGTACATGTTCGAAAGTAAGAGCATGAAGCTCCGAACACAAATACCAGCAGAAATGCTAGCAAGCATTGATCTAAAGTACTTCAATGAGTCAACAAGAAAGAAAATAGAGAAGATAAGACCTCTTCTAATAGATGGTACAGCCTCATTAAGCCCAGGAATGATGATGGGCATGTTCAATATGCTGAGTACAGTTTTGGGAGTTTCGATTCTAAATCTAGGACAAAGGAGGTACACCAAAACAACATACTGGTGGGACGGACTCCAATCCTCTGATGACTTTGCTCTCATAGTGAATGCTCCGAATCATGAGGGAATACAAGCAGGGGTAGACAGATTCTATAGAACCTGCAAGCTGGTCGGAATCAACATGAGCAAAAAGAAGTCCTACATAAACAGGACAGGAACATTTGAATTCACAAGTTTTTTCTACCGCTATGGATTTGTAGCCAACTTCAGTATGGAGTTGCCCAGCTTTGGAGTGTCTGGGATCAATGAATCTGCAGACATGAGCATTGGAGTAACAGTAATAAAGAACAACATGATCAACAATGATCTTGGACCAGCAACAGCTCAAATGGCTCTTCAGCTATTCATCAAGGATTACAGATACACATACCGGTGTCACAGAGGAGACACACAAATTCAGACAAGGAGGTCATTCGAGCTGAAGAAGTTGTGGGAACAGACCCGTTCAAAAGCAGGACTGCTGGTCTCAGATGGAGGACCAAATCTATACAATATTCGGAATCTTCACATTCCAGAAGTCTGCTTGAAATGGGAGCTAATGGACGAAGACTATCAGGGAAGGCTTTGTAATCCCCTGAACCCGTTTGTCAGCCACAAGGAAATAGAGTCTGTGAACAACGCAGTGGTGATGCCAGCTCATGGCCCGGCCAAGAGCATGGAATATGATGCTGTTGCCACCACTCACTCCTGGATACCGAAGAGGAACCGCTCCATTCTCAATACAAGCCAAAGGGGAATCCTTGAAGACGAACAGATGTATCAAAAGTGCTGCAACCTGTTCGAAAAATTCTTCCCTAGCAGTTCATACAGGAGGCCAGTTGGAATTTCCAGCATGGTGGAGGCCATGGTTTCTAGGGCCCGAATTGACGCACGAATTGACTTCGAATCTGGACGGATTAAGAAGGAGGAGTTTGCTAAGATCATGAAGATCTGTTCCACCATTGAAGAGCTCAGACGGCAGAAATAG</t>
         </is>
       </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Flu-0318|A_PA</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
+      <c r="CU1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0318|A_PA</t>
+        </is>
+      </c>
+      <c r="CV1" t="inlineStr">
         <is>
           <t>ATGGAAGACTTTGTGCGACAATGCTTCAATCCAATGATTGTCGAGCTTGCGGAAAAAGCAATGAAAGAATATGGGGAAGATCCGAAAATCGAGACAAACAAATTTGCCGCAATATGCACACACTTAGAAGTCTGTTTCATGTATTCGGATTTCCATTTTATTAATGAACGAGGCGAATCAATGATTGTAGAATCTGGCGATCCAAATGCATTATTGAAACACCGATTTGAGATAATAGAAGGGAGAGACCGGGCAATGGCCTGGACAGTGGTGAATAGTATCTGCAACACCACAGGGGTCGAAAAGCCCAAATTCCTCCCTGATTTGTATGACTACAAAGAGAACCGATTCATTGAAATTGGAGTAACGCGAAGGGAAGTTCACATATACTATTTAGAAAAAGCCAACAAGATAAAGTCAGAGAAAACACATATTCACATATTCTCATTCACTGGAGAGGAAATGGCCACCAAGGCGGACTACACCCTTGATGAAGAGAGCAGAGCAAGAATAAAAACCAGACTGTTCACTATAAGACAAGAAATGGCCAGTAGAGGTCTATGGGATTCCTTTCGTCAATCCGAGAGAGGCGAAGAGACAATTGAAGAAAGATTTGAAATCGCAGGAACCATGCGCAGGCTTGCCAACCAAAGTCTTCCACCGAACTTCTCCAGCCTTGAAAACTTTAGAGCCTATGTGGATGGATTCGAACCGAACGGCTGCATTGAGGGCAAACTTTCTCAAATGTCAAAAGAAGTGAACGCCAGGATTGAGCCATTTCTGAAGACAACACCACGCCCTCTCAGATTACCTGATGGGCCTCCCTGTTCTCAGCGGTCGAAGTTCTTGCTGATGGATGCCCTTAAGTTGAGCATCGAAGACCCTAGCCATGAGGGGGAGGGCATACCGCTGTATGATGCAATCAAATGCATGAAGACATTTTTTGGCTGGAAAGAGCCCAACATCGTAAAGCCGCATGAGAAAGGCATAAACCCTAATTACCTCCTGACTTGGAAGCAGGTGCTGGCAGAACTTCAAGACATTGAAAATGAGGAGAAAATTCCAAAGACAAAGAACATGAAGAAAACAAGCCAATTGAAGTGGGCACTTGGTGAGAACATGGCTCCAGAGAAAGTGGACTTTGAGGACTGCAAAGATGTTAGCGATCTAAGACAGTACGACAGTAACGAACCAGAGTCTAGAACACTAGCAAGCTGGATTCAGAGTGAATTCAACAAGGCATGCGAACTGACAGATTCGAGTTGGATTGAACTTGATGAGATAGGGGAAGACGTTGCTCCAATCGAACACATTGCGAGTGTGAGGAGGAACTATTTCACAGCGGAGGTATCCCATTGCAGGGCCACTGAATACATAATGAAGGGAGTATACATAAACACAGCCCTATTGAATGCATCCTGTGCAGCCATGGATGACTTCCAATTGATTCCAATGATAAGTAAGTGCAGAACTAAAGAAGGAAGACGGAAGACAAATCTGTATGGATTCATTATAAAAGGAAGATCCCATTTGAGGAATGACACCGATGTGGTAAACTTTGTGAGCATGGAATTCTCTCTAACTGACCCGAGGCTGGAGCCACACAAATGGGAGAAGTACTGTGTTCTTGAGATAGGAGACATGCTCCTACGGACTGCAATAGGCCAAGTGTCGAGGCCCATGTTCCTGTATGTGAGAACCAATGGGACTTCCAAGATCAAAATGAAATGGGGCATGGAGATGAGGCGATGCCTTCTTCAGTCCCTTCAACAAATTGAGAGCATGATTGAGGCCGAATCTTCTGTCAAAGAGAAGGACATGTCCAAGGAATTCTTTGAAAACAAATCAGAAACATGGCCAATTGGAGAATCACCCAAAGGGGTGGAGGAAGGCTCTATTGGGAAAGTATGCAGAACATTGCTAGCAAAGTCTGTGTTCAACAGCCTATATGCATCTCCACAACTCGAGGGGTTTTCAGCTGAATCAAGAAAATTGCTTCTCATTGTTCAGGCACTTAGGGACAACCTGGAACCTGGAACCTTCGATCTTGGGGGGCTATATGAAGCAATTGAGGAGTGCCTGATTAACGATCCCTGGGTTTTGCTTAATGCATCTTGGTTCAACTCCTTCCTCACACATGCACTGAAATAG</t>
         </is>
       </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Flu-0318|A_NP</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
+      <c r="CW1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0318|A_NP</t>
+        </is>
+      </c>
+      <c r="CX1" t="inlineStr">
         <is>
           <t>ATGGCGTCTCAAGGCACCAAACGATCCTATGAACAAATGGAAACTGGTGGGGAACGCCAGAATGCCACTGAAATCAGAGCATCTGTTGGAAGAATGGTTGGCGGAATAGGAAGATTCTACATACAGATGTGCACTGAGCTCAAACTCAGTGATTATGAAGGGAGGCTGATCCAAAACAGCATAACCATAGAAAGGATGGTTCTCTCGGCATTTGATGAGAGGAGGAACAAGTACCTGGAGGAACATCCCAGTGCCGGGAAGGATCCCAAGAAGACTGGAGGTCCAATCTACAGGAGGAGAGATGGCAAATGGGTGAGAGAGTTGATCCTCTACGACAAAGAAGAGATCAGAAGAATTTGGCGTCAAGCTAATAATGGAGAGGATGCAACTGCTGGTCTCACTCATTTGATGATTTGGCATTCCAATCTGAATGATGCAACATACCAGAGAACAAGGGCACTTGTGCGTACTGGAATGGACCCTAGAATGTGCTCTCTGATGCAAGGCTCAACCCTCCCTAGGAGATCCGGGGCTGCTGGAGCAGCAGTGAAAGGAGTTGGAACAATGGTGATGGAACTAATTCGAATGATCAAGCGAGGGATCAATGATCGGAATTTCTGGAGAGGCGAAAACGGTCGGAGAACCAGGATTGCCTACGAGAGAATGTGCAACATCCTCAAGGGAAAGTTCCAAACAGCAGCACAACGGGCAATGATGGACCAAGTGAGAGAAAGCCGGAATCCTGGGAATGCTGAAATTGAAGATCTCATCTTTCTCGCACGATCTGCTCTCATCCTGAGGGGATCAGTGGCTCATAAGTCCTGTCTGCCTGCTTGCGTATATGGACTTGCTGTAGCCAGTGGATATGACTTTGAAAGAGAGGGATATTCTCTAGTCGGAATTGATCCTTTCCGTCTGCTCCAAAACAGCCAAGTCTTCAGTCTCATCAGACCGAACGAAAATCCAGCTCATAAGAGTCAGCTGGTATGGATGGCATGCCACTCTGCGGCATTTGAGGATCTGAGAGTTTCAAGCTTCATCAGAGGGACAAGAGTAGTCCCAAGAGGACAACTGTCCACCAGAGGAGTTCAGATTGCTTCAAATGAAAACATGGAGACAATGGACTCCAGTACTCTTGAACTGAGGAGCAGATACTGGGCTATAAGAACAAGAAGTGGAGGAAACACTAACCAACAGAGAGCATCTGCAGGACAAATCAGCGTGCAGCCCACATTCTCTGTGCAAAGAAACCTCCCATTCGAGAGAGCAACCATCATGGCAGCATTTACGGGAAACACTGAAGGCAGAACTTCAGACATGAGAACTGAGATCATAAGGATGATGGAAAATGCCAGACCTGAAGATGTGTCTTTCCAGGGGCGGGGAGTCTTCGAGCTCTCGGACGAAAAGGCAACGAACCCGATCGTGCCTTCCTTTGACATGAGTAATGAAGGATCTTATTTCTTCGGAGACAATGCAGAGGAGTATGACAATTAA</t>
         </is>
       </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Flu-0318|A_NA</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
+      <c r="CY1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0318|A_NA</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
         <is>
           <t>ATGAATCCAAATCAAAAGATAACAACCATTGGATCAATCTGTATGGTAATTGGGACAGTCAGCTTGATGCTGCAAATTGGGAACATAATCTCAATATGGGTTAGCCATTCAATCCAAACAGGGAATCAATACCAGCCTGAACCATGCAATCAAAGCATCATTACCTATGAGAACAACACCTGGGTAAATCAGACGTATGTCAACATCAGCAATAACAATTTTCTTGCTGAGCAGGCTGTTACTTCGGTAACATTAGCGGGCAATTCATCTCTTTGCCCTATTAGTGGGTGGGCAATATACAGTAAGGACAACGGTATAAGAATTGGGTCCAAGGGGGATGTGTTTGTCATAAGAGAACCGTTCATCTCATGCTCCCACTTGGAATGCAGAACCTTTTTCCTGACTCAGGGAGCTCTGCTGAATGACAAACATTCTAATGGGACAGTTAAGGATAGAAGCCCTTATAGAACTTTGATGAGTTGTCCCGTGGGTGAGGCTCCTTCCCCGTACAATTCAAGATTTGAGTCTGTTGCTTGGTCGGCAAGTGCTTGTCATGATGGCATCAGTTGGTTGACAATCGGTATTTCTGGTCCAGACAATGGAGCTGTGGCTGTATTGAAGTACAATGGCATAATAACGGATACTATCAAGAGTTGGAGAAACAACATTTTGAGAACTCAAGAATCTGAATGTGCTTGCGTAAATGGCTCTTGCTTCACCGTAATGACTGATGGACCAAGCAATGGGCAGGCCTCGTATAAAATCTTCAAGATAGAGAAAGGGAAAGTTGTCAAATCAGTTGAATTGAATGCCCCTAATTACCACTACGAGGAATGTTCCTGTTATCCTGATGCGGGTGATATTATATGTGTGTGCAGGGACAATTGGCACGGCTCAAACCGGCCGTGGATATCTTTTAATCAAAATCTGGAGTATCAAATAGGATATATATGCAGTGGGGTTTTCGGGGACAATCCCCGCCCCAATGATGGAACAGGCAGTTGCAGTCCAATGTCCTCTAATGGGGCATATGGGGTGAAAGGGTTTTCATTTAAGTACGGTAATGGGGTTTGGATCGGAAGAACAAAAGGCACTAGTTCCAGAAGCGGCTTTGAGATGATTTGGGACCCGAATGGGTGGACTGAGACGGACAGTAGTTTCTCAGTGAAGCAAGACATTGTAGAAATAACTGACTGGTCAGGATATAGTGGGAGTTTTGTCCAGCATCCAGAACTGACAGGATTAGATTGCATGAGGCCTTGTTTCTGGGTTGAGCTAATTAGAGGGAGGCCCAAAGAGAACACAATTTGGACTAGCGGGAGCAGCATATCCTTTTGTGGTGTAAATAGTGACACTGTGGGTTGGTCTTGGCCAGACGGTGCTGAGTTGCCATTCACCATTGACAAGTAG</t>
         </is>
       </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Flu-0318|A_MP</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0318|A_MP</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
         <is>
           <t>ATGAGTCTTCTAACCGAGGTCGAAACGTACGTTCTCTCTATCGTCCCGTCGGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTTGAAGATGTCTTTGCAGGGAAGAACACCGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATACTGTCACCTCTGACTAAGGGGATTTTGGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCTCTAAGTGGAAATGGAGACCCAAACAACATGGACAGGGCAGTCAAGTTGTACAGGAAACTGAAGAGAGAAATAACATTCCATGGGGCTAAAGAAGTTGCACTTAGTTACTCAACCGGTGCACTTGCCAGTTGTATGGGTCTCATATACAACAGGATGGGGACGGTGACCGCAGAAGTGGCATTGGGCCTAGTGTGTGCCACCTGTGAGCAGATTGCTGATTCACAGCATCGGTCTCACAGACAGATAGCTACCACCACCAACCCACTAATCAGACATGAAAACAGAATGGTTTTGGCCAGTACTACAGCTAAGGCTATGGAGCAGATGGCTGGATCGAGTGAGCAAGCAGTGGAAGCCATGGAGGTTGCTAGTCAGGCTAGGCAAATGGTGCAGGCGATGAGGACCATTGGAACTCATCCTAGCTCCAGTGCCGGTCTGAGAGATGATCTCCTTGAAAATTTGCAGGCCTACCAAAAACGAATGGGAGTGCAACTGCAGCGATTCAAGTGATCCTCTCGTTATTGCAGCAAGTATCATTGGGATCTTGCACTTGATATTGTGGATTCTTGATCGCCTTTTCTTCAAATGCGTTTATCGTCGCCTTAAATACGGTTTGAAAGGAGGGCCTTCTACGGAAGGAGTACCTGAGTCCATGAGGGAAGAGTACCGGCAGGAACAGCAGAGTGCTGTGGATGTTGACGATGGTCATTTTGTCAACATAGAGATGGAGTAA</t>
         </is>
       </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Flu-0318|A_NS</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0318|A_NS</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
         <is>
           <t>ATGGATTCCAACACTGTGTCAAGCTTTCAGGTAGACTGCTTTCTTTGGCATGTCCGCAAACAATTTGCAGACCAAGAACTGGGTGATGCCCCATTCCTTGACCGGCTCCGCCGAGACCAGAAGTCTCTAAGAGGAAGAGGCAGCACTCTTGGTCTGGACATCGAGACGGCCACTCGTGCTGGAAAGCAGATAGTGGAGAGGATTCTGGAGGAAGAATCCGACGAGGCACTCAAAATGACTATTGCCTCTGTGCCTGCTCCACGCTACCTAACTGACATGACTCTTGAAGAGATGTCAAGAGACTGGTTCATGCTCATGCCCAAGCAAAAAGTGGCAGGCTCCCTCTGTATCAGAATGGACCAGGCGATTATGGATAAGAACATCATACTGAAGGCAAACTTCAGTGTGATCTTCAATCGGCTGGAGACACTAATACTACTCAGAGCTTTCACTGAAGAGGGAGCAATTGTCGGCGAAATTTCACCATTGCCTTCTCTTCCAGGACATACTGATGAGGATGTCAAAAATGCAATTGGGGTCCTCATCGGAGGACTTGAATGGAATGATAACACAGTTCGAGTCTCTGAAATTTTACAGAGATTCGCTTGGAGAAGCAGTAATGAGGATGGGAGACCTCCACTCCCTCCAAAGCAGAAACGGAAAATGGAGAGAACAATTGAGTCAGAAGTTTGAAGAAATAAGGTGGCTGATTGAAGAGGTGCGACACAGACTAAAGATCACAGAAAATAGTTTTGAACAAATAACATTTATGCAAGCCTTACAACTACTGCTTGAAGTGGAGCAAGAGATACGAACTTTCTCGTTTCAGCTTATTTAA</t>
         </is>
       </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Flu-0321|A_NA</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0321|A_NA</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
         <is>
           <t>ATGAATCCAAATCAAAAGATAACAACCATTGGATCAATCTGTATGGTAATTGGGACAGTCAGCTTGATGCTGCAAATTGGGAACATAATCTCAATATGGGTTAGCCATTCAATCCAAACAGGGAATCAATACCAGCCTGAACCATGCAATCAAAGCATCATTACCTATGAGAACAACACCTGGGTAAATCAGACGTATGTCAACATCAGCAATAACAATTTTCTTGCTGAGCAGGCTGTTACTTCGGTAACATTAGCGGGCAATTCATCTCTTTGCCCTATTAGTGGGTGGGCAATATACAGTAAGGACAACGGTATAAGAATTGGGTCCAAGGGGGATGTGTTTGTCATAAGAGAACCGTTCATCTCATGCTCCCACTTGGAATGCAGAACCTTTTTCCTGACTCAGGGAGCTCTGCTGAATGACAAACATTCTAATGGGACAGTTAAGGATAGAAGCCCTTATAGAACTTTGATGAGTTGTCCCGTGGGTGAGGCTCCTTNCCCGTACAATTCAAGATTTGAGTCTGTTGCTTGGTCGGCAAGTGCTTGTCATGATGGCATCAGTTGGTTGACAATCGGTATTTCTGGTCCAGACAATGGAGCTGTGGCTGTATTGAAGTACAATGGCATAATAACGGATACTATCAAGAGTTGGAGAAACAACATTTTGAGAACTCAAGAATCTGAATGTGCTTGCGTAAATGGCTCTTGCTTCACCGTAATGACTGATGGACCAAGCAATGGGCAGGCCTCGTATAAAATCTTCAAGATAGAGAAAGGGAAAGTTGTCAAATCAGTTGAATTGAATGCCCCTAATTACCACTACGAGGAATGTTCCTGTTATCCTGATGCGGGTGATATTATATGTGTGTGCAGGGACAATTGGCACGGCTCAAACCGGCCGTGGATATCTTTTAATCAAAATCTGGAGTATCAAATAGGATATATATGCAGTGGGGTTTTCGGGGACAATCCCCGCCCCAATGATGGAACAGGCAGTTGCAGTCCAATGTCCTCTAATGGGGCATATGGGGTAAAAGGGTTTTCATTTAAGTACGGTAATGGGGTTTGGATCGGAAGAACAAAAGGCACTAGTTCCAGAAGCGGCTTTGAGATGATTTGGGACCCGAATGGGTGGACTGAGACGGACAGTAGTTTCTCAGTGAAGCAAGACATTGTAGAAATAACTGACTGGTCAGGATATAGTGGGAGTTTTGTCCAGCATCCAGAACTGACAGGATTAGATTGCATGAGGCCTTGTTTCTGGGTTGAGCTAATTAGAGGGAGGCCCAAAGAGAACACAATTTGGACTAGCGGGAGCAGCATATCCTTTTGTGGTGTAAATAGTGACACTGTGGGTTGGTCTTGGCCAGACGGTGCTGAGTTGCCATTCACCATTGACAAGTAG</t>
         </is>
       </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Flu-0321|A_MP</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0321|A_MP</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
         <is>
           <t>ATGAGTCTTCTAACCGAGGTCGAAACGTACGTTCTCTCTATCGTCCCGTCGGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTTGAAGATGTCTTTGCAGGGAAGAACACCGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATACTGTCACCTCTGACTAAGGGGATTTTGGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCTCTAAGTGGAAATGGAGACCCAAACAACATGGACAGGGCAGTCAAGTTGTACAGGAAACTGAAGAGAGAAATAACATTCCATGGGGCTAAAGAAGTTGCACTTAGTTACTCAACCGGTGCACTTGCCAGTTGTATGGGTCTCATATACAACAGGATGGGGACGGTGACCGCAGAAGTGGCATTGGGCCTAGTGTGTGCCACCTGTGAGCAGATTGCTGATTCACAGCATCGGTCTCACAGACAGATAGCTACCACCACCAACCCACTAATCAGACATGAAAACAGAATGGTTTTGGCCAGTACTACAGCTAAGGCTATGGAGCAGATGGCTGGATCGAGTGAGCAAGCAGTGGAAGCCATGGAGGTTGCTAGTCAGGCTAGGCAAATGGTGCAGGCGATGAGGACCATTGGAACTCATCCTAGCTCCAGTGCCGGTCTGAGAGATGATCTCCTTGAAAATTTGCAGGCCTACCAAAAACGAATGGGAGTGCAACTGCAGCGATTCAAGTGATCCTCTCGTTATTGCAGCAAGTATCATTGGGATCTTGCACTTGATATTGTGGATTCTTGATCGCCTTTTCTTCAAATGCGTTTATCGTCGCCTTAAATACGGTTTGAAAGGAGGGCCTTCTACGGAAGGAGTACCTGAGTCCATGAGGGAAGAGTACCGGCAGGAACAGCAGAGTGCTGTGGATGTTGACGATGGTCATTTTGTCAACATAGAGATGGAGTAA</t>
         </is>
       </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Flu-0321|A_NS</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0321|A_NS</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
         <is>
           <t>ATGGATTCCAACACTGTGTCAAGCTTTCAGGTAGACTGCTTTCTTTGGCATGTCCGCAAACAATTTGCAGACCAAGAACTGGGTGATGCCCCATTCCTTGACCGGCTCCGCCGAGACCAGAAGTCTCTAAGAGGAAGAGGCAGCACTCTTGGTCTGGACATCGAGACGGCCACTCGTGCTGGAAAGCAGATAGTGGAGAGGATTCTGGAGGAAGAATCCGACGAGGCACTCAAAATGACTATTGCCTCTGTGCCTGCTCCACGCTACCTAACTGACATGACTCTTGAAGAGATGTCAAGAGACTGGTTCATGCTCATGCCCAAGCAAAAAGTGGCAGGCTCCCTCTGTATCAGAATGGACCAGGCGATTATGGATAAGAACATCATACTGAAGGCAAACTTCAGTGTGATCTTCAATCGGCTGGAGACACTAATACTACTCAGAGCTTTCACTGAAGAGGGAGCAATTGTCGGCGAAATTTCACCATTGCCTTCTCTTCCAGGACATACTGATGAGGATGTCAAAAATGCAATTGGGGTCCTCATCGGAGGACTTGAATGGAATGATAACACAGTTCGAGTCTCTGAAATTTTACAGAGATTCGCTTGGAGAAGCAGTAATGAGGATGGGAGACCTCCACTCCCTCCAAAGCAGAAACGGAAAATGGAGAGAACAATTGAGTCAGAAGTTTGAAGAAATAAGGTGGCTGATTGAAGAGGTGCGACACAGACTAAAGATCACAGAAAATAGTTTTGAACAAATAACATTTATGCAAGCCTTACAACTACTGCTTGAAGTGGAGCAAGAGATACGAACTTTCTCGTTTCAGCTTATTTAA</t>
         </is>
       </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Flu-0323|A_MP</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0323|A_MP</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
         <is>
           <t>ATGAGTCTTCTAACCGAGGTCGAAACGTACGTTCTCTCTATCGTCCCGTCGGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTTGAAGATGTCTTTGCAGGGAAGAACACCGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATACTGTCACCTCTGACTAAGGGGATTTTGGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCTCTAAGTGGAAATGGAGACCCAAACAACATGGACAGGGCAGTCAAGTTGTACAGGAAACTGAAGAGAGAAATAACATTCCATGGGGCTAAAGAAGTTGCACTTAGTTACTCAACCGGTGCACTTGCCAGTTGTATGGGTCTCATATACAACAGGATGGGGACGGTGACCGCAGAAGTGGCATTGGGCCTAGTGTGTGCCACCTGTGAGCAGATTGCTGATTCACAGCATCGGTCTCACAGACAGATAGCTACCACCACCAACCCACTAATCAGACATGAAAACAGAATGGTTTTGGCCAGTACTACAGCTAAGGCTATGGAGCAGATGGCTGGATCGAGTGAGCAAGCAGTGGAAGCCATGGAGGTTGCTAGTCAGGCTAGGCAAATGGTGCAGGCGATGAGGACCATTGGAACTCATCCTAGCTCCAGTGCCGGTCTGAGAGATGATCTCCTTGAAAATTTGCAGGCCTACCAAAAACGAATGGGAGTGCAACTGCAGCGATTCAAGTGATCCTCTCGTTATTGCAGCAAGTATCATTGGGATCTTGCACTTGATATTGTGGAGTCTTGATCGCCTTTTCTTCAAATGCGTTTATCGTCGCCTTAAATACGGTTTGAAAGGAGGGCCTTCTACGGAAGGAGTACCTGAGTCCATGAGGGAAGAGTACCGGCAGGAACAGCAGAGTGCTGTGGATGTTGACGATGGTCATTTTGTCAACATAGAGATGGAGTAA</t>
         </is>
       </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Flu-0323|A_NS</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0323|A_NS</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
         <is>
           <t>ATGGATTCCAACACTGTGTCAAGCTTTCAGGTAGACTGCTTTCTTTGGCATGTCCGCAAACAATTTGCAGACCAAGAACTGGGTGATGCCCCATTCCTTGACCGGCTCCGCCGAGACCAGAAGTCTCTAAGAGGAAGAGGCAGCACTCTTGGTCTGGACATCGAGACGGCCACTCGTGCTGGAAAGCAGATAGTGGAGAGGATTCTGGAGGACGAATCCGACGAGGCACTCAAAATGACTATTGCCTCTGTGCCTGCTCCACGCTACCTAACTGACATGACTCTTGAAGAGATGTCAAGAGACTGGTTCATGCTCATGCCCAAGCAAAAAGTGGCAGGCTCCCTCTGTATCAGAATGGACCAGGCGATTATGGATAAGAACATCATACTGAAGGCAAACTTCAGTGTGATCTTCAATCGGCTGGAGACACTAATACTACTCAGAGCTTTCACTGAAGAGGGAGCAATTGTCGGCGAAATTTCACCATTGCCTTCTCTTCCAGGACATACTGATGAGGATGTCAAAAATGCAATTGGGGTCCTCATCGGAGGACTTGAATGGAATGATAACACAGTTCGAGTCTCTGAAATTTTACAGAGATTCGCTTGGAGAAGCAGTAATGAGGATGGGAGACCTCCACTCCCTCCAAAGCAGAAACGGAAAATGGAGAGAACAATTGAGTCAGAAGTTTGAAGAAATAAGGTGGCTGATTGAAGAGGTGCGACACAGACTAAAGATCACAGAAAATAGTTTTGAACAAATAACATTTATGCAAGCCTTACAACTACTGCTTGAAGTGGAGCAAGAGATACGAACTTTCTCGTTTCAGCTTATTTAA</t>
         </is>
       </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Flu-0325|A_NP</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0325|A_NP</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
         <is>
           <t>ATGGCGTCTCAAGGCACCAAACGATCATATGAACAAATGGAAACTGGTGGGGAACGCCAGAATGCCACTGAAATCAGAGCATCTGTTGGAAGAATGGTTGGCGGAATAGGAAGATTCTACATACAGATGTGCACTGAGCTCAAACTCAGTGATTATGAAGGGAGGCTGATCCAAAACAGCATAACCATAGAAAGAATGGTTCTCTCGGCATTTGATGAGAGGAGGAACAAGTACCTGGAGGAACATCCCAGTGCCGGGAAGGATNCCAAGAAGACTGGAGGTCCAATCTACAGGAGGAGAGATGGCAAATGGGTGAGAGAGTTGATCCTCTACGACAAAGAAGAGATCAGAAGAATTTGGCGTCAAGCCAATAATGGAGAGGATGCAACTGCTGGTCTCACTCATTTGATGATTTGGCATTCCAATCTGAATGATGCAACATACCAGAGAACAAGGGCACTTGTGCGTACTGGAATGGACCCTAGAATGTGCTCTCTGATGCAAGGCTCAACCCTCCCTAGGAGATCCGGGGCTGCTGGAGCAGCAGTGAAAGGAGTTGGAACAATGGTGATGGAACTAATTCGAATGATCAAGCGAGGGATCAATGATCGGAATTTCTGGAGAGGCGAAAACGGTCGGAGAACCAGGATTGCCTACGAGAGAATGTGCAACATCCTCAAGGGAAAGTTCCAAACAGCAGCACAACGGGCAATGATGGACCAAGTGAGAGAAAGCCGGAATCCTGGGAATGCTGAAATTGAAGATCTCATCTTTCTCGCACGATCTGCTCTCATCCTGAGGGGATCAGTGGCTCATAAGTCCNNNNTGCCTGCTTGCGTATATGGACNTGCTGTAGCCAGTGGATATGACTTTGNAAGANAGGNATANNNNNNNNTNGNANNNNATCCTTTNCGTNNNCTCCAAAACNGCCNAGTNTTNNGTCTNATCNNACNNNANNNNANTNNAGCTNATNNNAGTNAGCTGGTATNGANGGNNTGCCACTNTNNGGCANTNGANNNNNNNNNNNNTTNNAGNTTNATCAGNNGNANANNNNNNGTNCNNAGAGGNNNACNGTCCACCAGANNAGTTCAGATTGCTTCAAATGAAAACATGGAGACAATGGACTCCAGTACTCTTGAACTGAGGAGCAGATACTGGGCTATNAGAACAAGAAGTGGAGGAAACACTAACCAACAGAGAGCATCTGCAGGACAAATCAGCGTGCAGCCCACATTCTCTGTGCAAAGAAACCTCCCATTCGAGAGAGCAACCATCATGGCAGCATTTACGGGAAACACTGAAGGCAGAACTTCAGACATGAGAACTGAGATCATAAGGATGATGGAAAATGCCAGACCTGAAGATGTGTCTTTCCAGGGGCGGGGAGTCTTCGAGCTCTCGGACGAAAAGGCAACGAACCCGATCGTGCCTTCCTTTGACATGAGTAATGAAGGATCTTATTTCTTCGGAGACAATGCAGAGGAGTATGACAATTAA</t>
         </is>
       </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Flu-0325|A_MP</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0325|A_MP</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
         <is>
           <t>ATGAGTCTTCTAACCGAGGTCGAAACGTACGTTCTCTCTATCGTCCCGTCGGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTTGAAGATGTCTTTGCAGGGAAGAACACCGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATACTGTCACCTCTGACTAAGGGGATTTTGGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCTCTAAGTGGAAATGGAGACCCAAACAACATGGACAGGGCAGTCAAGTTGTACAGGAAACTGAAGAGAGAAATAACATTCCATGGGGCTAAAGAAGTTGCACTTAGTTACTCAACCGGTGCACTTGCCAGTTGTATGGGTCTCATATACAACAGGATGGGGACGGTGACCGCAGAAGTGGCATTGGGCCTAGTGTGTGCCACCTGTGAGCAGATTGCTGATTCACAGCATCGGTCTCACAGACAGATAGCTACCACCACCAACCCACTAATCAGACATGAAAACAGAATGGTTTTGGCCAGTACTACAGCTAAGGCTATGGAGCAGATGGCTGGATCGAGTGAGCAAGCAGTGGAAGCCATGGAGGTTGCTAGTCAGGCTAGGCAAATGGTGCAGGCGATGAGGACCATTGGAACTCATCCTAGCTCCAGTGCCGGTCTGAGAGATGATCTCCTTGAAAATTTGCAGGCCTACCAAAAACGAATGGGAGTGCAACTGCAGCGATTCAAGTGATCCTCTCGTTATTGCAGCAAGTATCATTGGGATCTTGCACTTGATATTGTGGAGTCTTGATCGCCTTTTCTTCAAATGCGTTTATCGTCGCCTTAAATACGGTTTGAAAGGAGGGCCTTCTACGGAAGGAGTACCTGAGTCCATGAGGGAAGAGTACCGGCAGGAACAGCAGAGTGCTGTGGATGTTGACGATGGTCATTTTGTCAACATAGAGATGGAGTAA</t>
         </is>
       </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Flu-0325|A_NS</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0325|A_NS</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
         <is>
           <t>ATGGATTCCAACACTGTGTCAAGCTTTCAGGTAGACTGCTTTCTTTGGCATGTCCGCAAACAATTTGCAGACCAAGAACTGGGTGATGCCCCATTCCTTGACCGGCTCCGCCGAGACCAGAAGTCTCTAAGAGGAAGAGGCAGCACTCTTGGTCTGGACATCGAGACGGCCACTCGTGCTGGAAAGCAGATAGTGGAGAGGATTCTGGAGGACGAATCCGACGAGGCACTCAAAATGACTATTGCCTCTGTGCCTGCTCCACGCTACCTAACTGACATGACTCTTGAAGAGATGTCAAGAGACTGGTTCATGCTCATGCCCAAGCAAAAAGTGGCAGGCTCCCTCTGTATCAGAATGGACCAGGCGATTATGGATAAGAACATCATACTGAAGGCAAACTTCAGTGTGATCTTCAATCGGCTGGAGACACTAATACTACTCAGAGCTTTCACTGAAGAGGGAGCAATTGTCGGCGAAATTTCACCATTGCCTTCTCTTCCAGGACATACTGATGAGGATGTCAAAAATGCAATTGGGGTCCTCATCGGAGGACTTGAATGGAATGATAACACAGTTCGAGTCTCTGAAATTTTACAGAGATTCGCTTGGAGAAGCAGTAATGAGGATGGGAGACCTCCACTCCCTCCAAAGCAGAAACGGAAAATGGAGAGAACAATTGAGTCAGAAGTTTGAAGAAATAAGGTGGCTGATTGAAGAGGTGCGACACAGACTAAAGATCACAGAAAATAGTTTTGAACAAATAACATTTATGCAAGCCTTACAACTACTGCTTGAAGTGGAGCAAGAGATACGAACTTTCTCGTTTCAGCTTATTTAA</t>
         </is>
       </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Flu-0326|A_NP</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0326|A_NP</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
         <is>
           <t>ATGGCGTCTCAAGGCACCAAACGATCATATGAACAAATGGAAACTGGTGGGGAACGCCAGAATGCCACTGAAATCAGAGCATCTGTTGGAAGAATGGTTGGCGGAATAGGAAGATTCTACATACAGATGTGCACTGAGCTCAAACTCAGTGATTATGAAGGGAGGCTGATCCAAAACAGCATAACCATAGAAAGAATGGTTCTCTCGGCATTTGATGAGAGGAGGAACAAGTACCTGGAGGAACATCCCAGTGCCGGGAAGGATCCCAAGAAGACTGGAGGTCCAATCTACAGGAGGAGAGATGGCAAATGGGTGAGAGAGTTGATCCTCTACGACAAAGAAGAGATCAGAAGAATTTGGCGTCAAGCCAATAATGGAGAGGATGCAACTGCTGGTCTCACTCATTTGATGATTTGGCATTCCAATCTGAATGATGCAACATACCAGAGAACAAGGGCACTTGTGCGTACTGGAATGGACCCTAGAATGTGCTCTCTGATGCAAGGCTCAACCCTCCCTAGGAGATCCGGGGCTGCTGGAGCAGCAGTGAAAGGAGTTGGAACAATGGTGATGGAACTAATTCGAATGATCAAGCGAGGGATCAATGATCGGAATTTCTGGAGAGGCGAAAACGGTCGGAGAACCAGGATTGCCTACGAGAGAATGTGCAACATCCTCAAGGGAAAGTTCCAAACAGCAGCACAACGGGCAATGATGGACCAAGTGAGAGAAAGCCGGAATCCTGGGAATGCTGAAATTGAAGATCTCATCTTTCTCGCACGATCTGCTCTCATCCTGAGGGGATCAGTGGCTCATAAGTCCTGTCTGCCTGCTTGCGTATATGGACTTGCTGTAGCCAGTGGATATGACTTTGAAAGAGAGGGATATTCTCTAGTCGGAATTGATCCTTTCCGTCTGCTCCAAAACAGCCAAGTCTTCAGTCTCATCAGACCGAACGAAAATCCAGCTCATAAGAGTCAGCTGGTATGGATGGCATGCCACTCTGCGGCATTTGAGGATCTGAGAGTTTCAAGCTTCATCAGAGGGACAAGAGTAGTCCCAAGAGGACAACTGTCCACCAGAGGAGTTCAGATTGCTTCAAATGAAAACATGGAGACAATGGACTCCAGTACTCTTGAACTGAGGAGCAGATACTGGGCTATAAGAACAAGAAGTGGAGGAAACACTAACCAACAGAGAGCATCTGCAGGACAAATCAGCGTGCAGCCCACATTCTCTGTGCAAAGAAACCTCCCATTCGAGAGAGCAACCATCATGGCAGCATTTACGGGAAACACTGAAGGCAGAACTTCAGACATGAGAACTGAGATCATAAGGATGATGGAAAATGCCAGACCTGAAGATGTGTCTTTCCAGGGGCGGGGAGTCTTCGAGCTCTCGGACGAAAAGGCAACGAACCCGATCGTGCCTTCCTTTGACATGAGTAATGAAGGATCTTATTTCTTCGGAGACAATGCAGAGGAGTATGACAATTAA</t>
         </is>
       </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Flu-0326|A_MP</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0326|A_MP</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
         <is>
           <t>ATGAGTCTTCTAACCGAGGTCGAAACGTACGTTCTCTCTATCGTCCCGTCGGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTTGAAGATGTCTTTGCAGGGAAGAACACCGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATACTGTCACCTCTGACTAAGGGGATTTTGGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCTCTAAGTGGAAATGGAGACCCAAACAACATGGACAGGGCAGTCAAGTTGTACAGGAAACTGAAGAGAGAAATAACATTCCATGGGGCTAAAGAAGTTGCACTTAGTTACTCAACCGGTGCACTTGCCAGTTGTATGGGTCTCATATACAACAGGATGGGGACGGTGACCGCAGAAGTGGCATTGGGCCTAGTGTGTGCCACCTGTGAGCAGATTGCTGATTCACAGCATCGGTCTCACAGACAGATAGCTACCACCACCAACCCACTAATCAGACATGAAAACAGAATGGTTTTGGCCAGTACTACAGCTAAGGCTATGGAGCAGATGGCTGGATCGAGTGAGCAAGCAGTGGAAGCCATGGAGGTTGCTAGTCAGGCTAGGCAAATGGTGCAGGCGATGAGGACCATTGGAACTCATCCTAGCTCCAGTGCCGGTCTGAGAGATGATCTCCTTGAAAATTTGCAGGCCTACCAAAAACGAATGGGAGTGCAACTGCAGCGATTCAAGTGATCCTCTCGTTATTGCAGCAAGTATCATTGGGATCTTGCACTTGATATTGTGGAGTCTTGATCGCCTTTTCTTCAAATGCGTTTATCGTCGCCTTAAATACGGTTTGAAAGGAGGGCCTTCTACGGAAGGAGTACCTGAGTCCATGAGGGAAGAGTACCGGCAGGAACAGCAGAGTGCTGTGGATGTTGACGATGGTCATTTTGTCAACATAGAGATGGAGTAA</t>
         </is>
       </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Flu-0326|A_NS</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0326|A_NS</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>ATGGATTCCAACACTGTGTCAAGCTTTCAGGTAGACTGCTTTCTTTGGCATGTCCGCAAACAATTTGCAGACCAAGAACTGGGTGATGCCCCATTCCTTGACCGGCTCCGCCGAGACCAGAAGTCTCTAAGAGGAAGAGGCAGCACTCTTGGTCTGGACATCGAGACGGCCACTCGTGCTGGAAAGCAGATAGTGGAGAGGATTCTGGAGGACGAATCCGACGAGGCACTCAAAATGACTATTGCCTCTGTGCCTGCTCCACGCTACCTAACTGACATGACTCTTGAAGAGATGTCAAGAGACTGGTTCATGCTCATGCCCAAGCAAAAAGTGGCAGGCTCCCTCTGTATCAGAATGGACCAGGCGATTATGGATAAGAACATCATACTGAAGGCAAACTTCAGTGTGATCTTCAATCGGCTGGAGACACTAATACTACTCAGAGCTTTCACTGAAGAGGGAGCAATTGTCGGCGAAATTTCACCATTGCCTTCTCTTCCAGGACATACTGATGAGGATGTCAAAAATGCAATTGGGGTCCTCATCGGAGGACTTGAATGGAATGATAACACAGTTCGAGTCTCTGAAATTTTACAGAGATTCGCTTGGAGAAGCAGTAATGAGGATGGGAGACCTCCACTCCCTCCAAAGCAGAAACGGAAAATGGAGAGAACAATTGAGTCAGAAGTTTGAAGAAATAAGGTGGCTGATTGAAGAGGTGCGACACAGACTAAAGATCACAGAAAATAGTTTTGAACAAATAACATTTATGCAAGCCTTACAACTACTGCTTGAAGTGGAGCAAGAGATACGAACTTTCTCGTTTCAGCTTATTTAA</t>
         </is>
       </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Flu-0330|A_NP</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0330|A_NP</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
         <is>
           <t>ATGGCGTCTCAAGGCACCAAACGATCCTATGAACAAATGGAAACTGGTGGGGAACGCCAGAATGCCACTGAAATCAGAGCATCTGTTGGAAGAATGGTTGGCGGAATAGGAAGATTCTACATACAGATGTGCACTGAGCTCAAACTCAGTGATTATGAAGGGAGGCTGATCCAAAACAGCATAACCATAGAAAGGATGGTTCTCTCGGCATTTGATGAGAGGAGGAACAAGTACCTGGAGGAACATCCCAGTGCCGGGAAGGATCCCAAGAAGACTGGAGGTCCAATCTACAGGAGGAGAGATGGCAAATGGGTGAGAGAGTTGATCCTCTACGACAAAGAAGAGATCAGAAGAATTTGGCGTCAAGCTAATAATGGAGAGGATGCAACTGCTGGTCTCACTCATTTGATGATTTGGCATTCCAATCTGAATGATGCAACATACCAGAGAACAAGGGCACTTGTGCGTACTGGAATGGACCCTAGAATGTGCTCTCTGATGCAAGGATCAACCCTCCCTAGGAGATCCGGGGCTGCTGGAGCAGCAGTGAAAGGAGTTGGAACAATGGTGATGGAACTAATTCGAATGATCAAGCGAGGGATCAATGATCGGAATTTCTGGAGAGGCGAAAACGGTCGGAGAACCAGGATTGCCTACGAGAGAATGTGCAACATCCTCAAGGGAAAGTTCCAAACAGCAGCACAACGGGCAATGATGGACCAAGTGAGAGAAAGCCGGAATCCTGGGAATGCTGAAATTGAAGATCTCATCTTTCTCGCACGATCTGCTCTCATCCTGAGGGGATCAGTGGCTCATAAGTCCTGTCTGCCTGCTTGCGTATATGGACTTGCTGTAGCCAGTGGATATGACTTTGAAAGAGAGGGATATTCTCTAGTCGGAATTGATCCTTTCCGTCTGCTCCAAAACAGCCAAGTCTTCAGTCTCATCAGACCGAACGAAAATCCAGCTCATAAGAGTCAGCTGGTATGGATGGCATGCCACTCTGCGGCATTTGAGGATCTGAGAGTTTCAAGCTTCATCAGAGGGACAAGAGTAGTCCCAAGAGGACAACTGTCCACCAGAGGAGTTCAGATTGCTTCAAATGAAAACATGGAGACAATGGACTCCAGTACTCTTGAACTGAGGAGCAGATACTGGGCTATAAGAACAAGAAGTGGAGGAAACACTAACCAACAGAGAGCATCTGCAGGACAAATCAGCGTGCAGCCCACATTCTCTGTGCAAAGAAACCTCCCATTCGAGAGAGCAACCATCATGGCAGCATTTACGGGAAACACTGAAGGCAGAACTTCAGACATGAGAACGGAGATCATAAGGATGATGGAAAATGCCAGACCTGAAGATGTGTCTTTCCAGGGGCGGGGAGTCTTCGAGCTCTCGGACGAAAAGGCAACGAACCCGATCGTGCCTTCCTTTGACATGAGTAATGAAGGATCTTATTTCTTCGGAGACAATGCAGAGGAGTATGACAATTAA</t>
         </is>
       </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Flu-0330|A_MP</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0330|A_MP</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
         <is>
           <t>ATGAGTCTTCTAACCGAGGTCGAAACGTACGTTCTCTCTATCGTCCCGTCGGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTTGAAGATGTCTTTGCAGGGAAGAACACCGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATACTGTCACCTCTGACTAAGGGGATTTTGGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCTCTAAGTGGAAATGGAGACCCAAACAACATGGACAGGGCAGTCAAGTTGTACAGGAAACTGAAGAGAGAAATAACATTCCATGGGGCTAAAGAAGTTGCACTTAGTTACTCAACCGGTGCACTTGCCAGTTGTATGGGTCTCATATACAACAGGATGGGGACGGTGACCGCAGAAGTGGCATTGGGCCTAGTGTGTGCCACCTGTGAGCAGATTGCTGATTCACAGCATCGGTCTCACAGACAGATAGCTACCACCACCAACCCACTAATCAGACATGAAAACAGAATGGTTTTGGCCAGTACTACAGCTAAGGCTATGGAGCAGATGGCTGGATCGAGTGAGCAAGCAGTGGAAGCCATGGAGGTTGCTAGTCAGGCTAGGCAAATGGTGCAGGCGATGAGGACCATTGGAACTCATCCTAGCTCCAGTGCCGGTCTGAGAGATGATCTCCTTGAAAATTTGCAGGCCTACCAAAAACGAATGGGAGTGCAACTGCAGCGATTCAAGTGATCCTCTCGTTATTGCAGCAAGTATCATTGGGATCTTGCACTTGATATTGTGGATTCTTGATCGCCTTTTCTTCAAATGCGTTTATCGTCGCCTTAAATACGGTTTGAAAGGAGGGCCTTCTACGGAAGGAGTACCTGAGTCCATGAGGGAAGAGTACCGGCAGGAACAGCAGAGTGCTGTGGATGTTGACGATGGTCATTTTGTCAACATAGAGATGGAGTAA</t>
         </is>
       </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Flu-0330|A_NS</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0330|A_NS</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
         <is>
           <t>ATGGATTCCAACACTGTGTCAAGCTTTCAGGTAGACTGCTTTCTTTGGCATGTCCGCAAACAATTTGCAGACCAAGAACTGGGTGATGCCCCATTCCTTGACCGGCTCCGCCGAGACCAGAAGTCTCTAAGAGGAAGAGGCAGCACTCTTGGTCTGGACATCGAGACGGCCACTCGTGCTGGAAAGCAGATAGTGGAGAGGATTCTGGAGGAAGAATCCGACGAGGCACTCAAAATGACTATTGCCTCTGTGCCTGCTCCACGCTACCTAACTGACATGACTCTTGAAGAGATGTCAAGAGACTGGTTCATGCTCATGCCCAAGCAAAAAGTGGCAGGCTCCCTCTGTATCAGAATGGACCAGGCGATTATGGATAAGAACATCATACTGAAGGCAAACTTCAGTGTGATCTTCAATCGGCTGGAGACACTAATACTACTCAGAGCTTTCACTGAAGAGGGAGCAATTGTCGGCGAAATTTCACCATTGCCTTCTCTTCCAGGACATACTGATGAGGATGTCAAAAATGCAATTGGGGTCCTCATCGGAGGACTTGAATGGAATGATAACACAGTTCGAGTCTCTGAAATTTTACAGAGATTCGCTTGGAGAAGCAGTAATGAGGATGGGAGACCTCCACTCCCTCCAAAGCAGAAACGGAAAATGGAGAGAACAATTGAGTCAGAAGTTTGAAGAAATAAGGTGGCTGATTGAAGAGGTGCGACACAGACTAAAGATCACAGAAAATAGTTTTGAACAAATAACATTTATGCAAGCCTTACAACTACTGCTTGAAGTGGAGCAAGAGATACGAACTTTCTCGTTTCAGCTTATTTAA</t>
         </is>
       </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Flu-0402|A_PB2</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0402|A_PB2</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
         <is>
           <t>ATGGAGAGAATAAAAGAACTAAGAGATCTAATGTCACAGTCTCGCACTCGCGAGATACTGACCAAAACCACTGTTGACCACATGGCCATAATCAAAAGGTACACATCGGGAAGGCAAGAGAAGAACCCCGCACTCAGAATGAAATGGATGATGGCAATGAAATATCCAATTACAGCAGATAAGCGAATAATGGAAATGATCCCTGAGAGGAATGAACAAGGGCAAACTCTCTGGAGCAAAACAAACGATGCCGGATCAGACCGAGTGATGGTATCACCCCTGGCTGTGACATGGTGGAACAGGAACGGACCAACAACAAGTACAGTTCACTACCCAAAGGTATATAAAACTTATTTCGAAAAAGTTGAAAGGTTGAAAAACGGGACCTTTGGCCCTGTGCACTTCAGAAACCAAGTTAAAATAAGACGGAGGGTCGATATAAACCCGGGCCATGCTGATCTCAGTGCCAAAGAGGCGCAGGATGTAATCATGGAAGTCGTCTTCCCAAATGAAGTGGGAGCAAGGATATTGACGTCGGAGTCACAACTGACGATAACAAAGGAGAAAAAGGAAGAACTCCAGGACTGCAAAATCGCTCCTCTGATGGTTGCATACATGCTAGAAAGAGAGTTGGTTCGCAAGACGAGGTTTCTCCCAGTTGCTGGTGGGACAAGCAGTGTCTACATTGAGGTGCTGCATTTGACCCAGGGGACATGCTGGGAGCAGATGTACACTCCGGGAGGAGAAGTGAGGAACGATGATGTAGACCAAAGCTTGATCATTGCTGCCAGGAATATAGTAAGAAGAGCAACAGTATCAGCAGATCCATTAGCATCTCTATTGGAGATGTGTCACAGCACACAAATTGGGGGAATAAGGATGGTGGACATCCTTCGGCAAAATCCAACAGAGGAACAAGCCGTGGATATATGCAAGGCAGCAATGGGCTTGAGGATTAGCTCATCTTTCAGCTTTGGTGGATTCACTTTTAAAAGAACAAGTGGATCGTCAGTCAAAAAAGAAGAAGAAGTGCTAACAGGCAACCTTCAAACATTGAAAATAAGAGTACATGAGGGGTATGAAGAGTTCACAATGGTTGGGAGAAGAGCAACGGCCATTCTCAGGAAAGCAACCAGAAGACTGATCCAGCTAATTGTAAGTGGGAGAGACGAGCAGTCAATTGCTGAAGCAATAATTGTGGCCATGGTATTCTCACAAGAGGACTGCATGATTAAAGCAGTTAGAGGTGACCTGAATTTTGTCAATAGGGCGAACCAGCGGCTAAACCCAATGCATCAACTCTTGAGGCATTTCCAAAAGGATGCAAAGGTGCTTTTCCAAAATTGGGGAATTGAACCCATTGACAATGTGATGGGAATGATCGGGGTAATGCCCGACATGACCCCAAGTACTGAGATGTCGCTGAGGGGAATAAGAGTCAGTAAGATGGGAGTAGATGAATACTCAAGTACAGAGCGAGTAGTAGTAAGTATCGACCGGTTTTTAAGAGTTCGAGACCAACAGGGAAACGTACTATTATCACCCGAAGAGGTCAGTGAGACACAAGGAACGGAGAAACTGACAATCACTTATTCGTCATCAATGATGTGGGAGATCAATGGTCCTGAGTCGGTATTGGTCAATACTTATCAGTGGATAATTAGAAACTGGGAAACCGTAAAAATTCAATGGTCACAGGRTCCCACAATGTTGTATAATAAGATGGAATTCGAGCCATTCCAGTCTCTAGTCCCTAAGGCAGCCAGAGGTCAATACAGTGGGTTTGTGAGAACACTATTCCAGCAAATGCGAGATGTGCTTGGAACATTTGACACTGTTCAGATAGTAAAACTCCTCCCCTTTGCTGCCGCCCCACCGGAACAAAGTAGGATGCAGTTCTCCTCTCTGACTGTGAATGTAAGAGGATCAGGAATGAGGATACTGGTAAGAGGCAATTCACCAGTGTTCAATTATAACAAGGCCACCAAGAGGCTCACAGTTCTCGGGAAAGATGCAGGTGCATTGACCGAAGATCCAGATGAAGGCACAGCTGGAGTGGAGTCTGCTGTTTTAAGAGGATTCCTCATTTTGGGCAAAGAAGACAAGAGATATGGCCCAGCATTGAGCATCAATGAGCTGAGCAATCTTGCAAAGGGAGAGAAGGCTAATGTGCTAATTGGGCAAGGAGACGTAGTGTTGGTGATGAAACGGAAACGGGACTCTAGCATACTTACTGACAGCCAGACAGCGACCAAAAGGATTCGGATGGCCATCAATTAG</t>
         </is>
       </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Flu-0402|A_PB1</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0402|A_PB1</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
         <is>
           <t>ATGGATGTCAATCCGACTTTACTTTTCTTGAAGGTTCCAGCGCAAAATGCCATAAGCACCACATTCCCGTATACTGGAGATCCCCCATACAGCCATGGAACAGGAACAGGATATACCATGGACACAGTTAACAGAACACATCAGTATTCAGAAAAAGGGAAATGGACAACAAACTCAGAAACTGGAGCACCTCAACTCAATCCAATTGATGGACCATTGCCTGAAGACAATGAACCAAGTGGGTATGCACAAACGGACTGTGTCCTTGAAGCAATGGCTTTCCTTGAAGAGTCCCACCCAGGAATCTTTGAAAACTCGTGTCTTGAAACGATGGAAGTTGTTCAACAAACAAGAGTGGACAAGTTGACTCAAGGCCGTCAGACCTATGATTGGACGTTGAACAGGAATCAGCCGGCTGCAACTGCATTAGCTAATACTATAGAGATCTTCAGATCTAACGGCCTCACAGCCAATGAATCAGGAAGGCTAATAGATTTTCTCAAGGATGTGATGGAATCAATGGATAAGGAGGAAATGGAAATAACAACGCATTTCCAAAGGAAAAGAAGAGTGAGAGACAACATGACCAAGAAAATGGTCACACAAAGGACAATAGGAAAGAAGAAACAGAGGCTAAATAAAAAGAGCTATCTAATAAGAGCATTGACACTGAACACGATGACAAAAGACGCCGAAAGAGGCAAATTAAAAAGAAGGGCAATTGCGACACCTGGAATGCAAATCAGAGGGTTTGTGTACTTTGTTGAAACATTAGCGAGGAGCATTTGTGATAAGCTTGAACAATCTGGACTCCCAGTTGGGGGCAATGAAAAGAAGGCTAAACTGGCAAATGTTGTGAGAAAAATGATGACTAATTCGCAGGACACAGAGCTCTCTTTCACAATCACTGGAGACAACACCAAATGGAATGAAAATCAGAACCCTAGGATGTTTCTGGCAATGATAACATATATAACAAGGAACCAACCTGAATGGTTCAGGAATGTCTTAAGCATTGCACCTATAATGTTCTCAAATAAAATGGCAAGACTAGGGAAAGGGTACATGTTCGAAAGTAAGAGCATGAAGCTTCGAACACAAATACCAGCAGAAATGCTAGCAAGCATTGATATGAAGTACTTCAATGAGTCAACAAGAAAGAAAATAGAGAAGATAAGACCTCTTCTAATAGATGATACAGCCTCATTAAGCCCAGGAATGATGATGGGCATGTTCAATATGCTGAGTACAGTTTTGGGAGTTTCGATTCTAAATCTAGGACAAAGGAGGTACACCAAAACAACATACTGGTGGGACGGACTCCAATCCTCTGATGACTTTGCTCTCATAGTGAATGCTCCGAATCATGAGGGAATACAAGCAGGGGTAGACAGATTCTATAGAACCTGCAAACTGGTTGGAATCAACATGAGCAAAAAGAAGTCCTACATAAACAGGACAGGAACATTTGAATTCACAAGTTTTTTCTACCGCTATGGATTTGTAGCCAACTTCAGTATGGAGTTGCCCAGCTTTGGAGTGTCTGGGATCAATGAATCTGCAGACATGAGCATTGGAGTAACAGTGATAAAGAACAACATGATCAACAATGATCTTGGACCAGCAACAGCTCAAATGGCTCTTCAGCTATTCATCAAGGATTACAGATACACATACCGATGTCACAGAGGAGACACACAAATTCAGACAAGGAGGTCATTCGAGCTGAAGAAGTTGTGGGAACAGACCCGCTCAAAAGCAGGACTGCTGGTCTCAGATGGAGGGCCAAATCTATACAATATTCGGAATCTTCACATTCCAGAAGTCTGCTTGAAATGGGAGCTAATGGACGAAGACTATCAGGGAAGGCTTTGTAATCCCCTGAATCCGTTTGTCAGCCACAAGGAAATAGAGTCTGTGAACAACGCTGTGGTGATGCCAGCTCATGGCCCGGCCAAGAGCATGGAATATGATGCTGTTGCCACCACTCACTCCTGGATACCGAAGAGGAACCGCTCCATTCTCAATACAAGCCAAAGGGGAATCCTTGAAGACGAACAGATGTATCAAAAGTGCTGCAACCTGTTCGAAAAATTCTTCCCTAGCAGTTCATACAGGAGGCCAGTTGGAATTTCCAGCATGGTGGAGGCCATGGTTTCTAGGGCCCGAATTGACGCACGAATTGACTTCGAATCTGGACGGATTAAGAAGGAGGAGTTTGCTGAGACCATGAAGATCTGTTCCACCATTGAAGAGCTCAGACGGCAGAAATAG</t>
         </is>
       </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Flu-0402|A_PA</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
+      <c r="EK1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0402|A_PA</t>
+        </is>
+      </c>
+      <c r="EL1" t="inlineStr">
         <is>
           <t>ATGGAAGACTTTGTGCGACAATGCTTCAATCCAATGATTGTCGAGCTTGCGGAAAAAGCAATGAAAGAATATGGGGAAGATCCGAAAATCGAGACAAACAAATTTGCCGCAATATGCACACACTTAGAAGTCTGTTTCATGTATTCGGATTTCCATTTTATTGATGAACGAGGCGAATCAATGATTGTAGAATCTGGCGATCCAAATGCATTATTGAAACACCGATTTGAGATAATCGAAGGTAGAGACAGAGCAATGGCCTGGACAGTGGTGAATAGTATCTGCAACACCACAGGGGTCGAAAAGCCCAAATTCCTCCCTGATTTGTATGACTACAAAGAGAACCGATTCATTGAAATTGGGGTAACGCGAAGGGAAGTTCACATATACTATTTAGAAAAAGCCAACAAGATAAAATCAGAGAAAACACATATTCACATATTCTCATTCACTGGAGAGGAAATGGCCACCAAGGCGGACTACTCCCTTGATGAAGAGAGCAGAGCAAGAATAAAAACCAGACTGTTCACTATAAGACAAGAAATGGCCAGTAGAGGTCTATGGGATTCCTTTCGTCAATCCGAGAGAGGCGAAGAGACAATTGAAGAAAGATTTGAAATCACAGGAACCATGCGCAGGCTTGCCGACCAAAGTCTTCCACCGAACTTCTCCAGCCTTGAAAACTTTAGAGCCTATGTGGATGGATTCGAACCGAACGGCTGCATTGAGGGAAAACTTTCTCAAATGTCAAAAGAAGTGAACGCCAGAATTGAGCCATTTCTGAAGACAACACCACGCCCTCTCAGATTACCTGATGGGCCTCCCTGTTCTCAGCGATCGAAGTTCTTGCTGATGGATGCCCTTAAGTTGAGCATCGAAGACCCTAGCCATGAGGGGGAAGGCATACCGCTGTATGATGCAATCAAATGCATGAAGACATTTTTTGGCTGGAAAGAGCCCAACATCGTAAAGCCGCATGAGAAAGGCATAAACCCTAATTACCTCCTGGCTTGGAAGCAGGTGCTGGCAGAACTTCAAGACATTGAAAATGAGGAGAAAATTCCAAAAACAAAGAACATTAAGAAAACAAGCCAATTGAAGTGGGCACTTGGTGAGAACATGGCTCCAGAAAAAGTGGACTTTGAGGACTGCAAAGATGTTAGCGATCTAAGACAGTACGACAGTGACGAACCAGAGTCTAGATCACTAGCAAGCTGGATTCAGAGTGAATTCAACAAGGCATGCGAACTGACAGATTCGAGTTGGATTGAACTTGATGAGATAGGGGAAGACGTTGCTCCAATCGAACACATTGCGAGTGTGAGGAGGAACTATTTCACAGCGGAGGTATCCCATTGCAGGGCCACTGAATACATAATGAAGGGAGTATACATAAACACAGCCCTATTGAATGCATCCTGTGCAGCCATGGATGACTTCCAATTGATTCCAATGATAAGTAAGTGCAGAACTAAAGAAGGAAGACGGAAGACAAATCTGTATGGATTCATTATAAAAGGAAGATCCCATTTGAGGAATGACACCGATGTGGTAAACTTTGTGAGCATGGAATTCTCTCTAACTGACCCGAGGCTAGAGCCACACAAATGGGAAAAGTACTGTGTTCTTGAGATAGGAGACATGCTCCTACGGACTGCAATAGGCCAAGTGTCGAGGCCCATGTTCCTGTATGTGAGAACCAATGGAACTTCCAAGATCAAAATGAAATGGGGCATGGAGATGAGGCGATGCCTTCTTCAGTCCCTTCAACAAATTGAGAGCATGATTGAGGCCGAATCTTCTGTCAAAGAGAAGGACATGTCCAAGGAATTCTTTGAAAACAAATCAGAAACATGGCCAATTGGAGAATCACCCAAAGGGGTGGAGGAAGGCTCTATTGGGAAAGTGTGCAGAACATTGCTAGCAAAGTCTGTGTTCAACAGCCTATATGCATCTCCACAACTCGAGGGGTTTTCAGCTGAATCAAGAAAATTGCTTCTCATTGTTCAGGCACTTAGGGACAACCTGGAACCTGGAACCTTCGATCTTGGGGGGCTATATGAAGCAATTGAGGAGTGCCTGATTAACGATCCCTGGGTTTTGCTTAATGCATCTTGGTTCAACTCCTTCCTCACACATGCACTGAAATAG</t>
         </is>
       </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Flu-0402|A_HA</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
+      <c r="EM1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0402|A_HA</t>
+        </is>
+      </c>
+      <c r="EN1" t="inlineStr">
         <is>
           <t>ATGGAGAACATAGTACTACTTCTTGCAATAGTTAGCCTTGTTAAAAGTGATCAGATTTGCATTGGTTACCATGCAAACAATTCGACAGAGCAAGTTGACACGATAATGGAAAAGAACGTCACTGTTACACATGCCCAAGACATACTGGAAAAAACACACAACGGAAAGCTCTGTGATTTAAATGGGGTGAAGCCACTGATTTTAAAGGATTGTAGTGTAGCTGGATGGCTCCTCGGAAACCCAATGTGCGACGAATTCATCAGAGTGCCGGAATGGTCATACATAGTGGAGCGGGCTAACCCAGCCAATGACCTCTGTTACCCAGGGAGCCTCAATGACTATGAAGAACTGAAACACATGTTGAGCAGAATAAATCATTTTGAGAAGATTCAGATCATTCCCAAGAGTTCCTGGCCAAATCATGAAACATCACTAGGGGTGAGCGCAGCTTGTCCATACCAGGGAGCGCCCTCCTTTTTCAGAAATGTGGTATGGCTTATCAAAAAGAACGATGCATACCCAACAATAAAGATAAGCTACAATAATACTAATCGGGAAGATCTCTTGATACTTTGGGGGATTCATCATTCCAACAATGCAAAAGAACAGACAAATCTCTACAAAAACCCAACCACCTACATTTCAGTTGGAACATCAACTTTAAACCAGAGGTTGGCACCAAAAATAGCTACTAGATCCCAAGTAAACGGGCAACGTGGAAGAATGGACTTCTTCTGGACAATCTTAAAACCAGATGATGCAATCCATTTCGAGAGTAACGGAAATTTCATTGCTCCAGAATATGCATACAAAATTGTCAAGAAAGGGGACTCAACAGTTATGAAAAGTGGAGTGGAATATGGCCACTGCAACACCAAATGTCAAACCCCAGTAGGTGCGATAAATTCTAGTATGCCATTCCACAACATACATCCTCTCACCATTGGGGAATGTCCCAAATACGTGAAGTCAAACAAGTTGGTCCTTGCGACTGGGCTCAGAAATAGTCCTCTAAGAGAAAAGAGAAGAAAAAGAGGTCTGTTTGGGGCGATAGCAGGGTTTATAGAGGGAGGATGGCAGGGAATGGTTGATGGTTGGTATGGATACCATCATAGCAATRAGCAGGGGAGTGGGTACGCTGCGGACAAAGAATCCACCCAAAAGGCAATAGATGGAGTTACCAATAAGGTCAACTCAATCATTGACAAAATGAACACTCAATTTGAGGCAGTTGGAAGGGAGTTTAACAACTTAGAAARGAGGATAGAGAATTTGAACAAGAAAATGGAAGACGGATTCCTAGATGTCTGGACCTATAATGCTGAACTTCTAGTCCTCATGGAAAACGAGAGGACTCTAGACTTCCATGATTCAAATGTCAAGAACCTTTACGACAAAGTCAGATTACAGCTTAGGGATAATGCAAAGGAGCTGGGTAAYGGCTGTTTCGAATTCTATCACAAATGTGATAATGAATGTATGGAAAGTGTGAGAAATGGGACGTATGACTACCCTCAGTATTCAGAAGAAGCAAGATTAAAAAGAGAAGAAATAAGCGGAGTGAAATTAGAATCAGTAGGAACTTACCAGATACTGTCAATTTATTCAACAGCGGCAAGTTCCCTAGCACTGGCAATCATGATGGCTGGTCTATCTTTATGGATGTGCTCCAATGGGTCGTTACAATGCAGAATTTGCATTTAG</t>
         </is>
       </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Flu-0402|A_NA</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
+      <c r="EO1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0402|A_NA</t>
+        </is>
+      </c>
+      <c r="EP1" t="inlineStr">
         <is>
           <t>ATGAATCCAAATCAAAAGATAACAACCATTGGATCAATCTGTATGGTAATTGGGATAGTCAGCTTGATGCTGCAAATTGGGAACATAATCTCAATATGGGTTAGCCATTCAATCCAAACAGGGAATCAATACCAGCCTGAACCATGCAATCAAAGCATCATTACCTATGAGAACAACACCTGGGTAAATCAGACGTATGTCAACATCAGCAATACCAATTTTCTTGCTGAGCAGGCTGTTACTTCGGTAACATTAGCGGGCAATTCATCTCTTTGCCCTATTAGTGGGTGGGCAATATACAGTAAGGACAACGGTATAAGAATTGGGTCCAAGGGGAATGTGTTTGTTATAAGAGAACCGTTCATCTCATGCTCCCACTTGGAATGCAGAGCCTTTTTCCTGACCCAGGGAGCTCTGCTGAATGACAAACATTCTAATGGGACAGTTAAGGATAGAAGCCCTTATAGAACTTTGATGAGTTGTCCCGTGGGTGAGGCTCCTTCCCCGTATAATTCAAGATTTGAGTCTGTTGCTTGGTCGGCAAGTGCTTGTCATGATGGCATCAGTTGGTTGACAATCGGTATTTCTGGTCCAGACAATGGAGCTGTGGCTGTATTGAAGTACAATGGCATAATAAYGGATACTATCAAGAGTTGGAGAAACAACATTTTGAGAACTCAAGAATCTGAATGTGCTTGCGTAAATGGCTCTTGCTTCACCGTAATGACTGATGGACCAAGCAATGGGCAGGCCTCATATAAAATCTTCAAGATAGAGAAAGGGAAAGTTGTCAAGTCAGTTGAGATGAATGCCCCTAATTACCACTACGAGGAATGCTCCTGTTATCCTGATGCGGGTGATATTATGTGTGTGTGCAGGGACAATTGGCATGGCTCAAATCGGCCGTGGGTATCTTTTAATCAAAATCTGGAGTATCAAATAGGATATATATGCAGTGGGGTATTCGGGGACAATCCCCGCCCCAATGATGGAACAGGCAGTTGCAGTCCAATGCCCTCYAATGGGGCATATGGGGTAAAAGGGTTTTCATTTAAGTACGGTAATGGGGTTTGGATCGGAAGAACAAAAAGCACTAGTTCCAGAAGCGGCTTTGAGATGATTTGGGATCCGAATGGGTGGACTGAGACGGACAGTAGTTTCTCAGTGAAGCAAGACATTGTAGAAATAACTGACTGGTCAGGATATAGTGGGAGTTTTGTCCAGCATCCAGAACTGACAGGATTAGATTGCATGAGGCCTTGTTTCTGGGTTGAGCTAATCAGAGGGAGGCCCAAAGAGAACACAATTTGGACTAGCGGGAGCAGCATATCCTTTTGTGGTGTAAATAGTGACACTGTGGGTTGGTCTTGGCCAGACGGTGCTGAGTTGCCATTCACCATTGACAAGTAG</t>
         </is>
       </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Flu-0402|A_MP</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
+      <c r="EQ1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0402|A_MP</t>
+        </is>
+      </c>
+      <c r="ER1" t="inlineStr">
         <is>
           <t>ATGAGTCTTCTAACCGAGGTCGAAACGTACGTTCTCTCTATCGTCCCGTCGGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTTGAAGATGTCTTTGCAGGGAAGAACACCGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATCCTGTCACCTCTGACTAAGGGGATTTTGGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCTCTAAGTGGAACTGGAGACCCAAACAACATGGACAGGGCAGTCAAGTTGTACAGGAAACTAAAGAGAGAGATAACATTCCACGGTGCTAAAGAAGTTGCACTCAGTTACTCAACCGGTGCACTTGCCAGTTGTATGGGTCTCATATACAACAGGATGGGGACGGTGACCGCAGAAGTGGCATTGGGCCTAGTGTGTGCCACCTGTGAGCAGATTGCTGATTCACAGCATCGGTCTCACAGACAGATAGCTACCACCACCAACCCACTAATCAGACATGAAAACAGAATGGTTTTGGCCAGTACTACAGCTAAGGCTATGGAGCAGATGGCTGGATCGAGTGAGCAAGCAGTGGAAGCCATGGAGGTTGCTAGTCAGGCTAGGCAGATGGTGCAGGCGATGAGGACCATTGGAACTCATCCTAGCTCCAGTGCCGGTCTGAGAGATGATCTCCTTGAAAATTTGCAGGCCTACCAAAAACGGATGGGAGTGCAACTGCAGCGATTCAAGTGATCCTCTCGTTATTGCCGCAAGTATCATTGGGATCTTGCACTTGATATTGTGGATTCTTGATCGCCTTTTCTTCAAATGCGTTTATCGTCGCCTTAAATACGGTTTGAAAGGAGGGCCTTCTACGGAAGGAGTACCTGAGTCCATGAGGGAAGAGTACCGGCAGGAACAGCAGAGTGCTGTGGATGTCGACGATGGTCATTTTGTCAACATAGAGCTGGAGTAA</t>
         </is>
       </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Flu-0402|A_NS</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
+      <c r="ES1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0402|A_NS</t>
+        </is>
+      </c>
+      <c r="ET1" t="inlineStr">
         <is>
           <t>ATGGATTCCAACACTGTGTCAAGCTTTCAGGTAGACTGCTTTCTTTGGCATGTCCGCAAACGATTTGCAGACCAAGAACTGGGTGATGCCCCATTCCTTGACCGGCTCCGCCGAGACCAGAAGTCTCTAAGAGGAAGAGGCAGCACTCTTGGTCTGGACATCGAGACGGCCACTCGTGCTGGAAAGCAGATAGTGGAGAGGATTCTGGAGGAAGAATCCGACGAGGCACTCAAAATGACTATTGCCTCTGTGCCTGCTCCACGCTACCTAACTGACATGACTCTTGAAGAGATGTCAAGAGACTGGTTCATGCTCATGCCCAAGCAAAAAATGGCAGGCTCCCTCAGTATCAAAATGGACCAGGCGATTATGGATAAGAAAATCATACTGAAGGCAAACTTCAGTGTGATCTTCAATCGGCTGGAGACACTAATACTACTCAGAGCTTTCACTGAAGAAGGAGCAATTGTCGGCGAAATTTCACCATTGCCTTCTCTTCCAGGACATACTGATGAGGATGTCAAAAATGCAATTGGGGTCCTCATCGGAGGACTTGAATGGAATGATAACACAGTTCGAGTCTCTGAAACTTTACAGAGATTCGCTTGGAGAAGCAGTAATGAGGATGGGAGATCTCCACTCCCTCCAAAGCAGAAACGGAAAATGGAGAGAACAATTGAGTCAGAAGTTTGAAGAAATAAGGTGGCTGATTGAAGAAGTTCGACACAGACTAAAGATCACAGAAAATAGTTTTGAACAAATAACATTTATGCAAGCCTTACAACTACTGCTTGAAGTGGAGCAAGAGATAAGAACTTTCTCGTTTCAGCTTATTTAA</t>
         </is>
       </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Flu-0403|A_MP</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
+      <c r="EU1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0403|A_MP</t>
+        </is>
+      </c>
+      <c r="EV1" t="inlineStr">
         <is>
           <t>ATGAGTCTTCTAACCGAGGTCGAAACGTACGTTCTCTCTATCGTCCCGTCGGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTTGAAGATGTCTTTGCAGGGAAGAACACCGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATCCTGTCACCTCTGACTAAGGGGATTTTGGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCTCTAAGTGGAACTGGAGACCCAAACAACATGGACAGGGCAGTCAAGTTGTACAGGAAACTAAAGAGAGAGATAACATTCCAYGGTGCTAAAGAAGTTGCACTCAGTTACTCAACCGGTGCACTTGCCAGTTGTATGGGTCTCATATACAACAGGATGGGGACGGTGACCGCAGAAGTGGCATTGGGCCTAGTGTGTGCCACCTGTGAGCAGATTGCTGATTCACAGCATCGGTCTCACAGACAGATAGCTACCACCACCAACCCACTAATCAGACATGAAAACAGAATGGTTTTGGCCAGTACTACAGCTAAGGCTATGGAGCAGATGGCTGGATCGAGTGAGCAAGCAGTGGAAGCCATGGAGGTTGCTAGTCAGGCTAGGCAGATGGTGCAGGCGATGAGGACCATTGGAACTCATCCTAGCTCCAGTGCCGGTCTGAGAGATGATCTCCTTGAAAATTTGCAGGCCTACCAAAAACGGATGGGAGTGCAACTGCAGCGATTCAAGTGATCCTCTCGTTATTGCCGCAAGTATCATTGGGATCTTGCACTTGATATTGTGGATTCTTGATCGCCTTTTCTTCAAATGCGTTTATCGTCGCCTTAAATACGGTTTGAAAGGAGGGCCTTCTACGGAAGGAGTACCTGAGTCCATGAGGGAAGAGTACCGGCAGGAACAGCAGAGTGCTGTGGATGTYGACGATGGTCATTTTGTCAACATAGAGCTGGAGTAA</t>
         </is>
       </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Flu-0406|A_PB2</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
+      <c r="EW1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0406|A_PB2</t>
+        </is>
+      </c>
+      <c r="EX1" t="inlineStr">
         <is>
           <t>ATGGAGAGAATAAAAGAACTAAGAGATCTAATGTCACAGTCTCGCACTCGCGAGATACTGACCAAAACCACTGTTGACCACATGGCCATAATCAAAAGGTACACATCGGGAAGGCAAGAGAAGAACCCCGCACTCAGAATGAAATGGATGATGGCAATGAAATATCCAATTACAGCAGATAATCGAATAATGGAAATGATCCCTGAGAGGAATGAACAAGGGCAAACTCTCTGGAGCAAAACAAACGATGCCGGATCAGACCGAGTGATGGTATCACCCCTGGCTGTGACATGGTGGAACAGGAACGGACCAACAACAAGTACAGTTCACTACCCAAAGGTATATAAAACTTAYTTCGAAAAAGTTGAAAGGTTGAAAAACGGGACCTTTGGCCCTGTGCACTTCAGAAACCAAGTTAAAATAAGACGGAGGGTCGATATAAACCCGGGCCATGCTGATCTCAGTGCCAAAGAGGCGCAGGATGTAATCATGGAAGTCGTCTTCCCAAATGAAGTGGGAGCAAGGATATTGACGTCGGAGTCACAACTGACGATAACAAAGGAGAAAAAGGAAGAACTCCAGGACTGCAAAATCGCTCCTCTGATGGTTGCATACATGCTAGAAAGAGAGTTGGTTCGCAAGACGAGGTTTCTCCCAGTTGCTGGTGGGACAAGCAGTGTCTACATTGAGGTGCTGCATTTGACCCAGGGGACATGCTGGGAGCAGATGTACACTCCGGGAGGAGAAGTGAGGAACGATGATGTAGACCAAAGCTTGATCATTGCTGCCAGGAATATAGTAAGAAGAGCAACAGTATCAGCAGATCCATTAGCATCTCTATTGGAGATGTGTCACAGCACACAAATTGGGGGAATAAGGATGGTGGACATCCTTCGGCAAAATCCAACAGAAGAACAAGCCGTGGATATATGCAAGGCAGCAATGGGCTTGAGGATTAGCTCATCTTTCAGCTTTGGTGGATTCACTTTTAAAAGAACAAGTGGATCGTCAGTCAAAAAAGAAGAAGAAGTGCTAACAGGCAACCTTCAAACATTGAAAATAAGAGTACATGAGGGGTATGAAGAGTTCACAATGGTTGGGAGAAGAGCAACGGCCATTCTCAGGAAAGCAACCAAAAGACTGATCCAGCTAATTGTAAGTGGGAGAGACGAGCAGTCAATTGCTGAAGCAATAATTGTGGCCATGGTATTCTCACAAGAGGACTGCATGATTAAAGCAGTTAGAGGTGACCTGAATTTTGTCAATAGGGCGAACCAGCGACTAAACCCAATGCATCAACTCTTGAGGCATTTCCAAAAGGATGCAAAGGTGCTTTTCCAAAATTGGGGAATTGAACCCATTGACAATGTGATGGGAATGATCGGGGTAATGCCCGACATGACCCCAAGTACTGAGATGTCGCTGAGGGGAATAAGAGTCAGTAAGATGGGAGTAGATGAATACTCAAGTACAGAGCGAGTAGTAGTAAGTATCGACCGGTTTTTAAGAGTTCGAGACCANNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNTAATNNGAAANTNGGAAACCGTAAAAATTCAATGGTCACAGGATCCCACAATGTTGTATAATAAGATGGAATTCGAGCCATTCCAGTCTCTAGTCCCTAAGGCAGCCAGAGGTCAATACAGTGGGTTTGTGAGAACACTATTCCAGCAAATGCGAGATGTGCTTGGAACATTTGACACTGTTCAGATAGTAAAACTCCTCCCCTTTGCTGCCGCCCCACCGGAACAAAGTAGGATGCAGTTCTCCTCCCTGACTGTGAATGTAAGAGGATCAGGAATGAGGATACTGGTAAGAGGCAATTCACCAGTGTTCAATTATAACAAGGCCACCAAGAGGCTCACAGTTCTCGGGAAAGATGCAGGTGCATTGACCGAAGATCCAGATGAAGGCACAGCTGGAGTGGAGTCTGCTGTTTTAAGAGGATTCCTCATTTTGGGCAAAGAAGACAAGAGATATGGCCCAGCATTGAGCATCAATGAGCTGAGCAATCTTGCAAAGGGAGAGAAGGCTAATGTGCTAATTGGGCAAGGAGACGTAGTGTTGGTGATGAAACGGAAACGGGACTCTAGCATACTTACTGACAGCCAGACAGCGACCAAAAGGATTCGGATGGCCATCAATTAG</t>
         </is>
       </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Flu-0406|A_PB1</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
+      <c r="EY1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0406|A_PB1</t>
+        </is>
+      </c>
+      <c r="EZ1" t="inlineStr">
         <is>
           <t>ATGGATGTCAATCCGACTTTACTTTTCTTGAAGGTTCCAGCGCAAAATGCCATAAGCACCACATTCCCGTATACTGGAGATCCCCCATACAGCCATGGAACAGGAACAGGATATACCATGGACACAGTTAACAGAACACATCAGTATTCAGAAAAAGGGAAATGGACAACAAACTCAGAAACTGGAGCACCTCAACTCAATCCAATTGATGGACCATTGCCTGAGGACAATGAACCAAGTGGGTATGCACAAACGGACTGTGTCCTTGAAGCAATGGCTTTCCTTGAAGAGTCCCACCCAGGAATCTTTGAAAACTCGTGTCTTGAAACGATGGAAGTTGTTCAACAAACAAGAGTGGACAAGTTGACTCAAGGCCGTCAGACCTATGATTGGACGTTGAACAGGAATCAGCCGGCTGCAACTGCATTAGCTAATACTATAGAGATCTTCAGATCTAACGGCCTCACAGCCAATGAATCAGGAAGGCTAATAGATTTTCTCAGGGATGTGATGGAATCAATGGATAAGGAGGAAATGGAAATAACAACGCATTTCCAAAGGAAAAGAAGAGTGAGAGACAACATGACCAAGAAAATGGTCACACAAAGGACAATAGGAAAGAAGAAACAGAGGCTAAATAAAAAGAGCTATCTAATAAGAGCATTGACACTGAACACGATGACAAAAGAYGCCGAAAGAGGCAAATTAAAAAGAAGGGCAATTGCGACACCTGGAATGCAAATCAGAGGGTTTGTGTACTTTGTTGAAACATTAGCGAGGAGCATTTGTGATAAGCTTGAACAATCTGGACTCCCAGTTGGGGGCAATGAAAAGAAGGCTAAACTGGCAAATGTCGTGAGAAAAATGATGACCAATTCGCAGGACACAGAGCTCTCTTTCACAATCACTGGAGACAACACCAAATGGAATGAAAATCAGAACCCTAGGATGTTTCTGGCAATGATAACATATATAACAAGGAACCAACCTGAATGGTTCAGGAATGTCTTAAGCATTGCACCTATAATGTTCTCAAATAAAATGGCAAGACTAGGGAAAGGGTACATGTTCGAAAGTAAGAACATGAAGCTTCGAACACAAATACCAGCAGAAATGCTAGCAAGCATTGATATGAAGTACTTCAATGAGTCAACAAGAAAGAAAATAGAGAAGATAAGACCTCTTCTAATAGATGATACAGCCTCATTAAGCCCAGGAATGATGATGGGCATGTTCAATATGCTGAGTACAGTTTTGGGAGTTTCGATTCTAAATCTAGGACAAAGGAGGTACACCAAAACAACATACTGGTGGGACGGACTCCAATCCTCTGATGACTTTGCTCTCATAGTGAATGCTCCGAATCATGAGGGAATACAAGCAGGGGTAGACAGATTCTATAGAACCTGCAAACTGGTTGGAATCAACATGAGCAAAAAGAAGTCCTACATAAACAGGACAGGAACATTTGAATTCACAAGTTTTTTCTACCGCTATGGATTTGTAGCCAACTTCAGTATGGAGTTGCCCAGCTTTGGAGTGTCTGGGATCAATGAATCTGCAGACATGAGCATTGGAGTAACAGTGATAAAGAACAACATGATCAACAATGATCTTGGACCAGCAACAGCTCAAATGGCTCTTCAGCTATTCATCAAGGATTACAGATACACATACCGATGTCACAGAGGAGACACACAAATTCAGACAAGGAGGTCATTCGAGCTGAAGAAGTTGTGGGAACAGACCCGCTCAAAAGCAGGACTGCTGGTCTCAGATGGAGGACCAAATCTATACAATATTCGGAATCTTCACATTCCAGAAGTCTGCTTGAAATGGGAGCTAATGGACGAAGACTATCAGGGAAGGCTTTGTAATCCCCTGAATCCGTTTGTCAGCCACAAGGAAATAGAGTCTGTGAACAACGCTGTGGTGATGCCAGCTCATGGCCCGGCCAAGAGCATGGAATATGATGCTGTTGCCACCACTCACTCCTGGATACCGAAGAGGAACCGCTCCATTCTCAATACAAGCCAAAGGGGAATCCTTGAAGACGAACAGATGTATCAAAAGTGCTGCAATCTGTTCGAAAAATTCTTCCCTAGCAGTTCATACAGGAGGCCAGTTGGAATTTCCAGCATGGTGGAGGCCATGGTTTCTAGGGCCCGAATTGACGCACGAATTGACTTCGAATCTGGACGGATTAAGAAGGAGGAGTTTGCTGAGATCATGAAGATCTGTTCCACCATTGAAGAGCTCAGACGGCAGAAATAG</t>
         </is>
       </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Flu-0406|A_PA</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
+      <c r="FA1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0406|A_PA</t>
+        </is>
+      </c>
+      <c r="FB1" t="inlineStr">
         <is>
           <t>ATGGAAGACTTTGTGCGACAATGCTTCAATCCAATGATTGTCGAGCTTGCGGAAAAAGCAATGAAAGAATATGGGGAAGATCCGAAAATCGAGACAAACAAATTTGCCGCAATATGCACACACTTAGAAGTCTGTTTCATGTATTCGGATTTCCATTTTATTGATGAACGAGGCGAATCAATGATTGTAGAATCTGGCGATCCAAATGCATTATTGAAACACCGATTTGAGATAATCGAAGGTAGAGACAGAGCAATGGCCTGGACAGTGGTGAATAGTATCTGCAACACCACAGGGGTCGAAAAGCCCAAATTCCTCCCTGATTTGTATGACTACAAAGAGAACCGATTCATTGAAATTGGGGTAACGCGAAGGGAAGTTCACATATACTATTTAGAAAAAGCCAACAAGATAAAATCAGAGAAAACACATATTCACATATTCTCATTCACTGGAGAGGAAATGGCCACCAAGGCGGACTACTCCCTTGATGAAGAGAGCAGAGCAAGAATAAAAACCAGACTGTTCACTATAAGACAAGAAATGGCCAGTAGAGGTCTATGGGATTCCTTTCGTCAATCCGAGAGAGGCGAAGAGACAATTGAAGAAAGATTTGAAATCACAGGAACCATGCGCAGGCTTGCCGACCAAAGTCTTCCACCGAACTTCTCCAGCCTTGAAAACTTTAGAGCCTATGTGGATGGATTCGAACCGAACGGCTGCATTGAGGGCAAACTTTCTCAAATGTCAAAAGAAGTGAACGCCAGAATTGAGCCATTTCTGAAGACAACACCACGCCCTCTCAGATTACCTGATGGGCCTCCCTGTTCTCAGCGATCGAAGTTCTTGCTGATGGATGCCCTTAAGTTGAGCATCGAAGACCCTAGCCATGAGGGGGAAGGCATACCGCTGTATGATGCAATCAAATGCATGAAGACATTTTTTGGCTGGAAAGAGCCCAACATCGTAAAGCCGCATGAGAAAGGCATAAACCCTAATTACCTCCTGGCTTGGAAGCAGGTGCTGGCAGAACTTCAAGACATTGAAAATGAGGAGAAAATTCCAAAAACAAGGAACATGAAGAAAACAAGCCAATTGAAGTGGGCACTTGGTGAGAACATGGCTCCAGAAAAAGTGGACTTTGAGGACTGCAAAGATGTTAGCGATCTAAGACAGTACGACAGTGACGAACCAGAGTCTAGATCACTAGCAAGCTGGATTCAGAGTGAATTCAACAAGGCATGCGAACTGACAGATTCGAGTTGGATTGAACTTGATGAGATAGGGGAAGACGTTGCTCCAATCGAACACATTGCGAGTGTGAGGAGGAACTATTTCACAGCGGAGGTATCCCATTGCAGGGCCACTGAATACATAATGAAGGGAGTATACATAAACACAGCCCTATTGAATGCATCCTGTGCAGCCATGGATGACTTCCAATTGATTCCAATGATAAGTAAGTGCAGAACTAAAGAAGGAAGACGGAAGACAAATCTGTATGGATTCATTATAAAAGGAAGATCCCATTTGAGGAATGACACCGATGTGGTAAACTTTGTGAGCATGGAATTCTCTCTAACTGACCCAAGGCTAGAGCCACACAAATGGGAAAAGTACTGTGTTCTTGAGATAGGAGACATGCTCCTACGGACTGCAATAGGCCAAGTGTCGAGGCCCATGTTCCTGTATGTGAGAACCAATGGAACTTCCAAGATCAAAATGAAATGGGGCATGGAGATGAGGCGATGCCTTCTTCAGTCCCTTCAACAAATTGAGAGCATGATTGAGGCCGAATCTTCTGTCAAAGAGAAGGACATGTCCAAGGAATTCTTTGAAAACAAATCAGAAACATGGCCAATTGGGGAATCACCCAAAGGGGTGGAGGAAGGCTCTATTGGGAAAGTGTGCAGAACATTGCTAGCAAAGTCTGTGTTCAACAGCCTATATGCATCTCCACAACTCGAGGGGTTTTCAGCTGAATCAAGAAAATTGCTTCTCATTGTTCAGGCACTTAGGGACAACCTGGAACCTGGAACCTTCGATCTTGGGGGGCTATATGAAGCAATTGAGGAGTGCCTGATTAACGATCCCTGGGTTTTGCTTAATGCATCTTGGTTCAACTCCTTCCTCACACATGCACTGAAATAG</t>
         </is>
       </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Flu-0406|A_HA</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
+      <c r="FC1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0406|A_HA</t>
+        </is>
+      </c>
+      <c r="FD1" t="inlineStr">
         <is>
           <t>ATGGAGAACATAGTACTACTTCTTGCAATAGTTAGCCTTGTTAAAAGTGATCAGATTTGCATTGGTTACCATGCAAACAATTCGACAGAGCAAGTTGACACGATAATGGAAAAGAACGTCACTGTTACACATGCCCAAGACATACTGGAAAAAACACACAACGGAAAGCTCTGTGATTTAAATGGGGTGAAGCCACTGATTTTAAAGGATTGTAGTGTAGCTGGATGGCTCCTCGGAAACCCAATGTGCGACGAATTCATCAGAGTGCCGGAATGGTCATACATAGTGGAGCGGGCTAACCCAGCTAATGACCTCTGTTACCCAGGGAGCCTCAATGACTATGAAGAACTGAAACACATGTTGAGCAGAATAAATCATTTTGAGAAGATTCAGATCATTCCCAAGAGTTCCTGGCCAAATCATGAAACATCACTAGGGGTGAGCGCAGCTTGTCCATACCAGGGAGCGCCCTCCTTTTTCAGAAATGTGGTGTGGCTTATCAAAAAGAACGATGCATACCCAACAATAAAGATAAGCTACAATAATACTAATCGGGAAGATCTCTTGATACTTTGGGGGATTCATCATTCCAACAATGCAAAAGAACAGACAAATCTCTACAAAAACCCAACCACCTACATTTCAGTTGGAACATCAACTTTAAACCAGAGGTTGGCACCAAAAATAGCTACTAGATCCCAAGTAAACGGGCAACGTGGAAGAATGGACTTCTTCTGGACAATCTTAAAACCAGATGATGCAATCCATTTCGAGAGTAACGGAAATTTCATTGCTCCAGAATATGCATACAAAATTGTCAAGAAAGGGGACTCAACAGTTATGAAAAGTGGAGTGGAATATGGCCACTGCAACACCAAATGTCAAACCCCAGTAGGTGCGATAAATTCTAGTATGCCATTCCACAACATACATCCTCTCACCATCGGGGAATGTCCCAAATACGTGAAGTCAAACAAGTTGGTCCTTGCGACTGGGCTCAGAAATAGTCCTCTAAGAGAAAAGAGAAGAAAAAGAGGTCTGTTTGGGGCGATAGCAGGGTTTATAGAGGGAGGATGGCAGGGAATGGTTGATGGTTGGTATGGATACCATCATAGCAATGAGCAGGGGAGTGGGTACGCTGCGGACAAAGAATCCACCCAAAAGGCAATAGATGGAATTACCAATAAGGTCAACTCAATCATTGACAAAATGAACACTCAATTTGAGGCAGTTGGAAGGGAGTTTAACAACTTAGAAAGGAGGATAGAGAATTTGAACAAGAAAATGGAAGACGGATTCCTAGATGTCTGGACCTATAATGCTGAACTTCTAGTCCTCATGGAAAACGAGAGGACTCTAGACTTCCATGATTCAAATGTCAAGAACCTTTACGACAAAGTCAGATTACAGCTTAGGGATAATGCAAAGGAGCTGGGTAACGGCTGTTTCGAATTCTATCACAAATGTGATAATGAATGTATGGAAAGTGTGAGAAATGGGACGTATGACTACCCTCAGTATTCAGAAGAAGCAAGATTAAAAAGAGAAGAAATAAGCGGAGTGAAATTAGAATCAGTAGGAACTTACCAGATACTGTCAATTTATTCAACAGCGGCAAGTTCCCTAGCACTGGCAATCATGATGGCTGGTCTATCTTTATGGATGTGCTCCAATGGGTCGTTACAATGCAGAATTTGCATTTAG</t>
         </is>
       </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Flu-0406|A_NP</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
+      <c r="FE1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0406|A_NP</t>
+        </is>
+      </c>
+      <c r="FF1" t="inlineStr">
         <is>
           <t>ATGGCGTCTCAAGGCACCAAACGATCCTATGAACAAATGGAAACTGGTGGGGAACGCCAGAATGCCACTGAAATCAGAGCATCTGTTGGAAGAATGGTTGGCGGAATCGGGAGATTCTACATACAGATGTGTACTGAACTCAAACTCAGTGATTACGAAGGGAGGCTGATCCAAAACAGCATAACCATAGAAAGGATGGTTCTCTCGGCATTTGATGAGAGGAGGAACAAGTACCTGGAGGAACATCCCAGTGCCGGGAAGGATCCCAAGAAGACTGGAGGTCCAATCTACAGGAGGAGAGATGGCAAATGGGTGAGAGAGTTGATCCTCTACGACAAAGAAGAGATCAGAAGAATTTGGCGTCAAGCTAATAATGGAGAGGATGCAACTGCTGGTCTCACTCACTTGATGATTTGGCATTCCAATCTGAATGATGCCACATACCAGAGAACAAGGGCACTTGTGCGTACTGGAATGGACCCTAGAATGTGCTCTCTGATGCAAGGCTCAACCCTCCCTAGGAGATCAGGGGCTGCTGGAGCAGCAGTGAAAGGAGTTGGAACAATGGTGATGGAACTAATTCGAATGATCAAACGAGGGATCAATGATCGGAATTTCTGGAGAGGCGAAAACGGTCGGAGAACCAGGATTGCCTACGAGAGAATGTGCAACATTCTCAAGGGAAAGCTCCAAACAGCAGCACAACGGGCAATGATGGACCAAGTGAGAGAAAGCCGGAATCCTGGGAATGCTGAAATTGAAGATCTCATCTTTCTCGCACGATCTGCTCTCATCCTGAGGGGATCAGTGGCTCATAAGTCCTGTCTGCCTGCTTGCGTATATGGACTTGCTGTAGCCAGTGGATATGACTTTGAAAGAGAGGGATATTCTCTAGTCGGAATTGATCCTTTCCGTCTGCTCCAAAACAGCCAAGCCTTCAGTCTCATCAGACCGAACGAAAATCCAGCTCATAAAAGTCAGCTGGTATGGATGGCATGCCACTCTGCGGCATTTGAGGATCTGAGAGTGTCAAGCTTCATCAGAGGGACAAGAGTAGTCCCAAGAGGACAACTGTCCACCAGAGGAGTTCAGATTGCTTCAAATGAAAACATGGAGACAATGGACTCCAGTACTCTTGAACTGAGGAGCAGATATTGGGCTATAAGAACAAGAAGTGGAGGAAACACTAACCAACAGAGAGCATCTGCAGGACAAATCAGCGTACAGCCCACATTCTCTGTACAAAGAAACCTCCCATTCGAGAGAGCAACCATCATGGCAGCATTTACGGGAAACACTGAAGGCAGAACTTCAGATATGAGAACTGAGATCATAAGGATGATGGAAAATGCCAGACCTGAAGATGTGTCTTTCCAGGGGCGGGGAGTCTTCGAGCTCTCGGACGAAAAGGCAACGAACCCGATCGTGCCTTCCTTTGACATGAGTAATGAAGGATCTTATTTCTTCGGAGACAATGCAGAGGAGTATGACAATTAA</t>
         </is>
       </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Flu-0406|A_NA</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
+      <c r="FG1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0406|A_NA</t>
+        </is>
+      </c>
+      <c r="FH1" t="inlineStr">
         <is>
           <t>ATGAATCCAAATCAAAAGATAACAACCATTGGATCAATCTGTATGGTAATTGGGATAGTCAGCTTGATGCTGCAAATTGGGAACATAATCTCAATATGGGTTAGCCATTCAATCCAAACAGGGAATCAATACCAGCCTGAACCATGCAATCAAAGCATCATTACCTATGAGAACAACACCTGGGTAAATCAGACGTATGTCAACATCAGCAATACCAATTTTCTTGCTGAGCAAGCTGTTACTTCGGTAACATTAGCGGGCAATTCATCTCTTTGCCCTATTAGTGGGTGGGCAATATACAGTAAGGACAACGGTATAAGAATTGGGTCCAAGGGGAATGTGTTTGTTATAAGAGAACCGTTCATCTCATGCTCCCACTTGGAATGCAGAGCCTTTTTCCTGACCCAGGGAGCTCTGCTGAATGACAAACATTCTAATGGGACAGTTAAGGATAGAAGCCCTTATAGAACTTTGATGAGTTGTCCCGTGGGTGAGGCTCCTTCCCCGTATAATTCAAGATTTGAGTCTGTTGCTTGGTCGGCAAGTGCTTGTCATGATGGCATCAGTTGGTTGACAATCGGTATTTCTGGTCCAGACAATGGAGCTGTGGCTGTATTGAAGTACAATGGCATAATAACGGATACTATCAAGAGTTGGAGAAACAACATTTTAAGAACTCAAGAATCTGAATGTGCTTGCGTAAATGGCTCTTGCTTCACCGTAATGACTGATGGACCAAGCAATGGGCAGGCCTCATATAAAATCTTCAAGATAGAGAAAGGGAAAGTTGTCAAGTCAGTTGAGATGAATGCCCCTAATTACCACTACGAGGAATGCTCCTGTTATCCTGATGCGGGTGATATTATGTGTGTGTGCAGGGACAATTGGCATGGCTCAAATCGGCCGTGGGTATCTTTTAATCAAAATCTGGAGTATCAAATAGGATATATATGCAGTGGGGTTTTCGGGGACAATCCCCGCCCCAATGATGGAACAGGCAGTTGCAGTCCAATGCCCTCTAATGGGGCATATGGGGTAAAAGGGTTTTCATTTAAGTACGGTAATGGGGTTTGGATCGGAAGAACAAAAAGCACTAGTTCCAGAAGCGGCTTTGAGATGATTTGGGATCCGAATGGGTGGACTGAGACGGACAGTAGTTTCTCAGTGAAGCAAGACATTGTAGAAATAACTGACTGGTCAGGATATAGTGGGAGTTTTGTCCAGCATCCAGAACTGACAGGATTAGATTGCATGAGGCCTTGTTTCTGGGTTGAGCTAATCAGAGGGAAGCCCAAAGAGAACACAATTTGGACTAGCGGGAGCAGCATATCCTTTTGTGGTGTAAATAGTGACACTGTGGGTTGGTCTTGGCCAGACGGTGCTGAGTTGCCATTCACCATTGACAAGTAG</t>
         </is>
       </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Flu-0406|A_MP</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
+      <c r="FI1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0406|A_MP</t>
+        </is>
+      </c>
+      <c r="FJ1" t="inlineStr">
         <is>
           <t>ATGAGTCTTCTAACCGAGGTCGAAACGTACGTTCTCTCTATCGTCCCGTCGGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTTGAAGATGTCTTTGCAGGGAAGAACACCGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATCCTGTCACCTCTGACTAAGGGGATTTTGGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCTCTAAGTGGAACTGGAGACCCAAACAACATGGACAGGGCAGTCAAGTTGTACAGGAAACTAAAGAGAGAGATAACATTCCATGGTGCTAAAGAAGTTGCACTCAGTTACTCAACCGGTGCACTTGCCAGTTGTATGGGTCTCATATACAACAGGATGGGGACGGTGACCGCAGAAGTGGCATTGGGCCTAGTGTGTGCCACCTGTGAGCAGATTGCTGATTCACAGCATCGGTCTCACAGACAGATAGCTACCACCACCAACCCACTAATCAGACATGAAAACAGAATGGTTTTGGCCAGTACTACAGCTAAGGCTATGGAGCAGATGGCTGGATCGAGTGAGCAAGCAGTGGAAGCCATGGAGGTTGCTAGTCAGGCTAGGCAGATGGTGCAGGCGATGAGGACCATTGGAACTCATCCTAGCTCCAGTGCCGGTCTGAGAGATGATCTCCTTGAAAATTTGCAGGCCTACCAAAAACGGATGGGAGTGCAACTGCAGCGATTCAAGTGATCCTCTCGTTATTGCCGCAAGTATCATTGGGATCTTGCACTTGATATTGTGGATTCTTGATCGCCTTTTCTTCAAATGCGTTTATCGTCGCCTTAAATACGGTTTGAAAGGAGGGCCTTCTACGGAAGGAGTACCTGAGTCCATGAGGGAAGAGTACCGGCAGGAACAGCAGAGTGCTGTGGATGTTGACGATGGTCATTTTGTCAACATAGAGCTGGAGTAA</t>
         </is>
       </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Flu-0406|A_NS</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
+      <c r="FK1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0406|A_NS</t>
+        </is>
+      </c>
+      <c r="FL1" t="inlineStr">
         <is>
           <t>ATGGATTCCAACACTGTGTCAAGCTTTCAGGTAGACTGCTTTCTTTGGCATGTCCGCAAACGATTTGCAGACCAAGAACTGGGTGATGCCCCATTCCTTGACCGGCTCCGCCGAGACCAGAAGTCTCTAAGAGGAAGAAGCAGCACTCTTGGTCTGGACATCGAGACGGCCACTCGTGCTGGAAAGCAGATAGTGGAGAGGATTCTGGAGGAAGAATCCGACGAGGCACTCAAAATGACTATTGCCTCTGTGTCTGCTCCACGCTACCTAACTGACATGACTCTTGAAGAGATGTCAAGAGACTGGTTCATGCTCATGCCCAAGCAAAAAATGGCAGGCTCCCTCAGTATCAAAATGGACCAGGCGATTATGGATAAGAAAATCATACTGAAGGCAAACTTCAGTGTGATCTTCAATCGGCTGGAGACACTAATACTACTCAGAGCTTTCACTGAAGAAGGAGCAATTGTCGGCGAAATTTCACCATTGCCTTCTCTTCCAGGACATACTGATGAGGATGTCAAAAATGCAATTGGGGTCCTCATCGGAGGACTTGAATGGAATGATAACACAGTTCGAGTCTCTGAAACTTTACAGAGATTCGCTTGGAGAAGCAGTAATGAGGATGGGAGATCTCCACTCCCTCCAAAGCAGAAACGGAAAATGGAGAGAACAATTGAGTCAGAAGTTTGAAGAAATAAGGTGGCTGATTGRAGAAGTTCGACACAGACTAAAGATCACAGAAAATAGTTTTGAACAAATAACATTTATGCAAGCCTTACAACTACTGCTTGAAGTGGAGCAAGAGATAAGAACTTTCTCGTTTCAGCTTATTTAA</t>
         </is>

--- a/gisaid_batch_uploader_mira_batch_01.xlsx
+++ b/gisaid_batch_uploader_mira_batch_01.xlsx
@@ -3567,7 +3567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FL1"/>
+  <dimension ref="A1:A168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3576,837 +3576,1171 @@
           <t>&gt;Flu-0008|A_NS</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
         <is>
           <t>NNGGATTCCAACACTGTGTCAAGCTTNCAGGTAGACTGCTTTCTTTGGCATGTCCGCAAACGATTTGCAGACCAAGAACTGGGTGATGCCCCATTCCTTGACCGGCTNCGCCGAGACCAGAAGTCTCTNAGAGGAAGAGGCAGCACTCTTGGTCTGGACATCGAGACGGCCACTCGTGCTGGAAAGCAGATAGTGGAGAGGATTCTGGAGGAAGAATCCGACGAGGCACTCAAAATGACTATTGCCTCTGTGCCTGCTCCACGCTACCTAACTGACATGACTCTTGAAGAGATGTCAAGAGACTGGTTCATGCTCATGCCCAAGCAAAAAGTGGCAGGCTCCCTCTGTATCAGAATGGACCAGGCGATTATGGATAAGAACATCATACTGAAGGCAAACTTCAGTGTGATCTTCAATCGGCTGGAGACACTAATACTACTCAGAGCTTTCACTGAAGAGGGAGCAATTGTNGGCGAAATTTCACCATTGCCTTCTCTTCCAGGACATACTGATGAGGATGTCAAAAATGCAATTGGGGTCCTCATCGGAGGACTTGAATGGAATGATAACACAGTTCGAGTCTCTGAAATTTTACAGAGATTCGCTTGGAGAAGCAGTAATGAGGATGGGAGACCTCCACTCCCTCCAAAGCAGAAACGGAAAATGGAGAGAACAATTGAGTCAGAAGTTTGAAGAAATAAGGTGGCTGATTGAAGAGGTGCGACACAGANTAAAGATCACAGAAAATAGTTTTGAACAAATAACATTTATGCAAGCCTTACAACTACTGCTTGAAGTGGAGCAAGAGATACGAACTTTCTCGTTTCAGCTTATTTAA</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>&gt;Flu-0009|A_NP</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>ATGGCGTCTCAAGGCACCAAACGATCCTATGAACAAATGGAAACTGGTGGGGAACGCCAGAATGCCACTGAAATCAGAGCATCTGTTGGAAGAATGGTTGGCGGAATAGGAAGATTCTACATACAGATGTGCACTGAGCTCAAACTCAGTGATTACGAAGGGAGGCTGATCCAAAACAGCATAACCATAGAAAGGATGGTTCTCTCGGCATTTGATGAGAGGAGGAACAAGTACCTGGAGGAACATCCCAGTGCCGGGAAGGATCCCAAGAAGACTGGAGGTCCAATCTACAGGAGGAGAGATGGCAAATGGGTGAGAGAGTTGATCCTCTACGACAAAGAAGAGATCAGAAGAATTTGGCGTCAAGCTAATAATGGAGAGGATGCAACTGCTGGTCTCACTCATTTGATGATTTGGCATTCCAATCTGAATGATGCAACATACCAGAGAACAAGGGCACTTGTGCGTACTGGAATGGACCCTAGRATGTGCTCTCTGATGCAAGGCTCAACCCTCCCTAGGAGATCCGGGGCTGCTGGAGCAGCAGTGAAAGGAGTTGGAACAATGGTGATGGAACTAATTCGAATGATCAAACGAGGGATCAATGATCGGAATTTCTGGAGAGGCGAAAACGGTCGGAGAACCAGGATTGCCTACGAGAGAATGTGCAACATCCTCAAGGGAAAGTTCCAAACAGCAGCACAACGGGCAATGATGGACCAAGTGAGAGAAAGCCGGAATCCTGGGAATGCTGAAATTGAAGATCTCATCTTTCTCGCACSATCTGCTCTCATCCTGAGGGGATCAGTGGCTCATAAGTCCTGTCTGCCTGCTTGCGTATATGGACTTGCTGTAGCCAGTGGATATGACTTTGAAAGAGAGGGATATTCTCTAGTCGGAATTGATCCTTTCCGTCTGCTCCAAAACAGCCAAGTCTTCAGTCTCATCAGACCGAACGAAAATCCAGCTCATAAAAGTCAGCTGGTATGGATGGCATGCCACTCTGCGGCATTTGAGGATCTGAGAGTTTCAAGCTTCATCAGAGGGACAAGAGTAGTCCCAAGAGGACAACTGTCCACCAGAGGAGTTCAGATTGCTTCAAATGAAAACATGGAGACAATGGACTCCAGTACTCTTGAACTGAGGAGCAGRTACTGGGCTATAAGAACAAGAAGTGGAGGAAACACTAACCAACAGAGAGCATCTGCAGGACAAATCAGCGTACAGCCCACATTCTCTGTGCAAAGAAACCTCCCATTCGAGAGAGCAACCATCATGGCAGCATTTACGGGAAACACTGAAGGCAGAACTTCAGACATGAGAACTGAGATCATAAGGATGATGGAAAATGCCAGACCTGAAGATGTGTCTTTCCAGGGGCGGGGAGTCTTCGAGCTCTCGGACGAAAAGGCAACGAACCCGATCGTGCCTTCCTTTGACATGAGTAATGAAGGATCTTATTTCTTCGGAGACAATGCAGAGGAGTATGACAATTAA</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>&gt;Flu-0009|A_NA</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>ATGAATCCAAATCAAAAGATAACAACCATTGGATCAATCTGTATGGTAATTGGGACAGTCAGCTTGATGCTGCAAATTGGGAACATAATCTCAATATGGGTTAGCCATTCAATCCAAACAGGGAATCAATACCAGCCTGAACCATGCAATCAAAGCGTAATTACCTATGAGAACAACACCTGGGTAAATCAGACGTATGTCAACATTAGCAATACCAATTTTCTTGCTGAGCAGGCTGTTACTTCGGTAACATTAGCGGGCAATTCATCTCTTTGCCCTATTAGTGGGTGGGCAATATACAGTAAGGACAACGGTATAAGAATTGGGTCCAAGGGGGATGTGTTTGTTATAAGAGAACCGTTCATCTCATGCTCCCACTTGGAATGCAGAACCTTTTTCCTGACCCAGGGAGCTCTGCTGAATGACAAACATTCTAATGGGACAGTTAAGGATAGAAGCCCTTATAGAACTTTGATGAGTTGTCCCGTGGGTGAGGCTCCTTCCCCGTACAATTCAAGATTTGAGTCTGTTGCTTGGTCGGCAAGTGCTTGTCATGATGGCATCAGTTGGTTGACAATCGGTATTTCTGGTCCAGACAATGGAGCTGTGGCTGTATTGAAGTACAATGGCATAATAACGGATACTATCAAGAGTTGGAGAAACAACATTTTGAGAACTCAAGAATCTGAATGTGCTTGTGTAAATGGCTCTTGCTTCACCGTAATGACTGATGGACCAAGCAATGGGCAGGCCTCATATAAAATCTTCAAGATAGAGAAAGGGAAAGTTGTCAAATCAGTTGAATTGAATGCCCCTAATTACCACTACGAGGAATGTTCCTGTTATCCTGATGCGGGTGATATTATATGTGTGTGCAGGGACAATTGGCATGGCTCAAACCGGCCGTGGGTATCTTTTAATCAAAATCTGGAGTATCAAATAGGATATATATGCAGTGGGGTTTTCGGGGACAATCCCCGCCCCAATGATGGAACAGGCAGTTGCAGTCCAATGTCCTCTAATGGGGCATATGGGGTAAAAGGGTTCTCATTTAAGTACGGTAATGGGGTTTGGATCGGAAGAACAAAAGGCACTAGTTCCAGAAGCGGCTTTGAGATGATTTGGGACCCGAATGGGTGGACTGAGACGGACAGTAGTTTCTCAGTGAAGCAAGACATTGTAGAAATAACTGACTGGTCAGGATATAGTGGGAGTTTTGTCCAGCATCCAGAACTGACAGGATTAGATTGCATGAGGCCTTGTTTCTGGGTTGAGCTAATTAGAGGGAGGCCCAAAGAGAACACAATTTGGACTAGCGGGAGCAGCATATCCTTTTGTGGTGTAAATAGTGACACTGTGGGTTGGTCTTGGCCAGACGGTGCTGAGTTGCCATTCACCATTGACAAGTAG</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>&gt;Flu-0009|A_MP</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>ATGAGTCTTCTAACCGAGGTCGAAACGTACGTTCTCTCTATCGTCCCGTCGGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTTGAAGATGTTTTTGCAGGGAAGAACACCGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATACTGTCACCTCTGACTAAGGGGATTTTGGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCTCTAAGTGGAAATGGAGACCCAAACAACATGGACAGGGCAGTCAAGTTGTACAGGAAATTGAAGAGAGAAATAACATTTCATGGGGCTAAAGAAGTTGCACTCAGTTACTCAACCGGTGCACTTGCCAGTTGTATGGGTCTCATATACAACAGGATGGGGACGGTGACCGCAGAAGTGGCATTGGGCCTAGTGTGTGCCACCTGTGAGCAGATTGCTGATTCACAGCATCGGTCTCACAGACAGATAGCTACCACCACCAACCCACTAATCAGACATGAAAACAGAATGGTTTTGGCCAGTACTACAGCTAAGGCTATGGAGCAGATGGCTGGATCGAGTGAGCAAGCAGTGGAAGCCATGGAGGTTGCTAGTCAGGCTAGGCAAATGGTGCAGGCGATGAGGACCATTGGAACTCATCCTAGCTCCAGTGCCGGTCTGAGAGATGATCTCCTTGAAAATTTGCAGGCCTACCAAAAACGAATGGGAGTGCAACTGCAGCGATTCAAGTGATCCTCTCGTTATTGCCGCAAGTATCATTGGGATCTTGCACTTGATATTGTGGATTCTTGATCGCCTTTTCTTCAAATGCGTTTATCGTCGCCTTAAATACGGTTTGAAAGGAGGGCCTTCTACGGAAGGAGTACCTGAGTCCATGAGGGAAGAGTACCGGCAGGAACAGCAGAGTGCTGTGGATGTTGACGATGGTCATTTTGTCAACATAGAGATGGAGTAA</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>&gt;Flu-0009|A_NS</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>ATGGATTCCAACACTGTGTCAAGCTTTCAGGTAGACTGCTTTCTTTGGCATGTCCGCAAACGATTTGCAGACCAAGAACTGGGTGATGCCCCATTCCTTGACCGGCTCCGCCGAGACCAGAAGTCTCTAAGAGGAAGAGGCAGCACTCTTGGTCTGGACATCGAGACGGCCACTCGTGCTGGAAAGCAGATAGTGGAGAGGATTCTGGAGGAAGAATCCGACGAGGCACTCAAAATGACTATTGCCTCTGTGCCTGCTCCACGCTACCTAACTGACATGACTCTTGAAGAGATGTCAAGAGATTGGTTCATGCTCATGCCCAAGCAAAAAGTGGCAGGCTCCCTCTGTATCAGAATGGACCAGGCGATTATGGATAAGAACATCATACTGAAGGCAAACTTCAGTGTGATCTTCAATCGGCTGGAGACACTAATACTACTCAGAGCTTTCACTGAAGAGGGAGCAATTGTCGGCGAAATTTCACCATTGCCTTCTCTTCCAGGACATACTGATGAGGATGTCAAAAATGCAATTGGGGTCCTCATCGGAGGACTTGAATGGAATGATAACACAGTTCGAGTCTCTGAAATTTTACAGAGATTCGCTTGGAGAAGCAGTAATGAGGATGGGAGACCTCCACTCCCTCCAAAGCAGAAACGGAAAATGGAGAGAACAATTGAGTCAGAAGTTTGAAGAAATAAGGTGGCTGATTGAAGAGGTGCGACACAGATTAAAGATCACAGAAAATAGTTTTGAACAAATAACATTTATGCAAGCCTTACAACTACTGCTTGAAGTGGAGCAAGAGATACGAACTTTCTCGTTTCAGCTTATTTAA</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>&gt;Flu-0011|A_MP</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>ATGAGTCTTCTAACCGAGGTCGAAACGTACGTTCTCTCTATCGTCCCGTCGGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTTGAAGATGTCTTTGCAGGGAAGAACACCGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATACTGTCACCTCTGACTAAGGGGATTTTGGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCTCTAAGTGGAAATGGAGACCCAAACAACATGGACAGGGCAGTCAAGTTGTACAGGAAACTGAAGAGAGAAATAACATTCCATGGGGCTAAAGAAGTTGCACTCAGTTACTCAACCGGTGCACTTGCCAGTTGTATGGGTCTCATATACAACAGGATGGGGACGGTGACCGCAGAAGTGGCATTGGGCCTAGTGTGTGCCACCTGTGAGCAGATTGCTGATTCACAGCATCGGTCTCACAGACAGATAGCTACCACCACCAACCCACTAATCAGACATGAAAACAGAATGGTTTTGGCCAGTACTACAGCTAAGGCTATGGAGCAGATGGCTGGATCGAGTGAGCAAGCAGCGGAAGCCATGGAGGTTGCTAGTCAGGCTAGGCAAATGGTGCAGGCGATGAGGACCATTGGAACTCATCCTAGCTCCAGTGCCGGTCTGAGAGATGATCTCCTTGAAAATTTGCAGGCCTACCAAAAACGAATGGGAGTGCAACTGCAGCGATTCAAGTGATCCTCTCGTTATTGCCGCAAGTATCATTGGGATCTTGCACTTGATATTGTGGATTCTTGATCGCCTTTTCTTCAAATGCGTTTATCGTCGCCTTAAATACGGTTTGAAAGGAGGGCCTTCTACGGAAGGAGTACCTGAGTCCATGAGGGAAGAGTACCGGCAGGAACAGCAGAGTGCTGTGGATGTTGACGATGGTCATTTTGTCAACATAGAGATGGAGTAA</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>&gt;Flu-0011|A_NS</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>ATGGATTCCAACACTGTGTCAAGCTTTCAGGTAGACTGCTTTCTTTGGCATGTCCGCAAACGATTTGCAGACCAAGAACTGGGTGATGCCCCATTCCTTGACCGGCTCCGCCGAGACCAGAAGTCTCTAAGAGGAAGAGGCAGCACTCTTGGTCTGGACATCGAGACGGCCACTCGTGCTGGAAAGCAGATAGTGGAGAGGATTCTGGAGGAAGAATCCGACGAGGCACTCAAAATGACTATTGCCTCTGTGCCTGCTCCACGCTACCTAACTGACATGACTCTTGAAGAGATGTCAAGAGACTGGTTCATGCTCATGCCCAAGCAAAAAGTGGCAGGCTCCCTCTGTATCAGAATGGACCAGGCGATTATGGATAAGAACATCATACTGAAGGCAAACTTCAGTGTGATCTTCAATCGGCTGGAGACACTAATACTACTCAGAGCTTTCACTGAAGAGGGAGCAATTGTCGGCGAAATTTCACCATTGCCTTCTCTTCCAGGACATACTGATGAGGATGTCAAAAATGCAATTGGGGTCCTCATCGGAGGACTTGAATGGAATGATAACACAGTTCGAGTCTCTGAAATTTTACAGAGATTCGCTTGGAGAAGCAGTAATGAGGATGGGAGACCTCCACTCCCTCCAAAGCAGAAACGGAAAATGGAGAGAACAATTGAGTCAGAAGTTTGAAGAAATAAGGTGGCTGATTGAAGAGGTGCGACACAGACTAAAGATCACAGAAAATAGTTTTGAACAAATAACATTTATGCAAGCCTTACAACTACTGCTTGAAGTGGAGCAAGAGATACGAACTTTCTCGTTTCAGCTTATTTAA</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>&gt;Flu-0013|A_HA</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>ATGGAGAACATAGTACTACTTCTTGCAATAGTTAGCCTTGTTAAAAGTGACCAGATTTGCATTGGTTACCATGCAAACAATTCGACAGAGCAAGTTGACACGATAATGGAAAAGAACGTCACTGTTACACATGCCCAAGACATACTGGAAAAAACACACAACGGGAAGCTCTGTGATTTAAATGGGGTGAAGCCACTGATTTTAAAGGATTGTAGTGTAGCTGGATGGCTCCTCGGGAACCCAATGTGCGACGAATTCATCAGAGTGCCGGAATGGTCCTACATAGTGGAGCGAGCTAACCCAGCTAATGACCTCTGTTACCCAGGGAGCCTCAATGACTATGAAGAACTGAAACACATGTTGAGCAGAATAAATCATTTTGAGAAGATTCAGATCATTCCCAAGAGTTCCTGGCCAAATCATGAAACATCACTAGGGGTGAGCGCAGCTTGTCCATACCAGGGAGCGCCCTCCTTTTTCAGAAATGTGGTGTGGCTTATCAAAAAGAACGATGCATACCCAACAATAAAGATAAGCTACAATAATACTAATCGGGAAGATCTCTTGATACTGTGGGGGATTCATCATTCCAACARTGCAGAAGAGCAGACAAATCTCTACAAAAACCCAACCACCTACATTTCAGTTGGAACATCAACTTTAAACCAGAGGTTGGCACCAAAAATAGCTACTAGATCCCAAGTAAACGGGCAACGTGGAAGAATGGACTTCTTTTGGACAATCTTAAAACCAGATGATGCAATCCATTTCGAGAGTAACGGAAATTTCATTGCTCCAGAATATGCATACAAAATTGTCAAGAAAGGGGACTCAACAATTATGAAAAGTGGAGTGGAATATGGCCACTGCAACACCAAATGTCAAACCCCAGTAGGTGCTATAAATTCTAGTATGCCATTCCACAACATACATCCTCTCACCATTGGGGAATGCCCCAAATACGTGAAGTCAAACAAGTTGGTCCTTGCGACTGGGCTCAGAAATAGTCCTCTAAGAGAAAAGAGAAGAAAAAGAGGTCTGTTTGGGGCGATAGCAGGGTTTATAGAGGGAGGATGGCAGGGAATGGTTGATGGTTGGTATGGGTACCATCATAGCAATGAGCAGGGGAGTGGGTACGCTGCGGACAAAGAATCCACCCAAAAGGCAATAGATGGAGTTACCAATAAGGTCAACTCAATCATTGACAAAATGAACACTCAATTTGAGGCAGTTGGAAGGGAGTTTAATAACTTAGAAAGGAGGATAGAGAATTTGAACAAGAAAATGGAAGACGGATTCCTAGATGTCTGGACCTATAATGCTGAACTTCTAGTTCTCATGGAAAACGAGAGGACTCTAGATTTCCATGATTCAAATGTCAAGAACCTTTACGACAAAGTCAGATTACAGCTTAGGGATAATGCAAAGGAGCTGGGTAACGGCTGTTTCGAATTCTATCACAAATGTGATAATGAATGTATGGAAAGTGTGAGAAATGGGACGTATGACTACCCTCAGTATTCAGAAGAAGCAAGATTAAAAAGAGAAGAAATAAGCGGAGTGAAATTAGAATCAGTAGGAACTTACCAGATACTGTCAATTTATTCAACAGCGGCAAGTTCCCTAGCACTGGCAATCATGATGGCTGGTCTATCTTTATGGATGTGCTCCAATGGGTCGTTACAATGCAGAATTTGCATTTAG</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>&gt;Flu-0013|A_NP</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>ATGGCGTCTCAAGGCACCAAACGATCCTATGAACAAATGGAAACTGGTGGGGAACGCCAGAATGCCACTGAAATCAGAGCATCCGTTGGAAGAATGGTTGGCGGAATAGGAAGATTCTACATACAGATGTGCACTGAGCTCAAACTCAGTGATTACGAAGGGAGGCTGATCCAAAACAGCATAACCATAGAAAGGATGGTTCTCTCGGCATTTGATGAGAGGAGGAACAAGTACCTGGAGGAACATCCCAGTGCCGGGAAGGATCCCAAGAAGACTGGAGGTCCAATCTACAGGAGGAGAGATGGCAAATGGGTGAGAGAGTTGATCCTCTACGACAAAGAAGAGATCAGAAGAATTTGGCGTCAAGCTAATAATGGAGAGGATGCAACTGCTGGTCTCACTCATTTGATGATTTGGCATTCCAATCTGAATGATGCAACATACCAGAGAACAAGGGCACTTGTGCGTACTGGAATGGACCCTAGGATGTGCTCTCTGATGCAAGGCTCAACCCTCCCTAGGAGATCCGGGGCTGCTGGAGCAGCAGTGAAAGGAGTTGGAACAATGGTGATGGAACTAATTCGAATGATCAAACGAGGGATCAATGATCGGAATTTCTGGAGAGGCGAAAACGGTCGGAGAACCAGGATTGCCTACGAGAGAATGTGCAACATCCTCAAGGGAAAGTTCCAAACAGCAGCACAACGGGCAATGATGGACCAAGTGAGAGAAAGCCGGAATCCTGGGAATGCTGAAATTGAAGATCTCATCTTTCTCGCACSATCTGCTCTCATCCTGAGGGGATCAGTGGCTCATAAGTCCTGTCTGCCTGCTTGCGTATATGGACTTGCTGTAGCCAGTGGATATGACTTTGAAAGAGAGGGATATTCTCTAGTCGGAATTGATCCTTTCCGTCTGCTCCAAAACAGCCAAGTCTTCAGTCTCATCAGACCGAACGAAAATCCAGCTCATAAAAGTCAGCTGGTATGGATGGCATGCCACTCTGCGGCATTTGAGGATCTGAGAGTTTCAAGCTTCATCAGAGGGACAAGAGTAGTCCCAAGAGGACAACTGTCCACCAGAGGAGTTCAGATTGCTTCAAATGAAAACATGGAGACAATGGACTCCAGTACTCTTGAACTGAGGAGCAGATACTGGGCTATAAGAACAAGAAGTGGAGGAAACACTAACCAACAGAGAGCATCTGCAGGACAAATCAGCGTACAGCCCACATTCTCTGTGCAAAGAAACCTCCCATTCGAGAGAGCAACCATCATGGCAGCATTTACGGGAAACACTGAAGGCAGAACTTCAGACATGAGAACTGAGATCATAAGGATGATGGAAAATGCCAGACCTGAAGATGTGTCTTTCCAGGGGCGGGGAGTCTTCGAGCTCTCGGACGAAAAGGCAACGAACCCGATCGTGCCTTCCTTTGACATGAGTAATGAAGGATCTTATTTCTTCGGAGACAATGCAGAGGAGTATGACAATTAA</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>&gt;Flu-0013|A_NA</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>ATGAATCCAAATCAAAAGATAACAACCATTGGATCAATCTGTATGGTAATTGGGACAGTCAGCTTGATGCTGCAAATTGGGAACATAATCTCAATATGGGTTAGCCATTCAATCCAAACAGGGAATCAATACCAGCCTGAACCATGCAATCAAAGCATCATTACCTATGAGAACAACACCTGGGTAAATCAGACGTATGTCAACATCAGCAATACCAATTTTCTTGCTGAGCAGGCTGTTACTTCGGTAACATTAGCGGGCAATTCATCTCTTTGCCCTATTAGTGGGTGGGCAATATACAGTAAGGACAACGGTATAAGAATTGGGTCCAAGGGGGATGTGTTTGTTATAAGAGAACCGTTCATCTCATGCTCCCACTTGGAATGCAGAACCTTTTTCCTGACCCAGGGAGCTCTGCTGAATGACAAACATTCTAATGGGACAGTTAAGGATAGAAGCCCTTATAGAACTTTGATGAGTTGTCCCGTGGGTGAGGCTCCTTCCCCGTACAATTCAAGATTTGAGTCTGTTGCTTGGTCGGCAAGTGCTTGTCATGATGGCATCAGTTGGTTGACAATCGGTATTTCTGGTCCAGACAATGGAGCTGTGGCTGTATTGAAGTACAATGGCATAATAACGGATACTATCAAGAGTTGGAGAAACAACATTTTGAGAACTCAAGAATCTGAATGTGCTTGCGTAAATGGCTCTTGCTTCACCGTAATGACTGATGGACCAAGCAATGGGCAGGCCTCATATAAAATCTTCAAGATAGAGAAAGGGAAAGTTGTCAAATCAGTTGAATTGAATGCCCCTAATTACCACTACGAGGAATGTTCCTGTTATCCTGATGCGGGTGATATTATATGTGTGTGCAGGGACAATTGGCATGGCTCAAACCGGCCGTGGGTATCTTTTAATCAAAATCTGGAGTATCAAATAGGATATATATGCAGTGGGGTTTTCGGGGACAATCCCCGCCCCAATGATGGAACAGGCAGTTGCAGTCCAATGTCCTCTAATGGGGCATATGGGGTAAAAGGGTTTTCATTTAAGTACGGTAATGGGGTTTGGATCGGAAGAACAAAAGGCACTAGTTCCAGAAGCGGCTTTGAGATGATTTGGGACCCGAATGGGTGGACTGAGACGGACAGTAGTTTCTCAGTGAAGCAAGACATTGTAAAAATAACTGACTGGTCAGGATATAGTGGGAGTTTTGTCCAGCATCCAGAACTGACAGGATTAGATTGCATGAGGCCTTGTTTCTGGGTTGAGCTAATTAGAGGGAGGCCCAAAGAGAACACAATTTGGACTAGCGGGAGCAGCATATCCTTTTGTGGTGTAAATAGTGACACTGTGGGTTGGTCTTGGCCAGACGGTGCTGAGTTGCCATTCACCATTGACAAGTAG</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>&gt;Flu-0013|A_MP</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>ATGAGTCTTCTAACCGAGGTCGAAACGTACGTTCTCTCTATCGTCCCGTCGGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTTGAAGATGTCTTTGCAGGGAAGAACACCGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATACTGTCACCTCTGACTAAGGGGATTTTGGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCTCTAAGTGGAAATGGAGACCCAAACAACATGGACAGGGCAGTCAAGTTGTACAGGAAATTGAAGAGAGAAATAACATTCCATGGGGCTAAAGAAGTTGCACTCAGTTACTCAACCGGTGCACTTGCCAGTTGTATGGGTCTCATATACAACAGGATGGGGACGGTGACCGCAGAAGTGGCATTGGGCCTAGTGTGTGCCACCTGTGAGCAGATTGCTGATTCACAGCATCGGTCTCACAGACAGATAGCTACCACCACCAACCCACTAATCAGACATGAAAACAGAATGGTTTTGGCCAGTACTACAGCTAAGGCTATGGAGCAGATGGCTGGATCGAGTGAGCAAGCAGTGGAAGCCATGGAGGTTGCTAGTCAGGCTAGGCAAATGGTGCAGGCGATGAGGACCATTGGAACTCATCCTAGCTCCAGTGCCGGTCTGAGAGATGATCTCCTTGAAAATTTGCAGGCCTACCAAAAACGAATGGGAGTGCAACTGCAGCGATTCAAGTGATCCTCTCGTTATTGCCGCAAGTATCATTGGGATCTTGCACTTGATATTGTGGATTCTTGATCGCCTTTTCTTCAAATGCGTTTATCGTCGCCTTAAATACGGTTTGAAAGGAGGGCCTTCTACGGAAGGAGTACCTGAGTCCATGAGGGAAGAGTACCGGCAGGAACAGCAGAGTGCTGTGGATGTTGACGATGGTCATTTTGTCAACATAGAGATGGAGTAA</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>&gt;Flu-0013|A_NS</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>ATGGATTCCAACACTGTGTCAAGCTTCCAGGTAGACTGCTTTCTTTGGCATGTCCGCAAACGATTTGCAGACCAAGAACTGGGTGATGCCCCATTCCTTGACCGGCTCCGCCGAGACCAGAAGTCTCTAAGAGGAAGAGGCAGCACTCTTGGTCTGGACATCGAGACGGCCACTCGTGCTGGAAAGCAGATAGTGGAGAGGATTCTGGAGGAAGAATCCGACGAGGCACTCAAAATGACTATTGCCTCTGTGCCTGCTCCACGCTACCTAACTGACATGACTCTTGAAGAGATGTCAAGAGACTGGTTCATGCTCATGCCCAAGCAAAAAGTGGCAGGCTCCCTCTGTATCAGAATGGACCAGGCGATTATGGATAAGAACATCATACTGAAGGCAAACTTCAGTGTGATCTTCAATCGGCTGGAGACACTAATACTACTCAGAGCTTTCACTGAAGAGGGAGCAATTGTCGGCGAAATTTCACCATTGCCTTCTCTTCCAGGACATACTGATGAGGATGTCAAAAATGCAATTGGGGTCCTCATCGGAGGACTTGAATGGAATGATAACACAGTTCGAGTCTCTGAAATTTTACAGAGATTCGCTTGGAGAAGCAGTAATGAGGATGGGAGACCTCCACTCCCTCCAAAGCAGAAACGGAAAATGGAGAGAACAATTGAGTCAGAAGTTTGAAGAAATAAGGTGGCTGATTGAAGAGGTGCGACACAGACTAAAGATCACAGAAAATAGTTTTGAACAAATAACATTTATGCAAGCCTTACAACTACTGCTTGAAGTGGAGCAAGAGATACGAACTTTCTCGTTTCAGCTTATTTAA</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>&gt;Flu-0014|A_NS</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>ATGGATTCCAACACTGTGTCAAGCTTTCAGGTAGACTGCTTTCTTTGGCATGTCCGCAAACGATTTGCAGACCAAGAACTGGGTGATGCCCCATTCCTTGACCGGCTCCGCCGAGACCAGAAGTCTCTAAGAGGAAGAGGCAGCACTCTTGGTCTGGACATCGAGACGGCCACTCGTGCTGGAAAGCAGATAGTGGAGAGGATTCTGGAGGAAGAATCCGACGAGGCACTCAAAATGACTATTGCCTCTGTGCCTGCTCCACGCTACCTAACTGACATGACTCTTGAAGAGATGTCAAGAGANTGGTTCATGCTCATGCCCAAGCAAAAAGTGGCAGGCTCCCTCNGTATCAGAATGGACCAGGCGATTATGGATAAGAACATCATACTGAAGGCAAACTTCAGTGTGATCTTCAATCGGCTGGAGACACTAATACTACTCAGAGCTTTCACTGAAGAGGGAGCAATTGTCGGCGAAATTTCACCATTGCCTTCTCTTCCAGGACATACTGATGAGGATGTCAAAAATGCAATTGGGGTCCTCATCGGAGGACTTGAATGGAATGATAACACAGTTCGAGTCTCTGAAANTTTACAGAGATTCGCTTGGAGAAGCAGTAATGAGGATGGGAGACCTCCACTCCCTCCAAAGCAGAAACGGAAAATGGAGAGAACAATTGAGTCAGAAGTTTGAAGAAATAAGGTGGCTGATTGAAGANGTNCGACACAGANTAAAGATCACAGAAAATAGTTTTGAACAAATAACATTTATGCAAGCCTTACAACTACTGCTTGAAGTGGAGCAAGAGATANGAACTTTCTCGTTTCAGCTTATTTAA</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>&gt;Flu-0018|A_NS</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>ATGGATTCCAACACTGTGTCAAGCTTTCAGGTAGACTGCTTTCTTTGGCATGTCCGCAAACGATTTGCAGACCAAGAACTGGGTGATGCCCCATTCCTTGACCGGCTCCGCCGAGACCAGAAGTCTCTAAGAGGAAGAGGCAGCACTCTTGGTCTGGACATCGAGACGGCCACTCGTGCTGGAAAGCAGATAGTGGAGAGGATTCTGGAGGAAGAATCCGACGAGGCACTCAAAATGACTATTGCCTCTGTGCCTGCTCCACGCTACCTAACTGACATGACTCTTGAAGAGATGTCAAGAGAYTGGTTCATGCTCATGCCCAAGCAAAAAGTGGCAGGCTCCCTCWGTATCAGAATGGACCAGGCGATTATGGATAAGAACATCATACTGAAGGCAAACTTCAGTGTGATCTTCAATCGGCTGGAGACACTAATACTACTCAGAGCTTTCACTGAAGAGGGAGCAATTGTCGGCGAAATTTCACCATTGCCTTCTCTTCCAGGACATACTGATGAGGATGTCAAAAATGCAATTGGGGTCCTCATCGGAGGACTTGAATGGAATGATAACACAGTTCGAGTCTCTGAAAYTTTACAGAGATTCGCTTGGAGAAGCAGTAATGAGGATGGGAGACCTCCACTCCCTCCAAAGCAGAAACGGAAAATGGAGAGAACAATTGAGTCAGAAGTTTGAAGAAATAAGGTGGCTGATTGAAGARGTKCGACACAGAYTAAAGATCACAGAAAATAGTTTTGAACAAATAACATTTATGCAAGCCTTACAACTACTGCTTGAAGTGGAGCAAGAGATAMGAACTTTCTCGTTTCAGCTTATTTAA</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>&gt;Flu-0023|A_HA</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>ATGGAGGACATAGTACTACTTCTTGCAATAGTTAGCCTTGTTAAAAGTGATCAGATTTGCATTGGTTACCATGCAAACAATTCGACAGAGCAAGTTGACACGATAATGGAAAAGAACGTCACTGTTACACATGCCCAAGACATACTGGAAAAAACACACAACGGGAAACTCTGTGATTTAAATGGGGTGAAGCCACTGATTTTAAAGGATTGTAGTGTAGCTGGATGGCTCCTCGGAAACCCAATGTGCGACGAATTCATCAGAGTGCCGGAATGGTCCTACATAGTGGAGCGGGCTAACCCAGCTAATGACCTCTGTTACCCAGGGAGCCTCAATGACTATGAAGAACTGAAACACATGTTGAGCAGAATAAATCATTTTGAGAAGATTCAGATCATTCCCAAGAGTTCCTGGCCAAATCATGAAACATCACTAGGAGTGAGCGCAGCTTGTCCATACCAGGGAGCGCCCTCCNTTTTCAGAAATGTGGTGTGGCTTATCAAAAAGAACGATGCATACCCAACAATAAAGATAAGCTACAATAATACTAATCGGGAAGATCTCTTGATACTGTGGGGGATTCATCATTCCAACAATGCAAAAGAACAGACAAATCTCTACAAAAACCCAACCACCTACATTTCAGTTGGAACATCAACTTTAAACCAGAGGTTGGCACCAAAAATAGCTACTAGATCCCAAGTAAACGGGCAACGTGGAAGAATGGACTTCTTCTGGACAATCTTAAAACCAGATGATGCAATCCATTTCGAGAGTAACGGAAATTTCATTGCTCCAGAATATGCATACAAAATTGTCAAGAAAGGGGACTCAACAATTATGAAAAGTGGAGTGGAATATGGCCACTGCAACACCAAATGTCAAACCCCAGTAGGTGCGATAAATTCTAGTATGCCATTCCACAACATACATCCTCTCACCATTGGGGAATGCCCCAAATACGTGAAGTCAAACAAGTTGGTCCTTGCGACTGGGCTCAGAAATAGTCCTCTAAGAGAAAAGAGAAGNNNAAAAAGAGGTCTGTTTGGRGCRAWAGCAGGGTTTATAGAGGGAGGATGGCAGGGAATGGTTGATGGTTGGTATGGATACCATCATAGCAATRAGCAGGGGAGTGGGTACGCTGCGGACAAAGAATCCACCCAAAAGGCAATAGATGGAGTTACCAATAAGGTCAACTCAATCATTGACAAAATGAACACTCAATTTGAGGCAGTTGGAAGGGAGTTTAATAACTTAGAAAGGAGGATAGAGAATTTGAACAAGAAAATGGAAGACGGATTCCTAGATGTCTGGACCTATAATGCTGAACTTCTAGTTCTCATGGAAAACGAGAGGACTCTAGATTTCCATGATTCAAATGTCAAGAACCTTTACGACAAAGTCAGATTACAGCTTAGGGATAATGCAAAGGAGCTGGGTAACGGCTGTTTCGAATTCTATCACAAATGTGATAATGAATGTATGGAAAGTGTGAGAAATGGGACGTATGACTACCCTCAGTATTCAGAAGAAGCAAGATTAAAAAGAGAAGAAATAAGCGGAGTGAAATTAGAATCAGTAGGAACTTACCAGATACTGTCAATTTATTCAACAGCGGCAAGTTCCCTAGCACTGGCAATCATGATGGCTGGTCTATCTTTATGGATGTGCTCCAATGGGTCGTTACAATGCAGAATTTGCATTTAG</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>&gt;Flu-0023|A_NP</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>ATGGCGTCTCAAGGCACCAAACGATCCTATGAACAAATGGAAACTGGTGGGGAACGCCAGAATGCCACTGAAATCAGAGCTTCTGTTGGAAGAATGGTTGGCGGAATCGGGAGATTCTACATACAGATGTGCACTGAACTCAAACTCAGTGATTACGAAGGGAGGCTGATCCAAAACAGCATAACCATAGAAAGGATGGTTCTCTCGGCATTTGATGAGAGGAGGAACAAGTACCTGGAGGAACATCCCAGTGCCGGGAAGGATCCCAAGAAGACTGGAGGTCCAATCTACAGGAGGAGAGATGGCAAATGGGTGAGAGAGTTGATCCTCTACGACAAAGAAGAGATCAGAAGAATTTGGCGTCAAGCTAATAATGGAGAGGATGCAACTGCTGGTCTCACTCACTTGATGATTTGGCATTCCAATCTGAATGATGCCACATACCAGAGAACAAGGGCACTTGTGCGTACTGGAATGGACCCTAGAATGTGCTCTCTGATGCAAGGCTCAACCCTCCCTAGGAGATCAGGGGCTGCTGGAGCAGCAGTGAAAGGAGTTGGAACAATGGCGATGGAACTAATTCGAATGATCAAACGAGGGATCAATGATCGGAATTTCTGGAGAGGCGAAAACGGTCGGAGAACCAGGATTGCCTACGAGAGAATGTGCAACATTCTCAAGGGAAAGCTCCAAACAGCAGCACAACGGGCAATGATGGACCAAGTGAGAGAAAGCCGGAATCCTGGGAATGCTGAAATCGAAGATCTCATCTTTCTCGCACSATCTGCTCTCATCCTGAGGGGATCAGTGGCTCATAAGTCCTGTCTGCCTGCTTGCGTATATGGACTTGCTGTAGCCAGTGGATATGACTTTGAAAGAGAGGGATATTCTCTAGTCGGAATTGATCCTTTCCGTCTGCTCCAAAACAGCCAAGTCTTCAGTCTCATCAGACCGAACGAAAATCCAGCTCATAAAAGTCAGCTGGTATGGATGGCATGCCACTCTGCGGCATTTGAGGATCTGAGAGTGTCAAGCTTCATCAGAGGGACAAGAGTAGTCCCAAGAGGACAACTGTCCACCAGAGGAGTTCAGATTGCTTCAAATGAAAACATGGAGACAATGGACTCCAGTACTCTTGAACTGAGGAGCAGATATTGGGCTATAAGAACAAGAAGTGGAGGAAACACTAACCAACAGAGAGCATCTGCAGGACAAATCAGCGTACAGCCCACATTCTCTGTACAAAGAAACCTCCCATTCGAGAGAGCAACCATCATGGCAGCATTTACGGGAAACACTGAAGGCAGAACTTCAGATATGAGAACTGAGATCATAAGGATGATGGAAAATGCCAGACCTGAAGATGTGTCTTTCCAGGGGCGGGGAGTCTTCGAGCTCTCGGACGAAAAGGCAACGAACCCGATCGTGCCTTCCTTTGACATGAGTAATGAAGGATCTTATTTCTTCGGAGACAATGCAGAGGAGTATGACAATTAA</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>&gt;Flu-0023|A_NA</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>ATGAATCCAAATCAAAAGATAACAACCATTGGAACAATCTGTATGGTAATTGGGATAGTCAGCTTGATGCTGCAAATTGGGAACATAATCTCAATATGGGTTAGCCATTCAATCCAAACAGGGAATCAATACCAGCCTGAACCATGCAATCAAAGCATCATTACCTATGAGAACAACACCTGGGTAAATCAGACGTATGTCAAAATCAGCAATACCAATTTTCTTGCTGAGCAGGCTGTTACTTCGGTAACATTAGCGGGCAATTCATCTCTTTGCCCTATTAGTGGGTGGGCAATATACAGTAAGGACAACGGTATAAGAATTGGGTCCAAGGGGGATGTGTTTGTTATAAGAGAACCGTTCATCTCATGCTCCCACTTGGAATGCAGAACCTTTTTCCTGACCCAGGGAGCTCTGCTGAATGACAAACATTCTAATGGGACAGTTAAGGATAGAAGCCCTTATAGAACTTTGATGAGTTGTCCCGTGGGTGAGGCTCCTTCCCCGTATAATTCAAGATTTGAGTCTGTTGCTTGGTCGGCAAGTGCTTGTCATGATGGCATCAGTTGGTTGACAATCGGTATTTCTGGTCCAGACAATGGAGCTGTGGCTGTATTGAAGTACAATGGCATAATAACGGATACTATCAAGAGTTGGAGAAACAACATTTTGAGAACTCAAGAATCTGAATGTGCTTGCGTAAATGGCTCTTGCTTCACCGTAATGACTGATGGACCAAGCAATGGGCAGGCCTCATATAAAATCTTCAAGATAGAGAAAGGGAAAGTTGTCAAATCAGTTGAAATGAATGCCCCTAATTACCACTACGAGGAATGCTCCTGTTATCCTGATGCGGGTGATATTATGTGTGTGTGCAGGGACAATTGGCATGGCTCAAACCGGCCGTGGGTATCTTTTAATCAAAATCTGGAGTATCAAATAGGATATATATGCAGTGGGGTTTTCGGGGACAATCCCCGCCCCAATGATGGAACAGGCAGTTGCAGTCCAATGCCCTCTAATGGGGCATATGGGGTAAAAGGGTTTTCATTTAAGTACGGTAATGGGGTTTGGATCGGAAGAACAAAAAGCACTAGTTCCAGAAGCGGCTTTGAGATGATTTGGGATCCGAATGGGTGGACTGAGACGGACAGTAGTTTCTCAGTGAAGCAAGACATTGTAGAAATAACTGACTGGTCAGGATATAGTGGGAGTTTTGTCCAGCATCCAGAACTGACGGGATTAGATTGCATGAGGCCTTGTTTCTGGGTTGAGCTAATCAGAGGGAGGCCCAAAGAGAACACAATTTGGACTAGCGGGAGCAGCATATCCTTTTGTGGTGTAAATAGTGACACTGTGGGTTGGTCTTGGCCAGACGGTGCTGAGTTGCCATTCACCATTGACAAGTAG</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>&gt;Flu-0023|A_MP</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
         <is>
           <t>ATGAGTCTTCTAACCGAGGTCGAAACGTACGTTCTCTCTATCGTCCCGTCGGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTTGAAGATGTCTTTGCAGGGAAGAACACCGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATCCTGTCACCTCTGACTAAGGGGATTTTGGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCTCTAAGTGGAACTGGAGACCCAAACAACATGGACAGGGCAGTCAAGTTGTACAGGAAACTGAAGAGAGAGATAACATTCCATGGTGCTAAAGAAGTTGCACTCAGTTACTCAACCGGTGCACTTGCCAGTTGTATGGGTCTCATATACAACAGGATGGGGACGGTGACCGCAGAAGTGGCATTGGGCCTAGTGTGTGCCACCTGTGAGCAGATTGCTGATTCACAGCATCGGTCTCACAGACAGATAGCTACCACCACCAACCCACTAATCAGACATGAAAACAGAATGGTTTTGGCCAGTACTACAGCTAAGGCTATGGAGCAGATGGCTGGATCGAGTGAACAAGCAGTGGAAGCCATGGAGGTTGCTAGTCAGGCTAGGCAGATGGTGCAGGCAATGAGGACCATTGGAACTCATCCTAGCTCCAGTGCCGGTCTGAGAGATGATCTCCTTGAAAATTTGCAGGCCTACCAAAAACGGATGGGAGTGCAACTGCAGCGATTCAAGTGATCCTCTCGTTATTGCCGCAAGTATCATTGGGATCTTGCACTTGATATTGTGGATTCTTGATCGCCTTTTCTTCAAATGCGTTTATCGTCGCCTTAAATACGGTTTGAAAGGAGGGCCTTCTACGGAAGGAGTACCTGAGTCCATGAGGGAAGAGTACCGGCAGGAACAGCAGAGTGCTGTGGATGTTGACGATGGTCATTTTGTCAACATAGAGCTGGAGTAA</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>&gt;Flu-0023|A_NS</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>ATGGATTCCAACACTGTGTCAAGCTTTCAGGTAGACTGCTTTCTTTGGCATGTCCGCAAACGATTTGCAGACCAAGAACTGGGTGATGCCCCATTCCTTGACCGGCTCCGCCGAGACCAGAAGTCTCTAAGAGGAAGAGGCAGCACTCTTGGTCTGGACATCGAGACGGCCACTCGTGCTGGAAAGCAGATAGTGGAGAGGATTCTGGAGGAAGAATCCGACGAGGCACTCAAAATGACTATTGCCTCTGTGCCTGCTCCACGCTACCTAACTGACATGACTCTTGAAGAGATGTCAAGAGACTGGTTCATGCTCATGCCCAAGCAAAAAGTGGCAGGCTCCCTCAGTATCAGAATGGACCAGGCGATTATGGATAAGAACATCATACTGAAGGCAAACTTCAGTGTGATCTTCAATCGGCTGGAGACACTAATACTACTCAGAGCTTTCACTGAAGAGGGAGCAATTGTCGGCGAAATTTCACCATTGCCTTCTCTTCCAGGACATACTGATGAGGATGTCAAAAATGCAATTGGGGTCCTCATCGGAGGACTTGAATGGAATGATAACACAGTTCGAGTCTCTGAAACTTTACAGAGATTCGCTTGGAGAAGCAGTAATGAGGATGGGAGACCTCCACTCCCTCCAAAGCAGAAACGGAAAATGGAGAGAACAATTGAGTCAGAAGTTTGAAGAAATAAGGTGGCTGATTGAAGAAGTTCGACACAGACTAAAGATCACAGAAAATAGTTTTGAACAAATAACATTTATGCAAGCCTTACAACTACTGCTTGAAGTGGAGCAAGAGATAAGAACTTTCTCGTTTCAGCTTATTTAA</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>&gt;Flu-0027|A_MP</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t>ATGAGTCTTCTAACCGAGGTCGAAACGTACGTTCTCTCTATCGTCCCGTCGGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTTGAAGATGTCTTTGCAGGGAAGAACACCGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATACTGTCACCTCTGACTAAGGGGATTTTGGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCTCTAAGTGGAAATGGAGACCCAAACAACATGGACAGGGCAGTCAAGTTGTACAGGAAATTGAAGAGAGAAATAACATTCCATGGGGCTAAAGAAGTTGCACTCAGTTACTCAACCGGTGCACTTGCCAGTTGTATGGGTCTCATATACAACAGGATGGGGACGGTGACCGCAGAAGTGGCATTGGGCCTAGTGTGTGCCACCTGTGAGCAGATTGCTGATTCACAGCATCGGTCTCACAGACAGATAGCTACCACCACCAACCCACTAATCAGACATGAAAACAGAATGGTTTTGGCCAGTACTACAGCTAAGGCTATGGAGCAGATGGCTGGATCGAGTGAGCAAGCAGTGGAAGCCATGGAGGTTGCTAGTCAGGCTAGGCAAATGGTGCAGGCGATGAGGACCATTGGAACTCATCCTAGCTCCAGTGCCGGTCTGAGAGATGATCTCCTTGAAAATTTGCAGGCCTACCAAAAACGAATGGGAGTGCAACTGCAGCGATTCAAGTGATCCTCTCGTTATTGCCGCAAGTATCATTGGGATCTTGCACTTGATATTGTGGATTCTTGATCGCCTTTTCTTCAAATGCGTTTATCGTCGCCTTAAATACGGTTTGAAAGGAGGGCCTTCTACGGAAGGAGTACCTGAGTCCATGAGGGAAGAGTACCGGCAGGAACAGCAGAGTGCTGTGGATGTTGACGATGGTCATTTTGTCAACATAGAGATGGAGTAA</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
         <is>
           <t>&gt;Flu-0027|A_NS</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
         <is>
           <t>ATGGATTCCAACACTGTGTCAAGCTTCCAGGTAGACTGCTTTCTTTGGCATGTCCGCAAACGATTTGCAGACCAAGAACTGGGTGATGCCCCATTCCTTGACCGGCTCCGCCGAGACCAGAAGTCTCTAAGAGGAAGAGGCAGCACTCTTGGTCTGGACATCGAGACGGCCACTCGTGCTGGAAAGCAGATAGTGGAGAGGATTCTGGAGGAAGAATCCGACGAGGCACTCAAAATGACTATTGCCTCTGTGCCTGCTCCACGCTACCTAACTGACATGACTCTTGAAGAGATGTCAAGAGACTGGTTCATGCTCATGCCCAAGCAAAAAGTGGCAGGCTCCCTCTGTATCAGAATGGACCAGGCGATTATGGATAAGAACATCATACTGAAGGCAAACTTCAGTGTGATCTTCAATCGGCTGGAGACACTAATACTACTCAGAGCTTTCACTGAAGAGGGAGCAATTGTCGGCGAAATTTCACCATTGCCTTCTCTTCCAGGACATACTGATGAGGATGTCAAAAATGCAATTGGGGTCCTCATCGGAGGACTTGAATGGAATGATAACACAGTTCGAGTCTCTGAAATTTTACAGAGATTCGCTTGGAGAAGCAGTAATGAGGATGGGAGACCTCCACTCCCTCCAAAGCAGAAACGGAAAATGGAGAGAACAATTGAGTCAGAAGTTTGAAGAAATAAGGTGGCTGATTGAAGAGGTGCGACACAGACTAAAGATCACAGAAAATAGTTTTGAACAAATAACATTTATGCAAGCCTTACAACTACTGCTTGAAGTGGAGCAAGAGATACGAACTTTCTCGTTTCAGCTTATTTAA</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
         <is>
           <t>&gt;Flu-0035|A_NP</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
         <is>
           <t>ATGGCGTCTCAAGGCACCAAACGATCCTATGAACAAATGGAAACTGGTGGGGAACGCCAGAATGCCACTGAAATCAGAGCATCTGTTGGAAGAATGGTTGGCGGAATAGGAAGATTCTACATACAGATGTGCACTGAGCTCAAACTCAGTGATTACGAAGGGAGGCTGATCCAAAACAGCATAACCATAGAAAGGATGGTTCTCTCGGCATTTGATGAGAGGAGGAACAAGTACCTGGAGGAACATCCCAGTGCCGGGAAGGATCCCAAGAAGACTGGAGGTCCAATCTACAGGAGGAGAGATGGCAAATGGGTGAGAGAGTTGATCCTCTACGACAAAGAAGAGATCAGAAGAATTTGGCGTCAAGCTAATAATGGAGAGGATGCAACTGCTGGTCTCACTCATTTGATGATTTGGCATTCCAATCTGAATGATGCAACATACCAGAGAACAAGGGCACTTGTGCGTACTGGAATGGACCCTAGAATGTGCTCTCTGATGCAAGGCTCAACCCTCCCTAGGAGATCCGGGGCTGCTGGAGCAGCAGTGAAAGGAGTTGGAACAATGGTGATGGAACTAATTCGAATGATCAAACGAGGGATCAATGATCGGAATTTCTGGAGAGGCGAAAACGGTCGGAGAACCAGGATTGCCTACGAGAGAATGTGCAACATCCTCAAGGGAAAGTTCCAAACAGCAGCACAACGGGCAATGATGGACCAAGTGAGAGAAAGCCGGAATCCTGGGAATGCTGAAATTGAAGATCTCATCTTTCTCGCACGATCTGCTCTCATCCTGAGGGGATCAGTGGCTCATAAGTCCTGTCTGCCTGCTTGCGTATATGGACTTGCTGTAGCCAGTGGATATGACTTTGAAAGAGAGGGATATTCTCTAGTCGGAATTGATCCTTTCCGTCTGCTCCAAAACAGCCAAGTCTTCAGTCTCATCAGACCGAACGAAAATCCAGCTCATAAAAGTCAGCTGGTATGGATGGCATGCCACTCTGCGGCATTTGAGGATCTGAGAGTTTCAAGCTTCATCAGAGGGACAAGAGTAGTCCCAAGAGGACAACTGTCCACCAGAGGAGTTCAGATTGCTTCAAATGAAAACATGGAGACAATGGACTCCAGTACTCTTGAACTGAGGAGCAGGTACTGGGCTATAAGAACAAGAAGTGGAGGAAACACTAACCAACAGAGAGCATCTGCAGGACAAATCAGCGTACAGCCCACATTCTCTGTGCAAAGAAACCTCCCATTCGAGAGAGCAACCATCATGGCAGCATTTACGGGAAACACTGAAGGCAGAACTTCAGACATGAGAACTGAGATCATAAGGATGATGGAAAATGCCAGACCTGAAGATGTGTCTTTCCAGGGGCGGGGAGTCTTCGAGCTCTCGGACGAAAAGGCAACGAACCCGATCGTGCCTTCCTTTGACATGAGTAATGAAGGATCTTATTTCTTCGGAGACAATGCAGAGGAGTATGACAATTAA</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
         <is>
           <t>&gt;Flu-0035|A_MP</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
         <is>
           <t>ATGAGTCTTCTAACCGAGGTCGAAACGTACGTTCTCTCTATCGTCCCGTCGGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTTGAAGATGTTTTTGCAGGGAAGAACACCGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATACTGTCACCTCTGACTAAGGGGATTTTGGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCTCTAAGTGGAAATGGAGACCCAAACAACATGGACAGGGCAGTCAAGTTGTACAGGAAATTGAAGAGAGAAATAACATTTCATGGGGCTAAAGAAGTTGCACTCAGTTACTCAACCGGTGCACTTGCCAGTTGTATGGGTCTCATATACAACAGGATGGGGACGGTGACCGCAGAAGTGGCATTGGGCCTAGTGTGTGCCACCTGTGAGCAGATTGCTGATTCACAGCATCGGTCTCACAGACAGATAGCTACCACCACCAACCCACTAATCAGACATGAAAACAGAATGGTTTTGGCCAGTACTACAGCTAAGGCTATGGAGCAGATGGCTGGATCGAGTGAGCAAGCAGTGGAAGCCATGGAGGTTGCTAGTCAGGCTAGGCAAATGGTGCAGGCGATGAGGACCATTGGAACTCATCCTAGCTCCAGTGCCGGTCTGAGAGATGATCTCCTTGAAAATTTGCAGGCCTACCAAAAACGAATGGGAGTGCAACTGCAGCGATTCAAGTGATCCTCTCGTTATTGCCGCAAGTATCATTGGGATCTTGCACTTGATATTGTGGATTCTTGATCGCCTTTTCTTCAAATGCGTTTATCGTCGCCTTAAATACGGTTTGAAAGGAGGGCCTTCTACGGAAGGAGTACCTGAGTCCATGAGGGAAGAGTACCGGCAGGAACAGCAGAGTGCTGTGGATGTTGACGATGGTCATTTTGTCAACATAGAGATGGAGTAA</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
         <is>
           <t>&gt;Flu-0035|A_NS</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
         <is>
           <t>ATGGATTCCAACACTGTGTCAAGCTTTCAGGTAGACTGCTTTCTTTGGCATGTCCGCAAACGATTTGCAGACCAAGAACTGGGTGATGCCCCATTCCTTGACCGGCTCCGCCGAGACCAGAAGTCTCTAAGAGGAAGAGGCAGCACTCTTGGTCTGGACATCGAGACGGCCACTCGTGCTGGAAAGCAGATAGTGGAGAGGATTCTGGAGGAAGAATCCGACGAGGCACTCAAAATGACTATTGCCTCTGTGCCTGCTCCACGCTACCTAACTGACATGACTCTTGAAGAGATGTCAAGAGATTGGTTCATGCTCATGCCCAAGCAAAAAGTGGCAGGCTCCCTCTGTATCAGAATGGACCAGGCGATTATGGATAAGAACATCATACTGAAGGCAAACTTCAGTGTGATCTTCAATCGGCTGGAGACACTAATACTACTCAGAGCTTTCACTGAAGAGGGAGCAATTGTCGGCGAAATTTCACCATTGCCTTCTCTTCCAGGACATACTGATGAGGATGTCAAAAATGCAATTGGGGTCCTCATCGGAGGACTTGAATGGAATGATAACACAGTTCGAGTCTCTGAAATTTTACAGAGATTCGCTTGGAGAAGCAGTAATGAGGATGGGAGACCTCCACTCCCTCCAAAGCAGAAACGGAAAATGGAGAGAACAATTGAGTCAGAAGTTTGAAGAAATAAGGTGGCTGATTGAAGAGGTGCGACACAGATTAAAGATCACAGAAAATAGTTTTGAACAAATAACATTTATGCAAGCCTTACAACTACTGCTTGAAGTGGAGCAAGAGATACGAACTTTCTCGTTTCAGCTTATTTAA</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
         <is>
           <t>&gt;Flu-0055|A_MP</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
         <is>
           <t>ATGAGTCTTCTAACCGAGGTCGAAACGTACGTTCTCTCTATCGTCCCGTCGGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTTGAAGATGTCTTTGCAGGGAAGAACACCGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATCCTGTCACCTCTGACTAAGGGGATTTTGGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCTCTAAGTGGAACTGGAGACCCAAACAACATGGACAGGGCAGTCAAGTTGTACAGGAAACTGAAGAGAGAGATAACATTCCATGGTGCTAAAGAAGTTGCACTCAGTTACTCAACCGGTGCACTTGCCAGTTGTATGGGTCTCATATACAACAGGATGGGGACGGTGACCGCAGAAGTGGCATTGGGCCTAGTGTGTGCCACCTGTGAGCAGATTGCTGATTCACAGCATCGGTCTCACAGACAGATAGCTACCACCACCAACCCACTAATCAGACATGAAAACAGAATGGTTTTGGCCAGTACTACAGCTAAGGCTATGGAGCAGATGGCTGGATCGAGTGARCAAGCAGTGGAAGCCATGGAGGTTGCTAGTCAGGCTAGGCARATGGTGCAGGCRATGAGGACCATTGGAACTCATCCTAGCTCCAGTGCCGGTCTGAGAGATGATCTCCTTGAAAATTTGCAGGCCTACCAAAAACGRATGGGAGTGCAACTGCAGCGATTCAAGTGATCCTCTCGTTATTGCCGCAAGTATCATTGGGATCTTGCACTTGATATTGTGGATTCTTGATCGCCTTTTCTTCAAATGCGTTTATCGTCGCCTTAAATACGGTTTGAAAGGAGGGCCTTCTACGGAAGGAGTACCTGAGTCCATGAGGGAAGAGTACCGGCAGGAACAGCAGAGTGCTGTGGATGTTGACGATGGTCATTTTGTCAACATAGAGMTGGAGTAA</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
         <is>
           <t>&gt;Flu-0205|A_MP</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
         <is>
           <t>NNNNGTCTTCTAACCGAGGTCGAAACGTACGTTCTCTCTATCGTCCCGTCGGGNCCCCTCAAAGCCGAGATCGCGCAGAGACTTGAAGATGTCTTTGCANGGAAGAACACCGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATCCTGTCACCTCTGACTAAGGGGATTTTGGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCTCTAAGTGGAACTGGAGACCCAAACAACATGGACAGGGCAGTCAAGTTGTACAGGAAACTAAAGAGAGAGATAACATTCCATGGTGCTAAAGAAGTTGCACTCAGTTACTCAACCGGTGCACTTGCCAGTTGTATGGGTCTCATATACAACAGGATGGGGACNGTGACCGCAGAAGTGGCATTGGGCCTAGTGTGTGCCACCTGTGAGCAGATTGCTGATTCACAGCATCGGTCTCACAGACAGATAGCTACCACCACCAACCCACTAATCAGACATGAAAACAGAATGGTTTTGGCCAGTACTACAGCTAAGGCTATGGAGCAGATGGCTGGATCGAGTGAGCAAGCAGTGGAAGCCATGGAGGTTGCTAGTCAGGCTAGGCAGATGGTGCAGGCGATGAGGACCATTGGAACTCATCCTAGCTCCAGTGCCGGTCTAAGAGATGATCTCCTTGAAAATTTGCAGGCCTACCAAAAACGGATGGGAGTGCAACTGCAGCGATTCAAGTGATCCTCTCGTTATTGCCGCAAGTATCATTGGGATCTTGCACTTGATATTGTGGATTCTTGATCGCCTTTTCTTCAAATGCGTTTATCGTCGCCTTAAATACGGTTTGAAAGGAGGGCCTTCTACGGAAGGAGTACCTGAGTCCATGAGGGAAGAGTACCGGCAGGAACAGCAGAGTGCTGTGGATGTTGACGATGGTCATTTTGTCAACATAGANNNNNNNNNN</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
         <is>
           <t>&gt;Flu-0206|A_MP</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
         <is>
           <t>ATGAGTCTTCTAACCGAGGTCGAAACGTACGTTCTCTCTATCGTCCCGTCGGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTTGAAGATGTCTTTGCAGGGAAGAACACCGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATCCTGTCACCTCTGACTAAGGGGATTTTGGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCTCTAAGTGGAACTGGAGACCCAAACAACATGGACAGGGCAGTCAAGTTGTACAGGAAACTAAAGAGAGAGATAACATTCCATGGTGCTAAAGAAGTTGCACTCAGTTACTCAACCGGTGCACTTGCCAGTTGTATGGGTCTCATATACAACAGGATGGGGACGGTGACCGCAGAAGTGGCATTGGGCCTAGTGTGTGCCACCTGTGAGCAGATTGCTGATTCACAGCATCGGTCTCACAGACAGATAGCTACCACCACCAACCCACTAATCAGACATGAAAACAGAATGGTTTTGGCCAGTACTACAGCTAAGGCTATGGAGCAGATGGCTGGATCGAGTGAGCAAGCAGTGGAAGCCATGGAGGTTGCTAGTCAGGCTAGGCAGATGGTGCAGGCGATGAGGACCATTGGAACTCATCCTAGCTCCAGTGCCGGTCTAAGAGATGATCTCCTTGAAAATTTGCAGGCCTACCAAAAACGGATGGGAGTGCAACTGCAGCGATTCAAGTGATCCTCTCGTTATTGCCGCAAGTATCATTGGGATCTTGCACTTGATATTGTGGATTCTTGATCGCCTTTTCTTCAAATGCGTTTATCGTCGCCTTAAATACGGTTTGAAAGGAGGGCCTTCTACGGAAGGAGTACCTGAGTCCATGAGGGAAGAGTACCGGCAGGAACAGCAGAGTGCTGTGGATGTTGACGATGGTCATTTTGTCAACATAGAGCTGGAGTAA</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
         <is>
           <t>&gt;Flu-0206|A_NS</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
         <is>
           <t>NNNGATTCCAACACTGTGTCAAGCTTTCAGGTAGACTGCTTTCTTTGGCATGTCCGCAAACGATTTGCAGACCAAGAACTGGGTGATGCCCCATTCCTTGACNGGCTCCGCCGAGACCAGAAGTCTCTAAGAGGAAGAGGCAGCACTCTTGGTCTGAACATCGAGACGGCCACTCGTGCTGGAAAGCAGATAGTGGAGAGGATTCTGGAGGAAGAATCCGACGAAGCACTCAAAATGACTATTGCCTCTGTGCCTGCTCCACGCTACCTAACTGACATGACTCTTGAAGAGATGTCAAGAGACTGGTTCATGCTCATGCCCAAGCNAAAAGTGGCAGGCTCCCTCAGTATCAGAATGGACCAGGCGATTATGGATAAGAACATCATACTGAAGGCAAACTTCAGTGTGATCTTCAATCGGCTGGAGACACTAATACTACTCAGAGCTTTCACTGAAGAAGGAGCAATTGTCGGCGAAATTTCACCATTGCCTTCTCTTCCAGGACATACTGATGAGGATGTCAAAAATGCAATTGGGGTCCTCATCGGAGGATTTGAATGGAATGATAACACAGTTCGAGTCTCTGAAACTTTACAGAGGTTCGCTTGGAGAAGCAGTAATGAGGATGGGAGACCTCCACTCCCTCCAAAGCAGAAACGGAAAATGGAGAGAACAATTGAGTCAGAAGTTTGAAGAAATAAGGTGGCTGATTGAAGAAGTTCGACACAGACTAAAGATCACAGAAAATAGTTTTGAACAAATAACATTTATGCAAGCCTTACAACTACTGCTTGAAGTGGAGCAAGAGATAAGAACTTTCTCGTTTCAGCTTATTNNN</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
         <is>
           <t>&gt;Flu-0314|A_NA</t>
         </is>
       </c>
-      <c r="BF1" t="inlineStr">
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
         <is>
           <t>ATGAATCCAAATCAAAAGATAACAACCATTGGATCAATCTGTATGGTAATTGGGACAGTCAGCTTGATGCTGCAAATTGGGAACATAATCTCAATATGGGTTAGCCATTCAATCCAAACAGGGAATCAATACCAGCCTGAACCATGCAATCAAAGCATCATTACCTATGAGAACAACACCTGGGTAAATCAGACGTATGTCAACATCAGCAATAACAATTTTCTTGCTGAGCAGGCTGTTACTTCGGTAACATTAGCGGGCAATTCATCTCTTTGCCCTATTAGTGGGTGGGCAATATACAGTAAGGACAACGGTATAAGAATTGGGTCCAAGGGGGATGTGTTTGTCATAAGAGAACCGTTCATCTCATGCTCCCACTTGGAATGCAGAACCTTTTTCCTGACTCAGGGAGCTCTGCTGAATGACAAACATTCTAATGGGACAGTTAAGGATAGAAGCCCTTATAGAACTTTGATGAGTTGTCCCGTGGGTGAGGCTCCTTCCCCGTACAATTCAAGATTTGAGTCTGTTGCTTGGTCGGCAAGTGCTTGTCATGATGGCATCAGTTGGTTGACAATCGGTATTTCTGGTCCAGACAATGGAGCTGTGGCTGTATTGAAGTACAATGGCATAATAACGGATACTATCAAGAGTTGGAGAAACAACATTTTGAGAACTCAAGAATCTGAATGTGCTTGCGTAAATGGCTCTTGCTTCACCGTAATGACTGATGGACCAAGCAATGGGCAGGCCTCGTATAAAATCTTCAAGATAGAGAAAGGGAAAGTTGTCAAATCAGTTGAATTGAATGCCCCTAATTACCACTACGAGGAATGTTCCTGTTATCCTGATGCGGGTGATATTATATGTGTGTGCAGGGACAATTGGCACGGCTCAAACCGGCCGTGGATATCTTTTAATCAAAATCTGGAGTATCAAATAGGATATATATGCAGTGGGGTTTTCGGGGACAATCCCCGCCCCAATGATGGAACAGGCAGTTGCAGTCCAATGTCCTCTAATGGGGCATATGGGGTRAAAGGGTTTTCATTTAAGTACGGTAATGGGGTTTGGATCGGAAGAACAAAAGGCACTAGTTCCAGAAGCGGCTTTGAGATGATTTGGGACCCGAATGGGTGGACTGAGACGGACAGTAGTTTCTCAGTGAAGCAAGACATTGTAGAAATAACTGACTGGTCAGGATATAGTGGGAGTTTTGTCCAGCATCCAGAACTGACAGGATTAGATTGCATGAGGCCTTGTTTCTGGGTTGAGCTAATTAGAGGGAGGCCCAAAGAGAACACAATTTGGACTAGCGGGAGCAGCATATCCTTTTGTGGTGTAAATAGTGACACTGTGGGTTGGTCTTGGCCAGACGGTGCTGAGTTGCCATTCACCATTGACAAGTAG</t>
         </is>
       </c>
-      <c r="BG1" t="inlineStr">
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
         <is>
           <t>&gt;Flu-0314|A_MP</t>
         </is>
       </c>
-      <c r="BH1" t="inlineStr">
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
         <is>
           <t>ATGAGTCTTCTAACCGAGGTCGAAACGTACGTTCTCTCTATCGTCCCGTCGGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTTGAAGATGTCTTTGCAGGGAAGAACACCGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATACTGTCACCTCTGACTAAGGGGATTTTGGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCTCTAAGTGGAAATGGAGACCCAAACAACATGGACAGGGCAGTCAAGTTGTACAGGAAACTGAAGAGAGAAATAACATTCCATGGGGCTAAAGAAGTTGCACTTAGTTACTCAACCGGTGCACTTGCCAGTTGTATGGGTCTCATATACAACAGGATGGGGACGGTGACCGCAGAAGTGGCATTGGGCCTAGTGTGTGCCACCTGTGAGCAGATTGCTGATTCACAGCATCGGTCTCACAGACAGATAGCTACCACCACCAACCCACTAATCAGACATGAAAACAGAATGGTTTTGGCCAGTACTACAGCTAAGGCTATGGAGCAGATGGCTGGATCGAGTGAGCAAGCAGTGGAAGCCATGGAGGTTGCTAGTCAGGCTAGGCAAATGGTGCAGGCGATGAGGACCATTGGAACTCATCCTAGCTCCAGTGCCGGTCTGAGAGATGATCTCCTTGAAAATTTGCAGGCCTACCAAAAACGAATGGGAGTGCAACTGCAGCGATTCAAGTGATCCTCTCGTTATTGCAGCAAGTATCATTGGGATCTTGCACTTGATATTGTGGATTCTTGATCGCCTTTTCTTCAAATGCGTTTATCGTCGCCTTAAATACGGTTTGAAAGGAGGGCCTTCTACGGAAGGAGTACCTGAGTCCATGAGGGAAGAGTACCGGCAGGAACAGCAGAGTGCTGTGGATGTTGACGATGGTCATTTTGTCAACATAGAGATGGAGTAA</t>
         </is>
       </c>
-      <c r="BI1" t="inlineStr">
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
         <is>
           <t>&gt;Flu-0314|A_NS</t>
         </is>
       </c>
-      <c r="BJ1" t="inlineStr">
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
         <is>
           <t>ATGGATTCCAACACTGTGTCAAGCTTTCAGGTAGACTGCTTTCTTTGGCATGTCCGCAAACAATTTGCAGACCAAGAACTGGGTGATGCCCCATTCCTTGACCGGCTCCGCCGAGACCAGAAGTCTCTAAGAGGAAGAGGCAGCACTCTTGGTCTGGACATCGAGACGGCCACTCGTGCTGGAAAGCAGATAGTGGAGAGGATTCTGGAGGAAGAATCCGACGAGGCACTCAAAATGACTATTGCCTCTGTGCCTGCTCCACGCTACCTAACTGACATGACTCTTGAAGAGATGTCAAGAGACTGGTTCATGCTCATGCCCAAGCAAAAAGTGGCAGGCTCCCTCTGTATCAGAATGGACCAGGCGATTATGGATAAGAACATCATACTGAAGGCAAACTTCAGTGTGATCTTCAATCGGCTGGAGACACTAATACTACTCAGAGCTTTCACTGAAGAGGGAGCAATTGTCGGCGAAATTTCACCATTGCCTTCTCTTCCAGGACATACTGATGAGGATGTCAAAAATGCAATTGGGGTCCTCATCGGAGGACTTGAATGGAATGATAACACAGTTCGAGTCTCTGAAATTTTACAGAGATTCGCTTGGAGAAGCAGTAATGAGGATGGGAGACCTCCACTCCCTCCAAAGCAGAAACGGAAAATGGAGAGAACAATTGAGTCAGAAGTTTGAAGAAATAAGGTGGCTGATTGAAGAGGTGCGACACAGACTAAAGATCACAGAAAATAGTTTTGAACAAATAACATTTATGCAAGCCTTACAACTACTGCTTGAAGTGGAGCAAGAGATACGAACTTTCTCGTTTCAGCTTATTTAA</t>
         </is>
       </c>
-      <c r="BK1" t="inlineStr">
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
         <is>
           <t>&gt;Flu-0316|A_PB2</t>
         </is>
       </c>
-      <c r="BL1" t="inlineStr">
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
         <is>
           <t>ATGGAGAGAATAAAAGAACTAAGAGATCTAATGTCACAGTCTCGCACTCGCGAGATACTGACCAAAACCACTGTTGACCACATGGCCATAATCAAAAAGTACACATCGGGAAGGCAAGAGAAGAACCCCGCACTCAGAATGAAATGGATGATGGCAATGAAATATCCAATTACAGCAGATAAGCGAATAATGGAAATGATCCCTGAGAGGAATGAACAAGGGCAAACTCTCTGGAGCAAAACAAACGATGCCGGATCAGACCGAGTGATGGTATCACCCCTGGCTGTGACATGGTGGAACAGGAACGGACCAACAACAAGTACAGTTCACTACCCAAAGGTATATAAAACTTATTTCGAAAAAGTTAAAAGGTTGAAACACGGGACCTTTGGCCCTGTGCACTTCAGAAACCAAGTTAAGATAAGACGGAGGGTCGATATAAACCCGGGCCATGCTGACCTTAGTGCCAAAGAGGCACAGGATGTAATCATGGAAGTCGTCTTCCCAAATGAAGTGGGAGCTAGGATATTGACGTCGGAGTCACAACTGACGATAACAAAGGAGAAAAAGGAAGAACTCCAGGACTGCAAAATCGCTCCTCTGATGGTTGCATACATGCTAGAACGAGAGTTGGTTCGCAAGACGAGGTTTCTCCCAGTTGCTGGTGGGACAAGCAGTGTCTACATTGAGGTGCTGCATTTGACCCAGGGGACATGCTGGGAGCAGATGTACACTCCGGGAGGAGAAGTGAGGAACGATGATGTAGACCAAAGCTTGATCATTGCTGCCAGGAATATAGTAAGAAGAGCAACAGTATCAGCAGATCCGTTAGCATCTCTATTGGAGATGTGTCACAGCACACAAATTGGGGGAATAAGGATGGTAGACATCCTTCGGCAAAACCCAACAGAGGAACAAGCCGTGGATATATGCAAGGCAGCAATGGGCTTGAGGATTAGCTCATCTTTCAGCTTTGGTGGATTCACTTTTAAAAGAACAAGTGGATCGTCAGTCAAAAAAGAAGAAGAAGTGCTAACAGGCAACCTTCAAACATTGAAAATAAGAGTACATGAGGGGTATGAAGAGTTCACAATGGTTGGGAGAAGAGCAACGGCCATTCTCAGGAAAGCAACCAGAAGGCTGATCCAGCTAATAGTAAGTGGGAGAGACGAGCAGTCAATTGCTGAAGCAATAATTGTGGCCATGGTATTCTCACAAGAGGACTGCATGATTAAAGCAGTTAGAGGTGACCTGAATTTTGTCAATAGGGCGAACCAGCGACTAAACCCAATGCATCAACTCTTGAGGCATTTCCAAAAGGATGCAAAAGTGCTTTTCCAAAATTGGGGAATTGAACCCATTGACAATGTGATGGGAATGATCGGGGTAATGCCTGACATGACCCCAAGTACTGAGATGTCGCTGAGGGGAATAAGAGTCAGCAAGATGGGAGTAGATGAATACTCAAGCACAGAGCGAGTAGTAGTAAGCATCGACCGGTTTTTAAGAGTTCGAGACCAACGGGGGAACGTACTATTATCACCCGAAGAGGTCAGTGAGACACAAGGAACGGAGAAACTGACAATCACTTATTCGTCATCAATGATGTGGGAGATCAATGGTCCTGAGTCGGTGTTGGTCAATACTTATCAGTGGATAATTAGAAACTGGGAAACTGTAAAAATTCAATGGTCACAGGATCCCACAATGCTGTATAATAAGATGGAATTCGAGCCATTCCAGTCTCTAGTCCCTAAGGCAGCCAGAGGTCAATACAGTGGGTTTGTGAGAACACTATTCCAGCAAATGCGAGATGTGCTTGGAACATTTGACACTGTTCAGATAGTAAAACTCCTCCCCTTTGCTGCCGCCCCACCGGAACAAAGTAGGATGCAGTTCTCCTCCCTGACTGTGAATGTAAGAGGATCAGGAATGAGGATACTGGTAAGAGGCAATTCACCAGTGTTCAATTACAACAAGGCCACCAAGAGGCTCACAGTTCTCGGGAAAGATGCAGGTGCATTGACCGAAGATCCAGATGAAGGCACAGCTGGAGTGGAGTCTGCTGTTTTAAGAGGATTCCTCATTTTGGGCAAAGAAGACAAGAGATATGGCCCAGCATTGAGCATCAATGAGCTGAGCAATCTTGCAAAGGGAGAGAAGGCTAATGTGCTAATTGGGCAAGGAGACGTAGTGTTGGTGATGAAACGGAAACGGGACTCTAGCATACTTACTGACAGCCAGACAGCGACCAAAAGAATTCGGATGGCCATCAATTAG</t>
         </is>
       </c>
-      <c r="BM1" t="inlineStr">
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
         <is>
           <t>&gt;Flu-0316|A_PB1</t>
         </is>
       </c>
-      <c r="BN1" t="inlineStr">
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
         <is>
           <t>ATGGATGTCAATCCGACTTTACTTTTCTTGAAAGTTCCAGCGCAAAATGCCATAAGCACCACATTCCCGTATACTGGAGATCCTCCATACAGCCATGGAACAGGAACAGGATATACCATGGACACAGTTAACAGAACACATCAGTATTCAGAAAAAGGGAAATGGACAACAAACTCAGAAACTGGAGCACCTCAACTCAATCCAATTGATGGACCATTGCCTGAGGGCAATGAACCAAGTGGGTATGCACAAACGGACTGTGTCCTTGAAGCAATGGCTTTCCTTGAAGAGTCCCACCCAGGAATCTTTGAAAACTCGTGTCTTGAAACGATGGAAGTTGTTCAACAAACAAGAGTGGACAAGTTGACCCAAGGCCGTCAGACCTATGATTGGACGTTAAACAGGAATCAGCCGGCTGCAACTGCATTAGCTAATACTATAGAGGTCTTCAGATCTAACGGCCTCACAGCCAATGAATCAGGAAGGCTAATAGATTTTCTCAAGGATGTGATGGAATCAATGGATAAGGAGGAAATGGAAATAACAACGCATTTCCAAAGGAAAAGAAGAGTGAGAGACAACATGACCAAGAAAATGGTCACACAAAGGACAATAGGAAAGAAGAAACAGAGGCTAAATAAAAAGAGCTATCTAATAAGAGCATTGACACTGAACACGATGACAAAAGACGCCGAAAGAGGCAAATTAAAAAGAAGGGCAATTGCAACACCTGGAATGCAAATCAGAGGGTTTGTGTACTTTGTTGAGACATTAGCGAGGAGCATTTGTGATAAGCTTGAACAATCTGGACTCCCAGTTGGGGGCAATGAAAAGAAGGCTAAACTGGCAAATGTTGTGAGAAAAATGATGACTAATTCGCAGGACACAGAGCTCTCTTTCACAATCACTGGAGACAACACCAAATGGAATGAAAATCAGAACCCTAGGATGTTTCTGGCAATGATAACATATATAACAAGGAACCAACCTGAATGGTTCAGGAATGTCTTAAGCATTGCACCTATAATGTTCTCAAATAAAATGGCAAGACTAGGGAAAGGGTACATGTTCGAAAGTAAGAGCATGAAGCTCCGAACACAAATACCAGCAGAAATGCTAGCAAGCATTGATCTGAAGTACTTCAATGAGTCAACAAGAAAGAAAATAGAGAAGATAAGACCTCTTCTAATAGATGGTACAGCCTCATTAAGCCCAGGAATGATGATGGGCATGTTCAATATGCTGAGTACAGTTTTGGGAGTTTCGATTCTAAATCTAGGACAAAGGAGGTACACCAAAACAACATACTGGTGGGACGGACTCCAATCCTCTGATGACTTTGCTCTCATAGTGAATGCTCCGAATCATGAGGGAATACAAGCAGGGGTAGACAGATTCTATAGAACCTGCAAGCTGGTCGGAATCAACATGAGCAAAAAGAAGTCCTACATAAACAGGACAGGAACATTTGAATTCACAAGTTTTTTCTACCGCTATGGATTTGTAGCCAACTTCAGTATGGAGTTGCCCAGCTTTGGAGTGTCTGGGATCAATGAATCTGCAGACATGAGCATTGGAGTAACAGTAATAAAGAACAACATGATCAACAATGATCTTGGACCAGCAACAGCTCAAATGGCTCTTCAGCTATTCATCAAGGATTACAGATACACATACCGGTGTCACAGAGGAGACACACAAATTCAGACAAGGAGGTCATTCGAGCTGAAGAAGTTGTGGGAACAGACCCGTTCAAAAGCAGGACTGCTGGTCTCAGATGGAGGACCAAATCTATACAATATTCGGAATCTTCACATTCCAGAAGTCTGCTTGAAATGGGAGCTAATGGACGAAGACTATCAGGGAAGGCTTTGTAATCCCCTGAACCCGTTTGTCAGCCACAAGGAAATAGAGTCTGTGAACAACGCAGTGGTGATGCCAGCTCATGGCCCGGCCAAGAGCATGGAATATGATGCTGTTGCCACCACTCACTCCTGGATACCGAAGAGGAACCGCTCCATTCTCAATACAAGCCAAAGGGGAATCCTTGAAGACGAACAGATGTATCAAAAGTGCTGCAACCTGTTCGAAAAATTCTTCCCTAGCAGTTCATACAGGAGGCCAGTTGGAATTTCCAGCATGGTGGAGGCCATGGTTTCTAGGGCCCGAATTGACGCACGAATTGACTTCGAATCTGGACGGATTAAGAAGGAGGAGTTTGCTAAGATCATGAAGATCTGTTCCACCATTGAAGAGCTCAGACGGCAGAAATAG</t>
         </is>
       </c>
-      <c r="BO1" t="inlineStr">
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
         <is>
           <t>&gt;Flu-0316|A_PA</t>
         </is>
       </c>
-      <c r="BP1" t="inlineStr">
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
         <is>
           <t>ATGGAAGACTTTGTGCGACAATGCTTCAATCCAATGATTGTCGAGCTTGCGGAAAAAGCAATGAAAGAATATGGGGAAGATCCGAAAATCGAGACAAACAAATTTGCCGCAATATGCACACACTTAGAAGTCTGTTTCATGTATTCGGATTTCCATTTTATTAATGAACGAGGCGAATCAATGATTGTAGAATCTGGCGATCCAAATGCATTATTGAAACACCGATTTGAGATAATAGAAGGGAGAGACCGGGCAATGGCCTGGACAGTGGTGAATAGTATCTGCAACACCACAGGGGTCGAAAAGCCCAAATTCCTCCCTGATTTGTATGACTACAAAGAGAACCGATTCATTGAAATTGGAGTAACGCGAAGGGAAGTTCACATATACTATTTAGAAAAAGCCAACAAGATAAAGTCAGAGAAAACACATATTCACATATTCTCATTCACTGGAGAGGAAATGGCCACCAAGGCGGACTACACCCTTGATGAAGAGAGCAGAGCAAGAATAAAAACCAGACTGTTCACTATAAGACAAGAAATGGCCAGTAGAGGTCTATGGGATTCCTTTCGTCAATCCGAGAGAGGCGAAGAGACAATTGAAGAAAGATTTGAAATCGCAGGAACCATGCGCAGGCTTGCCAACCAAAGTCTTCCACCGAACTTCTCCAGCCTTGAAAACTTTAGAGCCTATGTGGATGGATTCGAACCGAACGGCTGCATTGAGGGCAAACTTTCTCAAATGTCAAAAGAAGTGAACGCCAGGATTGAGCCATTTCTGAAGACAACACCACGCCCTCTCAGATTACCTGATGGGCCTCCCTGTTCTCAGCGGTCGAAGTTCTTGCTGATGGATGCCCTTAAGTTGAGCATCGAAGACCCTAGCCATGAGGGGGAGGGCATACCGCTGTATGATGCAATCAAATGCATGAAGACATTTTTTGGCTGGAAAGAGCCCAACATCGTAAAGCCGCATGAGAAAGGCATAAACCCTAATTACCTCCTGACTTGGAAGCAGGTGCTGGCAGAACTTCAAGACATTGAAAATGAGGAGAAAATTCCAAAGACAAAGAACATGAAGAAAACAAGCCAATTGAAGTGGGCACTTGGTGAGAACATGGCTCCAGAGAAAGTGGACTTTGAGGACTGCAAAGATGTTAGCGATCTAAGACAGTACGACAGTAACGAACCAGAGTCTAGAACACTAGCAAGCTGGATTCAGAGTGAATTCAACAAGGCATGCGAACTGACAGATTCGAGTTGGATTGAACTTGATGAGATAGGGGAAGACGTTGCTCCAATCGAACACATTGCGAGTGTGAGGAGGAACTATTTCACAGCGGAGGTATCCCATTGCAGGGCCACTGAATACATAATGAAGGGAGTATACATAAACACAGCCCTATTGAATGCATCCTGTGCAGCCATGGATGACTTCCAATTGATTCCAATGATAAGTAAGTGCAGAACTAAAGAAGGAAGACGGAAGACAAATCTGTATGGATTCATTATAAAAGGAAGATCCCATTTGAGGAATGACACCGATGTGGTAAACTTTGTGAGCATGGAATTCTCTCTAACTGACCCGAGGCTGGAGCCACACAAATGGGAGAAGTACTGTGTTCTTGAGATAGGAGACATGCTCCTACGGACTGCAATAGGCCAAGTGTCGAGGCCCATGTTCCTGTATGTGAGAACCAATGGGACTTCCAAGATCAAAATGAAATGGGGCATGGAGATGAGGCGATGCCTTCTTCAGTCCCTTCAACAAATTGAGAGCATGATTGAGGCCGAATCTTCTGTCAAAGAGAAGGACATGTCCAAGGAATTCTTTGAAAACAAATCAGAAACATGGCCAATTGGAGAATCACCCAAAGGGGTGGAGGAAGGCTCTATTGGGAAAGTATGCAGAACATTGCTAGCAAAGTCTGTGTTCAACAGCCTATATGCATCTCCACAACTCGAGGGGTTTTCAGCTGAATCAAGAAAATTGCTTCTCATTGTTCAGGCACTTAGGGACAACCTGGAACCTGGAACCTTCGATCTTGGGGGGCTATATGAAGCAATTGAGGAGTGCCTGATTAACGATCCCTGGGTTTTGCTTAATGCATCTTGGTTCAACTCCTTCCTCACACATGCACTGAAATAG</t>
         </is>
       </c>
-      <c r="BQ1" t="inlineStr">
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
         <is>
           <t>&gt;Flu-0316|A_HA</t>
         </is>
       </c>
-      <c r="BR1" t="inlineStr">
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
         <is>
           <t>ATGGAGAACATAGTACTACTTCTTGCAATAGTTAGCCTTGTTAAAAGTGACCAGATTTGCATTGGTTACCATGCAAACAATTCGACAGAGCAAGTTGACACGATAATGGAAAAGAACGTCACTGTTACACATGCCCAAGACATACTGGAAAAAACACACAACGGGAAGCTCTGTGATTTAAATGGGGTGAAGCCACTGATTTTAAAGGATTGTAGTGTAGCTGGATGGCTCCTCGGGAACCCAATGTGCGACGAATTCATCAGAGTGCCGGAATGGTCCTACATAGTGGAGCGAGCTAACCCAGCTAATGACCTCTGTTACCCAGGGAGCCTCAATGACTATGAAGAACTGAAACACATGTTGAGCAGAATAAATCATTTTGAGAAGATTCAGATCATTCCCAARAGTTCCTGGCCAAATCATGAAACATCACTAGGGGTGAGCGCAGCTTGTCCATACCAGGGAGCGCCCTCCTTTTTCAGAAATGTGGTGTGGCTTATCAAAAAGAACGATGCATACCCAACAATAAAGATAAGCTACAATAATACTAATCGGGAAGATCTCTTGATACTGTGGGGGATTCATCATCCCAACAATGCAGAAGAGCAGACAAATCTCTACAAAAACCCAACCACCTACATTTCAGTTGGAACATCAACTTTAAACCAGAGATTGGCACCAAAAATAGCTACTAGATCCCAAGTAAACGGGCAACGTGGAAGAATGGACTTCTTTTGGACAATCTTAAAACCAGATGATGCAATCCATTTCGAGAGTAACGGAAATTTCATTGCTCCAGAATATGCATACAAAATTGTCAAGAAAGGGGACTCAACAATTATGAAAAGTGGAGTGGAATATGGCCACTGCAACACCAAATGTCAAACCCCAGTAGGTGCTATAAATTCTAGTATGCCATTCCACAACATACATCCTCTCACCATTGGGGAATGCCCCAAATACGTGAAATCAAACAAGTTGGTCCTTGCGACTGGGCTCAGAAATAGTCCTCTAAGAGAAAAGAGAAGAAAAAGAGGTCTGTTTGGGGCGATAGCAGGGTTTATAGAGGGAGGATGGCAGGGAATGGTTGATGGTTGGTATGGGTACCATCATAGCAATGAGCAGGGGAGTGGGTACGCTGCGGACAAAGAATCCACCCAAAAGGCAATAGATGGAGTTACCAATAAGGTCAACTCAATCATTGACAAAATGAACACTCAATTTGAGGCAGTTGGAAGGGAGTTTAATAACTTAGAAAGGAGGATAGAGAATTTGAACAAGAAAATGGAAGACGGATTCCTAGATGTCTGGACCTATAATGCTGAACTTCTAGTTCTTATGGAAAACGAGAGGACTCTAGATTTCCATGATTCAAATGTCAAGAACCTTTACGACAAAGTCAGATTACAGCTTAGGGATAATGCAAAGGAGCTGGGTAACGGCTGTTTCGAATTCTATCACAAATGTGATAATGAATGTATGGAAAGTGTGAGAAATGGGACGTATGACTACCCTCAGTATTCAGAAGAAGCAAGATTAAAAAGAGAAGAAATAAGCGGAGTGAAATTAGAATCAGTAGGAACTTACCAGATACTGTCAATTTATTCAACAGCGGCAAGTTCCCTAGCACTGGCAATCATGATGGCTGGTCTATCTTTATGGATGTGCTCCAATGGGTCGTTACAATGCAGAATTTGCATTTAG</t>
         </is>
       </c>
-      <c r="BS1" t="inlineStr">
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
         <is>
           <t>&gt;Flu-0316|A_NP</t>
         </is>
       </c>
-      <c r="BT1" t="inlineStr">
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
         <is>
           <t>ATGGCGTCTCAAGGCACCAAACGATCCTATGAACAAATGGAAACTGGTGGGGAACGCCAGAATGCCACTGAAATCAGAGCATCTGTTGGAAGAATGGTTGGCGGAATAGGAAGATTCTACATACAGATGTGCACTGAGCTCAAACTCAGTGATTATGAAGGGAGGCTGATCCAAAACAGCATAACCATAGAAAGGATGGTTCTCTCGGCATTTGATGAGAGGAGGAACAAGTACCTGGAGGAACATCCCAGTGCCGGGAAGGATCCCAAGAAGACTGGAGGTCCAATCTACAGGAGGAGAGATGGCAAATGGGTGAGAGAGTTGATCCTCTACGACAAAGAAGAGATCAGAAGAATTTGGCGTCAAGCTAATAATGGAGAGGATGCAACTGCTGGTCTCACTCATTTGATGATTTGGCATTCCAATCTGAATGATGCAACATACCAGAGAACAAGGGCACTTGTGCGTACTGGAATGGACCCTAGAATGTGCTCTCTGATGCAAGGATCAACCCTCCCTAGGAGATCCGGGGCTGCTGGAGCAGCAGTGAAAGGAGTTGGAACAATGGTGATGGAACTAATTCGAATGATCAAGCGAGGGATCAATGATCGGAATTTCTGGAGAGGCGAAAACGGTCGGAGAACCAGGATTGCCTACGAGAGAATGTGCAACATCCTCAAGGGAAAGTTCCAAACAGCAGCACAACGGGCAATGATGGACCAAGTGAGAGAAAGCCGGAATCCTGGGAATGCTGAAATTGAAGATCTCATCTTTCTCGCACGATCTGCTCTCATCCTGAGGGGATCAGTGGCTCATAAGTCCTGTCTGCCTGCTTGCGTATATGGACTTGCTGTAGCCAGTGGATATGACTTTGAAAGAGAGGGATATTCTCTAGTCGGAATTGATCCTTTCCGTCTGCTCCAAAACAGCCAAGTCTTCAGTCTCATCAGACCGAACGAAAATCCAGCTCATAAGAGTCAGCTGGTATGGATGGCATGCCACTCTGCGGCATTTGAGGATCTGAGAGTTTCAAGCTTCATCAGAGGGACAAGAGTAGTCCCAAGAGGACAACTGTCCACCAGAGGAGTTCAGATTGCTTCAAATGAAAACATGGAGACAATGGACTCCAGTACTCTTGAACTGAGGAGCAGATACTGGGCTATAAGAACAAGAAGTGGAGGAAACACTAACCAACAGAGAGCATCTGCAGGACAAATCAGCGTGCAGCCCACATTCTCTGTGCAAAGAAACCTCCCATTCGAGAGAGCAACCATCATGGCAGCATTTACGGGAAACACTGAAGGCAGAACTTCAGACATGAGAACGGAGATCATAAGGATGATGGAAAATGCCAGACCTGAAGATGTGTCTTTCCAGGGGCGGGGAGTCTTCGAGCTCTCGGACGAAAAGGCAACGAACCCGATCGTGCCTTCCTTTGACATGAGTAATGAAGGATCTTATTTCTTCGGAGACAATGCAGAGGAGTATGACAATTAA</t>
         </is>
       </c>
-      <c r="BU1" t="inlineStr">
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
         <is>
           <t>&gt;Flu-0316|A_NA</t>
         </is>
       </c>
-      <c r="BV1" t="inlineStr">
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
         <is>
           <t>ATGAATCCAAATCAAAAGATAACAACCATTGGATCAATCTGTATGGTAATTGGGACAGTCAGCTTGATGCTGCAAATTGGGAACATAATCTCAATATGGGTTAGCCATTCAATCCAAACAGGGAATCAATACCAGCCTGAACCATGCAATCAAAGCATCATTACCTATGAGAACAACACCTGGGTAAATCAGACGTATGTCAACATCAGCAATAACAATTTTCTTGCTGAGCAGGCTGTTACTTCGGTAACATTAGCGGGCAATTCATCTCTTTGCCCTATTAGTGGGTGGGCAATATACAGTAAGGACAACGGTATAAGAATTGGGTCCAAGGGGGATGTGTTTGTCATAAGAGAACCGTTCATCTCATGCTCCCACTTGGAATGCAGAACCTTTTTCCTGACTCAGGGAGCTCTGCTGAATGACAAACATTCTAATGGGACAGTTAAGGATAGAAGCCCTTATAGAACTTTGATGAGTTGTCCCGTGGGTGAGGCTCCTTCCCCGTACAATTCAAGATTTGAGTCTGTTGCTTGGTCGGCAAGTGCTTGTCATGATGGCATCAGTTGGTTGACAATCGGTATTTCTGGTCCAGACAATGGAGCTGTGGCTGTATTGAAGTACAATGGCATAATAACGGATACTATCAAGAGTTGGAGAAACAACATTTTGAGAACTCAAGAATCTGAATGTGCTTGCGTAAATGGCTCTTGCTTCACCGTAATGACTGATGGACCAAGCAATGGGCAGGCCTCGTATAAAATCTTCAAGATAGAGAAAGGGAAAGTTGTCAAATCAGTTGAATTGAATGCCCCTAATTACCACTACGAGGAATGTTCCTGTTATCCTGATGCGGGTGATATTATATGTGTGTGCAGGGACAATTGGCACGGCTCAAACCGGCCGTGGATATCTTTTAATCAAAATCTGGAGTATCAAATAGGATATATATGCAGTGGGGTTTTCGGGGACAATCCCCGCCCCAATGATGGAACAGGCAGTTGCAGTCCAATGTCCTCTAATGGGGCATATGGGGTAAAAGGGTTTTCATTTAAGTACGGTAATGGGGTTTGGATCGGAAGAACAAAAGGCACTAGTTCCAGAAGCGGCTTTGAGATGATTTGGGACCCGAATGGGTGGACTGAGACGGACAGTAGTTTCTCAGTGAAGCAAGACATTGTAGAAATAACTGACTGGTCAGGATATAGTGGGAGTTTTGTCCAGCATCCAGAACTGACAGGATTAGATTGCATGAGGCCTTGTTTCTGGGTTGAGCTAATTAGAGGGAGGCCCAAAGAGAACACAATTTGGACTAGCGGGAGCAGCATATCCTTTTGTGGTGTAAATAGTGACACTGTGGGTTGGTCTTGGCCAGACGGTGCTGAGTTGCCATTCACCATTGACAAGTAG</t>
         </is>
       </c>
-      <c r="BW1" t="inlineStr">
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
         <is>
           <t>&gt;Flu-0316|A_MP</t>
         </is>
       </c>
-      <c r="BX1" t="inlineStr">
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
         <is>
           <t>ATGAGTCTTCTAACCGAGGTCGAAACGTACGTTCTCTCTATCGTCCCGTCGGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTTGAAGATGTCTTTGCAGGGAAGAACACCGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATACTGTCACCTCTGACTAAGGGGATTTTGGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCTCTAAGTGGAAATGGAGACCCAAACAACATGGACAGGGCAGTCAAGTTGTACAGGAAACTGAAGAGAGAAATAACATTCCATGGGGCTAAAGAAGTTGCACTTAGTTACTCAACCGGTGCACTTGCCAGTTGTATGGGTCTCATATACAACAGGATGGGGACGGTGACCGCAGAAGTGGCATTGGGCCTAGTGTGTGCCACCTGTGAGCAGATTGCTGATTCACAGCATCGGTCTCACAGACAGATAGCTACCACCACCAACCCACTAATCAGACATGAAAACAGAATGGTTTTGGCCAGTACTACAGCTAAGGCTATGGAGCAGATGGCTGGATCGAGTGAGCAAGCAGTGGAAGCCATGGAGGTTGCTAGTCAGGCTAGGCAAATGGTGCAGGCGATGAGGACCATTGGAACTCATCCTAGCTCCAGTGCCGGTCTGAGAGATGATCTCCTTGAAAATTTGCAGGCCTACCAAAAACGAATGGGAGTGCAACTGCAGCGATTCAAGTGATCCTCTCGTTATTGCAGCAAGTATCATTGGGATCTTGCACTTGATATTGTGGATTCTTGATCGCCTTTTCTTCAAATGCGTTTATCGTCGCCTTAAATACGGTTTGAAAGGAGGGCCTTCTACGGAAGGAGTACCTGAGTCCATGAGGGAAGAGTACCGGCAGGAACAGCAGAGTGCTGTGGATGTTGACGATGGTCATTTTGTCAACATAGAGATGGAGTAA</t>
         </is>
       </c>
-      <c r="BY1" t="inlineStr">
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
         <is>
           <t>&gt;Flu-0316|A_NS</t>
         </is>
       </c>
-      <c r="BZ1" t="inlineStr">
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
         <is>
           <t>ATGGATTCCAACACTGTGTCAAGCTTTCAGGTAGACTGCTTTCTTTGGCATGTCCGCAAACAATTTGCAGACCAAGAACTGGGTGATGCCCCATTCCTTGACCGGCTCCGCCGAGACCAGAAGTCTCTAAGAGGAAGAGGCAGCACTCTTGGTCTGGACATCGAGACGGCCACTCGTGCTGGAAAGCAGATAGTGGAGAGGATTCTGGAGGAAGAATCCGACGAGGCACTCAAAATGACTATTGCCTCTGTGCCTGCTCCACGCTACCTAACTGACATGACTCTTGAAGAGATGTCAAGAGACTGGTTCATGCTCATGCCCAAGCAAAAAGTGGCAGGCTCCCTCTGTATCAGAATGGACCAGGCGATTATGGATAAGAACATCATACTGAAGGCAAACTTCAGTGTGATCTTCAATCGGCTGGAGACACTAATACTACTCAGAGCTTTCACTGAAGAGGGAGCAATTGTCGGCGAAATTTCACCATTGCCTTCTCTTCCAGGACATACTGATGAGGATGTCAAAAATGCAATTGGGGTCCTCATCGGAGGACTTGAATGGAATGATAACACAGTTCGAGTCTCTGAAATTTTACAGAGATTCGCTTGGAGAAGCAGTAATGAGGATGGGAGACCTCCACTCCCTCCAAAGCAGAAACGGAAAATGGAGAGAACAATTGAGTCAGAAGTTTGAAGAAATAAGGTGGCTGATTGAAGAGGTGCGACACAGACTAAAGATCACAGAAAATAGTTTTGAACAAATAACATTTATGCAAGCCTTACAACTACTGCTTGAAGTGGAGCAAGAGATACGAACTTTCTCGTTTCAGCTTATTTAA</t>
         </is>
       </c>
-      <c r="CA1" t="inlineStr">
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
         <is>
           <t>&gt;Flu-0317|A_PB2</t>
         </is>
       </c>
-      <c r="CB1" t="inlineStr">
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
         <is>
           <t>ATGGAGAGAATAAAAGAACTAAGAGATCTAATGTCACAGTCTCGCACTCGCGAGATACTGACCAAAACCACTGTTGACCACATGGCCATAATCAAAAAGTACACATCGGGAAGGCAAGAGAAGAACCCCGCACTCAGAATGAAATGGATGATGGCAATGAAATATCCAATTACAGCAGATAAGCGAATAATGGAAATGATCCCTGAGAGGAATGAACAAGGGCAAACTCTCTGGAGCAAAACAAACGATGCCGGATCAGACCGAGTGATGGTATCACCCCTGGCTGTGACATGGTGGAACAGGAACGGACCAACAACAAGTACAGTTCACTACCCAAAGGTATATAAAACTTATTTCGAAAAAGTTAAAAGGTTGAAACACGGGACCTTTGGCCCTGTGCACTTCAGAAACCAAGTTAAGATAAGACGGAGGGTCGATATAAACCCGGGCCATGCTGACCTTAGTGCCAAAGAGGCACAGGATGTAATCATGGAAGTCGTCTTCCCAAATGAAGTGGGAGCTAGGATATTGACGTCGGAGTCACAACTGACGATAACAAAGGAGAAAAAGGAAGAACTCCAGGACTGCAAAATCGCTCCTCTGATGGTTGCATACATGCTAGAACGAGAGTTGGTTCGCAAGACGAGGTTTCTCCCAGTTGCTGGTGGGACAAGCAGTGTCTACATTGAGGTGCTGCATTTGACCCAGGGGACATGCTGGGAGCAGATGTACACTCCGGGAGGAGAAGTGAGGAACGATGATGTAGACCAAAGCTTGATCATTGCTGCCAGGAATATAGTAAGAAGAGCAACAGTATCAGCAGATCCGTTAGCATCTCTATTGGAGATGTGTCACAGCACACAAATTGGGGGAATAAGGATGGTAGACATCCTTCGGCAAAACCCAACAGAGGAACAAGCCGTGGATATATGCAAGGCAGCAATGGGCTTGAGGATTAGCTCATCTTTCAGCTTTGGTGGATTCACTTTTAAAAGAACAAGTGGATCGTCAGTCAAAAAAGAAGAAGAAGTGCTAACAGGCAACCTTCAAACATTGAAAATAAGAGTACATGAGGGGTATGAAGAGTTCACAATGGTTGGGAGAAGAGCAACGGCCATTCTCAGGAAAGCAACCAGAAGGCTGATCCAGCTAATAGTAAGTGGGAGAGACGAGCAGTCAATTGCTGAAGCAATAATTGTGGCCATGGTATTCTCACAAGAGGACTGCATGATTAAAGCAGTTAGAGGTGACCTGAATTTTGTCAATAGGGCGAACCAGCGACTAAACCCAATGCATCAACTCTTGAGGCATTTCCAAAAGGATGCAAAAGTGCTTTTCCAAAATTGGGGAATTGAACCCATTGACAATGTGATGGGAATGATCGGGGTAATGCCTGACATGACCCCAAGTACTGAGATGTCGCTGAGGGGAATAAGAGTCAGCAAGATGGGAGTAGATGAATACTCAAGCACAGAGCGAGTAGTAGTAAGCATCGACCGGTTTTTAAGAGTTCGAGACCAACGGGGGAACGTACTATTATCACCCGAAGAGGTCAGTGAGACACAAGGAACGGAGAAACTGACAATCACTTATTCGTCATCAATGATGTGGGAGATCAATGGTCCTGAGTCGGTGTTGGTCAATACTTATCAGTGGATAATTAGAAACTGGGAAACTGTAAAAATTCAATGGTCACAGGATCCCACAATGCTGTATAATAAGATGGAATTCGAGCCATTCCAGTCTCTAGTCCCTAAGGCAGCCAGAGGTCAATACAGTGGGTTTGTGAGAACACTATTCCAGCAAATGCGAGATGTGCTTGGAACATTTGACACTGTTCAGATAGTAAAACTCCTCCCCTTTGCTGCCGCCCCACCGGAACAAAGTAGGATGCAGTTCTCCTCCCTGACTGTGAATGTAAGAGGATCAGGAATGAGGATACTGGTAAGAGGCAATTCACCAGTGTTCAATTACAACAAGGCCACCAAGAGGCTCACAGTTCTCGGGAAAGATGCAGGTGCATTGACCGAAGATCCAGATGAAGGCACAGCTGGAGTGGAGTCTGCTGTTTTAAGAGGATTCCTCATTTTGGGCAAAGAAGACAAGAGATATGGCCCAGCATTGAGCATCAATGAGCTGAGCAATCTTGCAAAGGGAGAGAAGGCTAATGTGCTAATTGGGCAAGGAGACGTAGTGTTGGTGATGAAACGGAAACGGGACTCTAGCATACTTACTGACAGCCAGACAGCGACCAAAAGAATTCGGATGGCCATCAATTAG</t>
         </is>
       </c>
-      <c r="CC1" t="inlineStr">
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
         <is>
           <t>&gt;Flu-0317|A_PB1</t>
         </is>
       </c>
-      <c r="CD1" t="inlineStr">
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
         <is>
           <t>ATGGATGTCAATCCGACTTTACTTTTCTTGAAAGTTCCAGCGCAAAATGCCATAAGCACCACATTCCCGTATACTGGAGATCCTCCATACAGCCATGGAACAGGAACAGGATATACCATGGACACAGTTAACAGAACACATCAGTATTCAGAAAAAGGGAAATGGACAACAAACTCAGAAACTGGAGCACCTCAACTCAATCCAATTGATGGACCATTGCCTGAGGGCAATGAACCAAGTGGGTATGCACAAACGGACTGTGTCCTTGAAGCAATGGCTTTCCTTGAAGAGTCCCACCCAGGAATCTTTGAAAACTCGTGTCTTGAAACGATGGAAGTTGTTCAACAAACAAGAGTGGACAAGTTGACCCAAGGCCGTCAGACCTATGATTGGACGTTAAACAGGAATCAGCCGGCTGCAACTGCATTAGCTAATACTATAGAGGTCTTCAGATCTAACGGCCTCACAGCCAATGAATCAGGAAGGCTAATAGATTTTCTCAAGGATGTGATGGAATCAATGGATAAGGAGGAAATGGAAATAACAACGCATTTCCAAAGGAAAAGAAGAGTGAGAGACAACATGACCAAGAAAATGGTCACACAAAGGACAATAGGAAAGAAGAAACAGAGGCTAAATAAAAAGAGCTATCTAATAAGAGCATTGACACTGAACACGATGACAAAAGACGCCGAAAGAGGCAAATTAAAAAGAAGGGCAATTGCAACACCTGGAATGCAAATCAGAGGGTTTGTGTACTTTGTTGAGACATTAGCGAGGAGCATTTGTGATAAGCTTGAACAATCTGGACTCCCAGTTGGGGGCAATGAAAAGAAGGCTAAACTGGCAAATGTTGTGAGAAAAATGATGACTAATTCGCAGGACACAGAGCTCTCTTTCACAATCACTGGAGACAACACCAAATGGAATGAAAATCAGAACCCTAGGATGTTTCTGGCAATGATAACATATATAACAAGGAACCAACCTGAATGGTTCAGGAATGTCTTAAGCATTGCACCTATAATGTTCTCAAATAAAATGGCAAGACTAGGGAAAGGGTACATGTTCGAAAGTAAGAGCATGAAGCTCCGAACACAAATACCAGCAGAAATGCTAGCAAGCATTGATCTGAAGTACTTCAATGAGTCAACAAGAAAGAAAATAGAGAAGATAAGACCTCTTCTAATAGATGGTACAGCCTCATTAAGCCCAGGAATGATGATGGGCATGTTCAATATGCTGAGTACAGTTTTGGGAGTTTCGATTCTAAATCTAGGACAAAGGAGGTACACCAAAACAACATACTGGTGGGACGGACTCCAATCCTCTGATGACTTTGCTCTCATAGTGAATGCTCCGAATCATGAGGGAATACAAGCAGGGGTAGACAGATTCTATAGAACCTGCAAGCTGGTCGGAATCAACATGAGCAAAAAGAAGTCCTACATAAACAGGACAGGAACATTTGAATTCACAAGTTTTTTCTACCGCTATGGATTTGTAGCCAACTTCAGTATGGAGTTGCCCAGCTTTGGAGTGTCTGGGATCAATGAATCTGCAGACATGAGCATTGGAGTAACAGTAATAAAGAACAACATGATCAACAATGATCTTGGACCAGCAACAGCTCAAATGGCTCTTCAGCTATTCATCAAGGATTACAGATACACATACCGGTGTCACAGAGGAGACACACAAATTCAGACAAGGAGGTCATTCGAGCTGAAGAAGTTGTGGGAACAGACCCGTTCAAAAGCAGGACTGCTGGTCTCAGATGGAGGACCAAATCTATACAATATTCGGAATCTTCACATTCCAGAAGTCTGCTTGAAATGGGAGCTAATGGACGAAGACTATCAGGGAAGGCTTTGTAATCCCCTGAACCCGTTTGTCAGCCACAAGGAAATAGAGTCTGTGAACAACGCAGTGGTGATGCCAGCTCATGGCCCGGCCAAGAGCATGGAATATGATGCTGTTGCCACCACTCACTCCTGGATACCGAAGAGGAACCGCTCCATTCTCAATACAAGCCAAAGGGGAATCCTTGAAGACGAACAGATGTATCAAAAGTGCTGCAACCTGTTCGAAAAATTCTTCCCTAGCAGTTCATACAGGAGGCCAGTTGGAATTTCCAGCATGGTGGAGGCCATGGTTTCTAGGGCCCGAATTGACGCACGAATTGACTTCGAATCTGGACGGATTAAGAAGGAGGAGTTTGCTAAGATCATGAAGATCTGTTCCACCATTGAAGAGCTCAGACGGCAGAAATAG</t>
         </is>
       </c>
-      <c r="CE1" t="inlineStr">
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
         <is>
           <t>&gt;Flu-0317|A_PA</t>
         </is>
       </c>
-      <c r="CF1" t="inlineStr">
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
         <is>
           <t>ATGGAAGACTTTGTGCGACAATGCTTCAATCCAATGATTGTCGAGCTTGCGGAAAAAGCAATGAAAGAATATGGGGAAGATCCGAAAATCGAGACAAACAAATTTGCCGCAATATGCACACACTTAGAAGTCTGTTTCATGTATTCGGATTTCCATTTTATTAATGAACGAGGCGAATCAATGATTGTAGAATCTGGCGATCCAAATGCATTATTGAAACACCGATTTGAGATAATAGAAGGGAGAGACCGGGCAATGGCCTGGACAGTGGTGAATAGTATCTGCAACACCACAGGGGTCGAAAAGCCCAAATTCCTCCCTGATTTGTATGACTACAAAGAGAACCGATTCATTGAAATTGGAGTAACGCGAAGGGAAGTTCACATATACTATTTAGAAAAAGCCAACAAGATAAAGTCAGAGAAAACACATATTCACATATTCTCATTCACTGGAGAGGAAATGGCCACCAAGGCGGACTACACCCTTGATGAAGAGAGCAGAGCAAGAATAAAAACCAGACTGTTCACTATAAGACAAGAAATGGCCAGTAGAGGTCTATGGGATTCCTTTCGTCAATCCGAGAGAGGCGAAGAGACAATTGAAGAAAGATTTGAAATCGCAGGAACCATGCGCAGGCTTGCCAACCAAAGTCTTCCACCGAACTTCTCCAGCCTTGAAAACTTTAGAGCCTATGTGGATGGATTCGAACCGAACGGCTGCATTGAGGGCAAACTTTCTCAAATGTCAAAAGAAGTGAACGCCAGGATTGAGCCATTTCTGAAGACAACACCACGCCCTCTCAGATTACCTGATGGGCCTCCCTGTTCTCAGCGGTCGAAGTTCTTGCTGATGGATGCCCTTAAGTTGAGCATCGAAGACCCTAGCCATGAGGGGGAGGGCATACCGCTGTATGATGCAATCAAATGCATGAAGACATTTTTTGGCTGGAAAGAGCCCAACATCGTAAAGCCGCATGAGAAAGGCATAAACCCTAATTACCTCCTGACTTGGAAGCAGGTGCTGGCAGAACTTCAAGACATTGAAAATGAGGAGAAAATTCCAAAGACAAAGAACATGAAGAAAACAAGCCAATTGAAGTGGGCACTTGGTGAGAACATGGCTCCAGAGAAAGTGGACTTTGAGGACTGCAAAGATGTTAGCGATCTAAGACAGTACGACAGTAACGAACCAGAGTCTAGAACACTAGCAAGCTGGATTCAGAGTGAATTCAACAAGGCATGCGAACTGACAGATTCGAGTTGGATTGAACTTGATGAGATAGGGGAAGACGTTGCTCCAATCGAACACATTGCGAGTGTGAGGAGGAACTATTTCACAGCGGAGGTATCCCATTGCAGGGCCACTGAATACATAATGAAGGGAGTATACATAAACACAGCCCTATTGAATGCATCCTGTGCAGCCATGGATGACTTCCAATTGATTCCAATGATAAGTAAGTGCAGAACTAAAGAAGGAAGACGGAAGACAAATCTGTATGGATTCATTATAAAAGGAAGATCCCATTTGAGGAATGACACCGATGTGGTAAACTTTGTGAGCATGGAATTCTCTCTAACTGACCCGAGGCTGGAGCCACACAAATGGGAGAAGTACTGTGTTCTTGAGATAGGAGACATGCTCCTACGGACTGCAATAGGCCAAGTGTCGAGGCCCATGTTCCTGTATGTGAGAACCAATGGGACTTCCAAGATCAAAATGAAATGGGGCATGGAGATGAGGCGATGCCTTCTTCAGTCCCTTCAACAAATTGAGAGCATGATTGAGGCCGAATCTTCTGTCAAAGAGAAGGACATGTCCAAGGAATTCTTTGAAAACAAATCAGAAACATGGCCAATTGGAGAATCACCCAAAGGGGTGGAGGAAGGCTCTATTGGGAAAGTATGCAGAACATTGCTAGCAAAGTCTGTGTTCAACAGCCTATATGCATCTCCACAACTCGAGGGGTTTTCAGCTGAATCAAGAAAATTGCTTCTCATTGTTCAGGCACTTAGGGACAACCTGGAACCTGGAACCTTCGATCTTGGGGGGCTATATGAAGCAATTGAGGAGTGCCTGATTAACGATCCCTGGGTTTTGCTTAATGCATCTTGGTTCAACTCCTTCCTCACACATGCACTGAAATAG</t>
         </is>
       </c>
-      <c r="CG1" t="inlineStr">
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
         <is>
           <t>&gt;Flu-0317|A_HA</t>
         </is>
       </c>
-      <c r="CH1" t="inlineStr">
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
         <is>
           <t>ATGGAGAACATAGTACTACTTCTTGCAATAGTTAGCCTTGTTAAAAGTGACCAGATTTGCATTGGTTACCATGCAAACAATTCGACAGAGCAAGTTGACACGATAATGGAAAAGAACGTCACTGTTACACATGCCCAAGACATACTGGAAAAAACACACAACGGGAAGCTCTGTGATTTAAATGGGGTGAAGCCACTGATTTTAAAGGATTGTAGTGTAGCTGGATGGCTCCTCGGGAACCCAATGTGCGACGAATTCATCAGAGTGCCGGAATGGTCCTACATAGTGGAGCGAGCTAACCCAGCTAATGACCTCTGTTACCCAGGGAGCCTCAATGACTATGAAGAACTGAAACACATGTTGAGCAGAATAAATCATTTTGAGAAGATTCAGATCATTCCCAAGAGTTCCTGGCCAAATCATGAAACATCACTAGGGGTGAGCGCAGCTTGTCCATACCAGGGAGCGCCCTCCTTTTTCAGAAATGTGGTGTGGCTTATCAAAAAGAACGATGCATACCCAACAATAAAGATAAGCTACAATAATACTAATCGGGAAGATCTCTTGATACTGTGGGGGATTCATCATCCCAACAATGCAGAAGAGCAGACAAATCTCTACAAAAACCCAACCACCTACATTTCAGTTGGAACATCAACTTTAAACCAGAGATTGGCACCAAAAATAGCTACTAGATCCCAAGTAAACGGGCAACGTGGAAGAATGGACTTCTTTTGGACAATCTTAAAACCAGATGATGCAATCCATTTCGAGAGTAACGGAAATTTCATTGCTCCAGAATATGCATACAAAATTGTCAAGAAAGGGGACTCAACAATTATGAAAAGTGGAGTGGAATATGGCCACTGCAACACCAAATGTCAAACCCCAGTAGGTGCTATAAATTCTAGTATGCCATTCCACAACATACATCCTCTCACCATTGGGGAATGCCCCAAATACGTGAAATCAAACAAGTTGGTCCTTGCGACTGGGCTCAGAAATAGTCCTCTAAGAGAAAAGAGAAGAAAAAGAGGTCTGTTTGGGGCGATAGCAGGGTTTATAGAGGGAGGATGGCAGGGAATGGTTGATGGTTGGTATGGGTACCATCATAGCAATGAGCAGGGGAGTGGGTACGCTGCGGACAAAGAATCCACCCAAAAGGCAATAGATGGAGTTACCAATAAGGTCAACTCAATCATTGACAAAATGAACACTCAATTTGAGGCAGTTGGAAGGGAGTTTAATAACTTAGAAAGGAGGATAGAGAATTTGAACAAGAAAATGGAAGACGGATTCCTAGATGTCTGGACCTATAATGCTGAACTTCTAGTTCTTATGGAAAACGAGAGGACTCTAGATTTCCATGATTCAAATGTCAAGAACCTTTACGACAAAGTCAGATTACAGCTTAGGGATAATGCAAAGGAGCTGGGTAACGGCTGTTTCGAATTCTATCACAAATGTGATAATGAATGTATGGAAAGTGTGAGAAATGGGACGTATGACTACCCTCAGTATTCAGAAGAAGCAAGATTAAAAAGAGAAGAAATAAGCGGAGTGAAATTAGAATCAGTAGGAACTTACCAGATACTGTCAATTTATTCAACAGCGGCAAGTTCCCTAGCACTGGCAATCATGATGGCTGGTCTATCTTTATGGATGTGCTCCAATGGGTCGTTACAATGCAGAATTTGCATTTAG</t>
         </is>
       </c>
-      <c r="CI1" t="inlineStr">
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
         <is>
           <t>&gt;Flu-0317|A_NP</t>
         </is>
       </c>
-      <c r="CJ1" t="inlineStr">
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
         <is>
           <t>ATGGCGTCTCAAGGCACCAAACGATCCTATGAACAAATGGAAACTGGTGGGGAACGCCAGAATGCCACTGAAATCAGAGCATCTGTTGGAAGAATGGTTGGCGGAATAGGAAGATTCTACATACAGATGTGCACTGAGCTCAAACTCAGTGATTATGAAGGGAGGCTGATCCAAAACAGCATAACCATAGAAAGGATGGTTCTCTCGGCATTTGATGAGAGGAGGAACAAGTACCTGGAGGAACATCCCAGTGCCGGGAAGGATCCCAAGAAGACTGGAGGTCCAATCTACAGGAGGAGAGATGGCAAATGGGTGAGAGAGTTGATCCTCTACGACAAAGAAGAGATCAGAAGAATTTGGCGTCAAGCTAATAATGGAGAGGATGCAACTGCTGGTCTCACTCATTTGATGATTTGGCATTCCAATCTGAATGATGCAACATACCAGAGAACAAGGGCACTTGTGCGTACTGGAATGGACCCTAGAATGTGCTCTCTGATGCAAGGATCAACCCTCCCTAGGAGATCCGGGGCTGCTGGAGCAGCAGTGAAAGGAGTTGGAACAATGGTGATGGAACTAATTCGAATGATCAAGCGAGGGATCAATGATCGGAATTTCTGGAGAGGCGAAAACGGTCGGAGAACCAGGATTGCCTACGAGAGAATGTGCAACATCCTCAAGGGAAAGTTCCAAACAGCAGCACAACGGGCAATGATGGACCAAGTGAGAGAAAGCCGGAATCCTGGGAATGCTGAAATTGAAGATCTCATCTTTCTCGCACGATCTGCTCTCATCCTGAGGGGATCAGTGGCTCATAAGTCCTGTCTGCCTGCTTGCGTATATGGACTTGCTGTAGCCAGTGGATATGACTTTGAAAGAGAGGGATATTCTCTAGTCGGAATTGATCCTTTCCGTCTGCTCCAAAACAGCCAAGTCTTCAGTCTCATCAGACCGAACGAAAATCCAGCTCATAAGAGTCAGCTGGTATGGATGGCATGCCACTCTGCGGCATTTGAGGATCTGAGAGTTTCAAGCTTCATCAGAGGGACAAGAGTAGTCCCAAGAGGACAACTGTCCACCAGAGGAGTTCAGATTGCTTCAAATGAAAACATGGAGACAATGGACTCCAGTACTCTTGAACTGAGGAGCAGATACTGGGCTATAAGAACAAGAAGTGGAGGAAACACTAACCAACAGAGAGCATCTGCAGGACAAATCAGCGTGCAGCCCACATTCTCTGTGCAAAGAAACCTCCCATTCGAGAGAGCAACCATCATGGCAGCATTTACGGGAAACACTGAAGGCAGAACTTCAGACATGAGAACGGAGATCATAAGGATGATGGAAAATGCCAGACCTGAAGATGTGTCTTTCCAGGGGCGGGGAGTCTTCGAGCTCTCGGACGAAAAGGCAACGAACCCGATCGTGCCTTCCTTTGACATGAGTAATGAAGGATCTTATTTCTTCGGAGACAATGCAGAGGAGTATGACAATTAA</t>
         </is>
       </c>
-      <c r="CK1" t="inlineStr">
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
         <is>
           <t>&gt;Flu-0317|A_NA</t>
         </is>
       </c>
-      <c r="CL1" t="inlineStr">
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
         <is>
           <t>ATGAATCCAAATCAAAAGATAACAACCATTGGATCAATCTGTATGGTAATTGGGACAGTCAGCTTGATGCTGCAAATTGGGAACATAATCTCAATATGGGTTAGCCATTCAATCCAAACAGGGAATCAATACCAGCCTGAACCATGCAATCAAAGCATCATTACCTATGAGAACAACACCTGGGTAAATCAGACGTATGTCAACATCAGCAATAACAATTTTCTTGCTGAGCAGGCTGTTACTTCGGTAACATTAGCGGGCAATTCATCTCTTTGCCCTATTAGTGGGTGGGCAATATACAGTAAGGACAACGGTATAAGAATTGGGTCCAAGGGGGATGTGTTTGTCATAAGAGAACCGTTCATCTCATGCTCCCACTTGGAATGCAGAACCTTTTTCCTGACTCAGGGAGCTCTGCTGAATGACAAACATTCTAATGGGACAGTTAAGGATAGAAGCCCTTATAGAACTTTGATGAGTTGTCCCGTGGGTGAGGCTCCTTCCCCGTACAATTCAAGATTTGAGTCTGTTGCTTGGTCGGCAAGTGCTTGTCATGATGGCATCAGTTGGTTGACAATCGGTATTTCTGGTCCAGACAATGGAGCTGTGGCTGTATTGAAGTACAATGGCATAATAACGGATACTATCAAGAGTTGGAGAAACAACATTTTGAGAACTCAAGAATCTGAATGTGCTTGCGTAAATGGCTCTTGCTTCACCGTAATGACTGATGGACCAAGCAATGGGCAGGCCTCGTATAAAATCTTCAAGATAGAGAAAGGGAAAGTTGTCAAATCAGTTGAATTGAATGCCCCTAATTACCACTACGAGGAATGTTCCTGTTATCCTGATGCGGGTGATATTATATGTGTGTGCAGGGACAATTGGCACGGCTCAAACCGGCCGTGGATATCTTTTAATCAAAATCTGGAGTATCAAATAGGATATATATGCAGTGGGGTTTTCGGGGACAATCCCCGCCCCAATGATGGAACAGGCAGTTGCAGTCCAATGTCCTCTAATGGGGCATATGGGGTAAAAGGGTTTTCATTTAAGTACGGTAATGGGGTTTGGATCGGAAGAACAAAAGGCACTAGTTCCAGAAGCGGCTTTGAGATGATTTGGGACCCGAATGGGTGGACTGAGACGGACAGTAGTTTCTCAGTGAAGCAAGACATTGTAGAAATAACTGACTGGTCAGGATATAGTGGGAGTTTTGTCCAGCATCCAGAACTGACAGGATTAGATTGCATGAGGCCTTGTTTCTGGGTTGAGCTAATTAGAGGGAGGCCCAAAGAGAACACAATTTGGACTAGCGGGAGCAGCATATCCTTTTGTGGTGTAAATAGTGACACTGTGGGTTGGTCTTGGCCAGACGGTGCTGAGTTGCCATTCACCATTGACAAGTAG</t>
         </is>
       </c>
-      <c r="CM1" t="inlineStr">
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
         <is>
           <t>&gt;Flu-0317|A_MP</t>
         </is>
       </c>
-      <c r="CN1" t="inlineStr">
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
         <is>
           <t>ATGAGTCTTCTAACCGAGGTCGAAACGTACGTTCTCTCTATCGTCCCGTCGGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTTGAAGATGTCTTTGCAGGGAAGAACACCGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATACTGTCACCTCTGACTAAGGGGATTTTGGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCTCTAAGTGGAAATGGAGACCCAAACAACATGGACAGGGCAGTCAAGTTGTACAGGAAACTGAAGAGAGAAATAACATTCCATGGGGCTAAAGAAGTTGCACTTAGTTACTCAACCGGTGCACTTGCCAGTTGTATGGGTCTCATATACAACAGGATGGGGACGGTGACCGCAGAAGTGGCATTGGGCCTAGTGTGTGCCACCTGTGAGCAGATTGCTGATTCACAGCATCGGTCTCACAGACAGATAGCTACCACCACCAACCCACTAATCAGACATGAAAACAGAATGGTTTTGGCCAGTACTACAGCTAAGGCTATGGAGCAGATGGCTGGATCGAGTGAGCAAGCAGTGGAAGCCATGGAGGTTGCTAGTCAGGCTAGGCAAATGGTGCAGGCGATGAGGACCATTGGAACTCATCCTAGCTCCAGTGCCGGTCTGAGAGATGATCTCCTTGAAAATTTGCAGGCCTACCAAAAACGAATGGGAGTGCAACTGCAGCGATTCAAGTGATCCTCTCGTTATTGCAGCAAGTATCATTGGGATCTTGCACTTGATATTGTGGATTCTTGATCGCCTTTTCTTCAAATGCGTTTATCGTCGCCTTAAATACGGTTTGAAAGGAGGGCCTTCTACGGAAGGAGTACCTGAGTCCATGAGGGAAGAGTACCGGCAGGAACAGCAGAGTGCTGTGGATGTTGACGATGGTCATTTTGTCAACATAGAGATGGAGTAA</t>
         </is>
       </c>
-      <c r="CO1" t="inlineStr">
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
         <is>
           <t>&gt;Flu-0317|A_NS</t>
         </is>
       </c>
-      <c r="CP1" t="inlineStr">
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
         <is>
           <t>ATGGATTCCAACACTGTGTCAAGCTTTCAGGTAGACTGCTTTCTTTGGCATGTCCGCAAACAATTTGCAGACCAAGAACTGGGTGATGCCCCATTCCTTGACCGGCTCCGCCGAGACCAGAAGTCTCTAAGAGGAAGAGGCAGCACTCTTGGTCTGGACATCGAGACGGCCACTCGTGCTGGAAAGCAGATAGTGGAGAGGATTCTGGAGGAAGAATCCGACGAGGCACTCAAAATGACTATTGCCTCTGTGCCTGCTCCACGCTACCTAACTGACATGACTCTTGAAGAGATGTCAAGAGACTGGTTCATGCTCATGCCCAAGCAAAAAGTGGCAGGCTCCCTCTGTATCAGAATGGACCAGGCGATTATGGATAAGAACATCATACTGAAGGCAAACTTCAGTGTGATCTTCAATCGGCTGGAGACACTAATACTACTCAGAGCTTTCACTGAAGAGGGAGCAATTGTCGGCGAAATTTCACCATTGCCTTCTCTTCCAGGACATACTGATGAGGATGTCAAAAATGCAATTGGGGTCCTCATCGGAGGACTTGAATGGAATGATAACACAGTTCGAGTCTCTGAAATTTTACAGAGATTCGCTTGGAGAAGCAGTAATGAGGATGGGAGACCTCCACTCCCTCCAAAGCAGAAACGGAAAATGGAGAGAACAATTGAGTCAGAAGTTTGAAGAAATAAGGTGGCTGATTGAAGAGGTGCGACACAGACTAAAGATCACAGAAAATAGTTTTGAACAAATAACATTTATGCAAGCCTTACAACTACTGCTTGAAGTGGAGCAAGAGATACGAACTTTCTCGTTTCAGCTTATTTAA</t>
         </is>
       </c>
-      <c r="CQ1" t="inlineStr">
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
         <is>
           <t>&gt;Flu-0318|A_PB2</t>
         </is>
       </c>
-      <c r="CR1" t="inlineStr">
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
         <is>
           <t>ATGGAGAGAATAAAAGAACTAAGAGATCTAATGTCACAGTCTCGCACTCGCGAGATACTGACCAAAACCACTGTTGACCACATGGCCATAATCAAAAAGTACACATCGGGAAGGCAAGAGAAGAACCCCGCACTCAGAATGAAATGGATGATGGCAATGAAATATCCAATTACAGCAGATAAGCGAATAATGGAAATGATCCCTGAGAGGAATGAACAAGGGCAAACTCTCTGGAGCAAAACAAACGATGCCGGATCAGACCGAGTGATGGTATCACCCCTGGCTGTGACATGGTGGAACAGGAACGGACCAACAACAAGTACAGTTCACTACCCAAAGGTATATAAAACTTATTTCGAAAAAGTTAAAAGGTTGAAACACGGGACCTTTGGCCCTGTGCACTTCAGAAACCAAGTTAAGATAAGACGGAGGGTCGATATAAACCCGGGCCATGCTGACCTTAGTGCCAAAGAGGCACAGGATGTAATCATGGAAGTCGTCTTCCCAAATGAAGTGGGAGCTAGGATATTGACGTCGGAGTCACAACTGACGATAACAAATGAGAAAAAGGAAGAACTCCAGGACTGCAAAATCGCTCCTCTGATGGTTGCATACATGCTAGAACGAGAGTTGGTTCGCAAGACGAGGTTTCTCCCAGTTGCTGGTGGGACAAGCAGTGTCTACATTGAGGTGCTGCATTTGACCCAGGGGACATGCTGGGAGCAGATGTACACTCCGGGAGGAGAAGTGAGGAACGATGATGTAGACCAAAGCTTGATCATTGCTGCCAGGAATATAGTAAGAAGAGCAACAGTATCAGCAGATCCGTTAGCATCTCTATTGGAGATGTGTCACAGCACACAAATTGGGGGAATAAGGATGGTAGACATCCTTCGGCAAAACCCAACAGAGGAACAAGCCGTGGATATATGCAAGGCAGCAATGGGCTTGAGGATTAGTTCATCTTTCAGCTTTGGTGGATTCACTTTTAAAAGAACAAGTGGATCGTCAGTCAAAAAAGAAGAAGAAGTGCTAACAGGCAACCTTCAAACATTGAAAATAAGAGTACATGAGGGGTATGAAGAGTTCACAATGGTTGGGAGAAGAGCAACGGCCATTCTCAGGAAAGCAACCAGAAGGCTGATCCAGCTAATAGTAAGTGGGAGAGACGAGCAGTCAATTGCTGAAGCAATAATTGTGGCCATGGTATTCTCACAAGAGGACTGCATGATTAAAGCAGTTAGAGGTGACCTGAATTTTGTCAATAGGGCGAACCAGCGACTAAACCCAATGCATCAACTCTTGAGGCATTTCCAAAAGGATGCAAAAGTGCTTTTCCAAAATTGGGGAATTGAACCCATTGACAATGTGATGGGAATGATCGGGGTAATGCCTGACATGACCCCAAGTACTGAGATGTCGCTGAGGGGAATAAGAGTCAGCAAGATGGGAGTAGATGAATACTCAAGCACAGAGCGAGTAGTAGTAAGCATCGACCGGTTTTTAAGAGTTCGAGACCAACGGGGGAACGTACTATTATCACCCGAAGAGGTCAGTGAGACACAAGGAACGGAGAAACTGACAATCACTTATTCGTCATCAATGATGTGGGAGATCAATGGTCCTGAGTCGGTGTTGGTCAATACTTATCAGTGGATAATTAGAAACTGGGAAACTGTAAAAATTCAATGGTCACAGGATCCCACAATGCTGTATAATAAGATGGAATTCGAGCCATTCCAGTCTCTAGTCCCTAAGGCAGCCAGAGGTCAATACAGTGGGTTTGTGAGAACACTATTCCAGCAAATGCGAGATGTGCTTGGAACATTTGACACTGTTCAGATAGTAAAACTCCTCCCCTTTGCTGCCGCCCCACCGGAACAAAGTAGGATGCAGTTCTCCTCCCTGACTGTGAATGTAAGAGGATCAGGAATGAGGATACTGGTAAGAGGCAATTCACCAGTGTTCAATTACAACAAGGCCACCAAGAGGCTCACAGTTCTCGGGAAAGATGCAGGTGCATTGACCGAAGATCCAGATGAAGGCACAGCTGGAGTGGAGTCTGCTGTTTTAAGAGGATTCCTCATTTTGGGCAAAGAAGACAAGAGATATGGCCCAGCATTGAGCATCAATGAGCTGAGCAATCTTGCAAAGGGAGAGAAGGCTAATGTGCTAATTGGGCAAGGAGACGTAGTGTTGGTGATGAAACGGAAACGGGACTCTAGCATACTTACTGACAGCCAGACAGCGACCAAAAGAATTCGGATGGCCATCAATTAG</t>
         </is>
       </c>
-      <c r="CS1" t="inlineStr">
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
         <is>
           <t>&gt;Flu-0318|A_PB1</t>
         </is>
       </c>
-      <c r="CT1" t="inlineStr">
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
         <is>
           <t>ATGGATGTCAATCCGACTTTACTTTTCTTGAAAGTTCCAGCGCAAAATGCCATAAGCACCACATTCCCGTATACTGGAGATCCTCCATACAGCCATGGAACAGGAACAGGATATACCATGGACACAGTTAACAGAACACATCAGTATTCAGAAAAAGGGAAATGGACAACAAACTCAGAAACTGGAGCACCTCAACTCAATCCAATTGATGGACCATTGCCTGAGGGCAATGAACCAAGTGGGTATGCACAAACGGACTGTGTCCTTGAAGCAATGGCTTTCCTTGAAGAGTCCCACCCAGGAATCTTTGAAAACTCGTGTCTTGAAACGATGGAAGTTGTTCAACAAACAAGAGTGGACAAGTTGACCCAAGGCCGTCAGACCTATGATTGGACGTTAAACAGGAATCAGCCGGCTGCAACTGCATTAGCTAATACTATAGAGGTCTTCAGATCTAACGGCCTCACAGCCAATGAATCAGGAAGGCTAATAGATTTTCTCAAGGATGTGATGGAATCAATGGATAAGGAGGAAATGGAAATAACAACGCATTTCCAAAGGAAAAGAAGAGTGAGAGACAACATGACCAAGAAAATGGTCACACAAAGGACAATAGGAAAGAAGAAACAGAGGCTAAATAAAAAGAGCTATCTAATAAGAGCATTGACACTGAACACGATGACAAAAGACGCCGAAAGAGGCAAATTAAAAAGAAGGGCAATTGCAACACCTGGAATGCAAATCAGAGGGTTTGTGTACTTTGTTGAGACATTAGCGAGGAGCATTTGTGATAAGCTTGAACAATCTGGACTCCCAGTTGGGGGCAATGAAAAGAAGGCTAAACTGGCAAATGTTGTGAGAAAAATGATGACTAATTCGCAGGACACAGAGCTCTCTTTCACAATCACTGGAGACAACACCAAATGGAATGAAAATCAGAACCCTAGGATGTTTCTGGCAATGATAACATATATAACAAGGAACCAACCTGAATGGTTCAGGAATGTCTTAAGCATTGCACCTATAATGTTCTCAAATAAAATGGCAAGACTAGGGAAAGGGTACATGTTCGAAAGTAAGAGCATGAAGCTCCGAACACAAATACCAGCAGAAATGCTAGCAAGCATTGATCTAAAGTACTTCAATGAGTCAACAAGAAAGAAAATAGAGAAGATAAGACCTCTTCTAATAGATGGTACAGCCTCATTAAGCCCAGGAATGATGATGGGCATGTTCAATATGCTGAGTACAGTTTTGGGAGTTTCGATTCTAAATCTAGGACAAAGGAGGTACACCAAAACAACATACTGGTGGGACGGACTCCAATCCTCTGATGACTTTGCTCTCATAGTGAATGCTCCGAATCATGAGGGAATACAAGCAGGGGTAGACAGATTCTATAGAACCTGCAAGCTGGTCGGAATCAACATGAGCAAAAAGAAGTCCTACATAAACAGGACAGGAACATTTGAATTCACAAGTTTTTTCTACCGCTATGGATTTGTAGCCAACTTCAGTATGGAGTTGCCCAGCTTTGGAGTGTCTGGGATCAATGAATCTGCAGACATGAGCATTGGAGTAACAGTAATAAAGAACAACATGATCAACAATGATCTTGGACCAGCAACAGCTCAAATGGCTCTTCAGCTATTCATCAAGGATTACAGATACACATACCGGTGTCACAGAGGAGACACACAAATTCAGACAAGGAGGTCATTCGAGCTGAAGAAGTTGTGGGAACAGACCCGTTCAAAAGCAGGACTGCTGGTCTCAGATGGAGGACCAAATCTATACAATATTCGGAATCTTCACATTCCAGAAGTCTGCTTGAAATGGGAGCTAATGGACGAAGACTATCAGGGAAGGCTTTGTAATCCCCTGAACCCGTTTGTCAGCCACAAGGAAATAGAGTCTGTGAACAACGCAGTGGTGATGCCAGCTCATGGCCCGGCCAAGAGCATGGAATATGATGCTGTTGCCACCACTCACTCCTGGATACCGAAGAGGAACCGCTCCATTCTCAATACAAGCCAAAGGGGAATCCTTGAAGACGAACAGATGTATCAAAAGTGCTGCAACCTGTTCGAAAAATTCTTCCCTAGCAGTTCATACAGGAGGCCAGTTGGAATTTCCAGCATGGTGGAGGCCATGGTTTCTAGGGCCCGAATTGACGCACGAATTGACTTCGAATCTGGACGGATTAAGAAGGAGGAGTTTGCTAAGATCATGAAGATCTGTTCCACCATTGAAGAGCTCAGACGGCAGAAATAG</t>
         </is>
       </c>
-      <c r="CU1" t="inlineStr">
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
         <is>
           <t>&gt;Flu-0318|A_PA</t>
         </is>
       </c>
-      <c r="CV1" t="inlineStr">
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
         <is>
           <t>ATGGAAGACTTTGTGCGACAATGCTTCAATCCAATGATTGTCGAGCTTGCGGAAAAAGCAATGAAAGAATATGGGGAAGATCCGAAAATCGAGACAAACAAATTTGCCGCAATATGCACACACTTAGAAGTCTGTTTCATGTATTCGGATTTCCATTTTATTAATGAACGAGGCGAATCAATGATTGTAGAATCTGGCGATCCAAATGCATTATTGAAACACCGATTTGAGATAATAGAAGGGAGAGACCGGGCAATGGCCTGGACAGTGGTGAATAGTATCTGCAACACCACAGGGGTCGAAAAGCCCAAATTCCTCCCTGATTTGTATGACTACAAAGAGAACCGATTCATTGAAATTGGAGTAACGCGAAGGGAAGTTCACATATACTATTTAGAAAAAGCCAACAAGATAAAGTCAGAGAAAACACATATTCACATATTCTCATTCACTGGAGAGGAAATGGCCACCAAGGCGGACTACACCCTTGATGAAGAGAGCAGAGCAAGAATAAAAACCAGACTGTTCACTATAAGACAAGAAATGGCCAGTAGAGGTCTATGGGATTCCTTTCGTCAATCCGAGAGAGGCGAAGAGACAATTGAAGAAAGATTTGAAATCGCAGGAACCATGCGCAGGCTTGCCAACCAAAGTCTTCCACCGAACTTCTCCAGCCTTGAAAACTTTAGAGCCTATGTGGATGGATTCGAACCGAACGGCTGCATTGAGGGCAAACTTTCTCAAATGTCAAAAGAAGTGAACGCCAGGATTGAGCCATTTCTGAAGACAACACCACGCCCTCTCAGATTACCTGATGGGCCTCCCTGTTCTCAGCGGTCGAAGTTCTTGCTGATGGATGCCCTTAAGTTGAGCATCGAAGACCCTAGCCATGAGGGGGAGGGCATACCGCTGTATGATGCAATCAAATGCATGAAGACATTTTTTGGCTGGAAAGAGCCCAACATCGTAAAGCCGCATGAGAAAGGCATAAACCCTAATTACCTCCTGACTTGGAAGCAGGTGCTGGCAGAACTTCAAGACATTGAAAATGAGGAGAAAATTCCAAAGACAAAGAACATGAAGAAAACAAGCCAATTGAAGTGGGCACTTGGTGAGAACATGGCTCCAGAGAAAGTGGACTTTGAGGACTGCAAAGATGTTAGCGATCTAAGACAGTACGACAGTAACGAACCAGAGTCTAGAACACTAGCAAGCTGGATTCAGAGTGAATTCAACAAGGCATGCGAACTGACAGATTCGAGTTGGATTGAACTTGATGAGATAGGGGAAGACGTTGCTCCAATCGAACACATTGCGAGTGTGAGGAGGAACTATTTCACAGCGGAGGTATCCCATTGCAGGGCCACTGAATACATAATGAAGGGAGTATACATAAACACAGCCCTATTGAATGCATCCTGTGCAGCCATGGATGACTTCCAATTGATTCCAATGATAAGTAAGTGCAGAACTAAAGAAGGAAGACGGAAGACAAATCTGTATGGATTCATTATAAAAGGAAGATCCCATTTGAGGAATGACACCGATGTGGTAAACTTTGTGAGCATGGAATTCTCTCTAACTGACCCGAGGCTGGAGCCACACAAATGGGAGAAGTACTGTGTTCTTGAGATAGGAGACATGCTCCTACGGACTGCAATAGGCCAAGTGTCGAGGCCCATGTTCCTGTATGTGAGAACCAATGGGACTTCCAAGATCAAAATGAAATGGGGCATGGAGATGAGGCGATGCCTTCTTCAGTCCCTTCAACAAATTGAGAGCATGATTGAGGCCGAATCTTCTGTCAAAGAGAAGGACATGTCCAAGGAATTCTTTGAAAACAAATCAGAAACATGGCCAATTGGAGAATCACCCAAAGGGGTGGAGGAAGGCTCTATTGGGAAAGTATGCAGAACATTGCTAGCAAAGTCTGTGTTCAACAGCCTATATGCATCTCCACAACTCGAGGGGTTTTCAGCTGAATCAAGAAAATTGCTTCTCATTGTTCAGGCACTTAGGGACAACCTGGAACCTGGAACCTTCGATCTTGGGGGGCTATATGAAGCAATTGAGGAGTGCCTGATTAACGATCCCTGGGTTTTGCTTAATGCATCTTGGTTCAACTCCTTCCTCACACATGCACTGAAATAG</t>
         </is>
       </c>
-      <c r="CW1" t="inlineStr">
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
         <is>
           <t>&gt;Flu-0318|A_NP</t>
         </is>
       </c>
-      <c r="CX1" t="inlineStr">
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
         <is>
           <t>ATGGCGTCTCAAGGCACCAAACGATCCTATGAACAAATGGAAACTGGTGGGGAACGCCAGAATGCCACTGAAATCAGAGCATCTGTTGGAAGAATGGTTGGCGGAATAGGAAGATTCTACATACAGATGTGCACTGAGCTCAAACTCAGTGATTATGAAGGGAGGCTGATCCAAAACAGCATAACCATAGAAAGGATGGTTCTCTCGGCATTTGATGAGAGGAGGAACAAGTACCTGGAGGAACATCCCAGTGCCGGGAAGGATCCCAAGAAGACTGGAGGTCCAATCTACAGGAGGAGAGATGGCAAATGGGTGAGAGAGTTGATCCTCTACGACAAAGAAGAGATCAGAAGAATTTGGCGTCAAGCTAATAATGGAGAGGATGCAACTGCTGGTCTCACTCATTTGATGATTTGGCATTCCAATCTGAATGATGCAACATACCAGAGAACAAGGGCACTTGTGCGTACTGGAATGGACCCTAGAATGTGCTCTCTGATGCAAGGCTCAACCCTCCCTAGGAGATCCGGGGCTGCTGGAGCAGCAGTGAAAGGAGTTGGAACAATGGTGATGGAACTAATTCGAATGATCAAGCGAGGGATCAATGATCGGAATTTCTGGAGAGGCGAAAACGGTCGGAGAACCAGGATTGCCTACGAGAGAATGTGCAACATCCTCAAGGGAAAGTTCCAAACAGCAGCACAACGGGCAATGATGGACCAAGTGAGAGAAAGCCGGAATCCTGGGAATGCTGAAATTGAAGATCTCATCTTTCTCGCACGATCTGCTCTCATCCTGAGGGGATCAGTGGCTCATAAGTCCTGTCTGCCTGCTTGCGTATATGGACTTGCTGTAGCCAGTGGATATGACTTTGAAAGAGAGGGATATTCTCTAGTCGGAATTGATCCTTTCCGTCTGCTCCAAAACAGCCAAGTCTTCAGTCTCATCAGACCGAACGAAAATCCAGCTCATAAGAGTCAGCTGGTATGGATGGCATGCCACTCTGCGGCATTTGAGGATCTGAGAGTTTCAAGCTTCATCAGAGGGACAAGAGTAGTCCCAAGAGGACAACTGTCCACCAGAGGAGTTCAGATTGCTTCAAATGAAAACATGGAGACAATGGACTCCAGTACTCTTGAACTGAGGAGCAGATACTGGGCTATAAGAACAAGAAGTGGAGGAAACACTAACCAACAGAGAGCATCTGCAGGACAAATCAGCGTGCAGCCCACATTCTCTGTGCAAAGAAACCTCCCATTCGAGAGAGCAACCATCATGGCAGCATTTACGGGAAACACTGAAGGCAGAACTTCAGACATGAGAACTGAGATCATAAGGATGATGGAAAATGCCAGACCTGAAGATGTGTCTTTCCAGGGGCGGGGAGTCTTCGAGCTCTCGGACGAAAAGGCAACGAACCCGATCGTGCCTTCCTTTGACATGAGTAATGAAGGATCTTATTTCTTCGGAGACAATGCAGAGGAGTATGACAATTAA</t>
         </is>
       </c>
-      <c r="CY1" t="inlineStr">
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
         <is>
           <t>&gt;Flu-0318|A_NA</t>
         </is>
       </c>
-      <c r="CZ1" t="inlineStr">
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
         <is>
           <t>ATGAATCCAAATCAAAAGATAACAACCATTGGATCAATCTGTATGGTAATTGGGACAGTCAGCTTGATGCTGCAAATTGGGAACATAATCTCAATATGGGTTAGCCATTCAATCCAAACAGGGAATCAATACCAGCCTGAACCATGCAATCAAAGCATCATTACCTATGAGAACAACACCTGGGTAAATCAGACGTATGTCAACATCAGCAATAACAATTTTCTTGCTGAGCAGGCTGTTACTTCGGTAACATTAGCGGGCAATTCATCTCTTTGCCCTATTAGTGGGTGGGCAATATACAGTAAGGACAACGGTATAAGAATTGGGTCCAAGGGGGATGTGTTTGTCATAAGAGAACCGTTCATCTCATGCTCCCACTTGGAATGCAGAACCTTTTTCCTGACTCAGGGAGCTCTGCTGAATGACAAACATTCTAATGGGACAGTTAAGGATAGAAGCCCTTATAGAACTTTGATGAGTTGTCCCGTGGGTGAGGCTCCTTCCCCGTACAATTCAAGATTTGAGTCTGTTGCTTGGTCGGCAAGTGCTTGTCATGATGGCATCAGTTGGTTGACAATCGGTATTTCTGGTCCAGACAATGGAGCTGTGGCTGTATTGAAGTACAATGGCATAATAACGGATACTATCAAGAGTTGGAGAAACAACATTTTGAGAACTCAAGAATCTGAATGTGCTTGCGTAAATGGCTCTTGCTTCACCGTAATGACTGATGGACCAAGCAATGGGCAGGCCTCGTATAAAATCTTCAAGATAGAGAAAGGGAAAGTTGTCAAATCAGTTGAATTGAATGCCCCTAATTACCACTACGAGGAATGTTCCTGTTATCCTGATGCGGGTGATATTATATGTGTGTGCAGGGACAATTGGCACGGCTCAAACCGGCCGTGGATATCTTTTAATCAAAATCTGGAGTATCAAATAGGATATATATGCAGTGGGGTTTTCGGGGACAATCCCCGCCCCAATGATGGAACAGGCAGTTGCAGTCCAATGTCCTCTAATGGGGCATATGGGGTGAAAGGGTTTTCATTTAAGTACGGTAATGGGGTTTGGATCGGAAGAACAAAAGGCACTAGTTCCAGAAGCGGCTTTGAGATGATTTGGGACCCGAATGGGTGGACTGAGACGGACAGTAGTTTCTCAGTGAAGCAAGACATTGTAGAAATAACTGACTGGTCAGGATATAGTGGGAGTTTTGTCCAGCATCCAGAACTGACAGGATTAGATTGCATGAGGCCTTGTTTCTGGGTTGAGCTAATTAGAGGGAGGCCCAAAGAGAACACAATTTGGACTAGCGGGAGCAGCATATCCTTTTGTGGTGTAAATAGTGACACTGTGGGTTGGTCTTGGCCAGACGGTGCTGAGTTGCCATTCACCATTGACAAGTAG</t>
         </is>
       </c>
-      <c r="DA1" t="inlineStr">
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
         <is>
           <t>&gt;Flu-0318|A_MP</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
         <is>
           <t>ATGAGTCTTCTAACCGAGGTCGAAACGTACGTTCTCTCTATCGTCCCGTCGGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTTGAAGATGTCTTTGCAGGGAAGAACACCGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATACTGTCACCTCTGACTAAGGGGATTTTGGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCTCTAAGTGGAAATGGAGACCCAAACAACATGGACAGGGCAGTCAAGTTGTACAGGAAACTGAAGAGAGAAATAACATTCCATGGGGCTAAAGAAGTTGCACTTAGTTACTCAACCGGTGCACTTGCCAGTTGTATGGGTCTCATATACAACAGGATGGGGACGGTGACCGCAGAAGTGGCATTGGGCCTAGTGTGTGCCACCTGTGAGCAGATTGCTGATTCACAGCATCGGTCTCACAGACAGATAGCTACCACCACCAACCCACTAATCAGACATGAAAACAGAATGGTTTTGGCCAGTACTACAGCTAAGGCTATGGAGCAGATGGCTGGATCGAGTGAGCAAGCAGTGGAAGCCATGGAGGTTGCTAGTCAGGCTAGGCAAATGGTGCAGGCGATGAGGACCATTGGAACTCATCCTAGCTCCAGTGCCGGTCTGAGAGATGATCTCCTTGAAAATTTGCAGGCCTACCAAAAACGAATGGGAGTGCAACTGCAGCGATTCAAGTGATCCTCTCGTTATTGCAGCAAGTATCATTGGGATCTTGCACTTGATATTGTGGATTCTTGATCGCCTTTTCTTCAAATGCGTTTATCGTCGCCTTAAATACGGTTTGAAAGGAGGGCCTTCTACGGAAGGAGTACCTGAGTCCATGAGGGAAGAGTACCGGCAGGAACAGCAGAGTGCTGTGGATGTTGACGATGGTCATTTTGTCAACATAGAGATGGAGTAA</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
         <is>
           <t>&gt;Flu-0318|A_NS</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
         <is>
           <t>ATGGATTCCAACACTGTGTCAAGCTTTCAGGTAGACTGCTTTCTTTGGCATGTCCGCAAACAATTTGCAGACCAAGAACTGGGTGATGCCCCATTCCTTGACCGGCTCCGCCGAGACCAGAAGTCTCTAAGAGGAAGAGGCAGCACTCTTGGTCTGGACATCGAGACGGCCACTCGTGCTGGAAAGCAGATAGTGGAGAGGATTCTGGAGGAAGAATCCGACGAGGCACTCAAAATGACTATTGCCTCTGTGCCTGCTCCACGCTACCTAACTGACATGACTCTTGAAGAGATGTCAAGAGACTGGTTCATGCTCATGCCCAAGCAAAAAGTGGCAGGCTCCCTCTGTATCAGAATGGACCAGGCGATTATGGATAAGAACATCATACTGAAGGCAAACTTCAGTGTGATCTTCAATCGGCTGGAGACACTAATACTACTCAGAGCTTTCACTGAAGAGGGAGCAATTGTCGGCGAAATTTCACCATTGCCTTCTCTTCCAGGACATACTGATGAGGATGTCAAAAATGCAATTGGGGTCCTCATCGGAGGACTTGAATGGAATGATAACACAGTTCGAGTCTCTGAAATTTTACAGAGATTCGCTTGGAGAAGCAGTAATGAGGATGGGAGACCTCCACTCCCTCCAAAGCAGAAACGGAAAATGGAGAGAACAATTGAGTCAGAAGTTTGAAGAAATAAGGTGGCTGATTGAAGAGGTGCGACACAGACTAAAGATCACAGAAAATAGTTTTGAACAAATAACATTTATGCAAGCCTTACAACTACTGCTTGAAGTGGAGCAAGAGATACGAACTTTCTCGTTTCAGCTTATTTAA</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
         <is>
           <t>&gt;Flu-0321|A_NA</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
         <is>
           <t>ATGAATCCAAATCAAAAGATAACAACCATTGGATCAATCTGTATGGTAATTGGGACAGTCAGCTTGATGCTGCAAATTGGGAACATAATCTCAATATGGGTTAGCCATTCAATCCAAACAGGGAATCAATACCAGCCTGAACCATGCAATCAAAGCATCATTACCTATGAGAACAACACCTGGGTAAATCAGACGTATGTCAACATCAGCAATAACAATTTTCTTGCTGAGCAGGCTGTTACTTCGGTAACATTAGCGGGCAATTCATCTCTTTGCCCTATTAGTGGGTGGGCAATATACAGTAAGGACAACGGTATAAGAATTGGGTCCAAGGGGGATGTGTTTGTCATAAGAGAACCGTTCATCTCATGCTCCCACTTGGAATGCAGAACCTTTTTCCTGACTCAGGGAGCTCTGCTGAATGACAAACATTCTAATGGGACAGTTAAGGATAGAAGCCCTTATAGAACTTTGATGAGTTGTCCCGTGGGTGAGGCTCCTTNCCCGTACAATTCAAGATTTGAGTCTGTTGCTTGGTCGGCAAGTGCTTGTCATGATGGCATCAGTTGGTTGACAATCGGTATTTCTGGTCCAGACAATGGAGCTGTGGCTGTATTGAAGTACAATGGCATAATAACGGATACTATCAAGAGTTGGAGAAACAACATTTTGAGAACTCAAGAATCTGAATGTGCTTGCGTAAATGGCTCTTGCTTCACCGTAATGACTGATGGACCAAGCAATGGGCAGGCCTCGTATAAAATCTTCAAGATAGAGAAAGGGAAAGTTGTCAAATCAGTTGAATTGAATGCCCCTAATTACCACTACGAGGAATGTTCCTGTTATCCTGATGCGGGTGATATTATATGTGTGTGCAGGGACAATTGGCACGGCTCAAACCGGCCGTGGATATCTTTTAATCAAAATCTGGAGTATCAAATAGGATATATATGCAGTGGGGTTTTCGGGGACAATCCCCGCCCCAATGATGGAACAGGCAGTTGCAGTCCAATGTCCTCTAATGGGGCATATGGGGTAAAAGGGTTTTCATTTAAGTACGGTAATGGGGTTTGGATCGGAAGAACAAAAGGCACTAGTTCCAGAAGCGGCTTTGAGATGATTTGGGACCCGAATGGGTGGACTGAGACGGACAGTAGTTTCTCAGTGAAGCAAGACATTGTAGAAATAACTGACTGGTCAGGATATAGTGGGAGTTTTGTCCAGCATCCAGAACTGACAGGATTAGATTGCATGAGGCCTTGTTTCTGGGTTGAGCTAATTAGAGGGAGGCCCAAAGAGAACACAATTTGGACTAGCGGGAGCAGCATATCCTTTTGTGGTGTAAATAGTGACACTGTGGGTTGGTCTTGGCCAGACGGTGCTGAGTTGCCATTCACCATTGACAAGTAG</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
         <is>
           <t>&gt;Flu-0321|A_MP</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
         <is>
           <t>ATGAGTCTTCTAACCGAGGTCGAAACGTACGTTCTCTCTATCGTCCCGTCGGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTTGAAGATGTCTTTGCAGGGAAGAACACCGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATACTGTCACCTCTGACTAAGGGGATTTTGGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCTCTAAGTGGAAATGGAGACCCAAACAACATGGACAGGGCAGTCAAGTTGTACAGGAAACTGAAGAGAGAAATAACATTCCATGGGGCTAAAGAAGTTGCACTTAGTTACTCAACCGGTGCACTTGCCAGTTGTATGGGTCTCATATACAACAGGATGGGGACGGTGACCGCAGAAGTGGCATTGGGCCTAGTGTGTGCCACCTGTGAGCAGATTGCTGATTCACAGCATCGGTCTCACAGACAGATAGCTACCACCACCAACCCACTAATCAGACATGAAAACAGAATGGTTTTGGCCAGTACTACAGCTAAGGCTATGGAGCAGATGGCTGGATCGAGTGAGCAAGCAGTGGAAGCCATGGAGGTTGCTAGTCAGGCTAGGCAAATGGTGCAGGCGATGAGGACCATTGGAACTCATCCTAGCTCCAGTGCCGGTCTGAGAGATGATCTCCTTGAAAATTTGCAGGCCTACCAAAAACGAATGGGAGTGCAACTGCAGCGATTCAAGTGATCCTCTCGTTATTGCAGCAAGTATCATTGGGATCTTGCACTTGATATTGTGGATTCTTGATCGCCTTTTCTTCAAATGCGTTTATCGTCGCCTTAAATACGGTTTGAAAGGAGGGCCTTCTACGGAAGGAGTACCTGAGTCCATGAGGGAAGAGTACCGGCAGGAACAGCAGAGTGCTGTGGATGTTGACGATGGTCATTTTGTCAACATAGAGATGGAGTAA</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
         <is>
           <t>&gt;Flu-0321|A_NS</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
         <is>
           <t>ATGGATTCCAACACTGTGTCAAGCTTTCAGGTAGACTGCTTTCTTTGGCATGTCCGCAAACAATTTGCAGACCAAGAACTGGGTGATGCCCCATTCCTTGACCGGCTCCGCCGAGACCAGAAGTCTCTAAGAGGAAGAGGCAGCACTCTTGGTCTGGACATCGAGACGGCCACTCGTGCTGGAAAGCAGATAGTGGAGAGGATTCTGGAGGAAGAATCCGACGAGGCACTCAAAATGACTATTGCCTCTGTGCCTGCTCCACGCTACCTAACTGACATGACTCTTGAAGAGATGTCAAGAGACTGGTTCATGCTCATGCCCAAGCAAAAAGTGGCAGGCTCCCTCTGTATCAGAATGGACCAGGCGATTATGGATAAGAACATCATACTGAAGGCAAACTTCAGTGTGATCTTCAATCGGCTGGAGACACTAATACTACTCAGAGCTTTCACTGAAGAGGGAGCAATTGTCGGCGAAATTTCACCATTGCCTTCTCTTCCAGGACATACTGATGAGGATGTCAAAAATGCAATTGGGGTCCTCATCGGAGGACTTGAATGGAATGATAACACAGTTCGAGTCTCTGAAATTTTACAGAGATTCGCTTGGAGAAGCAGTAATGAGGATGGGAGACCTCCACTCCCTCCAAAGCAGAAACGGAAAATGGAGAGAACAATTGAGTCAGAAGTTTGAAGAAATAAGGTGGCTGATTGAAGAGGTGCGACACAGACTAAAGATCACAGAAAATAGTTTTGAACAAATAACATTTATGCAAGCCTTACAACTACTGCTTGAAGTGGAGCAAGAGATACGAACTTTCTCGTTTCAGCTTATTTAA</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
         <is>
           <t>&gt;Flu-0323|A_MP</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
         <is>
           <t>ATGAGTCTTCTAACCGAGGTCGAAACGTACGTTCTCTCTATCGTCCCGTCGGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTTGAAGATGTCTTTGCAGGGAAGAACACCGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATACTGTCACCTCTGACTAAGGGGATTTTGGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCTCTAAGTGGAAATGGAGACCCAAACAACATGGACAGGGCAGTCAAGTTGTACAGGAAACTGAAGAGAGAAATAACATTCCATGGGGCTAAAGAAGTTGCACTTAGTTACTCAACCGGTGCACTTGCCAGTTGTATGGGTCTCATATACAACAGGATGGGGACGGTGACCGCAGAAGTGGCATTGGGCCTAGTGTGTGCCACCTGTGAGCAGATTGCTGATTCACAGCATCGGTCTCACAGACAGATAGCTACCACCACCAACCCACTAATCAGACATGAAAACAGAATGGTTTTGGCCAGTACTACAGCTAAGGCTATGGAGCAGATGGCTGGATCGAGTGAGCAAGCAGTGGAAGCCATGGAGGTTGCTAGTCAGGCTAGGCAAATGGTGCAGGCGATGAGGACCATTGGAACTCATCCTAGCTCCAGTGCCGGTCTGAGAGATGATCTCCTTGAAAATTTGCAGGCCTACCAAAAACGAATGGGAGTGCAACTGCAGCGATTCAAGTGATCCTCTCGTTATTGCAGCAAGTATCATTGGGATCTTGCACTTGATATTGTGGAGTCTTGATCGCCTTTTCTTCAAATGCGTTTATCGTCGCCTTAAATACGGTTTGAAAGGAGGGCCTTCTACGGAAGGAGTACCTGAGTCCATGAGGGAAGAGTACCGGCAGGAACAGCAGAGTGCTGTGGATGTTGACGATGGTCATTTTGTCAACATAGAGATGGAGTAA</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
         <is>
           <t>&gt;Flu-0323|A_NS</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
         <is>
           <t>ATGGATTCCAACACTGTGTCAAGCTTTCAGGTAGACTGCTTTCTTTGGCATGTCCGCAAACAATTTGCAGACCAAGAACTGGGTGATGCCCCATTCCTTGACCGGCTCCGCCGAGACCAGAAGTCTCTAAGAGGAAGAGGCAGCACTCTTGGTCTGGACATCGAGACGGCCACTCGTGCTGGAAAGCAGATAGTGGAGAGGATTCTGGAGGACGAATCCGACGAGGCACTCAAAATGACTATTGCCTCTGTGCCTGCTCCACGCTACCTAACTGACATGACTCTTGAAGAGATGTCAAGAGACTGGTTCATGCTCATGCCCAAGCAAAAAGTGGCAGGCTCCCTCTGTATCAGAATGGACCAGGCGATTATGGATAAGAACATCATACTGAAGGCAAACTTCAGTGTGATCTTCAATCGGCTGGAGACACTAATACTACTCAGAGCTTTCACTGAAGAGGGAGCAATTGTCGGCGAAATTTCACCATTGCCTTCTCTTCCAGGACATACTGATGAGGATGTCAAAAATGCAATTGGGGTCCTCATCGGAGGACTTGAATGGAATGATAACACAGTTCGAGTCTCTGAAATTTTACAGAGATTCGCTTGGAGAAGCAGTAATGAGGATGGGAGACCTCCACTCCCTCCAAAGCAGAAACGGAAAATGGAGAGAACAATTGAGTCAGAAGTTTGAAGAAATAAGGTGGCTGATTGAAGAGGTGCGACACAGACTAAAGATCACAGAAAATAGTTTTGAACAAATAACATTTATGCAAGCCTTACAACTACTGCTTGAAGTGGAGCAAGAGATACGAACTTTCTCGTTTCAGCTTATTTAA</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
         <is>
           <t>&gt;Flu-0325|A_NP</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
         <is>
           <t>ATGGCGTCTCAAGGCACCAAACGATCATATGAACAAATGGAAACTGGTGGGGAACGCCAGAATGCCACTGAAATCAGAGCATCTGTTGGAAGAATGGTTGGCGGAATAGGAAGATTCTACATACAGATGTGCACTGAGCTCAAACTCAGTGATTATGAAGGGAGGCTGATCCAAAACAGCATAACCATAGAAAGAATGGTTCTCTCGGCATTTGATGAGAGGAGGAACAAGTACCTGGAGGAACATCCCAGTGCCGGGAAGGATNCCAAGAAGACTGGAGGTCCAATCTACAGGAGGAGAGATGGCAAATGGGTGAGAGAGTTGATCCTCTACGACAAAGAAGAGATCAGAAGAATTTGGCGTCAAGCCAATAATGGAGAGGATGCAACTGCTGGTCTCACTCATTTGATGATTTGGCATTCCAATCTGAATGATGCAACATACCAGAGAACAAGGGCACTTGTGCGTACTGGAATGGACCCTAGAATGTGCTCTCTGATGCAAGGCTCAACCCTCCCTAGGAGATCCGGGGCTGCTGGAGCAGCAGTGAAAGGAGTTGGAACAATGGTGATGGAACTAATTCGAATGATCAAGCGAGGGATCAATGATCGGAATTTCTGGAGAGGCGAAAACGGTCGGAGAACCAGGATTGCCTACGAGAGAATGTGCAACATCCTCAAGGGAAAGTTCCAAACAGCAGCACAACGGGCAATGATGGACCAAGTGAGAGAAAGCCGGAATCCTGGGAATGCTGAAATTGAAGATCTCATCTTTCTCGCACGATCTGCTCTCATCCTGAGGGGATCAGTGGCTCATAAGTCCNNNNTGCCTGCTTGCGTATATGGACNTGCTGTAGCCAGTGGATATGACTTTGNAAGANAGGNATANNNNNNNNTNGNANNNNATCCTTTNCGTNNNCTCCAAAACNGCCNAGTNTTNNGTCTNATCNNACNNNANNNNANTNNAGCTNATNNNAGTNAGCTGGTATNGANGGNNTGCCACTNTNNGGCANTNGANNNNNNNNNNNNTTNNAGNTTNATCAGNNGNANANNNNNNGTNCNNAGAGGNNNACNGTCCACCAGANNAGTTCAGATTGCTTCAAATGAAAACATGGAGACAATGGACTCCAGTACTCTTGAACTGAGGAGCAGATACTGGGCTATNAGAACAAGAAGTGGAGGAAACACTAACCAACAGAGAGCATCTGCAGGACAAATCAGCGTGCAGCCCACATTCTCTGTGCAAAGAAACCTCCCATTCGAGAGAGCAACCATCATGGCAGCATTTACGGGAAACACTGAAGGCAGAACTTCAGACATGAGAACTGAGATCATAAGGATGATGGAAAATGCCAGACCTGAAGATGTGTCTTTCCAGGGGCGGGGAGTCTTCGAGCTCTCGGACGAAAAGGCAACGAACCCGATCGTGCCTTCCTTTGACATGAGTAATGAAGGATCTTATTTCTTCGGAGACAATGCAGAGGAGTATGACAATTAA</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
         <is>
           <t>&gt;Flu-0325|A_MP</t>
         </is>
       </c>
-      <c r="DR1" t="inlineStr">
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
         <is>
           <t>ATGAGTCTTCTAACCGAGGTCGAAACGTACGTTCTCTCTATCGTCCCGTCGGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTTGAAGATGTCTTTGCAGGGAAGAACACCGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATACTGTCACCTCTGACTAAGGGGATTTTGGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCTCTAAGTGGAAATGGAGACCCAAACAACATGGACAGGGCAGTCAAGTTGTACAGGAAACTGAAGAGAGAAATAACATTCCATGGGGCTAAAGAAGTTGCACTTAGTTACTCAACCGGTGCACTTGCCAGTTGTATGGGTCTCATATACAACAGGATGGGGACGGTGACCGCAGAAGTGGCATTGGGCCTAGTGTGTGCCACCTGTGAGCAGATTGCTGATTCACAGCATCGGTCTCACAGACAGATAGCTACCACCACCAACCCACTAATCAGACATGAAAACAGAATGGTTTTGGCCAGTACTACAGCTAAGGCTATGGAGCAGATGGCTGGATCGAGTGAGCAAGCAGTGGAAGCCATGGAGGTTGCTAGTCAGGCTAGGCAAATGGTGCAGGCGATGAGGACCATTGGAACTCATCCTAGCTCCAGTGCCGGTCTGAGAGATGATCTCCTTGAAAATTTGCAGGCCTACCAAAAACGAATGGGAGTGCAACTGCAGCGATTCAAGTGATCCTCTCGTTATTGCAGCAAGTATCATTGGGATCTTGCACTTGATATTGTGGAGTCTTGATCGCCTTTTCTTCAAATGCGTTTATCGTCGCCTTAAATACGGTTTGAAAGGAGGGCCTTCTACGGAAGGAGTACCTGAGTCCATGAGGGAAGAGTACCGGCAGGAACAGCAGAGTGCTGTGGATGTTGACGATGGTCATTTTGTCAACATAGAGATGGAGTAA</t>
         </is>
       </c>
-      <c r="DS1" t="inlineStr">
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
         <is>
           <t>&gt;Flu-0325|A_NS</t>
         </is>
       </c>
-      <c r="DT1" t="inlineStr">
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
         <is>
           <t>ATGGATTCCAACACTGTGTCAAGCTTTCAGGTAGACTGCTTTCTTTGGCATGTCCGCAAACAATTTGCAGACCAAGAACTGGGTGATGCCCCATTCCTTGACCGGCTCCGCCGAGACCAGAAGTCTCTAAGAGGAAGAGGCAGCACTCTTGGTCTGGACATCGAGACGGCCACTCGTGCTGGAAAGCAGATAGTGGAGAGGATTCTGGAGGACGAATCCGACGAGGCACTCAAAATGACTATTGCCTCTGTGCCTGCTCCACGCTACCTAACTGACATGACTCTTGAAGAGATGTCAAGAGACTGGTTCATGCTCATGCCCAAGCAAAAAGTGGCAGGCTCCCTCTGTATCAGAATGGACCAGGCGATTATGGATAAGAACATCATACTGAAGGCAAACTTCAGTGTGATCTTCAATCGGCTGGAGACACTAATACTACTCAGAGCTTTCACTGAAGAGGGAGCAATTGTCGGCGAAATTTCACCATTGCCTTCTCTTCCAGGACATACTGATGAGGATGTCAAAAATGCAATTGGGGTCCTCATCGGAGGACTTGAATGGAATGATAACACAGTTCGAGTCTCTGAAATTTTACAGAGATTCGCTTGGAGAAGCAGTAATGAGGATGGGAGACCTCCACTCCCTCCAAAGCAGAAACGGAAAATGGAGAGAACAATTGAGTCAGAAGTTTGAAGAAATAAGGTGGCTGATTGAAGAGGTGCGACACAGACTAAAGATCACAGAAAATAGTTTTGAACAAATAACATTTATGCAAGCCTTACAACTACTGCTTGAAGTGGAGCAAGAGATACGAACTTTCTCGTTTCAGCTTATTTAA</t>
         </is>
       </c>
-      <c r="DU1" t="inlineStr">
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
         <is>
           <t>&gt;Flu-0326|A_NP</t>
         </is>
       </c>
-      <c r="DV1" t="inlineStr">
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
         <is>
           <t>ATGGCGTCTCAAGGCACCAAACGATCATATGAACAAATGGAAACTGGTGGGGAACGCCAGAATGCCACTGAAATCAGAGCATCTGTTGGAAGAATGGTTGGCGGAATAGGAAGATTCTACATACAGATGTGCACTGAGCTCAAACTCAGTGATTATGAAGGGAGGCTGATCCAAAACAGCATAACCATAGAAAGAATGGTTCTCTCGGCATTTGATGAGAGGAGGAACAAGTACCTGGAGGAACATCCCAGTGCCGGGAAGGATCCCAAGAAGACTGGAGGTCCAATCTACAGGAGGAGAGATGGCAAATGGGTGAGAGAGTTGATCCTCTACGACAAAGAAGAGATCAGAAGAATTTGGCGTCAAGCCAATAATGGAGAGGATGCAACTGCTGGTCTCACTCATTTGATGATTTGGCATTCCAATCTGAATGATGCAACATACCAGAGAACAAGGGCACTTGTGCGTACTGGAATGGACCCTAGAATGTGCTCTCTGATGCAAGGCTCAACCCTCCCTAGGAGATCCGGGGCTGCTGGAGCAGCAGTGAAAGGAGTTGGAACAATGGTGATGGAACTAATTCGAATGATCAAGCGAGGGATCAATGATCGGAATTTCTGGAGAGGCGAAAACGGTCGGAGAACCAGGATTGCCTACGAGAGAATGTGCAACATCCTCAAGGGAAAGTTCCAAACAGCAGCACAACGGGCAATGATGGACCAAGTGAGAGAAAGCCGGAATCCTGGGAATGCTGAAATTGAAGATCTCATCTTTCTCGCACGATCTGCTCTCATCCTGAGGGGATCAGTGGCTCATAAGTCCTGTCTGCCTGCTTGCGTATATGGACTTGCTGTAGCCAGTGGATATGACTTTGAAAGAGAGGGATATTCTCTAGTCGGAATTGATCCTTTCCGTCTGCTCCAAAACAGCCAAGTCTTCAGTCTCATCAGACCGAACGAAAATCCAGCTCATAAGAGTCAGCTGGTATGGATGGCATGCCACTCTGCGGCATTTGAGGATCTGAGAGTTTCAAGCTTCATCAGAGGGACAAGAGTAGTCCCAAGAGGACAACTGTCCACCAGAGGAGTTCAGATTGCTTCAAATGAAAACATGGAGACAATGGACTCCAGTACTCTTGAACTGAGGAGCAGATACTGGGCTATAAGAACAAGAAGTGGAGGAAACACTAACCAACAGAGAGCATCTGCAGGACAAATCAGCGTGCAGCCCACATTCTCTGTGCAAAGAAACCTCCCATTCGAGAGAGCAACCATCATGGCAGCATTTACGGGAAACACTGAAGGCAGAACTTCAGACATGAGAACTGAGATCATAAGGATGATGGAAAATGCCAGACCTGAAGATGTGTCTTTCCAGGGGCGGGGAGTCTTCGAGCTCTCGGACGAAAAGGCAACGAACCCGATCGTGCCTTCCTTTGACATGAGTAATGAAGGATCTTATTTCTTCGGAGACAATGCAGAGGAGTATGACAATTAA</t>
         </is>
       </c>
-      <c r="DW1" t="inlineStr">
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
         <is>
           <t>&gt;Flu-0326|A_MP</t>
         </is>
       </c>
-      <c r="DX1" t="inlineStr">
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
         <is>
           <t>ATGAGTCTTCTAACCGAGGTCGAAACGTACGTTCTCTCTATCGTCCCGTCGGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTTGAAGATGTCTTTGCAGGGAAGAACACCGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATACTGTCACCTCTGACTAAGGGGATTTTGGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCTCTAAGTGGAAATGGAGACCCAAACAACATGGACAGGGCAGTCAAGTTGTACAGGAAACTGAAGAGAGAAATAACATTCCATGGGGCTAAAGAAGTTGCACTTAGTTACTCAACCGGTGCACTTGCCAGTTGTATGGGTCTCATATACAACAGGATGGGGACGGTGACCGCAGAAGTGGCATTGGGCCTAGTGTGTGCCACCTGTGAGCAGATTGCTGATTCACAGCATCGGTCTCACAGACAGATAGCTACCACCACCAACCCACTAATCAGACATGAAAACAGAATGGTTTTGGCCAGTACTACAGCTAAGGCTATGGAGCAGATGGCTGGATCGAGTGAGCAAGCAGTGGAAGCCATGGAGGTTGCTAGTCAGGCTAGGCAAATGGTGCAGGCGATGAGGACCATTGGAACTCATCCTAGCTCCAGTGCCGGTCTGAGAGATGATCTCCTTGAAAATTTGCAGGCCTACCAAAAACGAATGGGAGTGCAACTGCAGCGATTCAAGTGATCCTCTCGTTATTGCAGCAAGTATCATTGGGATCTTGCACTTGATATTGTGGAGTCTTGATCGCCTTTTCTTCAAATGCGTTTATCGTCGCCTTAAATACGGTTTGAAAGGAGGGCCTTCTACGGAAGGAGTACCTGAGTCCATGAGGGAAGAGTACCGGCAGGAACAGCAGAGTGCTGTGGATGTTGACGATGGTCATTTTGTCAACATAGAGATGGAGTAA</t>
         </is>
       </c>
-      <c r="DY1" t="inlineStr">
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
         <is>
           <t>&gt;Flu-0326|A_NS</t>
         </is>
       </c>
-      <c r="DZ1" t="inlineStr">
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
         <is>
           <t>ATGGATTCCAACACTGTGTCAAGCTTTCAGGTAGACTGCTTTCTTTGGCATGTCCGCAAACAATTTGCAGACCAAGAACTGGGTGATGCCCCATTCCTTGACCGGCTCCGCCGAGACCAGAAGTCTCTAAGAGGAAGAGGCAGCACTCTTGGTCTGGACATCGAGACGGCCACTCGTGCTGGAAAGCAGATAGTGGAGAGGATTCTGGAGGACGAATCCGACGAGGCACTCAAAATGACTATTGCCTCTGTGCCTGCTCCACGCTACCTAACTGACATGACTCTTGAAGAGATGTCAAGAGACTGGTTCATGCTCATGCCCAAGCAAAAAGTGGCAGGCTCCCTCTGTATCAGAATGGACCAGGCGATTATGGATAAGAACATCATACTGAAGGCAAACTTCAGTGTGATCTTCAATCGGCTGGAGACACTAATACTACTCAGAGCTTTCACTGAAGAGGGAGCAATTGTCGGCGAAATTTCACCATTGCCTTCTCTTCCAGGACATACTGATGAGGATGTCAAAAATGCAATTGGGGTCCTCATCGGAGGACTTGAATGGAATGATAACACAGTTCGAGTCTCTGAAATTTTACAGAGATTCGCTTGGAGAAGCAGTAATGAGGATGGGAGACCTCCACTCCCTCCAAAGCAGAAACGGAAAATGGAGAGAACAATTGAGTCAGAAGTTTGAAGAAATAAGGTGGCTGATTGAAGAGGTGCGACACAGACTAAAGATCACAGAAAATAGTTTTGAACAAATAACATTTATGCAAGCCTTACAACTACTGCTTGAAGTGGAGCAAGAGATACGAACTTTCTCGTTTCAGCTTATTTAA</t>
         </is>
       </c>
-      <c r="EA1" t="inlineStr">
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
         <is>
           <t>&gt;Flu-0330|A_NP</t>
         </is>
       </c>
-      <c r="EB1" t="inlineStr">
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
         <is>
           <t>ATGGCGTCTCAAGGCACCAAACGATCCTATGAACAAATGGAAACTGGTGGGGAACGCCAGAATGCCACTGAAATCAGAGCATCTGTTGGAAGAATGGTTGGCGGAATAGGAAGATTCTACATACAGATGTGCACTGAGCTCAAACTCAGTGATTATGAAGGGAGGCTGATCCAAAACAGCATAACCATAGAAAGGATGGTTCTCTCGGCATTTGATGAGAGGAGGAACAAGTACCTGGAGGAACATCCCAGTGCCGGGAAGGATCCCAAGAAGACTGGAGGTCCAATCTACAGGAGGAGAGATGGCAAATGGGTGAGAGAGTTGATCCTCTACGACAAAGAAGAGATCAGAAGAATTTGGCGTCAAGCTAATAATGGAGAGGATGCAACTGCTGGTCTCACTCATTTGATGATTTGGCATTCCAATCTGAATGATGCAACATACCAGAGAACAAGGGCACTTGTGCGTACTGGAATGGACCCTAGAATGTGCTCTCTGATGCAAGGATCAACCCTCCCTAGGAGATCCGGGGCTGCTGGAGCAGCAGTGAAAGGAGTTGGAACAATGGTGATGGAACTAATTCGAATGATCAAGCGAGGGATCAATGATCGGAATTTCTGGAGAGGCGAAAACGGTCGGAGAACCAGGATTGCCTACGAGAGAATGTGCAACATCCTCAAGGGAAAGTTCCAAACAGCAGCACAACGGGCAATGATGGACCAAGTGAGAGAAAGCCGGAATCCTGGGAATGCTGAAATTGAAGATCTCATCTTTCTCGCACGATCTGCTCTCATCCTGAGGGGATCAGTGGCTCATAAGTCCTGTCTGCCTGCTTGCGTATATGGACTTGCTGTAGCCAGTGGATATGACTTTGAAAGAGAGGGATATTCTCTAGTCGGAATTGATCCTTTCCGTCTGCTCCAAAACAGCCAAGTCTTCAGTCTCATCAGACCGAACGAAAATCCAGCTCATAAGAGTCAGCTGGTATGGATGGCATGCCACTCTGCGGCATTTGAGGATCTGAGAGTTTCAAGCTTCATCAGAGGGACAAGAGTAGTCCCAAGAGGACAACTGTCCACCAGAGGAGTTCAGATTGCTTCAAATGAAAACATGGAGACAATGGACTCCAGTACTCTTGAACTGAGGAGCAGATACTGGGCTATAAGAACAAGAAGTGGAGGAAACACTAACCAACAGAGAGCATCTGCAGGACAAATCAGCGTGCAGCCCACATTCTCTGTGCAAAGAAACCTCCCATTCGAGAGAGCAACCATCATGGCAGCATTTACGGGAAACACTGAAGGCAGAACTTCAGACATGAGAACGGAGATCATAAGGATGATGGAAAATGCCAGACCTGAAGATGTGTCTTTCCAGGGGCGGGGAGTCTTCGAGCTCTCGGACGAAAAGGCAACGAACCCGATCGTGCCTTCCTTTGACATGAGTAATGAAGGATCTTATTTCTTCGGAGACAATGCAGAGGAGTATGACAATTAA</t>
         </is>
       </c>
-      <c r="EC1" t="inlineStr">
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
         <is>
           <t>&gt;Flu-0330|A_MP</t>
         </is>
       </c>
-      <c r="ED1" t="inlineStr">
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
         <is>
           <t>ATGAGTCTTCTAACCGAGGTCGAAACGTACGTTCTCTCTATCGTCCCGTCGGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTTGAAGATGTCTTTGCAGGGAAGAACACCGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATACTGTCACCTCTGACTAAGGGGATTTTGGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCTCTAAGTGGAAATGGAGACCCAAACAACATGGACAGGGCAGTCAAGTTGTACAGGAAACTGAAGAGAGAAATAACATTCCATGGGGCTAAAGAAGTTGCACTTAGTTACTCAACCGGTGCACTTGCCAGTTGTATGGGTCTCATATACAACAGGATGGGGACGGTGACCGCAGAAGTGGCATTGGGCCTAGTGTGTGCCACCTGTGAGCAGATTGCTGATTCACAGCATCGGTCTCACAGACAGATAGCTACCACCACCAACCCACTAATCAGACATGAAAACAGAATGGTTTTGGCCAGTACTACAGCTAAGGCTATGGAGCAGATGGCTGGATCGAGTGAGCAAGCAGTGGAAGCCATGGAGGTTGCTAGTCAGGCTAGGCAAATGGTGCAGGCGATGAGGACCATTGGAACTCATCCTAGCTCCAGTGCCGGTCTGAGAGATGATCTCCTTGAAAATTTGCAGGCCTACCAAAAACGAATGGGAGTGCAACTGCAGCGATTCAAGTGATCCTCTCGTTATTGCAGCAAGTATCATTGGGATCTTGCACTTGATATTGTGGATTCTTGATCGCCTTTTCTTCAAATGCGTTTATCGTCGCCTTAAATACGGTTTGAAAGGAGGGCCTTCTACGGAAGGAGTACCTGAGTCCATGAGGGAAGAGTACCGGCAGGAACAGCAGAGTGCTGTGGATGTTGACGATGGTCATTTTGTCAACATAGAGATGGAGTAA</t>
         </is>
       </c>
-      <c r="EE1" t="inlineStr">
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
         <is>
           <t>&gt;Flu-0330|A_NS</t>
         </is>
       </c>
-      <c r="EF1" t="inlineStr">
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
         <is>
           <t>ATGGATTCCAACACTGTGTCAAGCTTTCAGGTAGACTGCTTTCTTTGGCATGTCCGCAAACAATTTGCAGACCAAGAACTGGGTGATGCCCCATTCCTTGACCGGCTCCGCCGAGACCAGAAGTCTCTAAGAGGAAGAGGCAGCACTCTTGGTCTGGACATCGAGACGGCCACTCGTGCTGGAAAGCAGATAGTGGAGAGGATTCTGGAGGAAGAATCCGACGAGGCACTCAAAATGACTATTGCCTCTGTGCCTGCTCCACGCTACCTAACTGACATGACTCTTGAAGAGATGTCAAGAGACTGGTTCATGCTCATGCCCAAGCAAAAAGTGGCAGGCTCCCTCTGTATCAGAATGGACCAGGCGATTATGGATAAGAACATCATACTGAAGGCAAACTTCAGTGTGATCTTCAATCGGCTGGAGACACTAATACTACTCAGAGCTTTCACTGAAGAGGGAGCAATTGTCGGCGAAATTTCACCATTGCCTTCTCTTCCAGGACATACTGATGAGGATGTCAAAAATGCAATTGGGGTCCTCATCGGAGGACTTGAATGGAATGATAACACAGTTCGAGTCTCTGAAATTTTACAGAGATTCGCTTGGAGAAGCAGTAATGAGGATGGGAGACCTCCACTCCCTCCAAAGCAGAAACGGAAAATGGAGAGAACAATTGAGTCAGAAGTTTGAAGAAATAAGGTGGCTGATTGAAGAGGTGCGACACAGACTAAAGATCACAGAAAATAGTTTTGAACAAATAACATTTATGCAAGCCTTACAACTACTGCTTGAAGTGGAGCAAGAGATACGAACTTTCTCGTTTCAGCTTATTTAA</t>
         </is>
       </c>
-      <c r="EG1" t="inlineStr">
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
         <is>
           <t>&gt;Flu-0402|A_PB2</t>
         </is>
       </c>
-      <c r="EH1" t="inlineStr">
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
         <is>
           <t>ATGGAGAGAATAAAAGAACTAAGAGATCTAATGTCACAGTCTCGCACTCGCGAGATACTGACCAAAACCACTGTTGACCACATGGCCATAATCAAAAGGTACACATCGGGAAGGCAAGAGAAGAACCCCGCACTCAGAATGAAATGGATGATGGCAATGAAATATCCAATTACAGCAGATAAGCGAATAATGGAAATGATCCCTGAGAGGAATGAACAAGGGCAAACTCTCTGGAGCAAAACAAACGATGCCGGATCAGACCGAGTGATGGTATCACCCCTGGCTGTGACATGGTGGAACAGGAACGGACCAACAACAAGTACAGTTCACTACCCAAAGGTATATAAAACTTATTTCGAAAAAGTTGAAAGGTTGAAAAACGGGACCTTTGGCCCTGTGCACTTCAGAAACCAAGTTAAAATAAGACGGAGGGTCGATATAAACCCGGGCCATGCTGATCTCAGTGCCAAAGAGGCGCAGGATGTAATCATGGAAGTCGTCTTCCCAAATGAAGTGGGAGCAAGGATATTGACGTCGGAGTCACAACTGACGATAACAAAGGAGAAAAAGGAAGAACTCCAGGACTGCAAAATCGCTCCTCTGATGGTTGCATACATGCTAGAAAGAGAGTTGGTTCGCAAGACGAGGTTTCTCCCAGTTGCTGGTGGGACAAGCAGTGTCTACATTGAGGTGCTGCATTTGACCCAGGGGACATGCTGGGAGCAGATGTACACTCCGGGAGGAGAAGTGAGGAACGATGATGTAGACCAAAGCTTGATCATTGCTGCCAGGAATATAGTAAGAAGAGCAACAGTATCAGCAGATCCATTAGCATCTCTATTGGAGATGTGTCACAGCACACAAATTGGGGGAATAAGGATGGTGGACATCCTTCGGCAAAATCCAACAGAGGAACAAGCCGTGGATATATGCAAGGCAGCAATGGGCTTGAGGATTAGCTCATCTTTCAGCTTTGGTGGATTCACTTTTAAAAGAACAAGTGGATCGTCAGTCAAAAAAGAAGAAGAAGTGCTAACAGGCAACCTTCAAACATTGAAAATAAGAGTACATGAGGGGTATGAAGAGTTCACAATGGTTGGGAGAAGAGCAACGGCCATTCTCAGGAAAGCAACCAGAAGACTGATCCAGCTAATTGTAAGTGGGAGAGACGAGCAGTCAATTGCTGAAGCAATAATTGTGGCCATGGTATTCTCACAAGAGGACTGCATGATTAAAGCAGTTAGAGGTGACCTGAATTTTGTCAATAGGGCGAACCAGCGGCTAAACCCAATGCATCAACTCTTGAGGCATTTCCAAAAGGATGCAAAGGTGCTTTTCCAAAATTGGGGAATTGAACCCATTGACAATGTGATGGGAATGATCGGGGTAATGCCCGACATGACCCCAAGTACTGAGATGTCGCTGAGGGGAATAAGAGTCAGTAAGATGGGAGTAGATGAATACTCAAGTACAGAGCGAGTAGTAGTAAGTATCGACCGGTTTTTAAGAGTTCGAGACCAACAGGGAAACGTACTATTATCACCCGAAGAGGTCAGTGAGACACAAGGAACGGAGAAACTGACAATCACTTATTCGTCATCAATGATGTGGGAGATCAATGGTCCTGAGTCGGTATTGGTCAATACTTATCAGTGGATAATTAGAAACTGGGAAACCGTAAAAATTCAATGGTCACAGGRTCCCACAATGTTGTATAATAAGATGGAATTCGAGCCATTCCAGTCTCTAGTCCCTAAGGCAGCCAGAGGTCAATACAGTGGGTTTGTGAGAACACTATTCCAGCAAATGCGAGATGTGCTTGGAACATTTGACACTGTTCAGATAGTAAAACTCCTCCCCTTTGCTGCCGCCCCACCGGAACAAAGTAGGATGCAGTTCTCCTCTCTGACTGTGAATGTAAGAGGATCAGGAATGAGGATACTGGTAAGAGGCAATTCACCAGTGTTCAATTATAACAAGGCCACCAAGAGGCTCACAGTTCTCGGGAAAGATGCAGGTGCATTGACCGAAGATCCAGATGAAGGCACAGCTGGAGTGGAGTCTGCTGTTTTAAGAGGATTCCTCATTTTGGGCAAAGAAGACAAGAGATATGGCCCAGCATTGAGCATCAATGAGCTGAGCAATCTTGCAAAGGGAGAGAAGGCTAATGTGCTAATTGGGCAAGGAGACGTAGTGTTGGTGATGAAACGGAAACGGGACTCTAGCATACTTACTGACAGCCAGACAGCGACCAAAAGGATTCGGATGGCCATCAATTAG</t>
         </is>
       </c>
-      <c r="EI1" t="inlineStr">
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
         <is>
           <t>&gt;Flu-0402|A_PB1</t>
         </is>
       </c>
-      <c r="EJ1" t="inlineStr">
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
         <is>
           <t>ATGGATGTCAATCCGACTTTACTTTTCTTGAAGGTTCCAGCGCAAAATGCCATAAGCACCACATTCCCGTATACTGGAGATCCCCCATACAGCCATGGAACAGGAACAGGATATACCATGGACACAGTTAACAGAACACATCAGTATTCAGAAAAAGGGAAATGGACAACAAACTCAGAAACTGGAGCACCTCAACTCAATCCAATTGATGGACCATTGCCTGAAGACAATGAACCAAGTGGGTATGCACAAACGGACTGTGTCCTTGAAGCAATGGCTTTCCTTGAAGAGTCCCACCCAGGAATCTTTGAAAACTCGTGTCTTGAAACGATGGAAGTTGTTCAACAAACAAGAGTGGACAAGTTGACTCAAGGCCGTCAGACCTATGATTGGACGTTGAACAGGAATCAGCCGGCTGCAACTGCATTAGCTAATACTATAGAGATCTTCAGATCTAACGGCCTCACAGCCAATGAATCAGGAAGGCTAATAGATTTTCTCAAGGATGTGATGGAATCAATGGATAAGGAGGAAATGGAAATAACAACGCATTTCCAAAGGAAAAGAAGAGTGAGAGACAACATGACCAAGAAAATGGTCACACAAAGGACAATAGGAAAGAAGAAACAGAGGCTAAATAAAAAGAGCTATCTAATAAGAGCATTGACACTGAACACGATGACAAAAGACGCCGAAAGAGGCAAATTAAAAAGAAGGGCAATTGCGACACCTGGAATGCAAATCAGAGGGTTTGTGTACTTTGTTGAAACATTAGCGAGGAGCATTTGTGATAAGCTTGAACAATCTGGACTCCCAGTTGGGGGCAATGAAAAGAAGGCTAAACTGGCAAATGTTGTGAGAAAAATGATGACTAATTCGCAGGACACAGAGCTCTCTTTCACAATCACTGGAGACAACACCAAATGGAATGAAAATCAGAACCCTAGGATGTTTCTGGCAATGATAACATATATAACAAGGAACCAACCTGAATGGTTCAGGAATGTCTTAAGCATTGCACCTATAATGTTCTCAAATAAAATGGCAAGACTAGGGAAAGGGTACATGTTCGAAAGTAAGAGCATGAAGCTTCGAACACAAATACCAGCAGAAATGCTAGCAAGCATTGATATGAAGTACTTCAATGAGTCAACAAGAAAGAAAATAGAGAAGATAAGACCTCTTCTAATAGATGATACAGCCTCATTAAGCCCAGGAATGATGATGGGCATGTTCAATATGCTGAGTACAGTTTTGGGAGTTTCGATTCTAAATCTAGGACAAAGGAGGTACACCAAAACAACATACTGGTGGGACGGACTCCAATCCTCTGATGACTTTGCTCTCATAGTGAATGCTCCGAATCATGAGGGAATACAAGCAGGGGTAGACAGATTCTATAGAACCTGCAAACTGGTTGGAATCAACATGAGCAAAAAGAAGTCCTACATAAACAGGACAGGAACATTTGAATTCACAAGTTTTTTCTACCGCTATGGATTTGTAGCCAACTTCAGTATGGAGTTGCCCAGCTTTGGAGTGTCTGGGATCAATGAATCTGCAGACATGAGCATTGGAGTAACAGTGATAAAGAACAACATGATCAACAATGATCTTGGACCAGCAACAGCTCAAATGGCTCTTCAGCTATTCATCAAGGATTACAGATACACATACCGATGTCACAGAGGAGACACACAAATTCAGACAAGGAGGTCATTCGAGCTGAAGAAGTTGTGGGAACAGACCCGCTCAAAAGCAGGACTGCTGGTCTCAGATGGAGGGCCAAATCTATACAATATTCGGAATCTTCACATTCCAGAAGTCTGCTTGAAATGGGAGCTAATGGACGAAGACTATCAGGGAAGGCTTTGTAATCCCCTGAATCCGTTTGTCAGCCACAAGGAAATAGAGTCTGTGAACAACGCTGTGGTGATGCCAGCTCATGGCCCGGCCAAGAGCATGGAATATGATGCTGTTGCCACCACTCACTCCTGGATACCGAAGAGGAACCGCTCCATTCTCAATACAAGCCAAAGGGGAATCCTTGAAGACGAACAGATGTATCAAAAGTGCTGCAACCTGTTCGAAAAATTCTTCCCTAGCAGTTCATACAGGAGGCCAGTTGGAATTTCCAGCATGGTGGAGGCCATGGTTTCTAGGGCCCGAATTGACGCACGAATTGACTTCGAATCTGGACGGATTAAGAAGGAGGAGTTTGCTGAGACCATGAAGATCTGTTCCACCATTGAAGAGCTCAGACGGCAGAAATAG</t>
         </is>
       </c>
-      <c r="EK1" t="inlineStr">
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
         <is>
           <t>&gt;Flu-0402|A_PA</t>
         </is>
       </c>
-      <c r="EL1" t="inlineStr">
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
         <is>
           <t>ATGGAAGACTTTGTGCGACAATGCTTCAATCCAATGATTGTCGAGCTTGCGGAAAAAGCAATGAAAGAATATGGGGAAGATCCGAAAATCGAGACAAACAAATTTGCCGCAATATGCACACACTTAGAAGTCTGTTTCATGTATTCGGATTTCCATTTTATTGATGAACGAGGCGAATCAATGATTGTAGAATCTGGCGATCCAAATGCATTATTGAAACACCGATTTGAGATAATCGAAGGTAGAGACAGAGCAATGGCCTGGACAGTGGTGAATAGTATCTGCAACACCACAGGGGTCGAAAAGCCCAAATTCCTCCCTGATTTGTATGACTACAAAGAGAACCGATTCATTGAAATTGGGGTAACGCGAAGGGAAGTTCACATATACTATTTAGAAAAAGCCAACAAGATAAAATCAGAGAAAACACATATTCACATATTCTCATTCACTGGAGAGGAAATGGCCACCAAGGCGGACTACTCCCTTGATGAAGAGAGCAGAGCAAGAATAAAAACCAGACTGTTCACTATAAGACAAGAAATGGCCAGTAGAGGTCTATGGGATTCCTTTCGTCAATCCGAGAGAGGCGAAGAGACAATTGAAGAAAGATTTGAAATCACAGGAACCATGCGCAGGCTTGCCGACCAAAGTCTTCCACCGAACTTCTCCAGCCTTGAAAACTTTAGAGCCTATGTGGATGGATTCGAACCGAACGGCTGCATTGAGGGAAAACTTTCTCAAATGTCAAAAGAAGTGAACGCCAGAATTGAGCCATTTCTGAAGACAACACCACGCCCTCTCAGATTACCTGATGGGCCTCCCTGTTCTCAGCGATCGAAGTTCTTGCTGATGGATGCCCTTAAGTTGAGCATCGAAGACCCTAGCCATGAGGGGGAAGGCATACCGCTGTATGATGCAATCAAATGCATGAAGACATTTTTTGGCTGGAAAGAGCCCAACATCGTAAAGCCGCATGAGAAAGGCATAAACCCTAATTACCTCCTGGCTTGGAAGCAGGTGCTGGCAGAACTTCAAGACATTGAAAATGAGGAGAAAATTCCAAAAACAAAGAACATTAAGAAAACAAGCCAATTGAAGTGGGCACTTGGTGAGAACATGGCTCCAGAAAAAGTGGACTTTGAGGACTGCAAAGATGTTAGCGATCTAAGACAGTACGACAGTGACGAACCAGAGTCTAGATCACTAGCAAGCTGGATTCAGAGTGAATTCAACAAGGCATGCGAACTGACAGATTCGAGTTGGATTGAACTTGATGAGATAGGGGAAGACGTTGCTCCAATCGAACACATTGCGAGTGTGAGGAGGAACTATTTCACAGCGGAGGTATCCCATTGCAGGGCCACTGAATACATAATGAAGGGAGTATACATAAACACAGCCCTATTGAATGCATCCTGTGCAGCCATGGATGACTTCCAATTGATTCCAATGATAAGTAAGTGCAGAACTAAAGAAGGAAGACGGAAGACAAATCTGTATGGATTCATTATAAAAGGAAGATCCCATTTGAGGAATGACACCGATGTGGTAAACTTTGTGAGCATGGAATTCTCTCTAACTGACCCGAGGCTAGAGCCACACAAATGGGAAAAGTACTGTGTTCTTGAGATAGGAGACATGCTCCTACGGACTGCAATAGGCCAAGTGTCGAGGCCCATGTTCCTGTATGTGAGAACCAATGGAACTTCCAAGATCAAAATGAAATGGGGCATGGAGATGAGGCGATGCCTTCTTCAGTCCCTTCAACAAATTGAGAGCATGATTGAGGCCGAATCTTCTGTCAAAGAGAAGGACATGTCCAAGGAATTCTTTGAAAACAAATCAGAAACATGGCCAATTGGAGAATCACCCAAAGGGGTGGAGGAAGGCTCTATTGGGAAAGTGTGCAGAACATTGCTAGCAAAGTCTGTGTTCAACAGCCTATATGCATCTCCACAACTCGAGGGGTTTTCAGCTGAATCAAGAAAATTGCTTCTCATTGTTCAGGCACTTAGGGACAACCTGGAACCTGGAACCTTCGATCTTGGGGGGCTATATGAAGCAATTGAGGAGTGCCTGATTAACGATCCCTGGGTTTTGCTTAATGCATCTTGGTTCAACTCCTTCCTCACACATGCACTGAAATAG</t>
         </is>
       </c>
-      <c r="EM1" t="inlineStr">
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
         <is>
           <t>&gt;Flu-0402|A_HA</t>
         </is>
       </c>
-      <c r="EN1" t="inlineStr">
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
         <is>
           <t>ATGGAGAACATAGTACTACTTCTTGCAATAGTTAGCCTTGTTAAAAGTGATCAGATTTGCATTGGTTACCATGCAAACAATTCGACAGAGCAAGTTGACACGATAATGGAAAAGAACGTCACTGTTACACATGCCCAAGACATACTGGAAAAAACACACAACGGAAAGCTCTGTGATTTAAATGGGGTGAAGCCACTGATTTTAAAGGATTGTAGTGTAGCTGGATGGCTCCTCGGAAACCCAATGTGCGACGAATTCATCAGAGTGCCGGAATGGTCATACATAGTGGAGCGGGCTAACCCAGCCAATGACCTCTGTTACCCAGGGAGCCTCAATGACTATGAAGAACTGAAACACATGTTGAGCAGAATAAATCATTTTGAGAAGATTCAGATCATTCCCAAGAGTTCCTGGCCAAATCATGAAACATCACTAGGGGTGAGCGCAGCTTGTCCATACCAGGGAGCGCCCTCCTTTTTCAGAAATGTGGTATGGCTTATCAAAAAGAACGATGCATACCCAACAATAAAGATAAGCTACAATAATACTAATCGGGAAGATCTCTTGATACTTTGGGGGATTCATCATTCCAACAATGCAAAAGAACAGACAAATCTCTACAAAAACCCAACCACCTACATTTCAGTTGGAACATCAACTTTAAACCAGAGGTTGGCACCAAAAATAGCTACTAGATCCCAAGTAAACGGGCAACGTGGAAGAATGGACTTCTTCTGGACAATCTTAAAACCAGATGATGCAATCCATTTCGAGAGTAACGGAAATTTCATTGCTCCAGAATATGCATACAAAATTGTCAAGAAAGGGGACTCAACAGTTATGAAAAGTGGAGTGGAATATGGCCACTGCAACACCAAATGTCAAACCCCAGTAGGTGCGATAAATTCTAGTATGCCATTCCACAACATACATCCTCTCACCATTGGGGAATGTCCCAAATACGTGAAGTCAAACAAGTTGGTCCTTGCGACTGGGCTCAGAAATAGTCCTCTAAGAGAAAAGAGAAGAAAAAGAGGTCTGTTTGGGGCGATAGCAGGGTTTATAGAGGGAGGATGGCAGGGAATGGTTGATGGTTGGTATGGATACCATCATAGCAATRAGCAGGGGAGTGGGTACGCTGCGGACAAAGAATCCACCCAAAAGGCAATAGATGGAGTTACCAATAAGGTCAACTCAATCATTGACAAAATGAACACTCAATTTGAGGCAGTTGGAAGGGAGTTTAACAACTTAGAAARGAGGATAGAGAATTTGAACAAGAAAATGGAAGACGGATTCCTAGATGTCTGGACCTATAATGCTGAACTTCTAGTCCTCATGGAAAACGAGAGGACTCTAGACTTCCATGATTCAAATGTCAAGAACCTTTACGACAAAGTCAGATTACAGCTTAGGGATAATGCAAAGGAGCTGGGTAAYGGCTGTTTCGAATTCTATCACAAATGTGATAATGAATGTATGGAAAGTGTGAGAAATGGGACGTATGACTACCCTCAGTATTCAGAAGAAGCAAGATTAAAAAGAGAAGAAATAAGCGGAGTGAAATTAGAATCAGTAGGAACTTACCAGATACTGTCAATTTATTCAACAGCGGCAAGTTCCCTAGCACTGGCAATCATGATGGCTGGTCTATCTTTATGGATGTGCTCCAATGGGTCGTTACAATGCAGAATTTGCATTTAG</t>
         </is>
       </c>
-      <c r="EO1" t="inlineStr">
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
         <is>
           <t>&gt;Flu-0402|A_NA</t>
         </is>
       </c>
-      <c r="EP1" t="inlineStr">
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
         <is>
           <t>ATGAATCCAAATCAAAAGATAACAACCATTGGATCAATCTGTATGGTAATTGGGATAGTCAGCTTGATGCTGCAAATTGGGAACATAATCTCAATATGGGTTAGCCATTCAATCCAAACAGGGAATCAATACCAGCCTGAACCATGCAATCAAAGCATCATTACCTATGAGAACAACACCTGGGTAAATCAGACGTATGTCAACATCAGCAATACCAATTTTCTTGCTGAGCAGGCTGTTACTTCGGTAACATTAGCGGGCAATTCATCTCTTTGCCCTATTAGTGGGTGGGCAATATACAGTAAGGACAACGGTATAAGAATTGGGTCCAAGGGGAATGTGTTTGTTATAAGAGAACCGTTCATCTCATGCTCCCACTTGGAATGCAGAGCCTTTTTCCTGACCCAGGGAGCTCTGCTGAATGACAAACATTCTAATGGGACAGTTAAGGATAGAAGCCCTTATAGAACTTTGATGAGTTGTCCCGTGGGTGAGGCTCCTTCCCCGTATAATTCAAGATTTGAGTCTGTTGCTTGGTCGGCAAGTGCTTGTCATGATGGCATCAGTTGGTTGACAATCGGTATTTCTGGTCCAGACAATGGAGCTGTGGCTGTATTGAAGTACAATGGCATAATAAYGGATACTATCAAGAGTTGGAGAAACAACATTTTGAGAACTCAAGAATCTGAATGTGCTTGCGTAAATGGCTCTTGCTTCACCGTAATGACTGATGGACCAAGCAATGGGCAGGCCTCATATAAAATCTTCAAGATAGAGAAAGGGAAAGTTGTCAAGTCAGTTGAGATGAATGCCCCTAATTACCACTACGAGGAATGCTCCTGTTATCCTGATGCGGGTGATATTATGTGTGTGTGCAGGGACAATTGGCATGGCTCAAATCGGCCGTGGGTATCTTTTAATCAAAATCTGGAGTATCAAATAGGATATATATGCAGTGGGGTATTCGGGGACAATCCCCGCCCCAATGATGGAACAGGCAGTTGCAGTCCAATGCCCTCYAATGGGGCATATGGGGTAAAAGGGTTTTCATTTAAGTACGGTAATGGGGTTTGGATCGGAAGAACAAAAAGCACTAGTTCCAGAAGCGGCTTTGAGATGATTTGGGATCCGAATGGGTGGACTGAGACGGACAGTAGTTTCTCAGTGAAGCAAGACATTGTAGAAATAACTGACTGGTCAGGATATAGTGGGAGTTTTGTCCAGCATCCAGAACTGACAGGATTAGATTGCATGAGGCCTTGTTTCTGGGTTGAGCTAATCAGAGGGAGGCCCAAAGAGAACACAATTTGGACTAGCGGGAGCAGCATATCCTTTTGTGGTGTAAATAGTGACACTGTGGGTTGGTCTTGGCCAGACGGTGCTGAGTTGCCATTCACCATTGACAAGTAG</t>
         </is>
       </c>
-      <c r="EQ1" t="inlineStr">
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
         <is>
           <t>&gt;Flu-0402|A_MP</t>
         </is>
       </c>
-      <c r="ER1" t="inlineStr">
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
         <is>
           <t>ATGAGTCTTCTAACCGAGGTCGAAACGTACGTTCTCTCTATCGTCCCGTCGGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTTGAAGATGTCTTTGCAGGGAAGAACACCGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATCCTGTCACCTCTGACTAAGGGGATTTTGGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCTCTAAGTGGAACTGGAGACCCAAACAACATGGACAGGGCAGTCAAGTTGTACAGGAAACTAAAGAGAGAGATAACATTCCACGGTGCTAAAGAAGTTGCACTCAGTTACTCAACCGGTGCACTTGCCAGTTGTATGGGTCTCATATACAACAGGATGGGGACGGTGACCGCAGAAGTGGCATTGGGCCTAGTGTGTGCCACCTGTGAGCAGATTGCTGATTCACAGCATCGGTCTCACAGACAGATAGCTACCACCACCAACCCACTAATCAGACATGAAAACAGAATGGTTTTGGCCAGTACTACAGCTAAGGCTATGGAGCAGATGGCTGGATCGAGTGAGCAAGCAGTGGAAGCCATGGAGGTTGCTAGTCAGGCTAGGCAGATGGTGCAGGCGATGAGGACCATTGGAACTCATCCTAGCTCCAGTGCCGGTCTGAGAGATGATCTCCTTGAAAATTTGCAGGCCTACCAAAAACGGATGGGAGTGCAACTGCAGCGATTCAAGTGATCCTCTCGTTATTGCCGCAAGTATCATTGGGATCTTGCACTTGATATTGTGGATTCTTGATCGCCTTTTCTTCAAATGCGTTTATCGTCGCCTTAAATACGGTTTGAAAGGAGGGCCTTCTACGGAAGGAGTACCTGAGTCCATGAGGGAAGAGTACCGGCAGGAACAGCAGAGTGCTGTGGATGTCGACGATGGTCATTTTGTCAACATAGAGCTGGAGTAA</t>
         </is>
       </c>
-      <c r="ES1" t="inlineStr">
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
         <is>
           <t>&gt;Flu-0402|A_NS</t>
         </is>
       </c>
-      <c r="ET1" t="inlineStr">
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
         <is>
           <t>ATGGATTCCAACACTGTGTCAAGCTTTCAGGTAGACTGCTTTCTTTGGCATGTCCGCAAACGATTTGCAGACCAAGAACTGGGTGATGCCCCATTCCTTGACCGGCTCCGCCGAGACCAGAAGTCTCTAAGAGGAAGAGGCAGCACTCTTGGTCTGGACATCGAGACGGCCACTCGTGCTGGAAAGCAGATAGTGGAGAGGATTCTGGAGGAAGAATCCGACGAGGCACTCAAAATGACTATTGCCTCTGTGCCTGCTCCACGCTACCTAACTGACATGACTCTTGAAGAGATGTCAAGAGACTGGTTCATGCTCATGCCCAAGCAAAAAATGGCAGGCTCCCTCAGTATCAAAATGGACCAGGCGATTATGGATAAGAAAATCATACTGAAGGCAAACTTCAGTGTGATCTTCAATCGGCTGGAGACACTAATACTACTCAGAGCTTTCACTGAAGAAGGAGCAATTGTCGGCGAAATTTCACCATTGCCTTCTCTTCCAGGACATACTGATGAGGATGTCAAAAATGCAATTGGGGTCCTCATCGGAGGACTTGAATGGAATGATAACACAGTTCGAGTCTCTGAAACTTTACAGAGATTCGCTTGGAGAAGCAGTAATGAGGATGGGAGATCTCCACTCCCTCCAAAGCAGAAACGGAAAATGGAGAGAACAATTGAGTCAGAAGTTTGAAGAAATAAGGTGGCTGATTGAAGAAGTTCGACACAGACTAAAGATCACAGAAAATAGTTTTGAACAAATAACATTTATGCAAGCCTTACAACTACTGCTTGAAGTGGAGCAAGAGATAAGAACTTTCTCGTTTCAGCTTATTTAA</t>
         </is>
       </c>
-      <c r="EU1" t="inlineStr">
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
         <is>
           <t>&gt;Flu-0403|A_MP</t>
         </is>
       </c>
-      <c r="EV1" t="inlineStr">
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
         <is>
           <t>ATGAGTCTTCTAACCGAGGTCGAAACGTACGTTCTCTCTATCGTCCCGTCGGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTTGAAGATGTCTTTGCAGGGAAGAACACCGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATCCTGTCACCTCTGACTAAGGGGATTTTGGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCTCTAAGTGGAACTGGAGACCCAAACAACATGGACAGGGCAGTCAAGTTGTACAGGAAACTAAAGAGAGAGATAACATTCCAYGGTGCTAAAGAAGTTGCACTCAGTTACTCAACCGGTGCACTTGCCAGTTGTATGGGTCTCATATACAACAGGATGGGGACGGTGACCGCAGAAGTGGCATTGGGCCTAGTGTGTGCCACCTGTGAGCAGATTGCTGATTCACAGCATCGGTCTCACAGACAGATAGCTACCACCACCAACCCACTAATCAGACATGAAAACAGAATGGTTTTGGCCAGTACTACAGCTAAGGCTATGGAGCAGATGGCTGGATCGAGTGAGCAAGCAGTGGAAGCCATGGAGGTTGCTAGTCAGGCTAGGCAGATGGTGCAGGCGATGAGGACCATTGGAACTCATCCTAGCTCCAGTGCCGGTCTGAGAGATGATCTCCTTGAAAATTTGCAGGCCTACCAAAAACGGATGGGAGTGCAACTGCAGCGATTCAAGTGATCCTCTCGTTATTGCCGCAAGTATCATTGGGATCTTGCACTTGATATTGTGGATTCTTGATCGCCTTTTCTTCAAATGCGTTTATCGTCGCCTTAAATACGGTTTGAAAGGAGGGCCTTCTACGGAAGGAGTACCTGAGTCCATGAGGGAAGAGTACCGGCAGGAACAGCAGAGTGCTGTGGATGTYGACGATGGTCATTTTGTCAACATAGAGCTGGAGTAA</t>
         </is>
       </c>
-      <c r="EW1" t="inlineStr">
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
         <is>
           <t>&gt;Flu-0406|A_PB2</t>
         </is>
       </c>
-      <c r="EX1" t="inlineStr">
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
         <is>
           <t>ATGGAGAGAATAAAAGAACTAAGAGATCTAATGTCACAGTCTCGCACTCGCGAGATACTGACCAAAACCACTGTTGACCACATGGCCATAATCAAAAGGTACACATCGGGAAGGCAAGAGAAGAACCCCGCACTCAGAATGAAATGGATGATGGCAATGAAATATCCAATTACAGCAGATAATCGAATAATGGAAATGATCCCTGAGAGGAATGAACAAGGGCAAACTCTCTGGAGCAAAACAAACGATGCCGGATCAGACCGAGTGATGGTATCACCCCTGGCTGTGACATGGTGGAACAGGAACGGACCAACAACAAGTACAGTTCACTACCCAAAGGTATATAAAACTTAYTTCGAAAAAGTTGAAAGGTTGAAAAACGGGACCTTTGGCCCTGTGCACTTCAGAAACCAAGTTAAAATAAGACGGAGGGTCGATATAAACCCGGGCCATGCTGATCTCAGTGCCAAAGAGGCGCAGGATGTAATCATGGAAGTCGTCTTCCCAAATGAAGTGGGAGCAAGGATATTGACGTCGGAGTCACAACTGACGATAACAAAGGAGAAAAAGGAAGAACTCCAGGACTGCAAAATCGCTCCTCTGATGGTTGCATACATGCTAGAAAGAGAGTTGGTTCGCAAGACGAGGTTTCTCCCAGTTGCTGGTGGGACAAGCAGTGTCTACATTGAGGTGCTGCATTTGACCCAGGGGACATGCTGGGAGCAGATGTACACTCCGGGAGGAGAAGTGAGGAACGATGATGTAGACCAAAGCTTGATCATTGCTGCCAGGAATATAGTAAGAAGAGCAACAGTATCAGCAGATCCATTAGCATCTCTATTGGAGATGTGTCACAGCACACAAATTGGGGGAATAAGGATGGTGGACATCCTTCGGCAAAATCCAACAGAAGAACAAGCCGTGGATATATGCAAGGCAGCAATGGGCTTGAGGATTAGCTCATCTTTCAGCTTTGGTGGATTCACTTTTAAAAGAACAAGTGGATCGTCAGTCAAAAAAGAAGAAGAAGTGCTAACAGGCAACCTTCAAACATTGAAAATAAGAGTACATGAGGGGTATGAAGAGTTCACAATGGTTGGGAGAAGAGCAACGGCCATTCTCAGGAAAGCAACCAAAAGACTGATCCAGCTAATTGTAAGTGGGAGAGACGAGCAGTCAATTGCTGAAGCAATAATTGTGGCCATGGTATTCTCACAAGAGGACTGCATGATTAAAGCAGTTAGAGGTGACCTGAATTTTGTCAATAGGGCGAACCAGCGACTAAACCCAATGCATCAACTCTTGAGGCATTTCCAAAAGGATGCAAAGGTGCTTTTCCAAAATTGGGGAATTGAACCCATTGACAATGTGATGGGAATGATCGGGGTAATGCCCGACATGACCCCAAGTACTGAGATGTCGCTGAGGGGAATAAGAGTCAGTAAGATGGGAGTAGATGAATACTCAAGTACAGAGCGAGTAGTAGTAAGTATCGACCGGTTTTTAAGAGTTCGAGACCANNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNTAATNNGAAANTNGGAAACCGTAAAAATTCAATGGTCACAGGATCCCACAATGTTGTATAATAAGATGGAATTCGAGCCATTCCAGTCTCTAGTCCCTAAGGCAGCCAGAGGTCAATACAGTGGGTTTGTGAGAACACTATTCCAGCAAATGCGAGATGTGCTTGGAACATTTGACACTGTTCAGATAGTAAAACTCCTCCCCTTTGCTGCCGCCCCACCGGAACAAAGTAGGATGCAGTTCTCCTCCCTGACTGTGAATGTAAGAGGATCAGGAATGAGGATACTGGTAAGAGGCAATTCACCAGTGTTCAATTATAACAAGGCCACCAAGAGGCTCACAGTTCTCGGGAAAGATGCAGGTGCATTGACCGAAGATCCAGATGAAGGCACAGCTGGAGTGGAGTCTGCTGTTTTAAGAGGATTCCTCATTTTGGGCAAAGAAGACAAGAGATATGGCCCAGCATTGAGCATCAATGAGCTGAGCAATCTTGCAAAGGGAGAGAAGGCTAATGTGCTAATTGGGCAAGGAGACGTAGTGTTGGTGATGAAACGGAAACGGGACTCTAGCATACTTACTGACAGCCAGACAGCGACCAAAAGGATTCGGATGGCCATCAATTAG</t>
         </is>
       </c>
-      <c r="EY1" t="inlineStr">
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
         <is>
           <t>&gt;Flu-0406|A_PB1</t>
         </is>
       </c>
-      <c r="EZ1" t="inlineStr">
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
         <is>
           <t>ATGGATGTCAATCCGACTTTACTTTTCTTGAAGGTTCCAGCGCAAAATGCCATAAGCACCACATTCCCGTATACTGGAGATCCCCCATACAGCCATGGAACAGGAACAGGATATACCATGGACACAGTTAACAGAACACATCAGTATTCAGAAAAAGGGAAATGGACAACAAACTCAGAAACTGGAGCACCTCAACTCAATCCAATTGATGGACCATTGCCTGAGGACAATGAACCAAGTGGGTATGCACAAACGGACTGTGTCCTTGAAGCAATGGCTTTCCTTGAAGAGTCCCACCCAGGAATCTTTGAAAACTCGTGTCTTGAAACGATGGAAGTTGTTCAACAAACAAGAGTGGACAAGTTGACTCAAGGCCGTCAGACCTATGATTGGACGTTGAACAGGAATCAGCCGGCTGCAACTGCATTAGCTAATACTATAGAGATCTTCAGATCTAACGGCCTCACAGCCAATGAATCAGGAAGGCTAATAGATTTTCTCAGGGATGTGATGGAATCAATGGATAAGGAGGAAATGGAAATAACAACGCATTTCCAAAGGAAAAGAAGAGTGAGAGACAACATGACCAAGAAAATGGTCACACAAAGGACAATAGGAAAGAAGAAACAGAGGCTAAATAAAAAGAGCTATCTAATAAGAGCATTGACACTGAACACGATGACAAAAGAYGCCGAAAGAGGCAAATTAAAAAGAAGGGCAATTGCGACACCTGGAATGCAAATCAGAGGGTTTGTGTACTTTGTTGAAACATTAGCGAGGAGCATTTGTGATAAGCTTGAACAATCTGGACTCCCAGTTGGGGGCAATGAAAAGAAGGCTAAACTGGCAAATGTCGTGAGAAAAATGATGACCAATTCGCAGGACACAGAGCTCTCTTTCACAATCACTGGAGACAACACCAAATGGAATGAAAATCAGAACCCTAGGATGTTTCTGGCAATGATAACATATATAACAAGGAACCAACCTGAATGGTTCAGGAATGTCTTAAGCATTGCACCTATAATGTTCTCAAATAAAATGGCAAGACTAGGGAAAGGGTACATGTTCGAAAGTAAGAACATGAAGCTTCGAACACAAATACCAGCAGAAATGCTAGCAAGCATTGATATGAAGTACTTCAATGAGTCAACAAGAAAGAAAATAGAGAAGATAAGACCTCTTCTAATAGATGATACAGCCTCATTAAGCCCAGGAATGATGATGGGCATGTTCAATATGCTGAGTACAGTTTTGGGAGTTTCGATTCTAAATCTAGGACAAAGGAGGTACACCAAAACAACATACTGGTGGGACGGACTCCAATCCTCTGATGACTTTGCTCTCATAGTGAATGCTCCGAATCATGAGGGAATACAAGCAGGGGTAGACAGATTCTATAGAACCTGCAAACTGGTTGGAATCAACATGAGCAAAAAGAAGTCCTACATAAACAGGACAGGAACATTTGAATTCACAAGTTTTTTCTACCGCTATGGATTTGTAGCCAACTTCAGTATGGAGTTGCCCAGCTTTGGAGTGTCTGGGATCAATGAATCTGCAGACATGAGCATTGGAGTAACAGTGATAAAGAACAACATGATCAACAATGATCTTGGACCAGCAACAGCTCAAATGGCTCTTCAGCTATTCATCAAGGATTACAGATACACATACCGATGTCACAGAGGAGACACACAAATTCAGACAAGGAGGTCATTCGAGCTGAAGAAGTTGTGGGAACAGACCCGCTCAAAAGCAGGACTGCTGGTCTCAGATGGAGGACCAAATCTATACAATATTCGGAATCTTCACATTCCAGAAGTCTGCTTGAAATGGGAGCTAATGGACGAAGACTATCAGGGAAGGCTTTGTAATCCCCTGAATCCGTTTGTCAGCCACAAGGAAATAGAGTCTGTGAACAACGCTGTGGTGATGCCAGCTCATGGCCCGGCCAAGAGCATGGAATATGATGCTGTTGCCACCACTCACTCCTGGATACCGAAGAGGAACCGCTCCATTCTCAATACAAGCCAAAGGGGAATCCTTGAAGACGAACAGATGTATCAAAAGTGCTGCAATCTGTTCGAAAAATTCTTCCCTAGCAGTTCATACAGGAGGCCAGTTGGAATTTCCAGCATGGTGGAGGCCATGGTTTCTAGGGCCCGAATTGACGCACGAATTGACTTCGAATCTGGACGGATTAAGAAGGAGGAGTTTGCTGAGATCATGAAGATCTGTTCCACCATTGAAGAGCTCAGACGGCAGAAATAG</t>
         </is>
       </c>
-      <c r="FA1" t="inlineStr">
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
         <is>
           <t>&gt;Flu-0406|A_PA</t>
         </is>
       </c>
-      <c r="FB1" t="inlineStr">
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
         <is>
           <t>ATGGAAGACTTTGTGCGACAATGCTTCAATCCAATGATTGTCGAGCTTGCGGAAAAAGCAATGAAAGAATATGGGGAAGATCCGAAAATCGAGACAAACAAATTTGCCGCAATATGCACACACTTAGAAGTCTGTTTCATGTATTCGGATTTCCATTTTATTGATGAACGAGGCGAATCAATGATTGTAGAATCTGGCGATCCAAATGCATTATTGAAACACCGATTTGAGATAATCGAAGGTAGAGACAGAGCAATGGCCTGGACAGTGGTGAATAGTATCTGCAACACCACAGGGGTCGAAAAGCCCAAATTCCTCCCTGATTTGTATGACTACAAAGAGAACCGATTCATTGAAATTGGGGTAACGCGAAGGGAAGTTCACATATACTATTTAGAAAAAGCCAACAAGATAAAATCAGAGAAAACACATATTCACATATTCTCATTCACTGGAGAGGAAATGGCCACCAAGGCGGACTACTCCCTTGATGAAGAGAGCAGAGCAAGAATAAAAACCAGACTGTTCACTATAAGACAAGAAATGGCCAGTAGAGGTCTATGGGATTCCTTTCGTCAATCCGAGAGAGGCGAAGAGACAATTGAAGAAAGATTTGAAATCACAGGAACCATGCGCAGGCTTGCCGACCAAAGTCTTCCACCGAACTTCTCCAGCCTTGAAAACTTTAGAGCCTATGTGGATGGATTCGAACCGAACGGCTGCATTGAGGGCAAACTTTCTCAAATGTCAAAAGAAGTGAACGCCAGAATTGAGCCATTTCTGAAGACAACACCACGCCCTCTCAGATTACCTGATGGGCCTCCCTGTTCTCAGCGATCGAAGTTCTTGCTGATGGATGCCCTTAAGTTGAGCATCGAAGACCCTAGCCATGAGGGGGAAGGCATACCGCTGTATGATGCAATCAAATGCATGAAGACATTTTTTGGCTGGAAAGAGCCCAACATCGTAAAGCCGCATGAGAAAGGCATAAACCCTAATTACCTCCTGGCTTGGAAGCAGGTGCTGGCAGAACTTCAAGACATTGAAAATGAGGAGAAAATTCCAAAAACAAGGAACATGAAGAAAACAAGCCAATTGAAGTGGGCACTTGGTGAGAACATGGCTCCAGAAAAAGTGGACTTTGAGGACTGCAAAGATGTTAGCGATCTAAGACAGTACGACAGTGACGAACCAGAGTCTAGATCACTAGCAAGCTGGATTCAGAGTGAATTCAACAAGGCATGCGAACTGACAGATTCGAGTTGGATTGAACTTGATGAGATAGGGGAAGACGTTGCTCCAATCGAACACATTGCGAGTGTGAGGAGGAACTATTTCACAGCGGAGGTATCCCATTGCAGGGCCACTGAATACATAATGAAGGGAGTATACATAAACACAGCCCTATTGAATGCATCCTGTGCAGCCATGGATGACTTCCAATTGATTCCAATGATAAGTAAGTGCAGAACTAAAGAAGGAAGACGGAAGACAAATCTGTATGGATTCATTATAAAAGGAAGATCCCATTTGAGGAATGACACCGATGTGGTAAACTTTGTGAGCATGGAATTCTCTCTAACTGACCCAAGGCTAGAGCCACACAAATGGGAAAAGTACTGTGTTCTTGAGATAGGAGACATGCTCCTACGGACTGCAATAGGCCAAGTGTCGAGGCCCATGTTCCTGTATGTGAGAACCAATGGAACTTCCAAGATCAAAATGAAATGGGGCATGGAGATGAGGCGATGCCTTCTTCAGTCCCTTCAACAAATTGAGAGCATGATTGAGGCCGAATCTTCTGTCAAAGAGAAGGACATGTCCAAGGAATTCTTTGAAAACAAATCAGAAACATGGCCAATTGGGGAATCACCCAAAGGGGTGGAGGAAGGCTCTATTGGGAAAGTGTGCAGAACATTGCTAGCAAAGTCTGTGTTCAACAGCCTATATGCATCTCCACAACTCGAGGGGTTTTCAGCTGAATCAAGAAAATTGCTTCTCATTGTTCAGGCACTTAGGGACAACCTGGAACCTGGAACCTTCGATCTTGGGGGGCTATATGAAGCAATTGAGGAGTGCCTGATTAACGATCCCTGGGTTTTGCTTAATGCATCTTGGTTCAACTCCTTCCTCACACATGCACTGAAATAG</t>
         </is>
       </c>
-      <c r="FC1" t="inlineStr">
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
         <is>
           <t>&gt;Flu-0406|A_HA</t>
         </is>
       </c>
-      <c r="FD1" t="inlineStr">
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
         <is>
           <t>ATGGAGAACATAGTACTACTTCTTGCAATAGTTAGCCTTGTTAAAAGTGATCAGATTTGCATTGGTTACCATGCAAACAATTCGACAGAGCAAGTTGACACGATAATGGAAAAGAACGTCACTGTTACACATGCCCAAGACATACTGGAAAAAACACACAACGGAAAGCTCTGTGATTTAAATGGGGTGAAGCCACTGATTTTAAAGGATTGTAGTGTAGCTGGATGGCTCCTCGGAAACCCAATGTGCGACGAATTCATCAGAGTGCCGGAATGGTCATACATAGTGGAGCGGGCTAACCCAGCTAATGACCTCTGTTACCCAGGGAGCCTCAATGACTATGAAGAACTGAAACACATGTTGAGCAGAATAAATCATTTTGAGAAGATTCAGATCATTCCCAAGAGTTCCTGGCCAAATCATGAAACATCACTAGGGGTGAGCGCAGCTTGTCCATACCAGGGAGCGCCCTCCTTTTTCAGAAATGTGGTGTGGCTTATCAAAAAGAACGATGCATACCCAACAATAAAGATAAGCTACAATAATACTAATCGGGAAGATCTCTTGATACTTTGGGGGATTCATCATTCCAACAATGCAAAAGAACAGACAAATCTCTACAAAAACCCAACCACCTACATTTCAGTTGGAACATCAACTTTAAACCAGAGGTTGGCACCAAAAATAGCTACTAGATCCCAAGTAAACGGGCAACGTGGAAGAATGGACTTCTTCTGGACAATCTTAAAACCAGATGATGCAATCCATTTCGAGAGTAACGGAAATTTCATTGCTCCAGAATATGCATACAAAATTGTCAAGAAAGGGGACTCAACAGTTATGAAAAGTGGAGTGGAATATGGCCACTGCAACACCAAATGTCAAACCCCAGTAGGTGCGATAAATTCTAGTATGCCATTCCACAACATACATCCTCTCACCATCGGGGAATGTCCCAAATACGTGAAGTCAAACAAGTTGGTCCTTGCGACTGGGCTCAGAAATAGTCCTCTAAGAGAAAAGAGAAGAAAAAGAGGTCTGTTTGGGGCGATAGCAGGGTTTATAGAGGGAGGATGGCAGGGAATGGTTGATGGTTGGTATGGATACCATCATAGCAATGAGCAGGGGAGTGGGTACGCTGCGGACAAAGAATCCACCCAAAAGGCAATAGATGGAATTACCAATAAGGTCAACTCAATCATTGACAAAATGAACACTCAATTTGAGGCAGTTGGAAGGGAGTTTAACAACTTAGAAAGGAGGATAGAGAATTTGAACAAGAAAATGGAAGACGGATTCCTAGATGTCTGGACCTATAATGCTGAACTTCTAGTCCTCATGGAAAACGAGAGGACTCTAGACTTCCATGATTCAAATGTCAAGAACCTTTACGACAAAGTCAGATTACAGCTTAGGGATAATGCAAAGGAGCTGGGTAACGGCTGTTTCGAATTCTATCACAAATGTGATAATGAATGTATGGAAAGTGTGAGAAATGGGACGTATGACTACCCTCAGTATTCAGAAGAAGCAAGATTAAAAAGAGAAGAAATAAGCGGAGTGAAATTAGAATCAGTAGGAACTTACCAGATACTGTCAATTTATTCAACAGCGGCAAGTTCCCTAGCACTGGCAATCATGATGGCTGGTCTATCTTTATGGATGTGCTCCAATGGGTCGTTACAATGCAGAATTTGCATTTAG</t>
         </is>
       </c>
-      <c r="FE1" t="inlineStr">
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
         <is>
           <t>&gt;Flu-0406|A_NP</t>
         </is>
       </c>
-      <c r="FF1" t="inlineStr">
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
         <is>
           <t>ATGGCGTCTCAAGGCACCAAACGATCCTATGAACAAATGGAAACTGGTGGGGAACGCCAGAATGCCACTGAAATCAGAGCATCTGTTGGAAGAATGGTTGGCGGAATCGGGAGATTCTACATACAGATGTGTACTGAACTCAAACTCAGTGATTACGAAGGGAGGCTGATCCAAAACAGCATAACCATAGAAAGGATGGTTCTCTCGGCATTTGATGAGAGGAGGAACAAGTACCTGGAGGAACATCCCAGTGCCGGGAAGGATCCCAAGAAGACTGGAGGTCCAATCTACAGGAGGAGAGATGGCAAATGGGTGAGAGAGTTGATCCTCTACGACAAAGAAGAGATCAGAAGAATTTGGCGTCAAGCTAATAATGGAGAGGATGCAACTGCTGGTCTCACTCACTTGATGATTTGGCATTCCAATCTGAATGATGCCACATACCAGAGAACAAGGGCACTTGTGCGTACTGGAATGGACCCTAGAATGTGCTCTCTGATGCAAGGCTCAACCCTCCCTAGGAGATCAGGGGCTGCTGGAGCAGCAGTGAAAGGAGTTGGAACAATGGTGATGGAACTAATTCGAATGATCAAACGAGGGATCAATGATCGGAATTTCTGGAGAGGCGAAAACGGTCGGAGAACCAGGATTGCCTACGAGAGAATGTGCAACATTCTCAAGGGAAAGCTCCAAACAGCAGCACAACGGGCAATGATGGACCAAGTGAGAGAAAGCCGGAATCCTGGGAATGCTGAAATTGAAGATCTCATCTTTCTCGCACGATCTGCTCTCATCCTGAGGGGATCAGTGGCTCATAAGTCCTGTCTGCCTGCTTGCGTATATGGACTTGCTGTAGCCAGTGGATATGACTTTGAAAGAGAGGGATATTCTCTAGTCGGAATTGATCCTTTCCGTCTGCTCCAAAACAGCCAAGCCTTCAGTCTCATCAGACCGAACGAAAATCCAGCTCATAAAAGTCAGCTGGTATGGATGGCATGCCACTCTGCGGCATTTGAGGATCTGAGAGTGTCAAGCTTCATCAGAGGGACAAGAGTAGTCCCAAGAGGACAACTGTCCACCAGAGGAGTTCAGATTGCTTCAAATGAAAACATGGAGACAATGGACTCCAGTACTCTTGAACTGAGGAGCAGATATTGGGCTATAAGAACAAGAAGTGGAGGAAACACTAACCAACAGAGAGCATCTGCAGGACAAATCAGCGTACAGCCCACATTCTCTGTACAAAGAAACCTCCCATTCGAGAGAGCAACCATCATGGCAGCATTTACGGGAAACACTGAAGGCAGAACTTCAGATATGAGAACTGAGATCATAAGGATGATGGAAAATGCCAGACCTGAAGATGTGTCTTTCCAGGGGCGGGGAGTCTTCGAGCTCTCGGACGAAAAGGCAACGAACCCGATCGTGCCTTCCTTTGACATGAGTAATGAAGGATCTTATTTCTTCGGAGACAATGCAGAGGAGTATGACAATTAA</t>
         </is>
       </c>
-      <c r="FG1" t="inlineStr">
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
         <is>
           <t>&gt;Flu-0406|A_NA</t>
         </is>
       </c>
-      <c r="FH1" t="inlineStr">
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
         <is>
           <t>ATGAATCCAAATCAAAAGATAACAACCATTGGATCAATCTGTATGGTAATTGGGATAGTCAGCTTGATGCTGCAAATTGGGAACATAATCTCAATATGGGTTAGCCATTCAATCCAAACAGGGAATCAATACCAGCCTGAACCATGCAATCAAAGCATCATTACCTATGAGAACAACACCTGGGTAAATCAGACGTATGTCAACATCAGCAATACCAATTTTCTTGCTGAGCAAGCTGTTACTTCGGTAACATTAGCGGGCAATTCATCTCTTTGCCCTATTAGTGGGTGGGCAATATACAGTAAGGACAACGGTATAAGAATTGGGTCCAAGGGGAATGTGTTTGTTATAAGAGAACCGTTCATCTCATGCTCCCACTTGGAATGCAGAGCCTTTTTCCTGACCCAGGGAGCTCTGCTGAATGACAAACATTCTAATGGGACAGTTAAGGATAGAAGCCCTTATAGAACTTTGATGAGTTGTCCCGTGGGTGAGGCTCCTTCCCCGTATAATTCAAGATTTGAGTCTGTTGCTTGGTCGGCAAGTGCTTGTCATGATGGCATCAGTTGGTTGACAATCGGTATTTCTGGTCCAGACAATGGAGCTGTGGCTGTATTGAAGTACAATGGCATAATAACGGATACTATCAAGAGTTGGAGAAACAACATTTTAAGAACTCAAGAATCTGAATGTGCTTGCGTAAATGGCTCTTGCTTCACCGTAATGACTGATGGACCAAGCAATGGGCAGGCCTCATATAAAATCTTCAAGATAGAGAAAGGGAAAGTTGTCAAGTCAGTTGAGATGAATGCCCCTAATTACCACTACGAGGAATGCTCCTGTTATCCTGATGCGGGTGATATTATGTGTGTGTGCAGGGACAATTGGCATGGCTCAAATCGGCCGTGGGTATCTTTTAATCAAAATCTGGAGTATCAAATAGGATATATATGCAGTGGGGTTTTCGGGGACAATCCCCGCCCCAATGATGGAACAGGCAGTTGCAGTCCAATGCCCTCTAATGGGGCATATGGGGTAAAAGGGTTTTCATTTAAGTACGGTAATGGGGTTTGGATCGGAAGAACAAAAAGCACTAGTTCCAGAAGCGGCTTTGAGATGATTTGGGATCCGAATGGGTGGACTGAGACGGACAGTAGTTTCTCAGTGAAGCAAGACATTGTAGAAATAACTGACTGGTCAGGATATAGTGGGAGTTTTGTCCAGCATCCAGAACTGACAGGATTAGATTGCATGAGGCCTTGTTTCTGGGTTGAGCTAATCAGAGGGAAGCCCAAAGAGAACACAATTTGGACTAGCGGGAGCAGCATATCCTTTTGTGGTGTAAATAGTGACACTGTGGGTTGGTCTTGGCCAGACGGTGCTGAGTTGCCATTCACCATTGACAAGTAG</t>
         </is>
       </c>
-      <c r="FI1" t="inlineStr">
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
         <is>
           <t>&gt;Flu-0406|A_MP</t>
         </is>
       </c>
-      <c r="FJ1" t="inlineStr">
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
         <is>
           <t>ATGAGTCTTCTAACCGAGGTCGAAACGTACGTTCTCTCTATCGTCCCGTCGGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTTGAAGATGTCTTTGCAGGGAAGAACACCGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATCCTGTCACCTCTGACTAAGGGGATTTTGGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCTCTAAGTGGAACTGGAGACCCAAACAACATGGACAGGGCAGTCAAGTTGTACAGGAAACTAAAGAGAGAGATAACATTCCATGGTGCTAAAGAAGTTGCACTCAGTTACTCAACCGGTGCACTTGCCAGTTGTATGGGTCTCATATACAACAGGATGGGGACGGTGACCGCAGAAGTGGCATTGGGCCTAGTGTGTGCCACCTGTGAGCAGATTGCTGATTCACAGCATCGGTCTCACAGACAGATAGCTACCACCACCAACCCACTAATCAGACATGAAAACAGAATGGTTTTGGCCAGTACTACAGCTAAGGCTATGGAGCAGATGGCTGGATCGAGTGAGCAAGCAGTGGAAGCCATGGAGGTTGCTAGTCAGGCTAGGCAGATGGTGCAGGCGATGAGGACCATTGGAACTCATCCTAGCTCCAGTGCCGGTCTGAGAGATGATCTCCTTGAAAATTTGCAGGCCTACCAAAAACGGATGGGAGTGCAACTGCAGCGATTCAAGTGATCCTCTCGTTATTGCCGCAAGTATCATTGGGATCTTGCACTTGATATTGTGGATTCTTGATCGCCTTTTCTTCAAATGCGTTTATCGTCGCCTTAAATACGGTTTGAAAGGAGGGCCTTCTACGGAAGGAGTACCTGAGTCCATGAGGGAAGAGTACCGGCAGGAACAGCAGAGTGCTGTGGATGTTGACGATGGTCATTTTGTCAACATAGAGCTGGAGTAA</t>
         </is>
       </c>
-      <c r="FK1" t="inlineStr">
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
         <is>
           <t>&gt;Flu-0406|A_NS</t>
         </is>
       </c>
-      <c r="FL1" t="inlineStr">
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
         <is>
           <t>ATGGATTCCAACACTGTGTCAAGCTTTCAGGTAGACTGCTTTCTTTGGCATGTCCGCAAACGATTTGCAGACCAAGAACTGGGTGATGCCCCATTCCTTGACCGGCTCCGCCGAGACCAGAAGTCTCTAAGAGGAAGAAGCAGCACTCTTGGTCTGGACATCGAGACGGCCACTCGTGCTGGAAAGCAGATAGTGGAGAGGATTCTGGAGGAAGAATCCGACGAGGCACTCAAAATGACTATTGCCTCTGTGTCTGCTCCACGCTACCTAACTGACATGACTCTTGAAGAGATGTCAAGAGACTGGTTCATGCTCATGCCCAAGCAAAAAATGGCAGGCTCCCTCAGTATCAAAATGGACCAGGCGATTATGGATAAGAAAATCATACTGAAGGCAAACTTCAGTGTGATCTTCAATCGGCTGGAGACACTAATACTACTCAGAGCTTTCACTGAAGAAGGAGCAATTGTCGGCGAAATTTCACCATTGCCTTCTCTTCCAGGACATACTGATGAGGATGTCAAAAATGCAATTGGGGTCCTCATCGGAGGACTTGAATGGAATGATAACACAGTTCGAGTCTCTGAAACTTTACAGAGATTCGCTTGGAGAAGCAGTAATGAGGATGGGAGATCTCCACTCCCTCCAAAGCAGAAACGGAAAATGGAGAGAACAATTGAGTCAGAAGTTTGAAGAAATAAGGTGGCTGATTGRAGAAGTTCGACACAGACTAAAGATCACAGAAAATAGTTTTGAACAAATAACATTTATGCAAGCCTTACAACTACTGCTTGAAGTGGAGCAAGAGATAAGAACTTTCTCGTTTCAGCTTATTTAA</t>
         </is>

--- a/gisaid_batch_uploader_mira_batch_01.xlsx
+++ b/gisaid_batch_uploader_mira_batch_01.xlsx
@@ -3567,7 +3567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A168"/>
+  <dimension ref="A1:FL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3576,1171 +3576,837 @@
           <t>&gt;Flu-0008|A_NS</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>NNGGATTCCAACACTGTGTCAAGCTTNCAGGTAGACTGCTTTCTTTGGCATGTCCGCAAACGATTTGCAGACCAAGAACTGGGTGATGCCCCATTCCTTGACCGGCTNCGCCGAGACCAGAAGTCTCTNAGAGGAAGAGGCAGCACTCTTGGTCTGGACATCGAGACGGCCACTCGTGCTGGAAAGCAGATAGTGGAGAGGATTCTGGAGGAAGAATCCGACGAGGCACTCAAAATGACTATTGCCTCTGTGCCTGCTCCACGCTACCTAACTGACATGACTCTTGAAGAGATGTCAAGAGACTGGTTCATGCTCATGCCCAAGCAAAAAGTGGCAGGCTCCCTCTGTATCAGAATGGACCAGGCGATTATGGATAAGAACATCATACTGAAGGCAAACTTCAGTGTGATCTTCAATCGGCTGGAGACACTAATACTACTCAGAGCTTTCACTGAAGAGGGAGCAATTGTNGGCGAAATTTCACCATTGCCTTCTCTTCCAGGACATACTGATGAGGATGTCAAAAATGCAATTGGGGTCCTCATCGGAGGACTTGAATGGAATGATAACACAGTTCGAGTCTCTGAAATTTTACAGAGATTCGCTTGGAGAAGCAGTAATGAGGATGGGAGACCTCCACTCCCTCCAAAGCAGAAACGGAAAATGGAGAGAACAATTGAGTCAGAAGTTTGAAGAAATAAGGTGGCTGATTGAAGAGGTGCGACACAGANTAAAGATCACAGAAAATAGTTTTGAACAAATAACATTTATGCAAGCCTTACAACTACTGCTTGAAGTGGAGCAAGAGATACGAACTTTCTCGTTTCAGCTTATTTAA</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>&gt;Flu-0009|A_NP</t>
         </is>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>ATGGCGTCTCAAGGCACCAAACGATCCTATGAACAAATGGAAACTGGTGGGGAACGCCAGAATGCCACTGAAATCAGAGCATCTGTTGGAAGAATGGTTGGCGGAATAGGAAGATTCTACATACAGATGTGCACTGAGCTCAAACTCAGTGATTACGAAGGGAGGCTGATCCAAAACAGCATAACCATAGAAAGGATGGTTCTCTCGGCATTTGATGAGAGGAGGAACAAGTACCTGGAGGAACATCCCAGTGCCGGGAAGGATCCCAAGAAGACTGGAGGTCCAATCTACAGGAGGAGAGATGGCAAATGGGTGAGAGAGTTGATCCTCTACGACAAAGAAGAGATCAGAAGAATTTGGCGTCAAGCTAATAATGGAGAGGATGCAACTGCTGGTCTCACTCATTTGATGATTTGGCATTCCAATCTGAATGATGCAACATACCAGAGAACAAGGGCACTTGTGCGTACTGGAATGGACCCTAGRATGTGCTCTCTGATGCAAGGCTCAACCCTCCCTAGGAGATCCGGGGCTGCTGGAGCAGCAGTGAAAGGAGTTGGAACAATGGTGATGGAACTAATTCGAATGATCAAACGAGGGATCAATGATCGGAATTTCTGGAGAGGCGAAAACGGTCGGAGAACCAGGATTGCCTACGAGAGAATGTGCAACATCCTCAAGGGAAAGTTCCAAACAGCAGCACAACGGGCAATGATGGACCAAGTGAGAGAAAGCCGGAATCCTGGGAATGCTGAAATTGAAGATCTCATCTTTCTCGCACSATCTGCTCTCATCCTGAGGGGATCAGTGGCTCATAAGTCCTGTCTGCCTGCTTGCGTATATGGACTTGCTGTAGCCAGTGGATATGACTTTGAAAGAGAGGGATATTCTCTAGTCGGAATTGATCCTTTCCGTCTGCTCCAAAACAGCCAAGTCTTCAGTCTCATCAGACCGAACGAAAATCCAGCTCATAAAAGTCAGCTGGTATGGATGGCATGCCACTCTGCGGCATTTGAGGATCTGAGAGTTTCAAGCTTCATCAGAGGGACAAGAGTAGTCCCAAGAGGACAACTGTCCACCAGAGGAGTTCAGATTGCTTCAAATGAAAACATGGAGACAATGGACTCCAGTACTCTTGAACTGAGGAGCAGRTACTGGGCTATAAGAACAAGAAGTGGAGGAAACACTAACCAACAGAGAGCATCTGCAGGACAAATCAGCGTACAGCCCACATTCTCTGTGCAAAGAAACCTCCCATTCGAGAGAGCAACCATCATGGCAGCATTTACGGGAAACACTGAAGGCAGAACTTCAGACATGAGAACTGAGATCATAAGGATGATGGAAAATGCCAGACCTGAAGATGTGTCTTTCCAGGGGCGGGGAGTCTTCGAGCTCTCGGACGAAAAGGCAACGAACCCGATCGTGCCTTCCTTTGACATGAGTAATGAAGGATCTTATTTCTTCGGAGACAATGCAGAGGAGTATGACAATTAA</t>
         </is>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>&gt;Flu-0009|A_NA</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>ATGAATCCAAATCAAAAGATAACAACCATTGGATCAATCTGTATGGTAATTGGGACAGTCAGCTTGATGCTGCAAATTGGGAACATAATCTCAATATGGGTTAGCCATTCAATCCAAACAGGGAATCAATACCAGCCTGAACCATGCAATCAAAGCGTAATTACCTATGAGAACAACACCTGGGTAAATCAGACGTATGTCAACATTAGCAATACCAATTTTCTTGCTGAGCAGGCTGTTACTTCGGTAACATTAGCGGGCAATTCATCTCTTTGCCCTATTAGTGGGTGGGCAATATACAGTAAGGACAACGGTATAAGAATTGGGTCCAAGGGGGATGTGTTTGTTATAAGAGAACCGTTCATCTCATGCTCCCACTTGGAATGCAGAACCTTTTTCCTGACCCAGGGAGCTCTGCTGAATGACAAACATTCTAATGGGACAGTTAAGGATAGAAGCCCTTATAGAACTTTGATGAGTTGTCCCGTGGGTGAGGCTCCTTCCCCGTACAATTCAAGATTTGAGTCTGTTGCTTGGTCGGCAAGTGCTTGTCATGATGGCATCAGTTGGTTGACAATCGGTATTTCTGGTCCAGACAATGGAGCTGTGGCTGTATTGAAGTACAATGGCATAATAACGGATACTATCAAGAGTTGGAGAAACAACATTTTGAGAACTCAAGAATCTGAATGTGCTTGTGTAAATGGCTCTTGCTTCACCGTAATGACTGATGGACCAAGCAATGGGCAGGCCTCATATAAAATCTTCAAGATAGAGAAAGGGAAAGTTGTCAAATCAGTTGAATTGAATGCCCCTAATTACCACTACGAGGAATGTTCCTGTTATCCTGATGCGGGTGATATTATATGTGTGTGCAGGGACAATTGGCATGGCTCAAACCGGCCGTGGGTATCTTTTAATCAAAATCTGGAGTATCAAATAGGATATATATGCAGTGGGGTTTTCGGGGACAATCCCCGCCCCAATGATGGAACAGGCAGTTGCAGTCCAATGTCCTCTAATGGGGCATATGGGGTAAAAGGGTTCTCATTTAAGTACGGTAATGGGGTTTGGATCGGAAGAACAAAAGGCACTAGTTCCAGAAGCGGCTTTGAGATGATTTGGGACCCGAATGGGTGGACTGAGACGGACAGTAGTTTCTCAGTGAAGCAAGACATTGTAGAAATAACTGACTGGTCAGGATATAGTGGGAGTTTTGTCCAGCATCCAGAACTGACAGGATTAGATTGCATGAGGCCTTGTTTCTGGGTTGAGCTAATTAGAGGGAGGCCCAAAGAGAACACAATTTGGACTAGCGGGAGCAGCATATCCTTTTGTGGTGTAAATAGTGACACTGTGGGTTGGTCTTGGCCAGACGGTGCTGAGTTGCCATTCACCATTGACAAGTAG</t>
         </is>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>&gt;Flu-0009|A_MP</t>
         </is>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>ATGAGTCTTCTAACCGAGGTCGAAACGTACGTTCTCTCTATCGTCCCGTCGGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTTGAAGATGTTTTTGCAGGGAAGAACACCGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATACTGTCACCTCTGACTAAGGGGATTTTGGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCTCTAAGTGGAAATGGAGACCCAAACAACATGGACAGGGCAGTCAAGTTGTACAGGAAATTGAAGAGAGAAATAACATTTCATGGGGCTAAAGAAGTTGCACTCAGTTACTCAACCGGTGCACTTGCCAGTTGTATGGGTCTCATATACAACAGGATGGGGACGGTGACCGCAGAAGTGGCATTGGGCCTAGTGTGTGCCACCTGTGAGCAGATTGCTGATTCACAGCATCGGTCTCACAGACAGATAGCTACCACCACCAACCCACTAATCAGACATGAAAACAGAATGGTTTTGGCCAGTACTACAGCTAAGGCTATGGAGCAGATGGCTGGATCGAGTGAGCAAGCAGTGGAAGCCATGGAGGTTGCTAGTCAGGCTAGGCAAATGGTGCAGGCGATGAGGACCATTGGAACTCATCCTAGCTCCAGTGCCGGTCTGAGAGATGATCTCCTTGAAAATTTGCAGGCCTACCAAAAACGAATGGGAGTGCAACTGCAGCGATTCAAGTGATCCTCTCGTTATTGCCGCAAGTATCATTGGGATCTTGCACTTGATATTGTGGATTCTTGATCGCCTTTTCTTCAAATGCGTTTATCGTCGCCTTAAATACGGTTTGAAAGGAGGGCCTTCTACGGAAGGAGTACCTGAGTCCATGAGGGAAGAGTACCGGCAGGAACAGCAGAGTGCTGTGGATGTTGACGATGGTCATTTTGTCAACATAGAGATGGAGTAA</t>
         </is>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>&gt;Flu-0009|A_NS</t>
         </is>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>ATGGATTCCAACACTGTGTCAAGCTTTCAGGTAGACTGCTTTCTTTGGCATGTCCGCAAACGATTTGCAGACCAAGAACTGGGTGATGCCCCATTCCTTGACCGGCTCCGCCGAGACCAGAAGTCTCTAAGAGGAAGAGGCAGCACTCTTGGTCTGGACATCGAGACGGCCACTCGTGCTGGAAAGCAGATAGTGGAGAGGATTCTGGAGGAAGAATCCGACGAGGCACTCAAAATGACTATTGCCTCTGTGCCTGCTCCACGCTACCTAACTGACATGACTCTTGAAGAGATGTCAAGAGATTGGTTCATGCTCATGCCCAAGCAAAAAGTGGCAGGCTCCCTCTGTATCAGAATGGACCAGGCGATTATGGATAAGAACATCATACTGAAGGCAAACTTCAGTGTGATCTTCAATCGGCTGGAGACACTAATACTACTCAGAGCTTTCACTGAAGAGGGAGCAATTGTCGGCGAAATTTCACCATTGCCTTCTCTTCCAGGACATACTGATGAGGATGTCAAAAATGCAATTGGGGTCCTCATCGGAGGACTTGAATGGAATGATAACACAGTTCGAGTCTCTGAAATTTTACAGAGATTCGCTTGGAGAAGCAGTAATGAGGATGGGAGACCTCCACTCCCTCCAAAGCAGAAACGGAAAATGGAGAGAACAATTGAGTCAGAAGTTTGAAGAAATAAGGTGGCTGATTGAAGAGGTGCGACACAGATTAAAGATCACAGAAAATAGTTTTGAACAAATAACATTTATGCAAGCCTTACAACTACTGCTTGAAGTGGAGCAAGAGATACGAACTTTCTCGTTTCAGCTTATTTAA</t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>&gt;Flu-0011|A_MP</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>ATGAGTCTTCTAACCGAGGTCGAAACGTACGTTCTCTCTATCGTCCCGTCGGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTTGAAGATGTCTTTGCAGGGAAGAACACCGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATACTGTCACCTCTGACTAAGGGGATTTTGGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCTCTAAGTGGAAATGGAGACCCAAACAACATGGACAGGGCAGTCAAGTTGTACAGGAAACTGAAGAGAGAAATAACATTCCATGGGGCTAAAGAAGTTGCACTCAGTTACTCAACCGGTGCACTTGCCAGTTGTATGGGTCTCATATACAACAGGATGGGGACGGTGACCGCAGAAGTGGCATTGGGCCTAGTGTGTGCCACCTGTGAGCAGATTGCTGATTCACAGCATCGGTCTCACAGACAGATAGCTACCACCACCAACCCACTAATCAGACATGAAAACAGAATGGTTTTGGCCAGTACTACAGCTAAGGCTATGGAGCAGATGGCTGGATCGAGTGAGCAAGCAGCGGAAGCCATGGAGGTTGCTAGTCAGGCTAGGCAAATGGTGCAGGCGATGAGGACCATTGGAACTCATCCTAGCTCCAGTGCCGGTCTGAGAGATGATCTCCTTGAAAATTTGCAGGCCTACCAAAAACGAATGGGAGTGCAACTGCAGCGATTCAAGTGATCCTCTCGTTATTGCCGCAAGTATCATTGGGATCTTGCACTTGATATTGTGGATTCTTGATCGCCTTTTCTTCAAATGCGTTTATCGTCGCCTTAAATACGGTTTGAAAGGAGGGCCTTCTACGGAAGGAGTACCTGAGTCCATGAGGGAAGAGTACCGGCAGGAACAGCAGAGTGCTGTGGATGTTGACGATGGTCATTTTGTCAACATAGAGATGGAGTAA</t>
         </is>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>&gt;Flu-0011|A_NS</t>
         </is>
       </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>ATGGATTCCAACACTGTGTCAAGCTTTCAGGTAGACTGCTTTCTTTGGCATGTCCGCAAACGATTTGCAGACCAAGAACTGGGTGATGCCCCATTCCTTGACCGGCTCCGCCGAGACCAGAAGTCTCTAAGAGGAAGAGGCAGCACTCTTGGTCTGGACATCGAGACGGCCACTCGTGCTGGAAAGCAGATAGTGGAGAGGATTCTGGAGGAAGAATCCGACGAGGCACTCAAAATGACTATTGCCTCTGTGCCTGCTCCACGCTACCTAACTGACATGACTCTTGAAGAGATGTCAAGAGACTGGTTCATGCTCATGCCCAAGCAAAAAGTGGCAGGCTCCCTCTGTATCAGAATGGACCAGGCGATTATGGATAAGAACATCATACTGAAGGCAAACTTCAGTGTGATCTTCAATCGGCTGGAGACACTAATACTACTCAGAGCTTTCACTGAAGAGGGAGCAATTGTCGGCGAAATTTCACCATTGCCTTCTCTTCCAGGACATACTGATGAGGATGTCAAAAATGCAATTGGGGTCCTCATCGGAGGACTTGAATGGAATGATAACACAGTTCGAGTCTCTGAAATTTTACAGAGATTCGCTTGGAGAAGCAGTAATGAGGATGGGAGACCTCCACTCCCTCCAAAGCAGAAACGGAAAATGGAGAGAACAATTGAGTCAGAAGTTTGAAGAAATAAGGTGGCTGATTGAAGAGGTGCGACACAGACTAAAGATCACAGAAAATAGTTTTGAACAAATAACATTTATGCAAGCCTTACAACTACTGCTTGAAGTGGAGCAAGAGATACGAACTTTCTCGTTTCAGCTTATTTAA</t>
         </is>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>&gt;Flu-0013|A_HA</t>
         </is>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>ATGGAGAACATAGTACTACTTCTTGCAATAGTTAGCCTTGTTAAAAGTGACCAGATTTGCATTGGTTACCATGCAAACAATTCGACAGAGCAAGTTGACACGATAATGGAAAAGAACGTCACTGTTACACATGCCCAAGACATACTGGAAAAAACACACAACGGGAAGCTCTGTGATTTAAATGGGGTGAAGCCACTGATTTTAAAGGATTGTAGTGTAGCTGGATGGCTCCTCGGGAACCCAATGTGCGACGAATTCATCAGAGTGCCGGAATGGTCCTACATAGTGGAGCGAGCTAACCCAGCTAATGACCTCTGTTACCCAGGGAGCCTCAATGACTATGAAGAACTGAAACACATGTTGAGCAGAATAAATCATTTTGAGAAGATTCAGATCATTCCCAAGAGTTCCTGGCCAAATCATGAAACATCACTAGGGGTGAGCGCAGCTTGTCCATACCAGGGAGCGCCCTCCTTTTTCAGAAATGTGGTGTGGCTTATCAAAAAGAACGATGCATACCCAACAATAAAGATAAGCTACAATAATACTAATCGGGAAGATCTCTTGATACTGTGGGGGATTCATCATTCCAACARTGCAGAAGAGCAGACAAATCTCTACAAAAACCCAACCACCTACATTTCAGTTGGAACATCAACTTTAAACCAGAGGTTGGCACCAAAAATAGCTACTAGATCCCAAGTAAACGGGCAACGTGGAAGAATGGACTTCTTTTGGACAATCTTAAAACCAGATGATGCAATCCATTTCGAGAGTAACGGAAATTTCATTGCTCCAGAATATGCATACAAAATTGTCAAGAAAGGGGACTCAACAATTATGAAAAGTGGAGTGGAATATGGCCACTGCAACACCAAATGTCAAACCCCAGTAGGTGCTATAAATTCTAGTATGCCATTCCACAACATACATCCTCTCACCATTGGGGAATGCCCCAAATACGTGAAGTCAAACAAGTTGGTCCTTGCGACTGGGCTCAGAAATAGTCCTCTAAGAGAAAAGAGAAGAAAAAGAGGTCTGTTTGGGGCGATAGCAGGGTTTATAGAGGGAGGATGGCAGGGAATGGTTGATGGTTGGTATGGGTACCATCATAGCAATGAGCAGGGGAGTGGGTACGCTGCGGACAAAGAATCCACCCAAAAGGCAATAGATGGAGTTACCAATAAGGTCAACTCAATCATTGACAAAATGAACACTCAATTTGAGGCAGTTGGAAGGGAGTTTAATAACTTAGAAAGGAGGATAGAGAATTTGAACAAGAAAATGGAAGACGGATTCCTAGATGTCTGGACCTATAATGCTGAACTTCTAGTTCTCATGGAAAACGAGAGGACTCTAGATTTCCATGATTCAAATGTCAAGAACCTTTACGACAAAGTCAGATTACAGCTTAGGGATAATGCAAAGGAGCTGGGTAACGGCTGTTTCGAATTCTATCACAAATGTGATAATGAATGTATGGAAAGTGTGAGAAATGGGACGTATGACTACCCTCAGTATTCAGAAGAAGCAAGATTAAAAAGAGAAGAAATAAGCGGAGTGAAATTAGAATCAGTAGGAACTTACCAGATACTGTCAATTTATTCAACAGCGGCAAGTTCCCTAGCACTGGCAATCATGATGGCTGGTCTATCTTTATGGATGTGCTCCAATGGGTCGTTACAATGCAGAATTTGCATTTAG</t>
         </is>
       </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>&gt;Flu-0013|A_NP</t>
         </is>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>ATGGCGTCTCAAGGCACCAAACGATCCTATGAACAAATGGAAACTGGTGGGGAACGCCAGAATGCCACTGAAATCAGAGCATCCGTTGGAAGAATGGTTGGCGGAATAGGAAGATTCTACATACAGATGTGCACTGAGCTCAAACTCAGTGATTACGAAGGGAGGCTGATCCAAAACAGCATAACCATAGAAAGGATGGTTCTCTCGGCATTTGATGAGAGGAGGAACAAGTACCTGGAGGAACATCCCAGTGCCGGGAAGGATCCCAAGAAGACTGGAGGTCCAATCTACAGGAGGAGAGATGGCAAATGGGTGAGAGAGTTGATCCTCTACGACAAAGAAGAGATCAGAAGAATTTGGCGTCAAGCTAATAATGGAGAGGATGCAACTGCTGGTCTCACTCATTTGATGATTTGGCATTCCAATCTGAATGATGCAACATACCAGAGAACAAGGGCACTTGTGCGTACTGGAATGGACCCTAGGATGTGCTCTCTGATGCAAGGCTCAACCCTCCCTAGGAGATCCGGGGCTGCTGGAGCAGCAGTGAAAGGAGTTGGAACAATGGTGATGGAACTAATTCGAATGATCAAACGAGGGATCAATGATCGGAATTTCTGGAGAGGCGAAAACGGTCGGAGAACCAGGATTGCCTACGAGAGAATGTGCAACATCCTCAAGGGAAAGTTCCAAACAGCAGCACAACGGGCAATGATGGACCAAGTGAGAGAAAGCCGGAATCCTGGGAATGCTGAAATTGAAGATCTCATCTTTCTCGCACSATCTGCTCTCATCCTGAGGGGATCAGTGGCTCATAAGTCCTGTCTGCCTGCTTGCGTATATGGACTTGCTGTAGCCAGTGGATATGACTTTGAAAGAGAGGGATATTCTCTAGTCGGAATTGATCCTTTCCGTCTGCTCCAAAACAGCCAAGTCTTCAGTCTCATCAGACCGAACGAAAATCCAGCTCATAAAAGTCAGCTGGTATGGATGGCATGCCACTCTGCGGCATTTGAGGATCTGAGAGTTTCAAGCTTCATCAGAGGGACAAGAGTAGTCCCAAGAGGACAACTGTCCACCAGAGGAGTTCAGATTGCTTCAAATGAAAACATGGAGACAATGGACTCCAGTACTCTTGAACTGAGGAGCAGATACTGGGCTATAAGAACAAGAAGTGGAGGAAACACTAACCAACAGAGAGCATCTGCAGGACAAATCAGCGTACAGCCCACATTCTCTGTGCAAAGAAACCTCCCATTCGAGAGAGCAACCATCATGGCAGCATTTACGGGAAACACTGAAGGCAGAACTTCAGACATGAGAACTGAGATCATAAGGATGATGGAAAATGCCAGACCTGAAGATGTGTCTTTCCAGGGGCGGGGAGTCTTCGAGCTCTCGGACGAAAAGGCAACGAACCCGATCGTGCCTTCCTTTGACATGAGTAATGAAGGATCTTATTTCTTCGGAGACAATGCAGAGGAGTATGACAATTAA</t>
         </is>
       </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>&gt;Flu-0013|A_NA</t>
         </is>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>ATGAATCCAAATCAAAAGATAACAACCATTGGATCAATCTGTATGGTAATTGGGACAGTCAGCTTGATGCTGCAAATTGGGAACATAATCTCAATATGGGTTAGCCATTCAATCCAAACAGGGAATCAATACCAGCCTGAACCATGCAATCAAAGCATCATTACCTATGAGAACAACACCTGGGTAAATCAGACGTATGTCAACATCAGCAATACCAATTTTCTTGCTGAGCAGGCTGTTACTTCGGTAACATTAGCGGGCAATTCATCTCTTTGCCCTATTAGTGGGTGGGCAATATACAGTAAGGACAACGGTATAAGAATTGGGTCCAAGGGGGATGTGTTTGTTATAAGAGAACCGTTCATCTCATGCTCCCACTTGGAATGCAGAACCTTTTTCCTGACCCAGGGAGCTCTGCTGAATGACAAACATTCTAATGGGACAGTTAAGGATAGAAGCCCTTATAGAACTTTGATGAGTTGTCCCGTGGGTGAGGCTCCTTCCCCGTACAATTCAAGATTTGAGTCTGTTGCTTGGTCGGCAAGTGCTTGTCATGATGGCATCAGTTGGTTGACAATCGGTATTTCTGGTCCAGACAATGGAGCTGTGGCTGTATTGAAGTACAATGGCATAATAACGGATACTATCAAGAGTTGGAGAAACAACATTTTGAGAACTCAAGAATCTGAATGTGCTTGCGTAAATGGCTCTTGCTTCACCGTAATGACTGATGGACCAAGCAATGGGCAGGCCTCATATAAAATCTTCAAGATAGAGAAAGGGAAAGTTGTCAAATCAGTTGAATTGAATGCCCCTAATTACCACTACGAGGAATGTTCCTGTTATCCTGATGCGGGTGATATTATATGTGTGTGCAGGGACAATTGGCATGGCTCAAACCGGCCGTGGGTATCTTTTAATCAAAATCTGGAGTATCAAATAGGATATATATGCAGTGGGGTTTTCGGGGACAATCCCCGCCCCAATGATGGAACAGGCAGTTGCAGTCCAATGTCCTCTAATGGGGCATATGGGGTAAAAGGGTTTTCATTTAAGTACGGTAATGGGGTTTGGATCGGAAGAACAAAAGGCACTAGTTCCAGAAGCGGCTTTGAGATGATTTGGGACCCGAATGGGTGGACTGAGACGGACAGTAGTTTCTCAGTGAAGCAAGACATTGTAAAAATAACTGACTGGTCAGGATATAGTGGGAGTTTTGTCCAGCATCCAGAACTGACAGGATTAGATTGCATGAGGCCTTGTTTCTGGGTTGAGCTAATTAGAGGGAGGCCCAAAGAGAACACAATTTGGACTAGCGGGAGCAGCATATCCTTTTGTGGTGTAAATAGTGACACTGTGGGTTGGTCTTGGCCAGACGGTGCTGAGTTGCCATTCACCATTGACAAGTAG</t>
         </is>
       </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>&gt;Flu-0013|A_MP</t>
         </is>
       </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>ATGAGTCTTCTAACCGAGGTCGAAACGTACGTTCTCTCTATCGTCCCGTCGGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTTGAAGATGTCTTTGCAGGGAAGAACACCGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATACTGTCACCTCTGACTAAGGGGATTTTGGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCTCTAAGTGGAAATGGAGACCCAAACAACATGGACAGGGCAGTCAAGTTGTACAGGAAATTGAAGAGAGAAATAACATTCCATGGGGCTAAAGAAGTTGCACTCAGTTACTCAACCGGTGCACTTGCCAGTTGTATGGGTCTCATATACAACAGGATGGGGACGGTGACCGCAGAAGTGGCATTGGGCCTAGTGTGTGCCACCTGTGAGCAGATTGCTGATTCACAGCATCGGTCTCACAGACAGATAGCTACCACCACCAACCCACTAATCAGACATGAAAACAGAATGGTTTTGGCCAGTACTACAGCTAAGGCTATGGAGCAGATGGCTGGATCGAGTGAGCAAGCAGTGGAAGCCATGGAGGTTGCTAGTCAGGCTAGGCAAATGGTGCAGGCGATGAGGACCATTGGAACTCATCCTAGCTCCAGTGCCGGTCTGAGAGATGATCTCCTTGAAAATTTGCAGGCCTACCAAAAACGAATGGGAGTGCAACTGCAGCGATTCAAGTGATCCTCTCGTTATTGCCGCAAGTATCATTGGGATCTTGCACTTGATATTGTGGATTCTTGATCGCCTTTTCTTCAAATGCGTTTATCGTCGCCTTAAATACGGTTTGAAAGGAGGGCCTTCTACGGAAGGAGTACCTGAGTCCATGAGGGAAGAGTACCGGCAGGAACAGCAGAGTGCTGTGGATGTTGACGATGGTCATTTTGTCAACATAGAGATGGAGTAA</t>
         </is>
       </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>&gt;Flu-0013|A_NS</t>
         </is>
       </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>ATGGATTCCAACACTGTGTCAAGCTTCCAGGTAGACTGCTTTCTTTGGCATGTCCGCAAACGATTTGCAGACCAAGAACTGGGTGATGCCCCATTCCTTGACCGGCTCCGCCGAGACCAGAAGTCTCTAAGAGGAAGAGGCAGCACTCTTGGTCTGGACATCGAGACGGCCACTCGTGCTGGAAAGCAGATAGTGGAGAGGATTCTGGAGGAAGAATCCGACGAGGCACTCAAAATGACTATTGCCTCTGTGCCTGCTCCACGCTACCTAACTGACATGACTCTTGAAGAGATGTCAAGAGACTGGTTCATGCTCATGCCCAAGCAAAAAGTGGCAGGCTCCCTCTGTATCAGAATGGACCAGGCGATTATGGATAAGAACATCATACTGAAGGCAAACTTCAGTGTGATCTTCAATCGGCTGGAGACACTAATACTACTCAGAGCTTTCACTGAAGAGGGAGCAATTGTCGGCGAAATTTCACCATTGCCTTCTCTTCCAGGACATACTGATGAGGATGTCAAAAATGCAATTGGGGTCCTCATCGGAGGACTTGAATGGAATGATAACACAGTTCGAGTCTCTGAAATTTTACAGAGATTCGCTTGGAGAAGCAGTAATGAGGATGGGAGACCTCCACTCCCTCCAAAGCAGAAACGGAAAATGGAGAGAACAATTGAGTCAGAAGTTTGAAGAAATAAGGTGGCTGATTGAAGAGGTGCGACACAGACTAAAGATCACAGAAAATAGTTTTGAACAAATAACATTTATGCAAGCCTTACAACTACTGCTTGAAGTGGAGCAAGAGATACGAACTTTCTCGTTTCAGCTTATTTAA</t>
         </is>
       </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>&gt;Flu-0014|A_NS</t>
         </is>
       </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>ATGGATTCCAACACTGTGTCAAGCTTTCAGGTAGACTGCTTTCTTTGGCATGTCCGCAAACGATTTGCAGACCAAGAACTGGGTGATGCCCCATTCCTTGACCGGCTCCGCCGAGACCAGAAGTCTCTAAGAGGAAGAGGCAGCACTCTTGGTCTGGACATCGAGACGGCCACTCGTGCTGGAAAGCAGATAGTGGAGAGGATTCTGGAGGAAGAATCCGACGAGGCACTCAAAATGACTATTGCCTCTGTGCCTGCTCCACGCTACCTAACTGACATGACTCTTGAAGAGATGTCAAGAGANTGGTTCATGCTCATGCCCAAGCAAAAAGTGGCAGGCTCCCTCNGTATCAGAATGGACCAGGCGATTATGGATAAGAACATCATACTGAAGGCAAACTTCAGTGTGATCTTCAATCGGCTGGAGACACTAATACTACTCAGAGCTTTCACTGAAGAGGGAGCAATTGTCGGCGAAATTTCACCATTGCCTTCTCTTCCAGGACATACTGATGAGGATGTCAAAAATGCAATTGGGGTCCTCATCGGAGGACTTGAATGGAATGATAACACAGTTCGAGTCTCTGAAANTTTACAGAGATTCGCTTGGAGAAGCAGTAATGAGGATGGGAGACCTCCACTCCCTCCAAAGCAGAAACGGAAAATGGAGAGAACAATTGAGTCAGAAGTTTGAAGAAATAAGGTGGCTGATTGAAGANGTNCGACACAGANTAAAGATCACAGAAAATAGTTTTGAACAAATAACATTTATGCAAGCCTTACAACTACTGCTTGAAGTGGAGCAAGAGATANGAACTTTCTCGTTTCAGCTTATTTAA</t>
         </is>
       </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>&gt;Flu-0018|A_NS</t>
         </is>
       </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>ATGGATTCCAACACTGTGTCAAGCTTTCAGGTAGACTGCTTTCTTTGGCATGTCCGCAAACGATTTGCAGACCAAGAACTGGGTGATGCCCCATTCCTTGACCGGCTCCGCCGAGACCAGAAGTCTCTAAGAGGAAGAGGCAGCACTCTTGGTCTGGACATCGAGACGGCCACTCGTGCTGGAAAGCAGATAGTGGAGAGGATTCTGGAGGAAGAATCCGACGAGGCACTCAAAATGACTATTGCCTCTGTGCCTGCTCCACGCTACCTAACTGACATGACTCTTGAAGAGATGTCAAGAGAYTGGTTCATGCTCATGCCCAAGCAAAAAGTGGCAGGCTCCCTCWGTATCAGAATGGACCAGGCGATTATGGATAAGAACATCATACTGAAGGCAAACTTCAGTGTGATCTTCAATCGGCTGGAGACACTAATACTACTCAGAGCTTTCACTGAAGAGGGAGCAATTGTCGGCGAAATTTCACCATTGCCTTCTCTTCCAGGACATACTGATGAGGATGTCAAAAATGCAATTGGGGTCCTCATCGGAGGACTTGAATGGAATGATAACACAGTTCGAGTCTCTGAAAYTTTACAGAGATTCGCTTGGAGAAGCAGTAATGAGGATGGGAGACCTCCACTCCCTCCAAAGCAGAAACGGAAAATGGAGAGAACAATTGAGTCAGAAGTTTGAAGAAATAAGGTGGCTGATTGAAGARGTKCGACACAGAYTAAAGATCACAGAAAATAGTTTTGAACAAATAACATTTATGCAAGCCTTACAACTACTGCTTGAAGTGGAGCAAGAGATAMGAACTTTCTCGTTTCAGCTTATTTAA</t>
         </is>
       </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>&gt;Flu-0023|A_HA</t>
         </is>
       </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>ATGGAGGACATAGTACTACTTCTTGCAATAGTTAGCCTTGTTAAAAGTGATCAGATTTGCATTGGTTACCATGCAAACAATTCGACAGAGCAAGTTGACACGATAATGGAAAAGAACGTCACTGTTACACATGCCCAAGACATACTGGAAAAAACACACAACGGGAAACTCTGTGATTTAAATGGGGTGAAGCCACTGATTTTAAAGGATTGTAGTGTAGCTGGATGGCTCCTCGGAAACCCAATGTGCGACGAATTCATCAGAGTGCCGGAATGGTCCTACATAGTGGAGCGGGCTAACCCAGCTAATGACCTCTGTTACCCAGGGAGCCTCAATGACTATGAAGAACTGAAACACATGTTGAGCAGAATAAATCATTTTGAGAAGATTCAGATCATTCCCAAGAGTTCCTGGCCAAATCATGAAACATCACTAGGAGTGAGCGCAGCTTGTCCATACCAGGGAGCGCCCTCCNTTTTCAGAAATGTGGTGTGGCTTATCAAAAAGAACGATGCATACCCAACAATAAAGATAAGCTACAATAATACTAATCGGGAAGATCTCTTGATACTGTGGGGGATTCATCATTCCAACAATGCAAAAGAACAGACAAATCTCTACAAAAACCCAACCACCTACATTTCAGTTGGAACATCAACTTTAAACCAGAGGTTGGCACCAAAAATAGCTACTAGATCCCAAGTAAACGGGCAACGTGGAAGAATGGACTTCTTCTGGACAATCTTAAAACCAGATGATGCAATCCATTTCGAGAGTAACGGAAATTTCATTGCTCCAGAATATGCATACAAAATTGTCAAGAAAGGGGACTCAACAATTATGAAAAGTGGAGTGGAATATGGCCACTGCAACACCAAATGTCAAACCCCAGTAGGTGCGATAAATTCTAGTATGCCATTCCACAACATACATCCTCTCACCATTGGGGAATGCCCCAAATACGTGAAGTCAAACAAGTTGGTCCTTGCGACTGGGCTCAGAAATAGTCCTCTAAGAGAAAAGAGAAGNNNAAAAAGAGGTCTGTTTGGRGCRAWAGCAGGGTTTATAGAGGGAGGATGGCAGGGAATGGTTGATGGTTGGTATGGATACCATCATAGCAATRAGCAGGGGAGTGGGTACGCTGCGGACAAAGAATCCACCCAAAAGGCAATAGATGGAGTTACCAATAAGGTCAACTCAATCATTGACAAAATGAACACTCAATTTGAGGCAGTTGGAAGGGAGTTTAATAACTTAGAAAGGAGGATAGAGAATTTGAACAAGAAAATGGAAGACGGATTCCTAGATGTCTGGACCTATAATGCTGAACTTCTAGTTCTCATGGAAAACGAGAGGACTCTAGATTTCCATGATTCAAATGTCAAGAACCTTTACGACAAAGTCAGATTACAGCTTAGGGATAATGCAAAGGAGCTGGGTAACGGCTGTTTCGAATTCTATCACAAATGTGATAATGAATGTATGGAAAGTGTGAGAAATGGGACGTATGACTACCCTCAGTATTCAGAAGAAGCAAGATTAAAAAGAGAAGAAATAAGCGGAGTGAAATTAGAATCAGTAGGAACTTACCAGATACTGTCAATTTATTCAACAGCGGCAAGTTCCCTAGCACTGGCAATCATGATGGCTGGTCTATCTTTATGGATGTGCTCCAATGGGTCGTTACAATGCAGAATTTGCATTTAG</t>
         </is>
       </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>&gt;Flu-0023|A_NP</t>
         </is>
       </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>ATGGCGTCTCAAGGCACCAAACGATCCTATGAACAAATGGAAACTGGTGGGGAACGCCAGAATGCCACTGAAATCAGAGCTTCTGTTGGAAGAATGGTTGGCGGAATCGGGAGATTCTACATACAGATGTGCACTGAACTCAAACTCAGTGATTACGAAGGGAGGCTGATCCAAAACAGCATAACCATAGAAAGGATGGTTCTCTCGGCATTTGATGAGAGGAGGAACAAGTACCTGGAGGAACATCCCAGTGCCGGGAAGGATCCCAAGAAGACTGGAGGTCCAATCTACAGGAGGAGAGATGGCAAATGGGTGAGAGAGTTGATCCTCTACGACAAAGAAGAGATCAGAAGAATTTGGCGTCAAGCTAATAATGGAGAGGATGCAACTGCTGGTCTCACTCACTTGATGATTTGGCATTCCAATCTGAATGATGCCACATACCAGAGAACAAGGGCACTTGTGCGTACTGGAATGGACCCTAGAATGTGCTCTCTGATGCAAGGCTCAACCCTCCCTAGGAGATCAGGGGCTGCTGGAGCAGCAGTGAAAGGAGTTGGAACAATGGCGATGGAACTAATTCGAATGATCAAACGAGGGATCAATGATCGGAATTTCTGGAGAGGCGAAAACGGTCGGAGAACCAGGATTGCCTACGAGAGAATGTGCAACATTCTCAAGGGAAAGCTCCAAACAGCAGCACAACGGGCAATGATGGACCAAGTGAGAGAAAGCCGGAATCCTGGGAATGCTGAAATCGAAGATCTCATCTTTCTCGCACSATCTGCTCTCATCCTGAGGGGATCAGTGGCTCATAAGTCCTGTCTGCCTGCTTGCGTATATGGACTTGCTGTAGCCAGTGGATATGACTTTGAAAGAGAGGGATATTCTCTAGTCGGAATTGATCCTTTCCGTCTGCTCCAAAACAGCCAAGTCTTCAGTCTCATCAGACCGAACGAAAATCCAGCTCATAAAAGTCAGCTGGTATGGATGGCATGCCACTCTGCGGCATTTGAGGATCTGAGAGTGTCAAGCTTCATCAGAGGGACAAGAGTAGTCCCAAGAGGACAACTGTCCACCAGAGGAGTTCAGATTGCTTCAAATGAAAACATGGAGACAATGGACTCCAGTACTCTTGAACTGAGGAGCAGATATTGGGCTATAAGAACAAGAAGTGGAGGAAACACTAACCAACAGAGAGCATCTGCAGGACAAATCAGCGTACAGCCCACATTCTCTGTACAAAGAAACCTCCCATTCGAGAGAGCAACCATCATGGCAGCATTTACGGGAAACACTGAAGGCAGAACTTCAGATATGAGAACTGAGATCATAAGGATGATGGAAAATGCCAGACCTGAAGATGTGTCTTTCCAGGGGCGGGGAGTCTTCGAGCTCTCGGACGAAAAGGCAACGAACCCGATCGTGCCTTCCTTTGACATGAGTAATGAAGGATCTTATTTCTTCGGAGACAATGCAGAGGAGTATGACAATTAA</t>
         </is>
       </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>&gt;Flu-0023|A_NA</t>
         </is>
       </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>ATGAATCCAAATCAAAAGATAACAACCATTGGAACAATCTGTATGGTAATTGGGATAGTCAGCTTGATGCTGCAAATTGGGAACATAATCTCAATATGGGTTAGCCATTCAATCCAAACAGGGAATCAATACCAGCCTGAACCATGCAATCAAAGCATCATTACCTATGAGAACAACACCTGGGTAAATCAGACGTATGTCAAAATCAGCAATACCAATTTTCTTGCTGAGCAGGCTGTTACTTCGGTAACATTAGCGGGCAATTCATCTCTTTGCCCTATTAGTGGGTGGGCAATATACAGTAAGGACAACGGTATAAGAATTGGGTCCAAGGGGGATGTGTTTGTTATAAGAGAACCGTTCATCTCATGCTCCCACTTGGAATGCAGAACCTTTTTCCTGACCCAGGGAGCTCTGCTGAATGACAAACATTCTAATGGGACAGTTAAGGATAGAAGCCCTTATAGAACTTTGATGAGTTGTCCCGTGGGTGAGGCTCCTTCCCCGTATAATTCAAGATTTGAGTCTGTTGCTTGGTCGGCAAGTGCTTGTCATGATGGCATCAGTTGGTTGACAATCGGTATTTCTGGTCCAGACAATGGAGCTGTGGCTGTATTGAAGTACAATGGCATAATAACGGATACTATCAAGAGTTGGAGAAACAACATTTTGAGAACTCAAGAATCTGAATGTGCTTGCGTAAATGGCTCTTGCTTCACCGTAATGACTGATGGACCAAGCAATGGGCAGGCCTCATATAAAATCTTCAAGATAGAGAAAGGGAAAGTTGTCAAATCAGTTGAAATGAATGCCCCTAATTACCACTACGAGGAATGCTCCTGTTATCCTGATGCGGGTGATATTATGTGTGTGTGCAGGGACAATTGGCATGGCTCAAACCGGCCGTGGGTATCTTTTAATCAAAATCTGGAGTATCAAATAGGATATATATGCAGTGGGGTTTTCGGGGACAATCCCCGCCCCAATGATGGAACAGGCAGTTGCAGTCCAATGCCCTCTAATGGGGCATATGGGGTAAAAGGGTTTTCATTTAAGTACGGTAATGGGGTTTGGATCGGAAGAACAAAAAGCACTAGTTCCAGAAGCGGCTTTGAGATGATTTGGGATCCGAATGGGTGGACTGAGACGGACAGTAGTTTCTCAGTGAAGCAAGACATTGTAGAAATAACTGACTGGTCAGGATATAGTGGGAGTTTTGTCCAGCATCCAGAACTGACGGGATTAGATTGCATGAGGCCTTGTTTCTGGGTTGAGCTAATCAGAGGGAGGCCCAAAGAGAACACAATTTGGACTAGCGGGAGCAGCATATCCTTTTGTGGTGTAAATAGTGACACTGTGGGTTGGTCTTGGCCAGACGGTGCTGAGTTGCCATTCACCATTGACAAGTAG</t>
         </is>
       </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>&gt;Flu-0023|A_MP</t>
         </is>
       </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>ATGAGTCTTCTAACCGAGGTCGAAACGTACGTTCTCTCTATCGTCCCGTCGGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTTGAAGATGTCTTTGCAGGGAAGAACACCGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATCCTGTCACCTCTGACTAAGGGGATTTTGGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCTCTAAGTGGAACTGGAGACCCAAACAACATGGACAGGGCAGTCAAGTTGTACAGGAAACTGAAGAGAGAGATAACATTCCATGGTGCTAAAGAAGTTGCACTCAGTTACTCAACCGGTGCACTTGCCAGTTGTATGGGTCTCATATACAACAGGATGGGGACGGTGACCGCAGAAGTGGCATTGGGCCTAGTGTGTGCCACCTGTGAGCAGATTGCTGATTCACAGCATCGGTCTCACAGACAGATAGCTACCACCACCAACCCACTAATCAGACATGAAAACAGAATGGTTTTGGCCAGTACTACAGCTAAGGCTATGGAGCAGATGGCTGGATCGAGTGAACAAGCAGTGGAAGCCATGGAGGTTGCTAGTCAGGCTAGGCAGATGGTGCAGGCAATGAGGACCATTGGAACTCATCCTAGCTCCAGTGCCGGTCTGAGAGATGATCTCCTTGAAAATTTGCAGGCCTACCAAAAACGGATGGGAGTGCAACTGCAGCGATTCAAGTGATCCTCTCGTTATTGCCGCAAGTATCATTGGGATCTTGCACTTGATATTGTGGATTCTTGATCGCCTTTTCTTCAAATGCGTTTATCGTCGCCTTAAATACGGTTTGAAAGGAGGGCCTTCTACGGAAGGAGTACCTGAGTCCATGAGGGAAGAGTACCGGCAGGAACAGCAGAGTGCTGTGGATGTTGACGATGGTCATTTTGTCAACATAGAGCTGGAGTAA</t>
         </is>
       </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>&gt;Flu-0023|A_NS</t>
         </is>
       </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>ATGGATTCCAACACTGTGTCAAGCTTTCAGGTAGACTGCTTTCTTTGGCATGTCCGCAAACGATTTGCAGACCAAGAACTGGGTGATGCCCCATTCCTTGACCGGCTCCGCCGAGACCAGAAGTCTCTAAGAGGAAGAGGCAGCACTCTTGGTCTGGACATCGAGACGGCCACTCGTGCTGGAAAGCAGATAGTGGAGAGGATTCTGGAGGAAGAATCCGACGAGGCACTCAAAATGACTATTGCCTCTGTGCCTGCTCCACGCTACCTAACTGACATGACTCTTGAAGAGATGTCAAGAGACTGGTTCATGCTCATGCCCAAGCAAAAAGTGGCAGGCTCCCTCAGTATCAGAATGGACCAGGCGATTATGGATAAGAACATCATACTGAAGGCAAACTTCAGTGTGATCTTCAATCGGCTGGAGACACTAATACTACTCAGAGCTTTCACTGAAGAGGGAGCAATTGTCGGCGAAATTTCACCATTGCCTTCTCTTCCAGGACATACTGATGAGGATGTCAAAAATGCAATTGGGGTCCTCATCGGAGGACTTGAATGGAATGATAACACAGTTCGAGTCTCTGAAACTTTACAGAGATTCGCTTGGAGAAGCAGTAATGAGGATGGGAGACCTCCACTCCCTCCAAAGCAGAAACGGAAAATGGAGAGAACAATTGAGTCAGAAGTTTGAAGAAATAAGGTGGCTGATTGAAGAAGTTCGACACAGACTAAAGATCACAGAAAATAGTTTTGAACAAATAACATTTATGCAAGCCTTACAACTACTGCTTGAAGTGGAGCAAGAGATAAGAACTTTCTCGTTTCAGCTTATTTAA</t>
         </is>
       </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>&gt;Flu-0027|A_MP</t>
         </is>
       </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>ATGAGTCTTCTAACCGAGGTCGAAACGTACGTTCTCTCTATCGTCCCGTCGGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTTGAAGATGTCTTTGCAGGGAAGAACACCGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATACTGTCACCTCTGACTAAGGGGATTTTGGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCTCTAAGTGGAAATGGAGACCCAAACAACATGGACAGGGCAGTCAAGTTGTACAGGAAATTGAAGAGAGAAATAACATTCCATGGGGCTAAAGAAGTTGCACTCAGTTACTCAACCGGTGCACTTGCCAGTTGTATGGGTCTCATATACAACAGGATGGGGACGGTGACCGCAGAAGTGGCATTGGGCCTAGTGTGTGCCACCTGTGAGCAGATTGCTGATTCACAGCATCGGTCTCACAGACAGATAGCTACCACCACCAACCCACTAATCAGACATGAAAACAGAATGGTTTTGGCCAGTACTACAGCTAAGGCTATGGAGCAGATGGCTGGATCGAGTGAGCAAGCAGTGGAAGCCATGGAGGTTGCTAGTCAGGCTAGGCAAATGGTGCAGGCGATGAGGACCATTGGAACTCATCCTAGCTCCAGTGCCGGTCTGAGAGATGATCTCCTTGAAAATTTGCAGGCCTACCAAAAACGAATGGGAGTGCAACTGCAGCGATTCAAGTGATCCTCTCGTTATTGCCGCAAGTATCATTGGGATCTTGCACTTGATATTGTGGATTCTTGATCGCCTTTTCTTCAAATGCGTTTATCGTCGCCTTAAATACGGTTTGAAAGGAGGGCCTTCTACGGAAGGAGTACCTGAGTCCATGAGGGAAGAGTACCGGCAGGAACAGCAGAGTGCTGTGGATGTTGACGATGGTCATTTTGTCAACATAGAGATGGAGTAA</t>
         </is>
       </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>&gt;Flu-0027|A_NS</t>
         </is>
       </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>ATGGATTCCAACACTGTGTCAAGCTTCCAGGTAGACTGCTTTCTTTGGCATGTCCGCAAACGATTTGCAGACCAAGAACTGGGTGATGCCCCATTCCTTGACCGGCTCCGCCGAGACCAGAAGTCTCTAAGAGGAAGAGGCAGCACTCTTGGTCTGGACATCGAGACGGCCACTCGTGCTGGAAAGCAGATAGTGGAGAGGATTCTGGAGGAAGAATCCGACGAGGCACTCAAAATGACTATTGCCTCTGTGCCTGCTCCACGCTACCTAACTGACATGACTCTTGAAGAGATGTCAAGAGACTGGTTCATGCTCATGCCCAAGCAAAAAGTGGCAGGCTCCCTCTGTATCAGAATGGACCAGGCGATTATGGATAAGAACATCATACTGAAGGCAAACTTCAGTGTGATCTTCAATCGGCTGGAGACACTAATACTACTCAGAGCTTTCACTGAAGAGGGAGCAATTGTCGGCGAAATTTCACCATTGCCTTCTCTTCCAGGACATACTGATGAGGATGTCAAAAATGCAATTGGGGTCCTCATCGGAGGACTTGAATGGAATGATAACACAGTTCGAGTCTCTGAAATTTTACAGAGATTCGCTTGGAGAAGCAGTAATGAGGATGGGAGACCTCCACTCCCTCCAAAGCAGAAACGGAAAATGGAGAGAACAATTGAGTCAGAAGTTTGAAGAAATAAGGTGGCTGATTGAAGAGGTGCGACACAGACTAAAGATCACAGAAAATAGTTTTGAACAAATAACATTTATGCAAGCCTTACAACTACTGCTTGAAGTGGAGCAAGAGATACGAACTTTCTCGTTTCAGCTTATTTAA</t>
         </is>
       </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>&gt;Flu-0035|A_NP</t>
         </is>
       </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>ATGGCGTCTCAAGGCACCAAACGATCCTATGAACAAATGGAAACTGGTGGGGAACGCCAGAATGCCACTGAAATCAGAGCATCTGTTGGAAGAATGGTTGGCGGAATAGGAAGATTCTACATACAGATGTGCACTGAGCTCAAACTCAGTGATTACGAAGGGAGGCTGATCCAAAACAGCATAACCATAGAAAGGATGGTTCTCTCGGCATTTGATGAGAGGAGGAACAAGTACCTGGAGGAACATCCCAGTGCCGGGAAGGATCCCAAGAAGACTGGAGGTCCAATCTACAGGAGGAGAGATGGCAAATGGGTGAGAGAGTTGATCCTCTACGACAAAGAAGAGATCAGAAGAATTTGGCGTCAAGCTAATAATGGAGAGGATGCAACTGCTGGTCTCACTCATTTGATGATTTGGCATTCCAATCTGAATGATGCAACATACCAGAGAACAAGGGCACTTGTGCGTACTGGAATGGACCCTAGAATGTGCTCTCTGATGCAAGGCTCAACCCTCCCTAGGAGATCCGGGGCTGCTGGAGCAGCAGTGAAAGGAGTTGGAACAATGGTGATGGAACTAATTCGAATGATCAAACGAGGGATCAATGATCGGAATTTCTGGAGAGGCGAAAACGGTCGGAGAACCAGGATTGCCTACGAGAGAATGTGCAACATCCTCAAGGGAAAGTTCCAAACAGCAGCACAACGGGCAATGATGGACCAAGTGAGAGAAAGCCGGAATCCTGGGAATGCTGAAATTGAAGATCTCATCTTTCTCGCACGATCTGCTCTCATCCTGAGGGGATCAGTGGCTCATAAGTCCTGTCTGCCTGCTTGCGTATATGGACTTGCTGTAGCCAGTGGATATGACTTTGAAAGAGAGGGATATTCTCTAGTCGGAATTGATCCTTTCCGTCTGCTCCAAAACAGCCAAGTCTTCAGTCTCATCAGACCGAACGAAAATCCAGCTCATAAAAGTCAGCTGGTATGGATGGCATGCCACTCTGCGGCATTTGAGGATCTGAGAGTTTCAAGCTTCATCAGAGGGACAAGAGTAGTCCCAAGAGGACAACTGTCCACCAGAGGAGTTCAGATTGCTTCAAATGAAAACATGGAGACAATGGACTCCAGTACTCTTGAACTGAGGAGCAGGTACTGGGCTATAAGAACAAGAAGTGGAGGAAACACTAACCAACAGAGAGCATCTGCAGGACAAATCAGCGTACAGCCCACATTCTCTGTGCAAAGAAACCTCCCATTCGAGAGAGCAACCATCATGGCAGCATTTACGGGAAACACTGAAGGCAGAACTTCAGACATGAGAACTGAGATCATAAGGATGATGGAAAATGCCAGACCTGAAGATGTGTCTTTCCAGGGGCGGGGAGTCTTCGAGCTCTCGGACGAAAAGGCAACGAACCCGATCGTGCCTTCCTTTGACATGAGTAATGAAGGATCTTATTTCTTCGGAGACAATGCAGAGGAGTATGACAATTAA</t>
         </is>
       </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>&gt;Flu-0035|A_MP</t>
         </is>
       </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>ATGAGTCTTCTAACCGAGGTCGAAACGTACGTTCTCTCTATCGTCCCGTCGGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTTGAAGATGTTTTTGCAGGGAAGAACACCGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATACTGTCACCTCTGACTAAGGGGATTTTGGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCTCTAAGTGGAAATGGAGACCCAAACAACATGGACAGGGCAGTCAAGTTGTACAGGAAATTGAAGAGAGAAATAACATTTCATGGGGCTAAAGAAGTTGCACTCAGTTACTCAACCGGTGCACTTGCCAGTTGTATGGGTCTCATATACAACAGGATGGGGACGGTGACCGCAGAAGTGGCATTGGGCCTAGTGTGTGCCACCTGTGAGCAGATTGCTGATTCACAGCATCGGTCTCACAGACAGATAGCTACCACCACCAACCCACTAATCAGACATGAAAACAGAATGGTTTTGGCCAGTACTACAGCTAAGGCTATGGAGCAGATGGCTGGATCGAGTGAGCAAGCAGTGGAAGCCATGGAGGTTGCTAGTCAGGCTAGGCAAATGGTGCAGGCGATGAGGACCATTGGAACTCATCCTAGCTCCAGTGCCGGTCTGAGAGATGATCTCCTTGAAAATTTGCAGGCCTACCAAAAACGAATGGGAGTGCAACTGCAGCGATTCAAGTGATCCTCTCGTTATTGCCGCAAGTATCATTGGGATCTTGCACTTGATATTGTGGATTCTTGATCGCCTTTTCTTCAAATGCGTTTATCGTCGCCTTAAATACGGTTTGAAAGGAGGGCCTTCTACGGAAGGAGTACCTGAGTCCATGAGGGAAGAGTACCGGCAGGAACAGCAGAGTGCTGTGGATGTTGACGATGGTCATTTTGTCAACATAGAGATGGAGTAA</t>
         </is>
       </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>&gt;Flu-0035|A_NS</t>
         </is>
       </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>ATGGATTCCAACACTGTGTCAAGCTTTCAGGTAGACTGCTTTCTTTGGCATGTCCGCAAACGATTTGCAGACCAAGAACTGGGTGATGCCCCATTCCTTGACCGGCTCCGCCGAGACCAGAAGTCTCTAAGAGGAAGAGGCAGCACTCTTGGTCTGGACATCGAGACGGCCACTCGTGCTGGAAAGCAGATAGTGGAGAGGATTCTGGAGGAAGAATCCGACGAGGCACTCAAAATGACTATTGCCTCTGTGCCTGCTCCACGCTACCTAACTGACATGACTCTTGAAGAGATGTCAAGAGATTGGTTCATGCTCATGCCCAAGCAAAAAGTGGCAGGCTCCCTCTGTATCAGAATGGACCAGGCGATTATGGATAAGAACATCATACTGAAGGCAAACTTCAGTGTGATCTTCAATCGGCTGGAGACACTAATACTACTCAGAGCTTTCACTGAAGAGGGAGCAATTGTCGGCGAAATTTCACCATTGCCTTCTCTTCCAGGACATACTGATGAGGATGTCAAAAATGCAATTGGGGTCCTCATCGGAGGACTTGAATGGAATGATAACACAGTTCGAGTCTCTGAAATTTTACAGAGATTCGCTTGGAGAAGCAGTAATGAGGATGGGAGACCTCCACTCCCTCCAAAGCAGAAACGGAAAATGGAGAGAACAATTGAGTCAGAAGTTTGAAGAAATAAGGTGGCTGATTGAAGAGGTGCGACACAGATTAAAGATCACAGAAAATAGTTTTGAACAAATAACATTTATGCAAGCCTTACAACTACTGCTTGAAGTGGAGCAAGAGATACGAACTTTCTCGTTTCAGCTTATTTAA</t>
         </is>
       </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>&gt;Flu-0055|A_MP</t>
         </is>
       </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>ATGAGTCTTCTAACCGAGGTCGAAACGTACGTTCTCTCTATCGTCCCGTCGGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTTGAAGATGTCTTTGCAGGGAAGAACACCGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATCCTGTCACCTCTGACTAAGGGGATTTTGGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCTCTAAGTGGAACTGGAGACCCAAACAACATGGACAGGGCAGTCAAGTTGTACAGGAAACTGAAGAGAGAGATAACATTCCATGGTGCTAAAGAAGTTGCACTCAGTTACTCAACCGGTGCACTTGCCAGTTGTATGGGTCTCATATACAACAGGATGGGGACGGTGACCGCAGAAGTGGCATTGGGCCTAGTGTGTGCCACCTGTGAGCAGATTGCTGATTCACAGCATCGGTCTCACAGACAGATAGCTACCACCACCAACCCACTAATCAGACATGAAAACAGAATGGTTTTGGCCAGTACTACAGCTAAGGCTATGGAGCAGATGGCTGGATCGAGTGARCAAGCAGTGGAAGCCATGGAGGTTGCTAGTCAGGCTAGGCARATGGTGCAGGCRATGAGGACCATTGGAACTCATCCTAGCTCCAGTGCCGGTCTGAGAGATGATCTCCTTGAAAATTTGCAGGCCTACCAAAAACGRATGGGAGTGCAACTGCAGCGATTCAAGTGATCCTCTCGTTATTGCCGCAAGTATCATTGGGATCTTGCACTTGATATTGTGGATTCTTGATCGCCTTTTCTTCAAATGCGTTTATCGTCGCCTTAAATACGGTTTGAAAGGAGGGCCTTCTACGGAAGGAGTACCTGAGTCCATGAGGGAAGAGTACCGGCAGGAACAGCAGAGTGCTGTGGATGTTGACGATGGTCATTTTGTCAACATAGAGMTGGAGTAA</t>
         </is>
       </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>&gt;Flu-0205|A_MP</t>
         </is>
       </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>NNNNGTCTTCTAACCGAGGTCGAAACGTACGTTCTCTCTATCGTCCCGTCGGGNCCCCTCAAAGCCGAGATCGCGCAGAGACTTGAAGATGTCTTTGCANGGAAGAACACCGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATCCTGTCACCTCTGACTAAGGGGATTTTGGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCTCTAAGTGGAACTGGAGACCCAAACAACATGGACAGGGCAGTCAAGTTGTACAGGAAACTAAAGAGAGAGATAACATTCCATGGTGCTAAAGAAGTTGCACTCAGTTACTCAACCGGTGCACTTGCCAGTTGTATGGGTCTCATATACAACAGGATGGGGACNGTGACCGCAGAAGTGGCATTGGGCCTAGTGTGTGCCACCTGTGAGCAGATTGCTGATTCACAGCATCGGTCTCACAGACAGATAGCTACCACCACCAACCCACTAATCAGACATGAAAACAGAATGGTTTTGGCCAGTACTACAGCTAAGGCTATGGAGCAGATGGCTGGATCGAGTGAGCAAGCAGTGGAAGCCATGGAGGTTGCTAGTCAGGCTAGGCAGATGGTGCAGGCGATGAGGACCATTGGAACTCATCCTAGCTCCAGTGCCGGTCTAAGAGATGATCTCCTTGAAAATTTGCAGGCCTACCAAAAACGGATGGGAGTGCAACTGCAGCGATTCAAGTGATCCTCTCGTTATTGCCGCAAGTATCATTGGGATCTTGCACTTGATATTGTGGATTCTTGATCGCCTTTTCTTCAAATGCGTTTATCGTCGCCTTAAATACGGTTTGAAAGGAGGGCCTTCTACGGAAGGAGTACCTGAGTCCATGAGGGAAGAGTACCGGCAGGAACAGCAGAGTGCTGTGGATGTTGACGATGGTCATTTTGTCAACATAGANNNNNNNNNN</t>
         </is>
       </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>&gt;Flu-0206|A_MP</t>
         </is>
       </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>ATGAGTCTTCTAACCGAGGTCGAAACGTACGTTCTCTCTATCGTCCCGTCGGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTTGAAGATGTCTTTGCAGGGAAGAACACCGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATCCTGTCACCTCTGACTAAGGGGATTTTGGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCTCTAAGTGGAACTGGAGACCCAAACAACATGGACAGGGCAGTCAAGTTGTACAGGAAACTAAAGAGAGAGATAACATTCCATGGTGCTAAAGAAGTTGCACTCAGTTACTCAACCGGTGCACTTGCCAGTTGTATGGGTCTCATATACAACAGGATGGGGACGGTGACCGCAGAAGTGGCATTGGGCCTAGTGTGTGCCACCTGTGAGCAGATTGCTGATTCACAGCATCGGTCTCACAGACAGATAGCTACCACCACCAACCCACTAATCAGACATGAAAACAGAATGGTTTTGGCCAGTACTACAGCTAAGGCTATGGAGCAGATGGCTGGATCGAGTGAGCAAGCAGTGGAAGCCATGGAGGTTGCTAGTCAGGCTAGGCAGATGGTGCAGGCGATGAGGACCATTGGAACTCATCCTAGCTCCAGTGCCGGTCTAAGAGATGATCTCCTTGAAAATTTGCAGGCCTACCAAAAACGGATGGGAGTGCAACTGCAGCGATTCAAGTGATCCTCTCGTTATTGCCGCAAGTATCATTGGGATCTTGCACTTGATATTGTGGATTCTTGATCGCCTTTTCTTCAAATGCGTTTATCGTCGCCTTAAATACGGTTTGAAAGGAGGGCCTTCTACGGAAGGAGTACCTGAGTCCATGAGGGAAGAGTACCGGCAGGAACAGCAGAGTGCTGTGGATGTTGACGATGGTCATTTTGTCAACATAGAGCTGGAGTAA</t>
         </is>
       </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>&gt;Flu-0206|A_NS</t>
         </is>
       </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>NNNGATTCCAACACTGTGTCAAGCTTTCAGGTAGACTGCTTTCTTTGGCATGTCCGCAAACGATTTGCAGACCAAGAACTGGGTGATGCCCCATTCCTTGACNGGCTCCGCCGAGACCAGAAGTCTCTAAGAGGAAGAGGCAGCACTCTTGGTCTGAACATCGAGACGGCCACTCGTGCTGGAAAGCAGATAGTGGAGAGGATTCTGGAGGAAGAATCCGACGAAGCACTCAAAATGACTATTGCCTCTGTGCCTGCTCCACGCTACCTAACTGACATGACTCTTGAAGAGATGTCAAGAGACTGGTTCATGCTCATGCCCAAGCNAAAAGTGGCAGGCTCCCTCAGTATCAGAATGGACCAGGCGATTATGGATAAGAACATCATACTGAAGGCAAACTTCAGTGTGATCTTCAATCGGCTGGAGACACTAATACTACTCAGAGCTTTCACTGAAGAAGGAGCAATTGTCGGCGAAATTTCACCATTGCCTTCTCTTCCAGGACATACTGATGAGGATGTCAAAAATGCAATTGGGGTCCTCATCGGAGGATTTGAATGGAATGATAACACAGTTCGAGTCTCTGAAACTTTACAGAGGTTCGCTTGGAGAAGCAGTAATGAGGATGGGAGACCTCCACTCCCTCCAAAGCAGAAACGGAAAATGGAGAGAACAATTGAGTCAGAAGTTTGAAGAAATAAGGTGGCTGATTGAAGAAGTTCGACACAGACTAAAGATCACAGAAAATAGTTTTGAACAAATAACATTTATGCAAGCCTTACAACTACTGCTTGAAGTGGAGCAAGAGATAAGAACTTTCTCGTTTCAGCTTATTNNN</t>
         </is>
       </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>&gt;Flu-0314|A_NA</t>
         </is>
       </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>ATGAATCCAAATCAAAAGATAACAACCATTGGATCAATCTGTATGGTAATTGGGACAGTCAGCTTGATGCTGCAAATTGGGAACATAATCTCAATATGGGTTAGCCATTCAATCCAAACAGGGAATCAATACCAGCCTGAACCATGCAATCAAAGCATCATTACCTATGAGAACAACACCTGGGTAAATCAGACGTATGTCAACATCAGCAATAACAATTTTCTTGCTGAGCAGGCTGTTACTTCGGTAACATTAGCGGGCAATTCATCTCTTTGCCCTATTAGTGGGTGGGCAATATACAGTAAGGACAACGGTATAAGAATTGGGTCCAAGGGGGATGTGTTTGTCATAAGAGAACCGTTCATCTCATGCTCCCACTTGGAATGCAGAACCTTTTTCCTGACTCAGGGAGCTCTGCTGAATGACAAACATTCTAATGGGACAGTTAAGGATAGAAGCCCTTATAGAACTTTGATGAGTTGTCCCGTGGGTGAGGCTCCTTCCCCGTACAATTCAAGATTTGAGTCTGTTGCTTGGTCGGCAAGTGCTTGTCATGATGGCATCAGTTGGTTGACAATCGGTATTTCTGGTCCAGACAATGGAGCTGTGGCTGTATTGAAGTACAATGGCATAATAACGGATACTATCAAGAGTTGGAGAAACAACATTTTGAGAACTCAAGAATCTGAATGTGCTTGCGTAAATGGCTCTTGCTTCACCGTAATGACTGATGGACCAAGCAATGGGCAGGCCTCGTATAAAATCTTCAAGATAGAGAAAGGGAAAGTTGTCAAATCAGTTGAATTGAATGCCCCTAATTACCACTACGAGGAATGTTCCTGTTATCCTGATGCGGGTGATATTATATGTGTGTGCAGGGACAATTGGCACGGCTCAAACCGGCCGTGGATATCTTTTAATCAAAATCTGGAGTATCAAATAGGATATATATGCAGTGGGGTTTTCGGGGACAATCCCCGCCCCAATGATGGAACAGGCAGTTGCAGTCCAATGTCCTCTAATGGGGCATATGGGGTRAAAGGGTTTTCATTTAAGTACGGTAATGGGGTTTGGATCGGAAGAACAAAAGGCACTAGTTCCAGAAGCGGCTTTGAGATGATTTGGGACCCGAATGGGTGGACTGAGACGGACAGTAGTTTCTCAGTGAAGCAAGACATTGTAGAAATAACTGACTGGTCAGGATATAGTGGGAGTTTTGTCCAGCATCCAGAACTGACAGGATTAGATTGCATGAGGCCTTGTTTCTGGGTTGAGCTAATTAGAGGGAGGCCCAAAGAGAACACAATTTGGACTAGCGGGAGCAGCATATCCTTTTGTGGTGTAAATAGTGACACTGTGGGTTGGTCTTGGCCAGACGGTGCTGAGTTGCCATTCACCATTGACAAGTAG</t>
         </is>
       </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>&gt;Flu-0314|A_MP</t>
         </is>
       </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>ATGAGTCTTCTAACCGAGGTCGAAACGTACGTTCTCTCTATCGTCCCGTCGGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTTGAAGATGTCTTTGCAGGGAAGAACACCGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATACTGTCACCTCTGACTAAGGGGATTTTGGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCTCTAAGTGGAAATGGAGACCCAAACAACATGGACAGGGCAGTCAAGTTGTACAGGAAACTGAAGAGAGAAATAACATTCCATGGGGCTAAAGAAGTTGCACTTAGTTACTCAACCGGTGCACTTGCCAGTTGTATGGGTCTCATATACAACAGGATGGGGACGGTGACCGCAGAAGTGGCATTGGGCCTAGTGTGTGCCACCTGTGAGCAGATTGCTGATTCACAGCATCGGTCTCACAGACAGATAGCTACCACCACCAACCCACTAATCAGACATGAAAACAGAATGGTTTTGGCCAGTACTACAGCTAAGGCTATGGAGCAGATGGCTGGATCGAGTGAGCAAGCAGTGGAAGCCATGGAGGTTGCTAGTCAGGCTAGGCAAATGGTGCAGGCGATGAGGACCATTGGAACTCATCCTAGCTCCAGTGCCGGTCTGAGAGATGATCTCCTTGAAAATTTGCAGGCCTACCAAAAACGAATGGGAGTGCAACTGCAGCGATTCAAGTGATCCTCTCGTTATTGCAGCAAGTATCATTGGGATCTTGCACTTGATATTGTGGATTCTTGATCGCCTTTTCTTCAAATGCGTTTATCGTCGCCTTAAATACGGTTTGAAAGGAGGGCCTTCTACGGAAGGAGTACCTGAGTCCATGAGGGAAGAGTACCGGCAGGAACAGCAGAGTGCTGTGGATGTTGACGATGGTCATTTTGTCAACATAGAGATGGAGTAA</t>
         </is>
       </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>&gt;Flu-0314|A_NS</t>
         </is>
       </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>ATGGATTCCAACACTGTGTCAAGCTTTCAGGTAGACTGCTTTCTTTGGCATGTCCGCAAACAATTTGCAGACCAAGAACTGGGTGATGCCCCATTCCTTGACCGGCTCCGCCGAGACCAGAAGTCTCTAAGAGGAAGAGGCAGCACTCTTGGTCTGGACATCGAGACGGCCACTCGTGCTGGAAAGCAGATAGTGGAGAGGATTCTGGAGGAAGAATCCGACGAGGCACTCAAAATGACTATTGCCTCTGTGCCTGCTCCACGCTACCTAACTGACATGACTCTTGAAGAGATGTCAAGAGACTGGTTCATGCTCATGCCCAAGCAAAAAGTGGCAGGCTCCCTCTGTATCAGAATGGACCAGGCGATTATGGATAAGAACATCATACTGAAGGCAAACTTCAGTGTGATCTTCAATCGGCTGGAGACACTAATACTACTCAGAGCTTTCACTGAAGAGGGAGCAATTGTCGGCGAAATTTCACCATTGCCTTCTCTTCCAGGACATACTGATGAGGATGTCAAAAATGCAATTGGGGTCCTCATCGGAGGACTTGAATGGAATGATAACACAGTTCGAGTCTCTGAAATTTTACAGAGATTCGCTTGGAGAAGCAGTAATGAGGATGGGAGACCTCCACTCCCTCCAAAGCAGAAACGGAAAATGGAGAGAACAATTGAGTCAGAAGTTTGAAGAAATAAGGTGGCTGATTGAAGAGGTGCGACACAGACTAAAGATCACAGAAAATAGTTTTGAACAAATAACATTTATGCAAGCCTTACAACTACTGCTTGAAGTGGAGCAAGAGATACGAACTTTCTCGTTTCAGCTTATTTAA</t>
         </is>
       </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>&gt;Flu-0316|A_PB2</t>
         </is>
       </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>ATGGAGAGAATAAAAGAACTAAGAGATCTAATGTCACAGTCTCGCACTCGCGAGATACTGACCAAAACCACTGTTGACCACATGGCCATAATCAAAAAGTACACATCGGGAAGGCAAGAGAAGAACCCCGCACTCAGAATGAAATGGATGATGGCAATGAAATATCCAATTACAGCAGATAAGCGAATAATGGAAATGATCCCTGAGAGGAATGAACAAGGGCAAACTCTCTGGAGCAAAACAAACGATGCCGGATCAGACCGAGTGATGGTATCACCCCTGGCTGTGACATGGTGGAACAGGAACGGACCAACAACAAGTACAGTTCACTACCCAAAGGTATATAAAACTTATTTCGAAAAAGTTAAAAGGTTGAAACACGGGACCTTTGGCCCTGTGCACTTCAGAAACCAAGTTAAGATAAGACGGAGGGTCGATATAAACCCGGGCCATGCTGACCTTAGTGCCAAAGAGGCACAGGATGTAATCATGGAAGTCGTCTTCCCAAATGAAGTGGGAGCTAGGATATTGACGTCGGAGTCACAACTGACGATAACAAAGGAGAAAAAGGAAGAACTCCAGGACTGCAAAATCGCTCCTCTGATGGTTGCATACATGCTAGAACGAGAGTTGGTTCGCAAGACGAGGTTTCTCCCAGTTGCTGGTGGGACAAGCAGTGTCTACATTGAGGTGCTGCATTTGACCCAGGGGACATGCTGGGAGCAGATGTACACTCCGGGAGGAGAAGTGAGGAACGATGATGTAGACCAAAGCTTGATCATTGCTGCCAGGAATATAGTAAGAAGAGCAACAGTATCAGCAGATCCGTTAGCATCTCTATTGGAGATGTGTCACAGCACACAAATTGGGGGAATAAGGATGGTAGACATCCTTCGGCAAAACCCAACAGAGGAACAAGCCGTGGATATATGCAAGGCAGCAATGGGCTTGAGGATTAGCTCATCTTTCAGCTTTGGTGGATTCACTTTTAAAAGAACAAGTGGATCGTCAGTCAAAAAAGAAGAAGAAGTGCTAACAGGCAACCTTCAAACATTGAAAATAAGAGTACATGAGGGGTATGAAGAGTTCACAATGGTTGGGAGAAGAGCAACGGCCATTCTCAGGAAAGCAACCAGAAGGCTGATCCAGCTAATAGTAAGTGGGAGAGACGAGCAGTCAATTGCTGAAGCAATAATTGTGGCCATGGTATTCTCACAAGAGGACTGCATGATTAAAGCAGTTAGAGGTGACCTGAATTTTGTCAATAGGGCGAACCAGCGACTAAACCCAATGCATCAACTCTTGAGGCATTTCCAAAAGGATGCAAAAGTGCTTTTCCAAAATTGGGGAATTGAACCCATTGACAATGTGATGGGAATGATCGGGGTAATGCCTGACATGACCCCAAGTACTGAGATGTCGCTGAGGGGAATAAGAGTCAGCAAGATGGGAGTAGATGAATACTCAAGCACAGAGCGAGTAGTAGTAAGCATCGACCGGTTTTTAAGAGTTCGAGACCAACGGGGGAACGTACTATTATCACCCGAAGAGGTCAGTGAGACACAAGGAACGGAGAAACTGACAATCACTTATTCGTCATCAATGATGTGGGAGATCAATGGTCCTGAGTCGGTGTTGGTCAATACTTATCAGTGGATAATTAGAAACTGGGAAACTGTAAAAATTCAATGGTCACAGGATCCCACAATGCTGTATAATAAGATGGAATTCGAGCCATTCCAGTCTCTAGTCCCTAAGGCAGCCAGAGGTCAATACAGTGGGTTTGTGAGAACACTATTCCAGCAAATGCGAGATGTGCTTGGAACATTTGACACTGTTCAGATAGTAAAACTCCTCCCCTTTGCTGCCGCCCCACCGGAACAAAGTAGGATGCAGTTCTCCTCCCTGACTGTGAATGTAAGAGGATCAGGAATGAGGATACTGGTAAGAGGCAATTCACCAGTGTTCAATTACAACAAGGCCACCAAGAGGCTCACAGTTCTCGGGAAAGATGCAGGTGCATTGACCGAAGATCCAGATGAAGGCACAGCTGGAGTGGAGTCTGCTGTTTTAAGAGGATTCCTCATTTTGGGCAAAGAAGACAAGAGATATGGCCCAGCATTGAGCATCAATGAGCTGAGCAATCTTGCAAAGGGAGAGAAGGCTAATGTGCTAATTGGGCAAGGAGACGTAGTGTTGGTGATGAAACGGAAACGGGACTCTAGCATACTTACTGACAGCCAGACAGCGACCAAAAGAATTCGGATGGCCATCAATTAG</t>
         </is>
       </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>&gt;Flu-0316|A_PB1</t>
         </is>
       </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
+      <c r="BN1" t="inlineStr">
         <is>
           <t>ATGGATGTCAATCCGACTTTACTTTTCTTGAAAGTTCCAGCGCAAAATGCCATAAGCACCACATTCCCGTATACTGGAGATCCTCCATACAGCCATGGAACAGGAACAGGATATACCATGGACACAGTTAACAGAACACATCAGTATTCAGAAAAAGGGAAATGGACAACAAACTCAGAAACTGGAGCACCTCAACTCAATCCAATTGATGGACCATTGCCTGAGGGCAATGAACCAAGTGGGTATGCACAAACGGACTGTGTCCTTGAAGCAATGGCTTTCCTTGAAGAGTCCCACCCAGGAATCTTTGAAAACTCGTGTCTTGAAACGATGGAAGTTGTTCAACAAACAAGAGTGGACAAGTTGACCCAAGGCCGTCAGACCTATGATTGGACGTTAAACAGGAATCAGCCGGCTGCAACTGCATTAGCTAATACTATAGAGGTCTTCAGATCTAACGGCCTCACAGCCAATGAATCAGGAAGGCTAATAGATTTTCTCAAGGATGTGATGGAATCAATGGATAAGGAGGAAATGGAAATAACAACGCATTTCCAAAGGAAAAGAAGAGTGAGAGACAACATGACCAAGAAAATGGTCACACAAAGGACAATAGGAAAGAAGAAACAGAGGCTAAATAAAAAGAGCTATCTAATAAGAGCATTGACACTGAACACGATGACAAAAGACGCCGAAAGAGGCAAATTAAAAAGAAGGGCAATTGCAACACCTGGAATGCAAATCAGAGGGTTTGTGTACTTTGTTGAGACATTAGCGAGGAGCATTTGTGATAAGCTTGAACAATCTGGACTCCCAGTTGGGGGCAATGAAAAGAAGGCTAAACTGGCAAATGTTGTGAGAAAAATGATGACTAATTCGCAGGACACAGAGCTCTCTTTCACAATCACTGGAGACAACACCAAATGGAATGAAAATCAGAACCCTAGGATGTTTCTGGCAATGATAACATATATAACAAGGAACCAACCTGAATGGTTCAGGAATGTCTTAAGCATTGCACCTATAATGTTCTCAAATAAAATGGCAAGACTAGGGAAAGGGTACATGTTCGAAAGTAAGAGCATGAAGCTCCGAACACAAATACCAGCAGAAATGCTAGCAAGCATTGATCTGAAGTACTTCAATGAGTCAACAAGAAAGAAAATAGAGAAGATAAGACCTCTTCTAATAGATGGTACAGCCTCATTAAGCCCAGGAATGATGATGGGCATGTTCAATATGCTGAGTACAGTTTTGGGAGTTTCGATTCTAAATCTAGGACAAAGGAGGTACACCAAAACAACATACTGGTGGGACGGACTCCAATCCTCTGATGACTTTGCTCTCATAGTGAATGCTCCGAATCATGAGGGAATACAAGCAGGGGTAGACAGATTCTATAGAACCTGCAAGCTGGTCGGAATCAACATGAGCAAAAAGAAGTCCTACATAAACAGGACAGGAACATTTGAATTCACAAGTTTTTTCTACCGCTATGGATTTGTAGCCAACTTCAGTATGGAGTTGCCCAGCTTTGGAGTGTCTGGGATCAATGAATCTGCAGACATGAGCATTGGAGTAACAGTAATAAAGAACAACATGATCAACAATGATCTTGGACCAGCAACAGCTCAAATGGCTCTTCAGCTATTCATCAAGGATTACAGATACACATACCGGTGTCACAGAGGAGACACACAAATTCAGACAAGGAGGTCATTCGAGCTGAAGAAGTTGTGGGAACAGACCCGTTCAAAAGCAGGACTGCTGGTCTCAGATGGAGGACCAAATCTATACAATATTCGGAATCTTCACATTCCAGAAGTCTGCTTGAAATGGGAGCTAATGGACGAAGACTATCAGGGAAGGCTTTGTAATCCCCTGAACCCGTTTGTCAGCCACAAGGAAATAGAGTCTGTGAACAACGCAGTGGTGATGCCAGCTCATGGCCCGGCCAAGAGCATGGAATATGATGCTGTTGCCACCACTCACTCCTGGATACCGAAGAGGAACCGCTCCATTCTCAATACAAGCCAAAGGGGAATCCTTGAAGACGAACAGATGTATCAAAAGTGCTGCAACCTGTTCGAAAAATTCTTCCCTAGCAGTTCATACAGGAGGCCAGTTGGAATTTCCAGCATGGTGGAGGCCATGGTTTCTAGGGCCCGAATTGACGCACGAATTGACTTCGAATCTGGACGGATTAAGAAGGAGGAGTTTGCTAAGATCATGAAGATCTGTTCCACCATTGAAGAGCTCAGACGGCAGAAATAG</t>
         </is>
       </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
+      <c r="BO1" t="inlineStr">
         <is>
           <t>&gt;Flu-0316|A_PA</t>
         </is>
       </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
+      <c r="BP1" t="inlineStr">
         <is>
           <t>ATGGAAGACTTTGTGCGACAATGCTTCAATCCAATGATTGTCGAGCTTGCGGAAAAAGCAATGAAAGAATATGGGGAAGATCCGAAAATCGAGACAAACAAATTTGCCGCAATATGCACACACTTAGAAGTCTGTTTCATGTATTCGGATTTCCATTTTATTAATGAACGAGGCGAATCAATGATTGTAGAATCTGGCGATCCAAATGCATTATTGAAACACCGATTTGAGATAATAGAAGGGAGAGACCGGGCAATGGCCTGGACAGTGGTGAATAGTATCTGCAACACCACAGGGGTCGAAAAGCCCAAATTCCTCCCTGATTTGTATGACTACAAAGAGAACCGATTCATTGAAATTGGAGTAACGCGAAGGGAAGTTCACATATACTATTTAGAAAAAGCCAACAAGATAAAGTCAGAGAAAACACATATTCACATATTCTCATTCACTGGAGAGGAAATGGCCACCAAGGCGGACTACACCCTTGATGAAGAGAGCAGAGCAAGAATAAAAACCAGACTGTTCACTATAAGACAAGAAATGGCCAGTAGAGGTCTATGGGATTCCTTTCGTCAATCCGAGAGAGGCGAAGAGACAATTGAAGAAAGATTTGAAATCGCAGGAACCATGCGCAGGCTTGCCAACCAAAGTCTTCCACCGAACTTCTCCAGCCTTGAAAACTTTAGAGCCTATGTGGATGGATTCGAACCGAACGGCTGCATTGAGGGCAAACTTTCTCAAATGTCAAAAGAAGTGAACGCCAGGATTGAGCCATTTCTGAAGACAACACCACGCCCTCTCAGATTACCTGATGGGCCTCCCTGTTCTCAGCGGTCGAAGTTCTTGCTGATGGATGCCCTTAAGTTGAGCATCGAAGACCCTAGCCATGAGGGGGAGGGCATACCGCTGTATGATGCAATCAAATGCATGAAGACATTTTTTGGCTGGAAAGAGCCCAACATCGTAAAGCCGCATGAGAAAGGCATAAACCCTAATTACCTCCTGACTTGGAAGCAGGTGCTGGCAGAACTTCAAGACATTGAAAATGAGGAGAAAATTCCAAAGACAAAGAACATGAAGAAAACAAGCCAATTGAAGTGGGCACTTGGTGAGAACATGGCTCCAGAGAAAGTGGACTTTGAGGACTGCAAAGATGTTAGCGATCTAAGACAGTACGACAGTAACGAACCAGAGTCTAGAACACTAGCAAGCTGGATTCAGAGTGAATTCAACAAGGCATGCGAACTGACAGATTCGAGTTGGATTGAACTTGATGAGATAGGGGAAGACGTTGCTCCAATCGAACACATTGCGAGTGTGAGGAGGAACTATTTCACAGCGGAGGTATCCCATTGCAGGGCCACTGAATACATAATGAAGGGAGTATACATAAACACAGCCCTATTGAATGCATCCTGTGCAGCCATGGATGACTTCCAATTGATTCCAATGATAAGTAAGTGCAGAACTAAAGAAGGAAGACGGAAGACAAATCTGTATGGATTCATTATAAAAGGAAGATCCCATTTGAGGAATGACACCGATGTGGTAAACTTTGTGAGCATGGAATTCTCTCTAACTGACCCGAGGCTGGAGCCACACAAATGGGAGAAGTACTGTGTTCTTGAGATAGGAGACATGCTCCTACGGACTGCAATAGGCCAAGTGTCGAGGCCCATGTTCCTGTATGTGAGAACCAATGGGACTTCCAAGATCAAAATGAAATGGGGCATGGAGATGAGGCGATGCCTTCTTCAGTCCCTTCAACAAATTGAGAGCATGATTGAGGCCGAATCTTCTGTCAAAGAGAAGGACATGTCCAAGGAATTCTTTGAAAACAAATCAGAAACATGGCCAATTGGAGAATCACCCAAAGGGGTGGAGGAAGGCTCTATTGGGAAAGTATGCAGAACATTGCTAGCAAAGTCTGTGTTCAACAGCCTATATGCATCTCCACAACTCGAGGGGTTTTCAGCTGAATCAAGAAAATTGCTTCTCATTGTTCAGGCACTTAGGGACAACCTGGAACCTGGAACCTTCGATCTTGGGGGGCTATATGAAGCAATTGAGGAGTGCCTGATTAACGATCCCTGGGTTTTGCTTAATGCATCTTGGTTCAACTCCTTCCTCACACATGCACTGAAATAG</t>
         </is>
       </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
+      <c r="BQ1" t="inlineStr">
         <is>
           <t>&gt;Flu-0316|A_HA</t>
         </is>
       </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
+      <c r="BR1" t="inlineStr">
         <is>
           <t>ATGGAGAACATAGTACTACTTCTTGCAATAGTTAGCCTTGTTAAAAGTGACCAGATTTGCATTGGTTACCATGCAAACAATTCGACAGAGCAAGTTGACACGATAATGGAAAAGAACGTCACTGTTACACATGCCCAAGACATACTGGAAAAAACACACAACGGGAAGCTCTGTGATTTAAATGGGGTGAAGCCACTGATTTTAAAGGATTGTAGTGTAGCTGGATGGCTCCTCGGGAACCCAATGTGCGACGAATTCATCAGAGTGCCGGAATGGTCCTACATAGTGGAGCGAGCTAACCCAGCTAATGACCTCTGTTACCCAGGGAGCCTCAATGACTATGAAGAACTGAAACACATGTTGAGCAGAATAAATCATTTTGAGAAGATTCAGATCATTCCCAARAGTTCCTGGCCAAATCATGAAACATCACTAGGGGTGAGCGCAGCTTGTCCATACCAGGGAGCGCCCTCCTTTTTCAGAAATGTGGTGTGGCTTATCAAAAAGAACGATGCATACCCAACAATAAAGATAAGCTACAATAATACTAATCGGGAAGATCTCTTGATACTGTGGGGGATTCATCATCCCAACAATGCAGAAGAGCAGACAAATCTCTACAAAAACCCAACCACCTACATTTCAGTTGGAACATCAACTTTAAACCAGAGATTGGCACCAAAAATAGCTACTAGATCCCAAGTAAACGGGCAACGTGGAAGAATGGACTTCTTTTGGACAATCTTAAAACCAGATGATGCAATCCATTTCGAGAGTAACGGAAATTTCATTGCTCCAGAATATGCATACAAAATTGTCAAGAAAGGGGACTCAACAATTATGAAAAGTGGAGTGGAATATGGCCACTGCAACACCAAATGTCAAACCCCAGTAGGTGCTATAAATTCTAGTATGCCATTCCACAACATACATCCTCTCACCATTGGGGAATGCCCCAAATACGTGAAATCAAACAAGTTGGTCCTTGCGACTGGGCTCAGAAATAGTCCTCTAAGAGAAAAGAGAAGAAAAAGAGGTCTGTTTGGGGCGATAGCAGGGTTTATAGAGGGAGGATGGCAGGGAATGGTTGATGGTTGGTATGGGTACCATCATAGCAATGAGCAGGGGAGTGGGTACGCTGCGGACAAAGAATCCACCCAAAAGGCAATAGATGGAGTTACCAATAAGGTCAACTCAATCATTGACAAAATGAACACTCAATTTGAGGCAGTTGGAAGGGAGTTTAATAACTTAGAAAGGAGGATAGAGAATTTGAACAAGAAAATGGAAGACGGATTCCTAGATGTCTGGACCTATAATGCTGAACTTCTAGTTCTTATGGAAAACGAGAGGACTCTAGATTTCCATGATTCAAATGTCAAGAACCTTTACGACAAAGTCAGATTACAGCTTAGGGATAATGCAAAGGAGCTGGGTAACGGCTGTTTCGAATTCTATCACAAATGTGATAATGAATGTATGGAAAGTGTGAGAAATGGGACGTATGACTACCCTCAGTATTCAGAAGAAGCAAGATTAAAAAGAGAAGAAATAAGCGGAGTGAAATTAGAATCAGTAGGAACTTACCAGATACTGTCAATTTATTCAACAGCGGCAAGTTCCCTAGCACTGGCAATCATGATGGCTGGTCTATCTTTATGGATGTGCTCCAATGGGTCGTTACAATGCAGAATTTGCATTTAG</t>
         </is>
       </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
+      <c r="BS1" t="inlineStr">
         <is>
           <t>&gt;Flu-0316|A_NP</t>
         </is>
       </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
+      <c r="BT1" t="inlineStr">
         <is>
           <t>ATGGCGTCTCAAGGCACCAAACGATCCTATGAACAAATGGAAACTGGTGGGGAACGCCAGAATGCCACTGAAATCAGAGCATCTGTTGGAAGAATGGTTGGCGGAATAGGAAGATTCTACATACAGATGTGCACTGAGCTCAAACTCAGTGATTATGAAGGGAGGCTGATCCAAAACAGCATAACCATAGAAAGGATGGTTCTCTCGGCATTTGATGAGAGGAGGAACAAGTACCTGGAGGAACATCCCAGTGCCGGGAAGGATCCCAAGAAGACTGGAGGTCCAATCTACAGGAGGAGAGATGGCAAATGGGTGAGAGAGTTGATCCTCTACGACAAAGAAGAGATCAGAAGAATTTGGCGTCAAGCTAATAATGGAGAGGATGCAACTGCTGGTCTCACTCATTTGATGATTTGGCATTCCAATCTGAATGATGCAACATACCAGAGAACAAGGGCACTTGTGCGTACTGGAATGGACCCTAGAATGTGCTCTCTGATGCAAGGATCAACCCTCCCTAGGAGATCCGGGGCTGCTGGAGCAGCAGTGAAAGGAGTTGGAACAATGGTGATGGAACTAATTCGAATGATCAAGCGAGGGATCAATGATCGGAATTTCTGGAGAGGCGAAAACGGTCGGAGAACCAGGATTGCCTACGAGAGAATGTGCAACATCCTCAAGGGAAAGTTCCAAACAGCAGCACAACGGGCAATGATGGACCAAGTGAGAGAAAGCCGGAATCCTGGGAATGCTGAAATTGAAGATCTCATCTTTCTCGCACGATCTGCTCTCATCCTGAGGGGATCAGTGGCTCATAAGTCCTGTCTGCCTGCTTGCGTATATGGACTTGCTGTAGCCAGTGGATATGACTTTGAAAGAGAGGGATATTCTCTAGTCGGAATTGATCCTTTCCGTCTGCTCCAAAACAGCCAAGTCTTCAGTCTCATCAGACCGAACGAAAATCCAGCTCATAAGAGTCAGCTGGTATGGATGGCATGCCACTCTGCGGCATTTGAGGATCTGAGAGTTTCAAGCTTCATCAGAGGGACAAGAGTAGTCCCAAGAGGACAACTGTCCACCAGAGGAGTTCAGATTGCTTCAAATGAAAACATGGAGACAATGGACTCCAGTACTCTTGAACTGAGGAGCAGATACTGGGCTATAAGAACAAGAAGTGGAGGAAACACTAACCAACAGAGAGCATCTGCAGGACAAATCAGCGTGCAGCCCACATTCTCTGTGCAAAGAAACCTCCCATTCGAGAGAGCAACCATCATGGCAGCATTTACGGGAAACACTGAAGGCAGAACTTCAGACATGAGAACGGAGATCATAAGGATGATGGAAAATGCCAGACCTGAAGATGTGTCTTTCCAGGGGCGGGGAGTCTTCGAGCTCTCGGACGAAAAGGCAACGAACCCGATCGTGCCTTCCTTTGACATGAGTAATGAAGGATCTTATTTCTTCGGAGACAATGCAGAGGAGTATGACAATTAA</t>
         </is>
       </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
+      <c r="BU1" t="inlineStr">
         <is>
           <t>&gt;Flu-0316|A_NA</t>
         </is>
       </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
+      <c r="BV1" t="inlineStr">
         <is>
           <t>ATGAATCCAAATCAAAAGATAACAACCATTGGATCAATCTGTATGGTAATTGGGACAGTCAGCTTGATGCTGCAAATTGGGAACATAATCTCAATATGGGTTAGCCATTCAATCCAAACAGGGAATCAATACCAGCCTGAACCATGCAATCAAAGCATCATTACCTATGAGAACAACACCTGGGTAAATCAGACGTATGTCAACATCAGCAATAACAATTTTCTTGCTGAGCAGGCTGTTACTTCGGTAACATTAGCGGGCAATTCATCTCTTTGCCCTATTAGTGGGTGGGCAATATACAGTAAGGACAACGGTATAAGAATTGGGTCCAAGGGGGATGTGTTTGTCATAAGAGAACCGTTCATCTCATGCTCCCACTTGGAATGCAGAACCTTTTTCCTGACTCAGGGAGCTCTGCTGAATGACAAACATTCTAATGGGACAGTTAAGGATAGAAGCCCTTATAGAACTTTGATGAGTTGTCCCGTGGGTGAGGCTCCTTCCCCGTACAATTCAAGATTTGAGTCTGTTGCTTGGTCGGCAAGTGCTTGTCATGATGGCATCAGTTGGTTGACAATCGGTATTTCTGGTCCAGACAATGGAGCTGTGGCTGTATTGAAGTACAATGGCATAATAACGGATACTATCAAGAGTTGGAGAAACAACATTTTGAGAACTCAAGAATCTGAATGTGCTTGCGTAAATGGCTCTTGCTTCACCGTAATGACTGATGGACCAAGCAATGGGCAGGCCTCGTATAAAATCTTCAAGATAGAGAAAGGGAAAGTTGTCAAATCAGTTGAATTGAATGCCCCTAATTACCACTACGAGGAATGTTCCTGTTATCCTGATGCGGGTGATATTATATGTGTGTGCAGGGACAATTGGCACGGCTCAAACCGGCCGTGGATATCTTTTAATCAAAATCTGGAGTATCAAATAGGATATATATGCAGTGGGGTTTTCGGGGACAATCCCCGCCCCAATGATGGAACAGGCAGTTGCAGTCCAATGTCCTCTAATGGGGCATATGGGGTAAAAGGGTTTTCATTTAAGTACGGTAATGGGGTTTGGATCGGAAGAACAAAAGGCACTAGTTCCAGAAGCGGCTTTGAGATGATTTGGGACCCGAATGGGTGGACTGAGACGGACAGTAGTTTCTCAGTGAAGCAAGACATTGTAGAAATAACTGACTGGTCAGGATATAGTGGGAGTTTTGTCCAGCATCCAGAACTGACAGGATTAGATTGCATGAGGCCTTGTTTCTGGGTTGAGCTAATTAGAGGGAGGCCCAAAGAGAACACAATTTGGACTAGCGGGAGCAGCATATCCTTTTGTGGTGTAAATAGTGACACTGTGGGTTGGTCTTGGCCAGACGGTGCTGAGTTGCCATTCACCATTGACAAGTAG</t>
         </is>
       </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
+      <c r="BW1" t="inlineStr">
         <is>
           <t>&gt;Flu-0316|A_MP</t>
         </is>
       </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
+      <c r="BX1" t="inlineStr">
         <is>
           <t>ATGAGTCTTCTAACCGAGGTCGAAACGTACGTTCTCTCTATCGTCCCGTCGGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTTGAAGATGTCTTTGCAGGGAAGAACACCGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATACTGTCACCTCTGACTAAGGGGATTTTGGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCTCTAAGTGGAAATGGAGACCCAAACAACATGGACAGGGCAGTCAAGTTGTACAGGAAACTGAAGAGAGAAATAACATTCCATGGGGCTAAAGAAGTTGCACTTAGTTACTCAACCGGTGCACTTGCCAGTTGTATGGGTCTCATATACAACAGGATGGGGACGGTGACCGCAGAAGTGGCATTGGGCCTAGTGTGTGCCACCTGTGAGCAGATTGCTGATTCACAGCATCGGTCTCACAGACAGATAGCTACCACCACCAACCCACTAATCAGACATGAAAACAGAATGGTTTTGGCCAGTACTACAGCTAAGGCTATGGAGCAGATGGCTGGATCGAGTGAGCAAGCAGTGGAAGCCATGGAGGTTGCTAGTCAGGCTAGGCAAATGGTGCAGGCGATGAGGACCATTGGAACTCATCCTAGCTCCAGTGCCGGTCTGAGAGATGATCTCCTTGAAAATTTGCAGGCCTACCAAAAACGAATGGGAGTGCAACTGCAGCGATTCAAGTGATCCTCTCGTTATTGCAGCAAGTATCATTGGGATCTTGCACTTGATATTGTGGATTCTTGATCGCCTTTTCTTCAAATGCGTTTATCGTCGCCTTAAATACGGTTTGAAAGGAGGGCCTTCTACGGAAGGAGTACCTGAGTCCATGAGGGAAGAGTACCGGCAGGAACAGCAGAGTGCTGTGGATGTTGACGATGGTCATTTTGTCAACATAGAGATGGAGTAA</t>
         </is>
       </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
+      <c r="BY1" t="inlineStr">
         <is>
           <t>&gt;Flu-0316|A_NS</t>
         </is>
       </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
+      <c r="BZ1" t="inlineStr">
         <is>
           <t>ATGGATTCCAACACTGTGTCAAGCTTTCAGGTAGACTGCTTTCTTTGGCATGTCCGCAAACAATTTGCAGACCAAGAACTGGGTGATGCCCCATTCCTTGACCGGCTCCGCCGAGACCAGAAGTCTCTAAGAGGAAGAGGCAGCACTCTTGGTCTGGACATCGAGACGGCCACTCGTGCTGGAAAGCAGATAGTGGAGAGGATTCTGGAGGAAGAATCCGACGAGGCACTCAAAATGACTATTGCCTCTGTGCCTGCTCCACGCTACCTAACTGACATGACTCTTGAAGAGATGTCAAGAGACTGGTTCATGCTCATGCCCAAGCAAAAAGTGGCAGGCTCCCTCTGTATCAGAATGGACCAGGCGATTATGGATAAGAACATCATACTGAAGGCAAACTTCAGTGTGATCTTCAATCGGCTGGAGACACTAATACTACTCAGAGCTTTCACTGAAGAGGGAGCAATTGTCGGCGAAATTTCACCATTGCCTTCTCTTCCAGGACATACTGATGAGGATGTCAAAAATGCAATTGGGGTCCTCATCGGAGGACTTGAATGGAATGATAACACAGTTCGAGTCTCTGAAATTTTACAGAGATTCGCTTGGAGAAGCAGTAATGAGGATGGGAGACCTCCACTCCCTCCAAAGCAGAAACGGAAAATGGAGAGAACAATTGAGTCAGAAGTTTGAAGAAATAAGGTGGCTGATTGAAGAGGTGCGACACAGACTAAAGATCACAGAAAATAGTTTTGAACAAATAACATTTATGCAAGCCTTACAACTACTGCTTGAAGTGGAGCAAGAGATACGAACTTTCTCGTTTCAGCTTATTTAA</t>
         </is>
       </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
+      <c r="CA1" t="inlineStr">
         <is>
           <t>&gt;Flu-0317|A_PB2</t>
         </is>
       </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
+      <c r="CB1" t="inlineStr">
         <is>
           <t>ATGGAGAGAATAAAAGAACTAAGAGATCTAATGTCACAGTCTCGCACTCGCGAGATACTGACCAAAACCACTGTTGACCACATGGCCATAATCAAAAAGTACACATCGGGAAGGCAAGAGAAGAACCCCGCACTCAGAATGAAATGGATGATGGCAATGAAATATCCAATTACAGCAGATAAGCGAATAATGGAAATGATCCCTGAGAGGAATGAACAAGGGCAAACTCTCTGGAGCAAAACAAACGATGCCGGATCAGACCGAGTGATGGTATCACCCCTGGCTGTGACATGGTGGAACAGGAACGGACCAACAACAAGTACAGTTCACTACCCAAAGGTATATAAAACTTATTTCGAAAAAGTTAAAAGGTTGAAACACGGGACCTTTGGCCCTGTGCACTTCAGAAACCAAGTTAAGATAAGACGGAGGGTCGATATAAACCCGGGCCATGCTGACCTTAGTGCCAAAGAGGCACAGGATGTAATCATGGAAGTCGTCTTCCCAAATGAAGTGGGAGCTAGGATATTGACGTCGGAGTCACAACTGACGATAACAAAGGAGAAAAAGGAAGAACTCCAGGACTGCAAAATCGCTCCTCTGATGGTTGCATACATGCTAGAACGAGAGTTGGTTCGCAAGACGAGGTTTCTCCCAGTTGCTGGTGGGACAAGCAGTGTCTACATTGAGGTGCTGCATTTGACCCAGGGGACATGCTGGGAGCAGATGTACACTCCGGGAGGAGAAGTGAGGAACGATGATGTAGACCAAAGCTTGATCATTGCTGCCAGGAATATAGTAAGAAGAGCAACAGTATCAGCAGATCCGTTAGCATCTCTATTGGAGATGTGTCACAGCACACAAATTGGGGGAATAAGGATGGTAGACATCCTTCGGCAAAACCCAACAGAGGAACAAGCCGTGGATATATGCAAGGCAGCAATGGGCTTGAGGATTAGCTCATCTTTCAGCTTTGGTGGATTCACTTTTAAAAGAACAAGTGGATCGTCAGTCAAAAAAGAAGAAGAAGTGCTAACAGGCAACCTTCAAACATTGAAAATAAGAGTACATGAGGGGTATGAAGAGTTCACAATGGTTGGGAGAAGAGCAACGGCCATTCTCAGGAAAGCAACCAGAAGGCTGATCCAGCTAATAGTAAGTGGGAGAGACGAGCAGTCAATTGCTGAAGCAATAATTGTGGCCATGGTATTCTCACAAGAGGACTGCATGATTAAAGCAGTTAGAGGTGACCTGAATTTTGTCAATAGGGCGAACCAGCGACTAAACCCAATGCATCAACTCTTGAGGCATTTCCAAAAGGATGCAAAAGTGCTTTTCCAAAATTGGGGAATTGAACCCATTGACAATGTGATGGGAATGATCGGGGTAATGCCTGACATGACCCCAAGTACTGAGATGTCGCTGAGGGGAATAAGAGTCAGCAAGATGGGAGTAGATGAATACTCAAGCACAGAGCGAGTAGTAGTAAGCATCGACCGGTTTTTAAGAGTTCGAGACCAACGGGGGAACGTACTATTATCACCCGAAGAGGTCAGTGAGACACAAGGAACGGAGAAACTGACAATCACTTATTCGTCATCAATGATGTGGGAGATCAATGGTCCTGAGTCGGTGTTGGTCAATACTTATCAGTGGATAATTAGAAACTGGGAAACTGTAAAAATTCAATGGTCACAGGATCCCACAATGCTGTATAATAAGATGGAATTCGAGCCATTCCAGTCTCTAGTCCCTAAGGCAGCCAGAGGTCAATACAGTGGGTTTGTGAGAACACTATTCCAGCAAATGCGAGATGTGCTTGGAACATTTGACACTGTTCAGATAGTAAAACTCCTCCCCTTTGCTGCCGCCCCACCGGAACAAAGTAGGATGCAGTTCTCCTCCCTGACTGTGAATGTAAGAGGATCAGGAATGAGGATACTGGTAAGAGGCAATTCACCAGTGTTCAATTACAACAAGGCCACCAAGAGGCTCACAGTTCTCGGGAAAGATGCAGGTGCATTGACCGAAGATCCAGATGAAGGCACAGCTGGAGTGGAGTCTGCTGTTTTAAGAGGATTCCTCATTTTGGGCAAAGAAGACAAGAGATATGGCCCAGCATTGAGCATCAATGAGCTGAGCAATCTTGCAAAGGGAGAGAAGGCTAATGTGCTAATTGGGCAAGGAGACGTAGTGTTGGTGATGAAACGGAAACGGGACTCTAGCATACTTACTGACAGCCAGACAGCGACCAAAAGAATTCGGATGGCCATCAATTAG</t>
         </is>
       </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
+      <c r="CC1" t="inlineStr">
         <is>
           <t>&gt;Flu-0317|A_PB1</t>
         </is>
       </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
+      <c r="CD1" t="inlineStr">
         <is>
           <t>ATGGATGTCAATCCGACTTTACTTTTCTTGAAAGTTCCAGCGCAAAATGCCATAAGCACCACATTCCCGTATACTGGAGATCCTCCATACAGCCATGGAACAGGAACAGGATATACCATGGACACAGTTAACAGAACACATCAGTATTCAGAAAAAGGGAAATGGACAACAAACTCAGAAACTGGAGCACCTCAACTCAATCCAATTGATGGACCATTGCCTGAGGGCAATGAACCAAGTGGGTATGCACAAACGGACTGTGTCCTTGAAGCAATGGCTTTCCTTGAAGAGTCCCACCCAGGAATCTTTGAAAACTCGTGTCTTGAAACGATGGAAGTTGTTCAACAAACAAGAGTGGACAAGTTGACCCAAGGCCGTCAGACCTATGATTGGACGTTAAACAGGAATCAGCCGGCTGCAACTGCATTAGCTAATACTATAGAGGTCTTCAGATCTAACGGCCTCACAGCCAATGAATCAGGAAGGCTAATAGATTTTCTCAAGGATGTGATGGAATCAATGGATAAGGAGGAAATGGAAATAACAACGCATTTCCAAAGGAAAAGAAGAGTGAGAGACAACATGACCAAGAAAATGGTCACACAAAGGACAATAGGAAAGAAGAAACAGAGGCTAAATAAAAAGAGCTATCTAATAAGAGCATTGACACTGAACACGATGACAAAAGACGCCGAAAGAGGCAAATTAAAAAGAAGGGCAATTGCAACACCTGGAATGCAAATCAGAGGGTTTGTGTACTTTGTTGAGACATTAGCGAGGAGCATTTGTGATAAGCTTGAACAATCTGGACTCCCAGTTGGGGGCAATGAAAAGAAGGCTAAACTGGCAAATGTTGTGAGAAAAATGATGACTAATTCGCAGGACACAGAGCTCTCTTTCACAATCACTGGAGACAACACCAAATGGAATGAAAATCAGAACCCTAGGATGTTTCTGGCAATGATAACATATATAACAAGGAACCAACCTGAATGGTTCAGGAATGTCTTAAGCATTGCACCTATAATGTTCTCAAATAAAATGGCAAGACTAGGGAAAGGGTACATGTTCGAAAGTAAGAGCATGAAGCTCCGAACACAAATACCAGCAGAAATGCTAGCAAGCATTGATCTGAAGTACTTCAATGAGTCAACAAGAAAGAAAATAGAGAAGATAAGACCTCTTCTAATAGATGGTACAGCCTCATTAAGCCCAGGAATGATGATGGGCATGTTCAATATGCTGAGTACAGTTTTGGGAGTTTCGATTCTAAATCTAGGACAAAGGAGGTACACCAAAACAACATACTGGTGGGACGGACTCCAATCCTCTGATGACTTTGCTCTCATAGTGAATGCTCCGAATCATGAGGGAATACAAGCAGGGGTAGACAGATTCTATAGAACCTGCAAGCTGGTCGGAATCAACATGAGCAAAAAGAAGTCCTACATAAACAGGACAGGAACATTTGAATTCACAAGTTTTTTCTACCGCTATGGATTTGTAGCCAACTTCAGTATGGAGTTGCCCAGCTTTGGAGTGTCTGGGATCAATGAATCTGCAGACATGAGCATTGGAGTAACAGTAATAAAGAACAACATGATCAACAATGATCTTGGACCAGCAACAGCTCAAATGGCTCTTCAGCTATTCATCAAGGATTACAGATACACATACCGGTGTCACAGAGGAGACACACAAATTCAGACAAGGAGGTCATTCGAGCTGAAGAAGTTGTGGGAACAGACCCGTTCAAAAGCAGGACTGCTGGTCTCAGATGGAGGACCAAATCTATACAATATTCGGAATCTTCACATTCCAGAAGTCTGCTTGAAATGGGAGCTAATGGACGAAGACTATCAGGGAAGGCTTTGTAATCCCCTGAACCCGTTTGTCAGCCACAAGGAAATAGAGTCTGTGAACAACGCAGTGGTGATGCCAGCTCATGGCCCGGCCAAGAGCATGGAATATGATGCTGTTGCCACCACTCACTCCTGGATACCGAAGAGGAACCGCTCCATTCTCAATACAAGCCAAAGGGGAATCCTTGAAGACGAACAGATGTATCAAAAGTGCTGCAACCTGTTCGAAAAATTCTTCCCTAGCAGTTCATACAGGAGGCCAGTTGGAATTTCCAGCATGGTGGAGGCCATGGTTTCTAGGGCCCGAATTGACGCACGAATTGACTTCGAATCTGGACGGATTAAGAAGGAGGAGTTTGCTAAGATCATGAAGATCTGTTCCACCATTGAAGAGCTCAGACGGCAGAAATAG</t>
         </is>
       </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
+      <c r="CE1" t="inlineStr">
         <is>
           <t>&gt;Flu-0317|A_PA</t>
         </is>
       </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
+      <c r="CF1" t="inlineStr">
         <is>
           <t>ATGGAAGACTTTGTGCGACAATGCTTCAATCCAATGATTGTCGAGCTTGCGGAAAAAGCAATGAAAGAATATGGGGAAGATCCGAAAATCGAGACAAACAAATTTGCCGCAATATGCACACACTTAGAAGTCTGTTTCATGTATTCGGATTTCCATTTTATTAATGAACGAGGCGAATCAATGATTGTAGAATCTGGCGATCCAAATGCATTATTGAAACACCGATTTGAGATAATAGAAGGGAGAGACCGGGCAATGGCCTGGACAGTGGTGAATAGTATCTGCAACACCACAGGGGTCGAAAAGCCCAAATTCCTCCCTGATTTGTATGACTACAAAGAGAACCGATTCATTGAAATTGGAGTAACGCGAAGGGAAGTTCACATATACTATTTAGAAAAAGCCAACAAGATAAAGTCAGAGAAAACACATATTCACATATTCTCATTCACTGGAGAGGAAATGGCCACCAAGGCGGACTACACCCTTGATGAAGAGAGCAGAGCAAGAATAAAAACCAGACTGTTCACTATAAGACAAGAAATGGCCAGTAGAGGTCTATGGGATTCCTTTCGTCAATCCGAGAGAGGCGAAGAGACAATTGAAGAAAGATTTGAAATCGCAGGAACCATGCGCAGGCTTGCCAACCAAAGTCTTCCACCGAACTTCTCCAGCCTTGAAAACTTTAGAGCCTATGTGGATGGATTCGAACCGAACGGCTGCATTGAGGGCAAACTTTCTCAAATGTCAAAAGAAGTGAACGCCAGGATTGAGCCATTTCTGAAGACAACACCACGCCCTCTCAGATTACCTGATGGGCCTCCCTGTTCTCAGCGGTCGAAGTTCTTGCTGATGGATGCCCTTAAGTTGAGCATCGAAGACCCTAGCCATGAGGGGGAGGGCATACCGCTGTATGATGCAATCAAATGCATGAAGACATTTTTTGGCTGGAAAGAGCCCAACATCGTAAAGCCGCATGAGAAAGGCATAAACCCTAATTACCTCCTGACTTGGAAGCAGGTGCTGGCAGAACTTCAAGACATTGAAAATGAGGAGAAAATTCCAAAGACAAAGAACATGAAGAAAACAAGCCAATTGAAGTGGGCACTTGGTGAGAACATGGCTCCAGAGAAAGTGGACTTTGAGGACTGCAAAGATGTTAGCGATCTAAGACAGTACGACAGTAACGAACCAGAGTCTAGAACACTAGCAAGCTGGATTCAGAGTGAATTCAACAAGGCATGCGAACTGACAGATTCGAGTTGGATTGAACTTGATGAGATAGGGGAAGACGTTGCTCCAATCGAACACATTGCGAGTGTGAGGAGGAACTATTTCACAGCGGAGGTATCCCATTGCAGGGCCACTGAATACATAATGAAGGGAGTATACATAAACACAGCCCTATTGAATGCATCCTGTGCAGCCATGGATGACTTCCAATTGATTCCAATGATAAGTAAGTGCAGAACTAAAGAAGGAAGACGGAAGACAAATCTGTATGGATTCATTATAAAAGGAAGATCCCATTTGAGGAATGACACCGATGTGGTAAACTTTGTGAGCATGGAATTCTCTCTAACTGACCCGAGGCTGGAGCCACACAAATGGGAGAAGTACTGTGTTCTTGAGATAGGAGACATGCTCCTACGGACTGCAATAGGCCAAGTGTCGAGGCCCATGTTCCTGTATGTGAGAACCAATGGGACTTCCAAGATCAAAATGAAATGGGGCATGGAGATGAGGCGATGCCTTCTTCAGTCCCTTCAACAAATTGAGAGCATGATTGAGGCCGAATCTTCTGTCAAAGAGAAGGACATGTCCAAGGAATTCTTTGAAAACAAATCAGAAACATGGCCAATTGGAGAATCACCCAAAGGGGTGGAGGAAGGCTCTATTGGGAAAGTATGCAGAACATTGCTAGCAAAGTCTGTGTTCAACAGCCTATATGCATCTCCACAACTCGAGGGGTTTTCAGCTGAATCAAGAAAATTGCTTCTCATTGTTCAGGCACTTAGGGACAACCTGGAACCTGGAACCTTCGATCTTGGGGGGCTATATGAAGCAATTGAGGAGTGCCTGATTAACGATCCCTGGGTTTTGCTTAATGCATCTTGGTTCAACTCCTTCCTCACACATGCACTGAAATAG</t>
         </is>
       </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
+      <c r="CG1" t="inlineStr">
         <is>
           <t>&gt;Flu-0317|A_HA</t>
         </is>
       </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
+      <c r="CH1" t="inlineStr">
         <is>
           <t>ATGGAGAACATAGTACTACTTCTTGCAATAGTTAGCCTTGTTAAAAGTGACCAGATTTGCATTGGTTACCATGCAAACAATTCGACAGAGCAAGTTGACACGATAATGGAAAAGAACGTCACTGTTACACATGCCCAAGACATACTGGAAAAAACACACAACGGGAAGCTCTGTGATTTAAATGGGGTGAAGCCACTGATTTTAAAGGATTGTAGTGTAGCTGGATGGCTCCTCGGGAACCCAATGTGCGACGAATTCATCAGAGTGCCGGAATGGTCCTACATAGTGGAGCGAGCTAACCCAGCTAATGACCTCTGTTACCCAGGGAGCCTCAATGACTATGAAGAACTGAAACACATGTTGAGCAGAATAAATCATTTTGAGAAGATTCAGATCATTCCCAAGAGTTCCTGGCCAAATCATGAAACATCACTAGGGGTGAGCGCAGCTTGTCCATACCAGGGAGCGCCCTCCTTTTTCAGAAATGTGGTGTGGCTTATCAAAAAGAACGATGCATACCCAACAATAAAGATAAGCTACAATAATACTAATCGGGAAGATCTCTTGATACTGTGGGGGATTCATCATCCCAACAATGCAGAAGAGCAGACAAATCTCTACAAAAACCCAACCACCTACATTTCAGTTGGAACATCAACTTTAAACCAGAGATTGGCACCAAAAATAGCTACTAGATCCCAAGTAAACGGGCAACGTGGAAGAATGGACTTCTTTTGGACAATCTTAAAACCAGATGATGCAATCCATTTCGAGAGTAACGGAAATTTCATTGCTCCAGAATATGCATACAAAATTGTCAAGAAAGGGGACTCAACAATTATGAAAAGTGGAGTGGAATATGGCCACTGCAACACCAAATGTCAAACCCCAGTAGGTGCTATAAATTCTAGTATGCCATTCCACAACATACATCCTCTCACCATTGGGGAATGCCCCAAATACGTGAAATCAAACAAGTTGGTCCTTGCGACTGGGCTCAGAAATAGTCCTCTAAGAGAAAAGAGAAGAAAAAGAGGTCTGTTTGGGGCGATAGCAGGGTTTATAGAGGGAGGATGGCAGGGAATGGTTGATGGTTGGTATGGGTACCATCATAGCAATGAGCAGGGGAGTGGGTACGCTGCGGACAAAGAATCCACCCAAAAGGCAATAGATGGAGTTACCAATAAGGTCAACTCAATCATTGACAAAATGAACACTCAATTTGAGGCAGTTGGAAGGGAGTTTAATAACTTAGAAAGGAGGATAGAGAATTTGAACAAGAAAATGGAAGACGGATTCCTAGATGTCTGGACCTATAATGCTGAACTTCTAGTTCTTATGGAAAACGAGAGGACTCTAGATTTCCATGATTCAAATGTCAAGAACCTTTACGACAAAGTCAGATTACAGCTTAGGGATAATGCAAAGGAGCTGGGTAACGGCTGTTTCGAATTCTATCACAAATGTGATAATGAATGTATGGAAAGTGTGAGAAATGGGACGTATGACTACCCTCAGTATTCAGAAGAAGCAAGATTAAAAAGAGAAGAAATAAGCGGAGTGAAATTAGAATCAGTAGGAACTTACCAGATACTGTCAATTTATTCAACAGCGGCAAGTTCCCTAGCACTGGCAATCATGATGGCTGGTCTATCTTTATGGATGTGCTCCAATGGGTCGTTACAATGCAGAATTTGCATTTAG</t>
         </is>
       </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
+      <c r="CI1" t="inlineStr">
         <is>
           <t>&gt;Flu-0317|A_NP</t>
         </is>
       </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
+      <c r="CJ1" t="inlineStr">
         <is>
           <t>ATGGCGTCTCAAGGCACCAAACGATCCTATGAACAAATGGAAACTGGTGGGGAACGCCAGAATGCCACTGAAATCAGAGCATCTGTTGGAAGAATGGTTGGCGGAATAGGAAGATTCTACATACAGATGTGCACTGAGCTCAAACTCAGTGATTATGAAGGGAGGCTGATCCAAAACAGCATAACCATAGAAAGGATGGTTCTCTCGGCATTTGATGAGAGGAGGAACAAGTACCTGGAGGAACATCCCAGTGCCGGGAAGGATCCCAAGAAGACTGGAGGTCCAATCTACAGGAGGAGAGATGGCAAATGGGTGAGAGAGTTGATCCTCTACGACAAAGAAGAGATCAGAAGAATTTGGCGTCAAGCTAATAATGGAGAGGATGCAACTGCTGGTCTCACTCATTTGATGATTTGGCATTCCAATCTGAATGATGCAACATACCAGAGAACAAGGGCACTTGTGCGTACTGGAATGGACCCTAGAATGTGCTCTCTGATGCAAGGATCAACCCTCCCTAGGAGATCCGGGGCTGCTGGAGCAGCAGTGAAAGGAGTTGGAACAATGGTGATGGAACTAATTCGAATGATCAAGCGAGGGATCAATGATCGGAATTTCTGGAGAGGCGAAAACGGTCGGAGAACCAGGATTGCCTACGAGAGAATGTGCAACATCCTCAAGGGAAAGTTCCAAACAGCAGCACAACGGGCAATGATGGACCAAGTGAGAGAAAGCCGGAATCCTGGGAATGCTGAAATTGAAGATCTCATCTTTCTCGCACGATCTGCTCTCATCCTGAGGGGATCAGTGGCTCATAAGTCCTGTCTGCCTGCTTGCGTATATGGACTTGCTGTAGCCAGTGGATATGACTTTGAAAGAGAGGGATATTCTCTAGTCGGAATTGATCCTTTCCGTCTGCTCCAAAACAGCCAAGTCTTCAGTCTCATCAGACCGAACGAAAATCCAGCTCATAAGAGTCAGCTGGTATGGATGGCATGCCACTCTGCGGCATTTGAGGATCTGAGAGTTTCAAGCTTCATCAGAGGGACAAGAGTAGTCCCAAGAGGACAACTGTCCACCAGAGGAGTTCAGATTGCTTCAAATGAAAACATGGAGACAATGGACTCCAGTACTCTTGAACTGAGGAGCAGATACTGGGCTATAAGAACAAGAAGTGGAGGAAACACTAACCAACAGAGAGCATCTGCAGGACAAATCAGCGTGCAGCCCACATTCTCTGTGCAAAGAAACCTCCCATTCGAGAGAGCAACCATCATGGCAGCATTTACGGGAAACACTGAAGGCAGAACTTCAGACATGAGAACGGAGATCATAAGGATGATGGAAAATGCCAGACCTGAAGATGTGTCTTTCCAGGGGCGGGGAGTCTTCGAGCTCTCGGACGAAAAGGCAACGAACCCGATCGTGCCTTCCTTTGACATGAGTAATGAAGGATCTTATTTCTTCGGAGACAATGCAGAGGAGTATGACAATTAA</t>
         </is>
       </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
+      <c r="CK1" t="inlineStr">
         <is>
           <t>&gt;Flu-0317|A_NA</t>
         </is>
       </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
+      <c r="CL1" t="inlineStr">
         <is>
           <t>ATGAATCCAAATCAAAAGATAACAACCATTGGATCAATCTGTATGGTAATTGGGACAGTCAGCTTGATGCTGCAAATTGGGAACATAATCTCAATATGGGTTAGCCATTCAATCCAAACAGGGAATCAATACCAGCCTGAACCATGCAATCAAAGCATCATTACCTATGAGAACAACACCTGGGTAAATCAGACGTATGTCAACATCAGCAATAACAATTTTCTTGCTGAGCAGGCTGTTACTTCGGTAACATTAGCGGGCAATTCATCTCTTTGCCCTATTAGTGGGTGGGCAATATACAGTAAGGACAACGGTATAAGAATTGGGTCCAAGGGGGATGTGTTTGTCATAAGAGAACCGTTCATCTCATGCTCCCACTTGGAATGCAGAACCTTTTTCCTGACTCAGGGAGCTCTGCTGAATGACAAACATTCTAATGGGACAGTTAAGGATAGAAGCCCTTATAGAACTTTGATGAGTTGTCCCGTGGGTGAGGCTCCTTCCCCGTACAATTCAAGATTTGAGTCTGTTGCTTGGTCGGCAAGTGCTTGTCATGATGGCATCAGTTGGTTGACAATCGGTATTTCTGGTCCAGACAATGGAGCTGTGGCTGTATTGAAGTACAATGGCATAATAACGGATACTATCAAGAGTTGGAGAAACAACATTTTGAGAACTCAAGAATCTGAATGTGCTTGCGTAAATGGCTCTTGCTTCACCGTAATGACTGATGGACCAAGCAATGGGCAGGCCTCGTATAAAATCTTCAAGATAGAGAAAGGGAAAGTTGTCAAATCAGTTGAATTGAATGCCCCTAATTACCACTACGAGGAATGTTCCTGTTATCCTGATGCGGGTGATATTATATGTGTGTGCAGGGACAATTGGCACGGCTCAAACCGGCCGTGGATATCTTTTAATCAAAATCTGGAGTATCAAATAGGATATATATGCAGTGGGGTTTTCGGGGACAATCCCCGCCCCAATGATGGAACAGGCAGTTGCAGTCCAATGTCCTCTAATGGGGCATATGGGGTAAAAGGGTTTTCATTTAAGTACGGTAATGGGGTTTGGATCGGAAGAACAAAAGGCACTAGTTCCAGAAGCGGCTTTGAGATGATTTGGGACCCGAATGGGTGGACTGAGACGGACAGTAGTTTCTCAGTGAAGCAAGACATTGTAGAAATAACTGACTGGTCAGGATATAGTGGGAGTTTTGTCCAGCATCCAGAACTGACAGGATTAGATTGCATGAGGCCTTGTTTCTGGGTTGAGCTAATTAGAGGGAGGCCCAAAGAGAACACAATTTGGACTAGCGGGAGCAGCATATCCTTTTGTGGTGTAAATAGTGACACTGTGGGTTGGTCTTGGCCAGACGGTGCTGAGTTGCCATTCACCATTGACAAGTAG</t>
         </is>
       </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
+      <c r="CM1" t="inlineStr">
         <is>
           <t>&gt;Flu-0317|A_MP</t>
         </is>
       </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
+      <c r="CN1" t="inlineStr">
         <is>
           <t>ATGAGTCTTCTAACCGAGGTCGAAACGTACGTTCTCTCTATCGTCCCGTCGGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTTGAAGATGTCTTTGCAGGGAAGAACACCGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATACTGTCACCTCTGACTAAGGGGATTTTGGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCTCTAAGTGGAAATGGAGACCCAAACAACATGGACAGGGCAGTCAAGTTGTACAGGAAACTGAAGAGAGAAATAACATTCCATGGGGCTAAAGAAGTTGCACTTAGTTACTCAACCGGTGCACTTGCCAGTTGTATGGGTCTCATATACAACAGGATGGGGACGGTGACCGCAGAAGTGGCATTGGGCCTAGTGTGTGCCACCTGTGAGCAGATTGCTGATTCACAGCATCGGTCTCACAGACAGATAGCTACCACCACCAACCCACTAATCAGACATGAAAACAGAATGGTTTTGGCCAGTACTACAGCTAAGGCTATGGAGCAGATGGCTGGATCGAGTGAGCAAGCAGTGGAAGCCATGGAGGTTGCTAGTCAGGCTAGGCAAATGGTGCAGGCGATGAGGACCATTGGAACTCATCCTAGCTCCAGTGCCGGTCTGAGAGATGATCTCCTTGAAAATTTGCAGGCCTACCAAAAACGAATGGGAGTGCAACTGCAGCGATTCAAGTGATCCTCTCGTTATTGCAGCAAGTATCATTGGGATCTTGCACTTGATATTGTGGATTCTTGATCGCCTTTTCTTCAAATGCGTTTATCGTCGCCTTAAATACGGTTTGAAAGGAGGGCCTTCTACGGAAGGAGTACCTGAGTCCATGAGGGAAGAGTACCGGCAGGAACAGCAGAGTGCTGTGGATGTTGACGATGGTCATTTTGTCAACATAGAGATGGAGTAA</t>
         </is>
       </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
+      <c r="CO1" t="inlineStr">
         <is>
           <t>&gt;Flu-0317|A_NS</t>
         </is>
       </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
+      <c r="CP1" t="inlineStr">
         <is>
           <t>ATGGATTCCAACACTGTGTCAAGCTTTCAGGTAGACTGCTTTCTTTGGCATGTCCGCAAACAATTTGCAGACCAAGAACTGGGTGATGCCCCATTCCTTGACCGGCTCCGCCGAGACCAGAAGTCTCTAAGAGGAAGAGGCAGCACTCTTGGTCTGGACATCGAGACGGCCACTCGTGCTGGAAAGCAGATAGTGGAGAGGATTCTGGAGGAAGAATCCGACGAGGCACTCAAAATGACTATTGCCTCTGTGCCTGCTCCACGCTACCTAACTGACATGACTCTTGAAGAGATGTCAAGAGACTGGTTCATGCTCATGCCCAAGCAAAAAGTGGCAGGCTCCCTCTGTATCAGAATGGACCAGGCGATTATGGATAAGAACATCATACTGAAGGCAAACTTCAGTGTGATCTTCAATCGGCTGGAGACACTAATACTACTCAGAGCTTTCACTGAAGAGGGAGCAATTGTCGGCGAAATTTCACCATTGCCTTCTCTTCCAGGACATACTGATGAGGATGTCAAAAATGCAATTGGGGTCCTCATCGGAGGACTTGAATGGAATGATAACACAGTTCGAGTCTCTGAAATTTTACAGAGATTCGCTTGGAGAAGCAGTAATGAGGATGGGAGACCTCCACTCCCTCCAAAGCAGAAACGGAAAATGGAGAGAACAATTGAGTCAGAAGTTTGAAGAAATAAGGTGGCTGATTGAAGAGGTGCGACACAGACTAAAGATCACAGAAAATAGTTTTGAACAAATAACATTTATGCAAGCCTTACAACTACTGCTTGAAGTGGAGCAAGAGATACGAACTTTCTCGTTTCAGCTTATTTAA</t>
         </is>
       </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
+      <c r="CQ1" t="inlineStr">
         <is>
           <t>&gt;Flu-0318|A_PB2</t>
         </is>
       </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
+      <c r="CR1" t="inlineStr">
         <is>
           <t>ATGGAGAGAATAAAAGAACTAAGAGATCTAATGTCACAGTCTCGCACTCGCGAGATACTGACCAAAACCACTGTTGACCACATGGCCATAATCAAAAAGTACACATCGGGAAGGCAAGAGAAGAACCCCGCACTCAGAATGAAATGGATGATGGCAATGAAATATCCAATTACAGCAGATAAGCGAATAATGGAAATGATCCCTGAGAGGAATGAACAAGGGCAAACTCTCTGGAGCAAAACAAACGATGCCGGATCAGACCGAGTGATGGTATCACCCCTGGCTGTGACATGGTGGAACAGGAACGGACCAACAACAAGTACAGTTCACTACCCAAAGGTATATAAAACTTATTTCGAAAAAGTTAAAAGGTTGAAACACGGGACCTTTGGCCCTGTGCACTTCAGAAACCAAGTTAAGATAAGACGGAGGGTCGATATAAACCCGGGCCATGCTGACCTTAGTGCCAAAGAGGCACAGGATGTAATCATGGAAGTCGTCTTCCCAAATGAAGTGGGAGCTAGGATATTGACGTCGGAGTCACAACTGACGATAACAAATGAGAAAAAGGAAGAACTCCAGGACTGCAAAATCGCTCCTCTGATGGTTGCATACATGCTAGAACGAGAGTTGGTTCGCAAGACGAGGTTTCTCCCAGTTGCTGGTGGGACAAGCAGTGTCTACATTGAGGTGCTGCATTTGACCCAGGGGACATGCTGGGAGCAGATGTACACTCCGGGAGGAGAAGTGAGGAACGATGATGTAGACCAAAGCTTGATCATTGCTGCCAGGAATATAGTAAGAAGAGCAACAGTATCAGCAGATCCGTTAGCATCTCTATTGGAGATGTGTCACAGCACACAAATTGGGGGAATAAGGATGGTAGACATCCTTCGGCAAAACCCAACAGAGGAACAAGCCGTGGATATATGCAAGGCAGCAATGGGCTTGAGGATTAGTTCATCTTTCAGCTTTGGTGGATTCACTTTTAAAAGAACAAGTGGATCGTCAGTCAAAAAAGAAGAAGAAGTGCTAACAGGCAACCTTCAAACATTGAAAATAAGAGTACATGAGGGGTATGAAGAGTTCACAATGGTTGGGAGAAGAGCAACGGCCATTCTCAGGAAAGCAACCAGAAGGCTGATCCAGCTAATAGTAAGTGGGAGAGACGAGCAGTCAATTGCTGAAGCAATAATTGTGGCCATGGTATTCTCACAAGAGGACTGCATGATTAAAGCAGTTAGAGGTGACCTGAATTTTGTCAATAGGGCGAACCAGCGACTAAACCCAATGCATCAACTCTTGAGGCATTTCCAAAAGGATGCAAAAGTGCTTTTCCAAAATTGGGGAATTGAACCCATTGACAATGTGATGGGAATGATCGGGGTAATGCCTGACATGACCCCAAGTACTGAGATGTCGCTGAGGGGAATAAGAGTCAGCAAGATGGGAGTAGATGAATACTCAAGCACAGAGCGAGTAGTAGTAAGCATCGACCGGTTTTTAAGAGTTCGAGACCAACGGGGGAACGTACTATTATCACCCGAAGAGGTCAGTGAGACACAAGGAACGGAGAAACTGACAATCACTTATTCGTCATCAATGATGTGGGAGATCAATGGTCCTGAGTCGGTGTTGGTCAATACTTATCAGTGGATAATTAGAAACTGGGAAACTGTAAAAATTCAATGGTCACAGGATCCCACAATGCTGTATAATAAGATGGAATTCGAGCCATTCCAGTCTCTAGTCCCTAAGGCAGCCAGAGGTCAATACAGTGGGTTTGTGAGAACACTATTCCAGCAAATGCGAGATGTGCTTGGAACATTTGACACTGTTCAGATAGTAAAACTCCTCCCCTTTGCTGCCGCCCCACCGGAACAAAGTAGGATGCAGTTCTCCTCCCTGACTGTGAATGTAAGAGGATCAGGAATGAGGATACTGGTAAGAGGCAATTCACCAGTGTTCAATTACAACAAGGCCACCAAGAGGCTCACAGTTCTCGGGAAAGATGCAGGTGCATTGACCGAAGATCCAGATGAAGGCACAGCTGGAGTGGAGTCTGCTGTTTTAAGAGGATTCCTCATTTTGGGCAAAGAAGACAAGAGATATGGCCCAGCATTGAGCATCAATGAGCTGAGCAATCTTGCAAAGGGAGAGAAGGCTAATGTGCTAATTGGGCAAGGAGACGTAGTGTTGGTGATGAAACGGAAACGGGACTCTAGCATACTTACTGACAGCCAGACAGCGACCAAAAGAATTCGGATGGCCATCAATTAG</t>
         </is>
       </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
+      <c r="CS1" t="inlineStr">
         <is>
           <t>&gt;Flu-0318|A_PB1</t>
         </is>
       </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
+      <c r="CT1" t="inlineStr">
         <is>
           <t>ATGGATGTCAATCCGACTTTACTTTTCTTGAAAGTTCCAGCGCAAAATGCCATAAGCACCACATTCCCGTATACTGGAGATCCTCCATACAGCCATGGAACAGGAACAGGATATACCATGGACACAGTTAACAGAACACATCAGTATTCAGAAAAAGGGAAATGGACAACAAACTCAGAAACTGGAGCACCTCAACTCAATCCAATTGATGGACCATTGCCTGAGGGCAATGAACCAAGTGGGTATGCACAAACGGACTGTGTCCTTGAAGCAATGGCTTTCCTTGAAGAGTCCCACCCAGGAATCTTTGAAAACTCGTGTCTTGAAACGATGGAAGTTGTTCAACAAACAAGAGTGGACAAGTTGACCCAAGGCCGTCAGACCTATGATTGGACGTTAAACAGGAATCAGCCGGCTGCAACTGCATTAGCTAATACTATAGAGGTCTTCAGATCTAACGGCCTCACAGCCAATGAATCAGGAAGGCTAATAGATTTTCTCAAGGATGTGATGGAATCAATGGATAAGGAGGAAATGGAAATAACAACGCATTTCCAAAGGAAAAGAAGAGTGAGAGACAACATGACCAAGAAAATGGTCACACAAAGGACAATAGGAAAGAAGAAACAGAGGCTAAATAAAAAGAGCTATCTAATAAGAGCATTGACACTGAACACGATGACAAAAGACGCCGAAAGAGGCAAATTAAAAAGAAGGGCAATTGCAACACCTGGAATGCAAATCAGAGGGTTTGTGTACTTTGTTGAGACATTAGCGAGGAGCATTTGTGATAAGCTTGAACAATCTGGACTCCCAGTTGGGGGCAATGAAAAGAAGGCTAAACTGGCAAATGTTGTGAGAAAAATGATGACTAATTCGCAGGACACAGAGCTCTCTTTCACAATCACTGGAGACAACACCAAATGGAATGAAAATCAGAACCCTAGGATGTTTCTGGCAATGATAACATATATAACAAGGAACCAACCTGAATGGTTCAGGAATGTCTTAAGCATTGCACCTATAATGTTCTCAAATAAAATGGCAAGACTAGGGAAAGGGTACATGTTCGAAAGTAAGAGCATGAAGCTCCGAACACAAATACCAGCAGAAATGCTAGCAAGCATTGATCTAAAGTACTTCAATGAGTCAACAAGAAAGAAAATAGAGAAGATAAGACCTCTTCTAATAGATGGTACAGCCTCATTAAGCCCAGGAATGATGATGGGCATGTTCAATATGCTGAGTACAGTTTTGGGAGTTTCGATTCTAAATCTAGGACAAAGGAGGTACACCAAAACAACATACTGGTGGGACGGACTCCAATCCTCTGATGACTTTGCTCTCATAGTGAATGCTCCGAATCATGAGGGAATACAAGCAGGGGTAGACAGATTCTATAGAACCTGCAAGCTGGTCGGAATCAACATGAGCAAAAAGAAGTCCTACATAAACAGGACAGGAACATTTGAATTCACAAGTTTTTTCTACCGCTATGGATTTGTAGCCAACTTCAGTATGGAGTTGCCCAGCTTTGGAGTGTCTGGGATCAATGAATCTGCAGACATGAGCATTGGAGTAACAGTAATAAAGAACAACATGATCAACAATGATCTTGGACCAGCAACAGCTCAAATGGCTCTTCAGCTATTCATCAAGGATTACAGATACACATACCGGTGTCACAGAGGAGACACACAAATTCAGACAAGGAGGTCATTCGAGCTGAAGAAGTTGTGGGAACAGACCCGTTCAAAAGCAGGACTGCTGGTCTCAGATGGAGGACCAAATCTATACAATATTCGGAATCTTCACATTCCAGAAGTCTGCTTGAAATGGGAGCTAATGGACGAAGACTATCAGGGAAGGCTTTGTAATCCCCTGAACCCGTTTGTCAGCCACAAGGAAATAGAGTCTGTGAACAACGCAGTGGTGATGCCAGCTCATGGCCCGGCCAAGAGCATGGAATATGATGCTGTTGCCACCACTCACTCCTGGATACCGAAGAGGAACCGCTCCATTCTCAATACAAGCCAAAGGGGAATCCTTGAAGACGAACAGATGTATCAAAAGTGCTGCAACCTGTTCGAAAAATTCTTCCCTAGCAGTTCATACAGGAGGCCAGTTGGAATTTCCAGCATGGTGGAGGCCATGGTTTCTAGGGCCCGAATTGACGCACGAATTGACTTCGAATCTGGACGGATTAAGAAGGAGGAGTTTGCTAAGATCATGAAGATCTGTTCCACCATTGAAGAGCTCAGACGGCAGAAATAG</t>
         </is>
       </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
+      <c r="CU1" t="inlineStr">
         <is>
           <t>&gt;Flu-0318|A_PA</t>
         </is>
       </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
+      <c r="CV1" t="inlineStr">
         <is>
           <t>ATGGAAGACTTTGTGCGACAATGCTTCAATCCAATGATTGTCGAGCTTGCGGAAAAAGCAATGAAAGAATATGGGGAAGATCCGAAAATCGAGACAAACAAATTTGCCGCAATATGCACACACTTAGAAGTCTGTTTCATGTATTCGGATTTCCATTTTATTAATGAACGAGGCGAATCAATGATTGTAGAATCTGGCGATCCAAATGCATTATTGAAACACCGATTTGAGATAATAGAAGGGAGAGACCGGGCAATGGCCTGGACAGTGGTGAATAGTATCTGCAACACCACAGGGGTCGAAAAGCCCAAATTCCTCCCTGATTTGTATGACTACAAAGAGAACCGATTCATTGAAATTGGAGTAACGCGAAGGGAAGTTCACATATACTATTTAGAAAAAGCCAACAAGATAAAGTCAGAGAAAACACATATTCACATATTCTCATTCACTGGAGAGGAAATGGCCACCAAGGCGGACTACACCCTTGATGAAGAGAGCAGAGCAAGAATAAAAACCAGACTGTTCACTATAAGACAAGAAATGGCCAGTAGAGGTCTATGGGATTCCTTTCGTCAATCCGAGAGAGGCGAAGAGACAATTGAAGAAAGATTTGAAATCGCAGGAACCATGCGCAGGCTTGCCAACCAAAGTCTTCCACCGAACTTCTCCAGCCTTGAAAACTTTAGAGCCTATGTGGATGGATTCGAACCGAACGGCTGCATTGAGGGCAAACTTTCTCAAATGTCAAAAGAAGTGAACGCCAGGATTGAGCCATTTCTGAAGACAACACCACGCCCTCTCAGATTACCTGATGGGCCTCCCTGTTCTCAGCGGTCGAAGTTCTTGCTGATGGATGCCCTTAAGTTGAGCATCGAAGACCCTAGCCATGAGGGGGAGGGCATACCGCTGTATGATGCAATCAAATGCATGAAGACATTTTTTGGCTGGAAAGAGCCCAACATCGTAAAGCCGCATGAGAAAGGCATAAACCCTAATTACCTCCTGACTTGGAAGCAGGTGCTGGCAGAACTTCAAGACATTGAAAATGAGGAGAAAATTCCAAAGACAAAGAACATGAAGAAAACAAGCCAATTGAAGTGGGCACTTGGTGAGAACATGGCTCCAGAGAAAGTGGACTTTGAGGACTGCAAAGATGTTAGCGATCTAAGACAGTACGACAGTAACGAACCAGAGTCTAGAACACTAGCAAGCTGGATTCAGAGTGAATTCAACAAGGCATGCGAACTGACAGATTCGAGTTGGATTGAACTTGATGAGATAGGGGAAGACGTTGCTCCAATCGAACACATTGCGAGTGTGAGGAGGAACTATTTCACAGCGGAGGTATCCCATTGCAGGGCCACTGAATACATAATGAAGGGAGTATACATAAACACAGCCCTATTGAATGCATCCTGTGCAGCCATGGATGACTTCCAATTGATTCCAATGATAAGTAAGTGCAGAACTAAAGAAGGAAGACGGAAGACAAATCTGTATGGATTCATTATAAAAGGAAGATCCCATTTGAGGAATGACACCGATGTGGTAAACTTTGTGAGCATGGAATTCTCTCTAACTGACCCGAGGCTGGAGCCACACAAATGGGAGAAGTACTGTGTTCTTGAGATAGGAGACATGCTCCTACGGACTGCAATAGGCCAAGTGTCGAGGCCCATGTTCCTGTATGTGAGAACCAATGGGACTTCCAAGATCAAAATGAAATGGGGCATGGAGATGAGGCGATGCCTTCTTCAGTCCCTTCAACAAATTGAGAGCATGATTGAGGCCGAATCTTCTGTCAAAGAGAAGGACATGTCCAAGGAATTCTTTGAAAACAAATCAGAAACATGGCCAATTGGAGAATCACCCAAAGGGGTGGAGGAAGGCTCTATTGGGAAAGTATGCAGAACATTGCTAGCAAAGTCTGTGTTCAACAGCCTATATGCATCTCCACAACTCGAGGGGTTTTCAGCTGAATCAAGAAAATTGCTTCTCATTGTTCAGGCACTTAGGGACAACCTGGAACCTGGAACCTTCGATCTTGGGGGGCTATATGAAGCAATTGAGGAGTGCCTGATTAACGATCCCTGGGTTTTGCTTAATGCATCTTGGTTCAACTCCTTCCTCACACATGCACTGAAATAG</t>
         </is>
       </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
+      <c r="CW1" t="inlineStr">
         <is>
           <t>&gt;Flu-0318|A_NP</t>
         </is>
       </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
+      <c r="CX1" t="inlineStr">
         <is>
           <t>ATGGCGTCTCAAGGCACCAAACGATCCTATGAACAAATGGAAACTGGTGGGGAACGCCAGAATGCCACTGAAATCAGAGCATCTGTTGGAAGAATGGTTGGCGGAATAGGAAGATTCTACATACAGATGTGCACTGAGCTCAAACTCAGTGATTATGAAGGGAGGCTGATCCAAAACAGCATAACCATAGAAAGGATGGTTCTCTCGGCATTTGATGAGAGGAGGAACAAGTACCTGGAGGAACATCCCAGTGCCGGGAAGGATCCCAAGAAGACTGGAGGTCCAATCTACAGGAGGAGAGATGGCAAATGGGTGAGAGAGTTGATCCTCTACGACAAAGAAGAGATCAGAAGAATTTGGCGTCAAGCTAATAATGGAGAGGATGCAACTGCTGGTCTCACTCATTTGATGATTTGGCATTCCAATCTGAATGATGCAACATACCAGAGAACAAGGGCACTTGTGCGTACTGGAATGGACCCTAGAATGTGCTCTCTGATGCAAGGCTCAACCCTCCCTAGGAGATCCGGGGCTGCTGGAGCAGCAGTGAAAGGAGTTGGAACAATGGTGATGGAACTAATTCGAATGATCAAGCGAGGGATCAATGATCGGAATTTCTGGAGAGGCGAAAACGGTCGGAGAACCAGGATTGCCTACGAGAGAATGTGCAACATCCTCAAGGGAAAGTTCCAAACAGCAGCACAACGGGCAATGATGGACCAAGTGAGAGAAAGCCGGAATCCTGGGAATGCTGAAATTGAAGATCTCATCTTTCTCGCACGATCTGCTCTCATCCTGAGGGGATCAGTGGCTCATAAGTCCTGTCTGCCTGCTTGCGTATATGGACTTGCTGTAGCCAGTGGATATGACTTTGAAAGAGAGGGATATTCTCTAGTCGGAATTGATCCTTTCCGTCTGCTCCAAAACAGCCAAGTCTTCAGTCTCATCAGACCGAACGAAAATCCAGCTCATAAGAGTCAGCTGGTATGGATGGCATGCCACTCTGCGGCATTTGAGGATCTGAGAGTTTCAAGCTTCATCAGAGGGACAAGAGTAGTCCCAAGAGGACAACTGTCCACCAGAGGAGTTCAGATTGCTTCAAATGAAAACATGGAGACAATGGACTCCAGTACTCTTGAACTGAGGAGCAGATACTGGGCTATAAGAACAAGAAGTGGAGGAAACACTAACCAACAGAGAGCATCTGCAGGACAAATCAGCGTGCAGCCCACATTCTCTGTGCAAAGAAACCTCCCATTCGAGAGAGCAACCATCATGGCAGCATTTACGGGAAACACTGAAGGCAGAACTTCAGACATGAGAACTGAGATCATAAGGATGATGGAAAATGCCAGACCTGAAGATGTGTCTTTCCAGGGGCGGGGAGTCTTCGAGCTCTCGGACGAAAAGGCAACGAACCCGATCGTGCCTTCCTTTGACATGAGTAATGAAGGATCTTATTTCTTCGGAGACAATGCAGAGGAGTATGACAATTAA</t>
         </is>
       </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
+      <c r="CY1" t="inlineStr">
         <is>
           <t>&gt;Flu-0318|A_NA</t>
         </is>
       </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
+      <c r="CZ1" t="inlineStr">
         <is>
           <t>ATGAATCCAAATCAAAAGATAACAACCATTGGATCAATCTGTATGGTAATTGGGACAGTCAGCTTGATGCTGCAAATTGGGAACATAATCTCAATATGGGTTAGCCATTCAATCCAAACAGGGAATCAATACCAGCCTGAACCATGCAATCAAAGCATCATTACCTATGAGAACAACACCTGGGTAAATCAGACGTATGTCAACATCAGCAATAACAATTTTCTTGCTGAGCAGGCTGTTACTTCGGTAACATTAGCGGGCAATTCATCTCTTTGCCCTATTAGTGGGTGGGCAATATACAGTAAGGACAACGGTATAAGAATTGGGTCCAAGGGGGATGTGTTTGTCATAAGAGAACCGTTCATCTCATGCTCCCACTTGGAATGCAGAACCTTTTTCCTGACTCAGGGAGCTCTGCTGAATGACAAACATTCTAATGGGACAGTTAAGGATAGAAGCCCTTATAGAACTTTGATGAGTTGTCCCGTGGGTGAGGCTCCTTCCCCGTACAATTCAAGATTTGAGTCTGTTGCTTGGTCGGCAAGTGCTTGTCATGATGGCATCAGTTGGTTGACAATCGGTATTTCTGGTCCAGACAATGGAGCTGTGGCTGTATTGAAGTACAATGGCATAATAACGGATACTATCAAGAGTTGGAGAAACAACATTTTGAGAACTCAAGAATCTGAATGTGCTTGCGTAAATGGCTCTTGCTTCACCGTAATGACTGATGGACCAAGCAATGGGCAGGCCTCGTATAAAATCTTCAAGATAGAGAAAGGGAAAGTTGTCAAATCAGTTGAATTGAATGCCCCTAATTACCACTACGAGGAATGTTCCTGTTATCCTGATGCGGGTGATATTATATGTGTGTGCAGGGACAATTGGCACGGCTCAAACCGGCCGTGGATATCTTTTAATCAAAATCTGGAGTATCAAATAGGATATATATGCAGTGGGGTTTTCGGGGACAATCCCCGCCCCAATGATGGAACAGGCAGTTGCAGTCCAATGTCCTCTAATGGGGCATATGGGGTGAAAGGGTTTTCATTTAAGTACGGTAATGGGGTTTGGATCGGAAGAACAAAAGGCACTAGTTCCAGAAGCGGCTTTGAGATGATTTGGGACCCGAATGGGTGGACTGAGACGGACAGTAGTTTCTCAGTGAAGCAAGACATTGTAGAAATAACTGACTGGTCAGGATATAGTGGGAGTTTTGTCCAGCATCCAGAACTGACAGGATTAGATTGCATGAGGCCTTGTTTCTGGGTTGAGCTAATTAGAGGGAGGCCCAAAGAGAACACAATTTGGACTAGCGGGAGCAGCATATCCTTTTGTGGTGTAAATAGTGACACTGTGGGTTGGTCTTGGCCAGACGGTGCTGAGTTGCCATTCACCATTGACAAGTAG</t>
         </is>
       </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
+      <c r="DA1" t="inlineStr">
         <is>
           <t>&gt;Flu-0318|A_MP</t>
         </is>
       </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
+      <c r="DB1" t="inlineStr">
         <is>
           <t>ATGAGTCTTCTAACCGAGGTCGAAACGTACGTTCTCTCTATCGTCCCGTCGGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTTGAAGATGTCTTTGCAGGGAAGAACACCGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATACTGTCACCTCTGACTAAGGGGATTTTGGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCTCTAAGTGGAAATGGAGACCCAAACAACATGGACAGGGCAGTCAAGTTGTACAGGAAACTGAAGAGAGAAATAACATTCCATGGGGCTAAAGAAGTTGCACTTAGTTACTCAACCGGTGCACTTGCCAGTTGTATGGGTCTCATATACAACAGGATGGGGACGGTGACCGCAGAAGTGGCATTGGGCCTAGTGTGTGCCACCTGTGAGCAGATTGCTGATTCACAGCATCGGTCTCACAGACAGATAGCTACCACCACCAACCCACTAATCAGACATGAAAACAGAATGGTTTTGGCCAGTACTACAGCTAAGGCTATGGAGCAGATGGCTGGATCGAGTGAGCAAGCAGTGGAAGCCATGGAGGTTGCTAGTCAGGCTAGGCAAATGGTGCAGGCGATGAGGACCATTGGAACTCATCCTAGCTCCAGTGCCGGTCTGAGAGATGATCTCCTTGAAAATTTGCAGGCCTACCAAAAACGAATGGGAGTGCAACTGCAGCGATTCAAGTGATCCTCTCGTTATTGCAGCAAGTATCATTGGGATCTTGCACTTGATATTGTGGATTCTTGATCGCCTTTTCTTCAAATGCGTTTATCGTCGCCTTAAATACGGTTTGAAAGGAGGGCCTTCTACGGAAGGAGTACCTGAGTCCATGAGGGAAGAGTACCGGCAGGAACAGCAGAGTGCTGTGGATGTTGACGATGGTCATTTTGTCAACATAGAGATGGAGTAA</t>
         </is>
       </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
+      <c r="DC1" t="inlineStr">
         <is>
           <t>&gt;Flu-0318|A_NS</t>
         </is>
       </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
+      <c r="DD1" t="inlineStr">
         <is>
           <t>ATGGATTCCAACACTGTGTCAAGCTTTCAGGTAGACTGCTTTCTTTGGCATGTCCGCAAACAATTTGCAGACCAAGAACTGGGTGATGCCCCATTCCTTGACCGGCTCCGCCGAGACCAGAAGTCTCTAAGAGGAAGAGGCAGCACTCTTGGTCTGGACATCGAGACGGCCACTCGTGCTGGAAAGCAGATAGTGGAGAGGATTCTGGAGGAAGAATCCGACGAGGCACTCAAAATGACTATTGCCTCTGTGCCTGCTCCACGCTACCTAACTGACATGACTCTTGAAGAGATGTCAAGAGACTGGTTCATGCTCATGCCCAAGCAAAAAGTGGCAGGCTCCCTCTGTATCAGAATGGACCAGGCGATTATGGATAAGAACATCATACTGAAGGCAAACTTCAGTGTGATCTTCAATCGGCTGGAGACACTAATACTACTCAGAGCTTTCACTGAAGAGGGAGCAATTGTCGGCGAAATTTCACCATTGCCTTCTCTTCCAGGACATACTGATGAGGATGTCAAAAATGCAATTGGGGTCCTCATCGGAGGACTTGAATGGAATGATAACACAGTTCGAGTCTCTGAAATTTTACAGAGATTCGCTTGGAGAAGCAGTAATGAGGATGGGAGACCTCCACTCCCTCCAAAGCAGAAACGGAAAATGGAGAGAACAATTGAGTCAGAAGTTTGAAGAAATAAGGTGGCTGATTGAAGAGGTGCGACACAGACTAAAGATCACAGAAAATAGTTTTGAACAAATAACATTTATGCAAGCCTTACAACTACTGCTTGAAGTGGAGCAAGAGATACGAACTTTCTCGTTTCAGCTTATTTAA</t>
         </is>
       </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
+      <c r="DE1" t="inlineStr">
         <is>
           <t>&gt;Flu-0321|A_NA</t>
         </is>
       </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
+      <c r="DF1" t="inlineStr">
         <is>
           <t>ATGAATCCAAATCAAAAGATAACAACCATTGGATCAATCTGTATGGTAATTGGGACAGTCAGCTTGATGCTGCAAATTGGGAACATAATCTCAATATGGGTTAGCCATTCAATCCAAACAGGGAATCAATACCAGCCTGAACCATGCAATCAAAGCATCATTACCTATGAGAACAACACCTGGGTAAATCAGACGTATGTCAACATCAGCAATAACAATTTTCTTGCTGAGCAGGCTGTTACTTCGGTAACATTAGCGGGCAATTCATCTCTTTGCCCTATTAGTGGGTGGGCAATATACAGTAAGGACAACGGTATAAGAATTGGGTCCAAGGGGGATGTGTTTGTCATAAGAGAACCGTTCATCTCATGCTCCCACTTGGAATGCAGAACCTTTTTCCTGACTCAGGGAGCTCTGCTGAATGACAAACATTCTAATGGGACAGTTAAGGATAGAAGCCCTTATAGAACTTTGATGAGTTGTCCCGTGGGTGAGGCTCCTTNCCCGTACAATTCAAGATTTGAGTCTGTTGCTTGGTCGGCAAGTGCTTGTCATGATGGCATCAGTTGGTTGACAATCGGTATTTCTGGTCCAGACAATGGAGCTGTGGCTGTATTGAAGTACAATGGCATAATAACGGATACTATCAAGAGTTGGAGAAACAACATTTTGAGAACTCAAGAATCTGAATGTGCTTGCGTAAATGGCTCTTGCTTCACCGTAATGACTGATGGACCAAGCAATGGGCAGGCCTCGTATAAAATCTTCAAGATAGAGAAAGGGAAAGTTGTCAAATCAGTTGAATTGAATGCCCCTAATTACCACTACGAGGAATGTTCCTGTTATCCTGATGCGGGTGATATTATATGTGTGTGCAGGGACAATTGGCACGGCTCAAACCGGCCGTGGATATCTTTTAATCAAAATCTGGAGTATCAAATAGGATATATATGCAGTGGGGTTTTCGGGGACAATCCCCGCCCCAATGATGGAACAGGCAGTTGCAGTCCAATGTCCTCTAATGGGGCATATGGGGTAAAAGGGTTTTCATTTAAGTACGGTAATGGGGTTTGGATCGGAAGAACAAAAGGCACTAGTTCCAGAAGCGGCTTTGAGATGATTTGGGACCCGAATGGGTGGACTGAGACGGACAGTAGTTTCTCAGTGAAGCAAGACATTGTAGAAATAACTGACTGGTCAGGATATAGTGGGAGTTTTGTCCAGCATCCAGAACTGACAGGATTAGATTGCATGAGGCCTTGTTTCTGGGTTGAGCTAATTAGAGGGAGGCCCAAAGAGAACACAATTTGGACTAGCGGGAGCAGCATATCCTTTTGTGGTGTAAATAGTGACACTGTGGGTTGGTCTTGGCCAGACGGTGCTGAGTTGCCATTCACCATTGACAAGTAG</t>
         </is>
       </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
+      <c r="DG1" t="inlineStr">
         <is>
           <t>&gt;Flu-0321|A_MP</t>
         </is>
       </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
+      <c r="DH1" t="inlineStr">
         <is>
           <t>ATGAGTCTTCTAACCGAGGTCGAAACGTACGTTCTCTCTATCGTCCCGTCGGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTTGAAGATGTCTTTGCAGGGAAGAACACCGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATACTGTCACCTCTGACTAAGGGGATTTTGGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCTCTAAGTGGAAATGGAGACCCAAACAACATGGACAGGGCAGTCAAGTTGTACAGGAAACTGAAGAGAGAAATAACATTCCATGGGGCTAAAGAAGTTGCACTTAGTTACTCAACCGGTGCACTTGCCAGTTGTATGGGTCTCATATACAACAGGATGGGGACGGTGACCGCAGAAGTGGCATTGGGCCTAGTGTGTGCCACCTGTGAGCAGATTGCTGATTCACAGCATCGGTCTCACAGACAGATAGCTACCACCACCAACCCACTAATCAGACATGAAAACAGAATGGTTTTGGCCAGTACTACAGCTAAGGCTATGGAGCAGATGGCTGGATCGAGTGAGCAAGCAGTGGAAGCCATGGAGGTTGCTAGTCAGGCTAGGCAAATGGTGCAGGCGATGAGGACCATTGGAACTCATCCTAGCTCCAGTGCCGGTCTGAGAGATGATCTCCTTGAAAATTTGCAGGCCTACCAAAAACGAATGGGAGTGCAACTGCAGCGATTCAAGTGATCCTCTCGTTATTGCAGCAAGTATCATTGGGATCTTGCACTTGATATTGTGGATTCTTGATCGCCTTTTCTTCAAATGCGTTTATCGTCGCCTTAAATACGGTTTGAAAGGAGGGCCTTCTACGGAAGGAGTACCTGAGTCCATGAGGGAAGAGTACCGGCAGGAACAGCAGAGTGCTGTGGATGTTGACGATGGTCATTTTGTCAACATAGAGATGGAGTAA</t>
         </is>
       </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
+      <c r="DI1" t="inlineStr">
         <is>
           <t>&gt;Flu-0321|A_NS</t>
         </is>
       </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
+      <c r="DJ1" t="inlineStr">
         <is>
           <t>ATGGATTCCAACACTGTGTCAAGCTTTCAGGTAGACTGCTTTCTTTGGCATGTCCGCAAACAATTTGCAGACCAAGAACTGGGTGATGCCCCATTCCTTGACCGGCTCCGCCGAGACCAGAAGTCTCTAAGAGGAAGAGGCAGCACTCTTGGTCTGGACATCGAGACGGCCACTCGTGCTGGAAAGCAGATAGTGGAGAGGATTCTGGAGGAAGAATCCGACGAGGCACTCAAAATGACTATTGCCTCTGTGCCTGCTCCACGCTACCTAACTGACATGACTCTTGAAGAGATGTCAAGAGACTGGTTCATGCTCATGCCCAAGCAAAAAGTGGCAGGCTCCCTCTGTATCAGAATGGACCAGGCGATTATGGATAAGAACATCATACTGAAGGCAAACTTCAGTGTGATCTTCAATCGGCTGGAGACACTAATACTACTCAGAGCTTTCACTGAAGAGGGAGCAATTGTCGGCGAAATTTCACCATTGCCTTCTCTTCCAGGACATACTGATGAGGATGTCAAAAATGCAATTGGGGTCCTCATCGGAGGACTTGAATGGAATGATAACACAGTTCGAGTCTCTGAAATTTTACAGAGATTCGCTTGGAGAAGCAGTAATGAGGATGGGAGACCTCCACTCCCTCCAAAGCAGAAACGGAAAATGGAGAGAACAATTGAGTCAGAAGTTTGAAGAAATAAGGTGGCTGATTGAAGAGGTGCGACACAGACTAAAGATCACAGAAAATAGTTTTGAACAAATAACATTTATGCAAGCCTTACAACTACTGCTTGAAGTGGAGCAAGAGATACGAACTTTCTCGTTTCAGCTTATTTAA</t>
         </is>
       </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
+      <c r="DK1" t="inlineStr">
         <is>
           <t>&gt;Flu-0323|A_MP</t>
         </is>
       </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
+      <c r="DL1" t="inlineStr">
         <is>
           <t>ATGAGTCTTCTAACCGAGGTCGAAACGTACGTTCTCTCTATCGTCCCGTCGGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTTGAAGATGTCTTTGCAGGGAAGAACACCGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATACTGTCACCTCTGACTAAGGGGATTTTGGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCTCTAAGTGGAAATGGAGACCCAAACAACATGGACAGGGCAGTCAAGTTGTACAGGAAACTGAAGAGAGAAATAACATTCCATGGGGCTAAAGAAGTTGCACTTAGTTACTCAACCGGTGCACTTGCCAGTTGTATGGGTCTCATATACAACAGGATGGGGACGGTGACCGCAGAAGTGGCATTGGGCCTAGTGTGTGCCACCTGTGAGCAGATTGCTGATTCACAGCATCGGTCTCACAGACAGATAGCTACCACCACCAACCCACTAATCAGACATGAAAACAGAATGGTTTTGGCCAGTACTACAGCTAAGGCTATGGAGCAGATGGCTGGATCGAGTGAGCAAGCAGTGGAAGCCATGGAGGTTGCTAGTCAGGCTAGGCAAATGGTGCAGGCGATGAGGACCATTGGAACTCATCCTAGCTCCAGTGCCGGTCTGAGAGATGATCTCCTTGAAAATTTGCAGGCCTACCAAAAACGAATGGGAGTGCAACTGCAGCGATTCAAGTGATCCTCTCGTTATTGCAGCAAGTATCATTGGGATCTTGCACTTGATATTGTGGAGTCTTGATCGCCTTTTCTTCAAATGCGTTTATCGTCGCCTTAAATACGGTTTGAAAGGAGGGCCTTCTACGGAAGGAGTACCTGAGTCCATGAGGGAAGAGTACCGGCAGGAACAGCAGAGTGCTGTGGATGTTGACGATGGTCATTTTGTCAACATAGAGATGGAGTAA</t>
         </is>
       </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
+      <c r="DM1" t="inlineStr">
         <is>
           <t>&gt;Flu-0323|A_NS</t>
         </is>
       </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
+      <c r="DN1" t="inlineStr">
         <is>
           <t>ATGGATTCCAACACTGTGTCAAGCTTTCAGGTAGACTGCTTTCTTTGGCATGTCCGCAAACAATTTGCAGACCAAGAACTGGGTGATGCCCCATTCCTTGACCGGCTCCGCCGAGACCAGAAGTCTCTAAGAGGAAGAGGCAGCACTCTTGGTCTGGACATCGAGACGGCCACTCGTGCTGGAAAGCAGATAGTGGAGAGGATTCTGGAGGACGAATCCGACGAGGCACTCAAAATGACTATTGCCTCTGTGCCTGCTCCACGCTACCTAACTGACATGACTCTTGAAGAGATGTCAAGAGACTGGTTCATGCTCATGCCCAAGCAAAAAGTGGCAGGCTCCCTCTGTATCAGAATGGACCAGGCGATTATGGATAAGAACATCATACTGAAGGCAAACTTCAGTGTGATCTTCAATCGGCTGGAGACACTAATACTACTCAGAGCTTTCACTGAAGAGGGAGCAATTGTCGGCGAAATTTCACCATTGCCTTCTCTTCCAGGACATACTGATGAGGATGTCAAAAATGCAATTGGGGTCCTCATCGGAGGACTTGAATGGAATGATAACACAGTTCGAGTCTCTGAAATTTTACAGAGATTCGCTTGGAGAAGCAGTAATGAGGATGGGAGACCTCCACTCCCTCCAAAGCAGAAACGGAAAATGGAGAGAACAATTGAGTCAGAAGTTTGAAGAAATAAGGTGGCTGATTGAAGAGGTGCGACACAGACTAAAGATCACAGAAAATAGTTTTGAACAAATAACATTTATGCAAGCCTTACAACTACTGCTTGAAGTGGAGCAAGAGATACGAACTTTCTCGTTTCAGCTTATTTAA</t>
         </is>
       </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
+      <c r="DO1" t="inlineStr">
         <is>
           <t>&gt;Flu-0325|A_NP</t>
         </is>
       </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
+      <c r="DP1" t="inlineStr">
         <is>
           <t>ATGGCGTCTCAAGGCACCAAACGATCATATGAACAAATGGAAACTGGTGGGGAACGCCAGAATGCCACTGAAATCAGAGCATCTGTTGGAAGAATGGTTGGCGGAATAGGAAGATTCTACATACAGATGTGCACTGAGCTCAAACTCAGTGATTATGAAGGGAGGCTGATCCAAAACAGCATAACCATAGAAAGAATGGTTCTCTCGGCATTTGATGAGAGGAGGAACAAGTACCTGGAGGAACATCCCAGTGCCGGGAAGGATNCCAAGAAGACTGGAGGTCCAATCTACAGGAGGAGAGATGGCAAATGGGTGAGAGAGTTGATCCTCTACGACAAAGAAGAGATCAGAAGAATTTGGCGTCAAGCCAATAATGGAGAGGATGCAACTGCTGGTCTCACTCATTTGATGATTTGGCATTCCAATCTGAATGATGCAACATACCAGAGAACAAGGGCACTTGTGCGTACTGGAATGGACCCTAGAATGTGCTCTCTGATGCAAGGCTCAACCCTCCCTAGGAGATCCGGGGCTGCTGGAGCAGCAGTGAAAGGAGTTGGAACAATGGTGATGGAACTAATTCGAATGATCAAGCGAGGGATCAATGATCGGAATTTCTGGAGAGGCGAAAACGGTCGGAGAACCAGGATTGCCTACGAGAGAATGTGCAACATCCTCAAGGGAAAGTTCCAAACAGCAGCACAACGGGCAATGATGGACCAAGTGAGAGAAAGCCGGAATCCTGGGAATGCTGAAATTGAAGATCTCATCTTTCTCGCACGATCTGCTCTCATCCTGAGGGGATCAGTGGCTCATAAGTCCNNNNTGCCTGCTTGCGTATATGGACNTGCTGTAGCCAGTGGATATGACTTTGNAAGANAGGNATANNNNNNNNTNGNANNNNATCCTTTNCGTNNNCTCCAAAACNGCCNAGTNTTNNGTCTNATCNNACNNNANNNNANTNNAGCTNATNNNAGTNAGCTGGTATNGANGGNNTGCCACTNTNNGGCANTNGANNNNNNNNNNNNTTNNAGNTTNATCAGNNGNANANNNNNNGTNCNNAGAGGNNNACNGTCCACCAGANNAGTTCAGATTGCTTCAAATGAAAACATGGAGACAATGGACTCCAGTACTCTTGAACTGAGGAGCAGATACTGGGCTATNAGAACAAGAAGTGGAGGAAACACTAACCAACAGAGAGCATCTGCAGGACAAATCAGCGTGCAGCCCACATTCTCTGTGCAAAGAAACCTCCCATTCGAGAGAGCAACCATCATGGCAGCATTTACGGGAAACACTGAAGGCAGAACTTCAGACATGAGAACTGAGATCATAAGGATGATGGAAAATGCCAGACCTGAAGATGTGTCTTTCCAGGGGCGGGGAGTCTTCGAGCTCTCGGACGAAAAGGCAACGAACCCGATCGTGCCTTCCTTTGACATGAGTAATGAAGGATCTTATTTCTTCGGAGACAATGCAGAGGAGTATGACAATTAA</t>
         </is>
       </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
+      <c r="DQ1" t="inlineStr">
         <is>
           <t>&gt;Flu-0325|A_MP</t>
         </is>
       </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
+      <c r="DR1" t="inlineStr">
         <is>
           <t>ATGAGTCTTCTAACCGAGGTCGAAACGTACGTTCTCTCTATCGTCCCGTCGGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTTGAAGATGTCTTTGCAGGGAAGAACACCGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATACTGTCACCTCTGACTAAGGGGATTTTGGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCTCTAAGTGGAAATGGAGACCCAAACAACATGGACAGGGCAGTCAAGTTGTACAGGAAACTGAAGAGAGAAATAACATTCCATGGGGCTAAAGAAGTTGCACTTAGTTACTCAACCGGTGCACTTGCCAGTTGTATGGGTCTCATATACAACAGGATGGGGACGGTGACCGCAGAAGTGGCATTGGGCCTAGTGTGTGCCACCTGTGAGCAGATTGCTGATTCACAGCATCGGTCTCACAGACAGATAGCTACCACCACCAACCCACTAATCAGACATGAAAACAGAATGGTTTTGGCCAGTACTACAGCTAAGGCTATGGAGCAGATGGCTGGATCGAGTGAGCAAGCAGTGGAAGCCATGGAGGTTGCTAGTCAGGCTAGGCAAATGGTGCAGGCGATGAGGACCATTGGAACTCATCCTAGCTCCAGTGCCGGTCTGAGAGATGATCTCCTTGAAAATTTGCAGGCCTACCAAAAACGAATGGGAGTGCAACTGCAGCGATTCAAGTGATCCTCTCGTTATTGCAGCAAGTATCATTGGGATCTTGCACTTGATATTGTGGAGTCTTGATCGCCTTTTCTTCAAATGCGTTTATCGTCGCCTTAAATACGGTTTGAAAGGAGGGCCTTCTACGGAAGGAGTACCTGAGTCCATGAGGGAAGAGTACCGGCAGGAACAGCAGAGTGCTGTGGATGTTGACGATGGTCATTTTGTCAACATAGAGATGGAGTAA</t>
         </is>
       </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
+      <c r="DS1" t="inlineStr">
         <is>
           <t>&gt;Flu-0325|A_NS</t>
         </is>
       </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
+      <c r="DT1" t="inlineStr">
         <is>
           <t>ATGGATTCCAACACTGTGTCAAGCTTTCAGGTAGACTGCTTTCTTTGGCATGTCCGCAAACAATTTGCAGACCAAGAACTGGGTGATGCCCCATTCCTTGACCGGCTCCGCCGAGACCAGAAGTCTCTAAGAGGAAGAGGCAGCACTCTTGGTCTGGACATCGAGACGGCCACTCGTGCTGGAAAGCAGATAGTGGAGAGGATTCTGGAGGACGAATCCGACGAGGCACTCAAAATGACTATTGCCTCTGTGCCTGCTCCACGCTACCTAACTGACATGACTCTTGAAGAGATGTCAAGAGACTGGTTCATGCTCATGCCCAAGCAAAAAGTGGCAGGCTCCCTCTGTATCAGAATGGACCAGGCGATTATGGATAAGAACATCATACTGAAGGCAAACTTCAGTGTGATCTTCAATCGGCTGGAGACACTAATACTACTCAGAGCTTTCACTGAAGAGGGAGCAATTGTCGGCGAAATTTCACCATTGCCTTCTCTTCCAGGACATACTGATGAGGATGTCAAAAATGCAATTGGGGTCCTCATCGGAGGACTTGAATGGAATGATAACACAGTTCGAGTCTCTGAAATTTTACAGAGATTCGCTTGGAGAAGCAGTAATGAGGATGGGAGACCTCCACTCCCTCCAAAGCAGAAACGGAAAATGGAGAGAACAATTGAGTCAGAAGTTTGAAGAAATAAGGTGGCTGATTGAAGAGGTGCGACACAGACTAAAGATCACAGAAAATAGTTTTGAACAAATAACATTTATGCAAGCCTTACAACTACTGCTTGAAGTGGAGCAAGAGATACGAACTTTCTCGTTTCAGCTTATTTAA</t>
         </is>
       </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
+      <c r="DU1" t="inlineStr">
         <is>
           <t>&gt;Flu-0326|A_NP</t>
         </is>
       </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
+      <c r="DV1" t="inlineStr">
         <is>
           <t>ATGGCGTCTCAAGGCACCAAACGATCATATGAACAAATGGAAACTGGTGGGGAACGCCAGAATGCCACTGAAATCAGAGCATCTGTTGGAAGAATGGTTGGCGGAATAGGAAGATTCTACATACAGATGTGCACTGAGCTCAAACTCAGTGATTATGAAGGGAGGCTGATCCAAAACAGCATAACCATAGAAAGAATGGTTCTCTCGGCATTTGATGAGAGGAGGAACAAGTACCTGGAGGAACATCCCAGTGCCGGGAAGGATCCCAAGAAGACTGGAGGTCCAATCTACAGGAGGAGAGATGGCAAATGGGTGAGAGAGTTGATCCTCTACGACAAAGAAGAGATCAGAAGAATTTGGCGTCAAGCCAATAATGGAGAGGATGCAACTGCTGGTCTCACTCATTTGATGATTTGGCATTCCAATCTGAATGATGCAACATACCAGAGAACAAGGGCACTTGTGCGTACTGGAATGGACCCTAGAATGTGCTCTCTGATGCAAGGCTCAACCCTCCCTAGGAGATCCGGGGCTGCTGGAGCAGCAGTGAAAGGAGTTGGAACAATGGTGATGGAACTAATTCGAATGATCAAGCGAGGGATCAATGATCGGAATTTCTGGAGAGGCGAAAACGGTCGGAGAACCAGGATTGCCTACGAGAGAATGTGCAACATCCTCAAGGGAAAGTTCCAAACAGCAGCACAACGGGCAATGATGGACCAAGTGAGAGAAAGCCGGAATCCTGGGAATGCTGAAATTGAAGATCTCATCTTTCTCGCACGATCTGCTCTCATCCTGAGGGGATCAGTGGCTCATAAGTCCTGTCTGCCTGCTTGCGTATATGGACTTGCTGTAGCCAGTGGATATGACTTTGAAAGAGAGGGATATTCTCTAGTCGGAATTGATCCTTTCCGTCTGCTCCAAAACAGCCAAGTCTTCAGTCTCATCAGACCGAACGAAAATCCAGCTCATAAGAGTCAGCTGGTATGGATGGCATGCCACTCTGCGGCATTTGAGGATCTGAGAGTTTCAAGCTTCATCAGAGGGACAAGAGTAGTCCCAAGAGGACAACTGTCCACCAGAGGAGTTCAGATTGCTTCAAATGAAAACATGGAGACAATGGACTCCAGTACTCTTGAACTGAGGAGCAGATACTGGGCTATAAGAACAAGAAGTGGAGGAAACACTAACCAACAGAGAGCATCTGCAGGACAAATCAGCGTGCAGCCCACATTCTCTGTGCAAAGAAACCTCCCATTCGAGAGAGCAACCATCATGGCAGCATTTACGGGAAACACTGAAGGCAGAACTTCAGACATGAGAACTGAGATCATAAGGATGATGGAAAATGCCAGACCTGAAGATGTGTCTTTCCAGGGGCGGGGAGTCTTCGAGCTCTCGGACGAAAAGGCAACGAACCCGATCGTGCCTTCCTTTGACATGAGTAATGAAGGATCTTATTTCTTCGGAGACAATGCAGAGGAGTATGACAATTAA</t>
         </is>
       </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>&gt;Flu-0326|A_MP</t>
         </is>
       </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>ATGAGTCTTCTAACCGAGGTCGAAACGTACGTTCTCTCTATCGTCCCGTCGGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTTGAAGATGTCTTTGCAGGGAAGAACACCGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATACTGTCACCTCTGACTAAGGGGATTTTGGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCTCTAAGTGGAAATGGAGACCCAAACAACATGGACAGGGCAGTCAAGTTGTACAGGAAACTGAAGAGAGAAATAACATTCCATGGGGCTAAAGAAGTTGCACTTAGTTACTCAACCGGTGCACTTGCCAGTTGTATGGGTCTCATATACAACAGGATGGGGACGGTGACCGCAGAAGTGGCATTGGGCCTAGTGTGTGCCACCTGTGAGCAGATTGCTGATTCACAGCATCGGTCTCACAGACAGATAGCTACCACCACCAACCCACTAATCAGACATGAAAACAGAATGGTTTTGGCCAGTACTACAGCTAAGGCTATGGAGCAGATGGCTGGATCGAGTGAGCAAGCAGTGGAAGCCATGGAGGTTGCTAGTCAGGCTAGGCAAATGGTGCAGGCGATGAGGACCATTGGAACTCATCCTAGCTCCAGTGCCGGTCTGAGAGATGATCTCCTTGAAAATTTGCAGGCCTACCAAAAACGAATGGGAGTGCAACTGCAGCGATTCAAGTGATCCTCTCGTTATTGCAGCAAGTATCATTGGGATCTTGCACTTGATATTGTGGAGTCTTGATCGCCTTTTCTTCAAATGCGTTTATCGTCGCCTTAAATACGGTTTGAAAGGAGGGCCTTCTACGGAAGGAGTACCTGAGTCCATGAGGGAAGAGTACCGGCAGGAACAGCAGAGTGCTGTGGATGTTGACGATGGTCATTTTGTCAACATAGAGATGGAGTAA</t>
         </is>
       </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>&gt;Flu-0326|A_NS</t>
         </is>
       </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>ATGGATTCCAACACTGTGTCAAGCTTTCAGGTAGACTGCTTTCTTTGGCATGTCCGCAAACAATTTGCAGACCAAGAACTGGGTGATGCCCCATTCCTTGACCGGCTCCGCCGAGACCAGAAGTCTCTAAGAGGAAGAGGCAGCACTCTTGGTCTGGACATCGAGACGGCCACTCGTGCTGGAAAGCAGATAGTGGAGAGGATTCTGGAGGACGAATCCGACGAGGCACTCAAAATGACTATTGCCTCTGTGCCTGCTCCACGCTACCTAACTGACATGACTCTTGAAGAGATGTCAAGAGACTGGTTCATGCTCATGCCCAAGCAAAAAGTGGCAGGCTCCCTCTGTATCAGAATGGACCAGGCGATTATGGATAAGAACATCATACTGAAGGCAAACTTCAGTGTGATCTTCAATCGGCTGGAGACACTAATACTACTCAGAGCTTTCACTGAAGAGGGAGCAATTGTCGGCGAAATTTCACCATTGCCTTCTCTTCCAGGACATACTGATGAGGATGTCAAAAATGCAATTGGGGTCCTCATCGGAGGACTTGAATGGAATGATAACACAGTTCGAGTCTCTGAAATTTTACAGAGATTCGCTTGGAGAAGCAGTAATGAGGATGGGAGACCTCCACTCCCTCCAAAGCAGAAACGGAAAATGGAGAGAACAATTGAGTCAGAAGTTTGAAGAAATAAGGTGGCTGATTGAAGAGGTGCGACACAGACTAAAGATCACAGAAAATAGTTTTGAACAAATAACATTTATGCAAGCCTTACAACTACTGCTTGAAGTGGAGCAAGAGATACGAACTTTCTCGTTTCAGCTTATTTAA</t>
         </is>
       </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>&gt;Flu-0330|A_NP</t>
         </is>
       </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>ATGGCGTCTCAAGGCACCAAACGATCCTATGAACAAATGGAAACTGGTGGGGAACGCCAGAATGCCACTGAAATCAGAGCATCTGTTGGAAGAATGGTTGGCGGAATAGGAAGATTCTACATACAGATGTGCACTGAGCTCAAACTCAGTGATTATGAAGGGAGGCTGATCCAAAACAGCATAACCATAGAAAGGATGGTTCTCTCGGCATTTGATGAGAGGAGGAACAAGTACCTGGAGGAACATCCCAGTGCCGGGAAGGATCCCAAGAAGACTGGAGGTCCAATCTACAGGAGGAGAGATGGCAAATGGGTGAGAGAGTTGATCCTCTACGACAAAGAAGAGATCAGAAGAATTTGGCGTCAAGCTAATAATGGAGAGGATGCAACTGCTGGTCTCACTCATTTGATGATTTGGCATTCCAATCTGAATGATGCAACATACCAGAGAACAAGGGCACTTGTGCGTACTGGAATGGACCCTAGAATGTGCTCTCTGATGCAAGGATCAACCCTCCCTAGGAGATCCGGGGCTGCTGGAGCAGCAGTGAAAGGAGTTGGAACAATGGTGATGGAACTAATTCGAATGATCAAGCGAGGGATCAATGATCGGAATTTCTGGAGAGGCGAAAACGGTCGGAGAACCAGGATTGCCTACGAGAGAATGTGCAACATCCTCAAGGGAAAGTTCCAAACAGCAGCACAACGGGCAATGATGGACCAAGTGAGAGAAAGCCGGAATCCTGGGAATGCTGAAATTGAAGATCTCATCTTTCTCGCACGATCTGCTCTCATCCTGAGGGGATCAGTGGCTCATAAGTCCTGTCTGCCTGCTTGCGTATATGGACTTGCTGTAGCCAGTGGATATGACTTTGAAAGAGAGGGATATTCTCTAGTCGGAATTGATCCTTTCCGTCTGCTCCAAAACAGCCAAGTCTTCAGTCTCATCAGACCGAACGAAAATCCAGCTCATAAGAGTCAGCTGGTATGGATGGCATGCCACTCTGCGGCATTTGAGGATCTGAGAGTTTCAAGCTTCATCAGAGGGACAAGAGTAGTCCCAAGAGGACAACTGTCCACCAGAGGAGTTCAGATTGCTTCAAATGAAAACATGGAGACAATGGACTCCAGTACTCTTGAACTGAGGAGCAGATACTGGGCTATAAGAACAAGAAGTGGAGGAAACACTAACCAACAGAGAGCATCTGCAGGACAAATCAGCGTGCAGCCCACATTCTCTGTGCAAAGAAACCTCCCATTCGAGAGAGCAACCATCATGGCAGCATTTACGGGAAACACTGAAGGCAGAACTTCAGACATGAGAACGGAGATCATAAGGATGATGGAAAATGCCAGACCTGAAGATGTGTCTTTCCAGGGGCGGGGAGTCTTCGAGCTCTCGGACGAAAAGGCAACGAACCCGATCGTGCCTTCCTTTGACATGAGTAATGAAGGATCTTATTTCTTCGGAGACAATGCAGAGGAGTATGACAATTAA</t>
         </is>
       </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>&gt;Flu-0330|A_MP</t>
         </is>
       </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>ATGAGTCTTCTAACCGAGGTCGAAACGTACGTTCTCTCTATCGTCCCGTCGGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTTGAAGATGTCTTTGCAGGGAAGAACACCGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATACTGTCACCTCTGACTAAGGGGATTTTGGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCTCTAAGTGGAAATGGAGACCCAAACAACATGGACAGGGCAGTCAAGTTGTACAGGAAACTGAAGAGAGAAATAACATTCCATGGGGCTAAAGAAGTTGCACTTAGTTACTCAACCGGTGCACTTGCCAGTTGTATGGGTCTCATATACAACAGGATGGGGACGGTGACCGCAGAAGTGGCATTGGGCCTAGTGTGTGCCACCTGTGAGCAGATTGCTGATTCACAGCATCGGTCTCACAGACAGATAGCTACCACCACCAACCCACTAATCAGACATGAAAACAGAATGGTTTTGGCCAGTACTACAGCTAAGGCTATGGAGCAGATGGCTGGATCGAGTGAGCAAGCAGTGGAAGCCATGGAGGTTGCTAGTCAGGCTAGGCAAATGGTGCAGGCGATGAGGACCATTGGAACTCATCCTAGCTCCAGTGCCGGTCTGAGAGATGATCTCCTTGAAAATTTGCAGGCCTACCAAAAACGAATGGGAGTGCAACTGCAGCGATTCAAGTGATCCTCTCGTTATTGCAGCAAGTATCATTGGGATCTTGCACTTGATATTGTGGATTCTTGATCGCCTTTTCTTCAAATGCGTTTATCGTCGCCTTAAATACGGTTTGAAAGGAGGGCCTTCTACGGAAGGAGTACCTGAGTCCATGAGGGAAGAGTACCGGCAGGAACAGCAGAGTGCTGTGGATGTTGACGATGGTCATTTTGTCAACATAGAGATGGAGTAA</t>
         </is>
       </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>&gt;Flu-0330|A_NS</t>
         </is>
       </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>ATGGATTCCAACACTGTGTCAAGCTTTCAGGTAGACTGCTTTCTTTGGCATGTCCGCAAACAATTTGCAGACCAAGAACTGGGTGATGCCCCATTCCTTGACCGGCTCCGCCGAGACCAGAAGTCTCTAAGAGGAAGAGGCAGCACTCTTGGTCTGGACATCGAGACGGCCACTCGTGCTGGAAAGCAGATAGTGGAGAGGATTCTGGAGGAAGAATCCGACGAGGCACTCAAAATGACTATTGCCTCTGTGCCTGCTCCACGCTACCTAACTGACATGACTCTTGAAGAGATGTCAAGAGACTGGTTCATGCTCATGCCCAAGCAAAAAGTGGCAGGCTCCCTCTGTATCAGAATGGACCAGGCGATTATGGATAAGAACATCATACTGAAGGCAAACTTCAGTGTGATCTTCAATCGGCTGGAGACACTAATACTACTCAGAGCTTTCACTGAAGAGGGAGCAATTGTCGGCGAAATTTCACCATTGCCTTCTCTTCCAGGACATACTGATGAGGATGTCAAAAATGCAATTGGGGTCCTCATCGGAGGACTTGAATGGAATGATAACACAGTTCGAGTCTCTGAAATTTTACAGAGATTCGCTTGGAGAAGCAGTAATGAGGATGGGAGACCTCCACTCCCTCCAAAGCAGAAACGGAAAATGGAGAGAACAATTGAGTCAGAAGTTTGAAGAAATAAGGTGGCTGATTGAAGAGGTGCGACACAGACTAAAGATCACAGAAAATAGTTTTGAACAAATAACATTTATGCAAGCCTTACAACTACTGCTTGAAGTGGAGCAAGAGATACGAACTTTCTCGTTTCAGCTTATTTAA</t>
         </is>
       </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>&gt;Flu-0402|A_PB2</t>
         </is>
       </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>ATGGAGAGAATAAAAGAACTAAGAGATCTAATGTCACAGTCTCGCACTCGCGAGATACTGACCAAAACCACTGTTGACCACATGGCCATAATCAAAAGGTACACATCGGGAAGGCAAGAGAAGAACCCCGCACTCAGAATGAAATGGATGATGGCAATGAAATATCCAATTACAGCAGATAAGCGAATAATGGAAATGATCCCTGAGAGGAATGAACAAGGGCAAACTCTCTGGAGCAAAACAAACGATGCCGGATCAGACCGAGTGATGGTATCACCCCTGGCTGTGACATGGTGGAACAGGAACGGACCAACAACAAGTACAGTTCACTACCCAAAGGTATATAAAACTTATTTCGAAAAAGTTGAAAGGTTGAAAAACGGGACCTTTGGCCCTGTGCACTTCAGAAACCAAGTTAAAATAAGACGGAGGGTCGATATAAACCCGGGCCATGCTGATCTCAGTGCCAAAGAGGCGCAGGATGTAATCATGGAAGTCGTCTTCCCAAATGAAGTGGGAGCAAGGATATTGACGTCGGAGTCACAACTGACGATAACAAAGGAGAAAAAGGAAGAACTCCAGGACTGCAAAATCGCTCCTCTGATGGTTGCATACATGCTAGAAAGAGAGTTGGTTCGCAAGACGAGGTTTCTCCCAGTTGCTGGTGGGACAAGCAGTGTCTACATTGAGGTGCTGCATTTGACCCAGGGGACATGCTGGGAGCAGATGTACACTCCGGGAGGAGAAGTGAGGAACGATGATGTAGACCAAAGCTTGATCATTGCTGCCAGGAATATAGTAAGAAGAGCAACAGTATCAGCAGATCCATTAGCATCTCTATTGGAGATGTGTCACAGCACACAAATTGGGGGAATAAGGATGGTGGACATCCTTCGGCAAAATCCAACAGAGGAACAAGCCGTGGATATATGCAAGGCAGCAATGGGCTTGAGGATTAGCTCATCTTTCAGCTTTGGTGGATTCACTTTTAAAAGAACAAGTGGATCGTCAGTCAAAAAAGAAGAAGAAGTGCTAACAGGCAACCTTCAAACATTGAAAATAAGAGTACATGAGGGGTATGAAGAGTTCACAATGGTTGGGAGAAGAGCAACGGCCATTCTCAGGAAAGCAACCAGAAGACTGATCCAGCTAATTGTAAGTGGGAGAGACGAGCAGTCAATTGCTGAAGCAATAATTGTGGCCATGGTATTCTCACAAGAGGACTGCATGATTAAAGCAGTTAGAGGTGACCTGAATTTTGTCAATAGGGCGAACCAGCGGCTAAACCCAATGCATCAACTCTTGAGGCATTTCCAAAAGGATGCAAAGGTGCTTTTCCAAAATTGGGGAATTGAACCCATTGACAATGTGATGGGAATGATCGGGGTAATGCCCGACATGACCCCAAGTACTGAGATGTCGCTGAGGGGAATAAGAGTCAGTAAGATGGGAGTAGATGAATACTCAAGTACAGAGCGAGTAGTAGTAAGTATCGACCGGTTTTTAAGAGTTCGAGACCAACAGGGAAACGTACTATTATCACCCGAAGAGGTCAGTGAGACACAAGGAACGGAGAAACTGACAATCACTTATTCGTCATCAATGATGTGGGAGATCAATGGTCCTGAGTCGGTATTGGTCAATACTTATCAGTGGATAATTAGAAACTGGGAAACCGTAAAAATTCAATGGTCACAGGRTCCCACAATGTTGTATAATAAGATGGAATTCGAGCCATTCCAGTCTCTAGTCCCTAAGGCAGCCAGAGGTCAATACAGTGGGTTTGTGAGAACACTATTCCAGCAAATGCGAGATGTGCTTGGAACATTTGACACTGTTCAGATAGTAAAACTCCTCCCCTTTGCTGCCGCCCCACCGGAACAAAGTAGGATGCAGTTCTCCTCTCTGACTGTGAATGTAAGAGGATCAGGAATGAGGATACTGGTAAGAGGCAATTCACCAGTGTTCAATTATAACAAGGCCACCAAGAGGCTCACAGTTCTCGGGAAAGATGCAGGTGCATTGACCGAAGATCCAGATGAAGGCACAGCTGGAGTGGAGTCTGCTGTTTTAAGAGGATTCCTCATTTTGGGCAAAGAAGACAAGAGATATGGCCCAGCATTGAGCATCAATGAGCTGAGCAATCTTGCAAAGGGAGAGAAGGCTAATGTGCTAATTGGGCAAGGAGACGTAGTGTTGGTGATGAAACGGAAACGGGACTCTAGCATACTTACTGACAGCCAGACAGCGACCAAAAGGATTCGGATGGCCATCAATTAG</t>
         </is>
       </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
+      <c r="EI1" t="inlineStr">
         <is>
           <t>&gt;Flu-0402|A_PB1</t>
         </is>
       </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
+      <c r="EJ1" t="inlineStr">
         <is>
           <t>ATGGATGTCAATCCGACTTTACTTTTCTTGAAGGTTCCAGCGCAAAATGCCATAAGCACCACATTCCCGTATACTGGAGATCCCCCATACAGCCATGGAACAGGAACAGGATATACCATGGACACAGTTAACAGAACACATCAGTATTCAGAAAAAGGGAAATGGACAACAAACTCAGAAACTGGAGCACCTCAACTCAATCCAATTGATGGACCATTGCCTGAAGACAATGAACCAAGTGGGTATGCACAAACGGACTGTGTCCTTGAAGCAATGGCTTTCCTTGAAGAGTCCCACCCAGGAATCTTTGAAAACTCGTGTCTTGAAACGATGGAAGTTGTTCAACAAACAAGAGTGGACAAGTTGACTCAAGGCCGTCAGACCTATGATTGGACGTTGAACAGGAATCAGCCGGCTGCAACTGCATTAGCTAATACTATAGAGATCTTCAGATCTAACGGCCTCACAGCCAATGAATCAGGAAGGCTAATAGATTTTCTCAAGGATGTGATGGAATCAATGGATAAGGAGGAAATGGAAATAACAACGCATTTCCAAAGGAAAAGAAGAGTGAGAGACAACATGACCAAGAAAATGGTCACACAAAGGACAATAGGAAAGAAGAAACAGAGGCTAAATAAAAAGAGCTATCTAATAAGAGCATTGACACTGAACACGATGACAAAAGACGCCGAAAGAGGCAAATTAAAAAGAAGGGCAATTGCGACACCTGGAATGCAAATCAGAGGGTTTGTGTACTTTGTTGAAACATTAGCGAGGAGCATTTGTGATAAGCTTGAACAATCTGGACTCCCAGTTGGGGGCAATGAAAAGAAGGCTAAACTGGCAAATGTTGTGAGAAAAATGATGACTAATTCGCAGGACACAGAGCTCTCTTTCACAATCACTGGAGACAACACCAAATGGAATGAAAATCAGAACCCTAGGATGTTTCTGGCAATGATAACATATATAACAAGGAACCAACCTGAATGGTTCAGGAATGTCTTAAGCATTGCACCTATAATGTTCTCAAATAAAATGGCAAGACTAGGGAAAGGGTACATGTTCGAAAGTAAGAGCATGAAGCTTCGAACACAAATACCAGCAGAAATGCTAGCAAGCATTGATATGAAGTACTTCAATGAGTCAACAAGAAAGAAAATAGAGAAGATAAGACCTCTTCTAATAGATGATACAGCCTCATTAAGCCCAGGAATGATGATGGGCATGTTCAATATGCTGAGTACAGTTTTGGGAGTTTCGATTCTAAATCTAGGACAAAGGAGGTACACCAAAACAACATACTGGTGGGACGGACTCCAATCCTCTGATGACTTTGCTCTCATAGTGAATGCTCCGAATCATGAGGGAATACAAGCAGGGGTAGACAGATTCTATAGAACCTGCAAACTGGTTGGAATCAACATGAGCAAAAAGAAGTCCTACATAAACAGGACAGGAACATTTGAATTCACAAGTTTTTTCTACCGCTATGGATTTGTAGCCAACTTCAGTATGGAGTTGCCCAGCTTTGGAGTGTCTGGGATCAATGAATCTGCAGACATGAGCATTGGAGTAACAGTGATAAAGAACAACATGATCAACAATGATCTTGGACCAGCAACAGCTCAAATGGCTCTTCAGCTATTCATCAAGGATTACAGATACACATACCGATGTCACAGAGGAGACACACAAATTCAGACAAGGAGGTCATTCGAGCTGAAGAAGTTGTGGGAACAGACCCGCTCAAAAGCAGGACTGCTGGTCTCAGATGGAGGGCCAAATCTATACAATATTCGGAATCTTCACATTCCAGAAGTCTGCTTGAAATGGGAGCTAATGGACGAAGACTATCAGGGAAGGCTTTGTAATCCCCTGAATCCGTTTGTCAGCCACAAGGAAATAGAGTCTGTGAACAACGCTGTGGTGATGCCAGCTCATGGCCCGGCCAAGAGCATGGAATATGATGCTGTTGCCACCACTCACTCCTGGATACCGAAGAGGAACCGCTCCATTCTCAATACAAGCCAAAGGGGAATCCTTGAAGACGAACAGATGTATCAAAAGTGCTGCAACCTGTTCGAAAAATTCTTCCCTAGCAGTTCATACAGGAGGCCAGTTGGAATTTCCAGCATGGTGGAGGCCATGGTTTCTAGGGCCCGAATTGACGCACGAATTGACTTCGAATCTGGACGGATTAAGAAGGAGGAGTTTGCTGAGACCATGAAGATCTGTTCCACCATTGAAGAGCTCAGACGGCAGAAATAG</t>
         </is>
       </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
+      <c r="EK1" t="inlineStr">
         <is>
           <t>&gt;Flu-0402|A_PA</t>
         </is>
       </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
+      <c r="EL1" t="inlineStr">
         <is>
           <t>ATGGAAGACTTTGTGCGACAATGCTTCAATCCAATGATTGTCGAGCTTGCGGAAAAAGCAATGAAAGAATATGGGGAAGATCCGAAAATCGAGACAAACAAATTTGCCGCAATATGCACACACTTAGAAGTCTGTTTCATGTATTCGGATTTCCATTTTATTGATGAACGAGGCGAATCAATGATTGTAGAATCTGGCGATCCAAATGCATTATTGAAACACCGATTTGAGATAATCGAAGGTAGAGACAGAGCAATGGCCTGGACAGTGGTGAATAGTATCTGCAACACCACAGGGGTCGAAAAGCCCAAATTCCTCCCTGATTTGTATGACTACAAAGAGAACCGATTCATTGAAATTGGGGTAACGCGAAGGGAAGTTCACATATACTATTTAGAAAAAGCCAACAAGATAAAATCAGAGAAAACACATATTCACATATTCTCATTCACTGGAGAGGAAATGGCCACCAAGGCGGACTACTCCCTTGATGAAGAGAGCAGAGCAAGAATAAAAACCAGACTGTTCACTATAAGACAAGAAATGGCCAGTAGAGGTCTATGGGATTCCTTTCGTCAATCCGAGAGAGGCGAAGAGACAATTGAAGAAAGATTTGAAATCACAGGAACCATGCGCAGGCTTGCCGACCAAAGTCTTCCACCGAACTTCTCCAGCCTTGAAAACTTTAGAGCCTATGTGGATGGATTCGAACCGAACGGCTGCATTGAGGGAAAACTTTCTCAAATGTCAAAAGAAGTGAACGCCAGAATTGAGCCATTTCTGAAGACAACACCACGCCCTCTCAGATTACCTGATGGGCCTCCCTGTTCTCAGCGATCGAAGTTCTTGCTGATGGATGCCCTTAAGTTGAGCATCGAAGACCCTAGCCATGAGGGGGAAGGCATACCGCTGTATGATGCAATCAAATGCATGAAGACATTTTTTGGCTGGAAAGAGCCCAACATCGTAAAGCCGCATGAGAAAGGCATAAACCCTAATTACCTCCTGGCTTGGAAGCAGGTGCTGGCAGAACTTCAAGACATTGAAAATGAGGAGAAAATTCCAAAAACAAAGAACATTAAGAAAACAAGCCAATTGAAGTGGGCACTTGGTGAGAACATGGCTCCAGAAAAAGTGGACTTTGAGGACTGCAAAGATGTTAGCGATCTAAGACAGTACGACAGTGACGAACCAGAGTCTAGATCACTAGCAAGCTGGATTCAGAGTGAATTCAACAAGGCATGCGAACTGACAGATTCGAGTTGGATTGAACTTGATGAGATAGGGGAAGACGTTGCTCCAATCGAACACATTGCGAGTGTGAGGAGGAACTATTTCACAGCGGAGGTATCCCATTGCAGGGCCACTGAATACATAATGAAGGGAGTATACATAAACACAGCCCTATTGAATGCATCCTGTGCAGCCATGGATGACTTCCAATTGATTCCAATGATAAGTAAGTGCAGAACTAAAGAAGGAAGACGGAAGACAAATCTGTATGGATTCATTATAAAAGGAAGATCCCATTTGAGGAATGACACCGATGTGGTAAACTTTGTGAGCATGGAATTCTCTCTAACTGACCCGAGGCTAGAGCCACACAAATGGGAAAAGTACTGTGTTCTTGAGATAGGAGACATGCTCCTACGGACTGCAATAGGCCAAGTGTCGAGGCCCATGTTCCTGTATGTGAGAACCAATGGAACTTCCAAGATCAAAATGAAATGGGGCATGGAGATGAGGCGATGCCTTCTTCAGTCCCTTCAACAAATTGAGAGCATGATTGAGGCCGAATCTTCTGTCAAAGAGAAGGACATGTCCAAGGAATTCTTTGAAAACAAATCAGAAACATGGCCAATTGGAGAATCACCCAAAGGGGTGGAGGAAGGCTCTATTGGGAAAGTGTGCAGAACATTGCTAGCAAAGTCTGTGTTCAACAGCCTATATGCATCTCCACAACTCGAGGGGTTTTCAGCTGAATCAAGAAAATTGCTTCTCATTGTTCAGGCACTTAGGGACAACCTGGAACCTGGAACCTTCGATCTTGGGGGGCTATATGAAGCAATTGAGGAGTGCCTGATTAACGATCCCTGGGTTTTGCTTAATGCATCTTGGTTCAACTCCTTCCTCACACATGCACTGAAATAG</t>
         </is>
       </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
+      <c r="EM1" t="inlineStr">
         <is>
           <t>&gt;Flu-0402|A_HA</t>
         </is>
       </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
+      <c r="EN1" t="inlineStr">
         <is>
           <t>ATGGAGAACATAGTACTACTTCTTGCAATAGTTAGCCTTGTTAAAAGTGATCAGATTTGCATTGGTTACCATGCAAACAATTCGACAGAGCAAGTTGACACGATAATGGAAAAGAACGTCACTGTTACACATGCCCAAGACATACTGGAAAAAACACACAACGGAAAGCTCTGTGATTTAAATGGGGTGAAGCCACTGATTTTAAAGGATTGTAGTGTAGCTGGATGGCTCCTCGGAAACCCAATGTGCGACGAATTCATCAGAGTGCCGGAATGGTCATACATAGTGGAGCGGGCTAACCCAGCCAATGACCTCTGTTACCCAGGGAGCCTCAATGACTATGAAGAACTGAAACACATGTTGAGCAGAATAAATCATTTTGAGAAGATTCAGATCATTCCCAAGAGTTCCTGGCCAAATCATGAAACATCACTAGGGGTGAGCGCAGCTTGTCCATACCAGGGAGCGCCCTCCTTTTTCAGAAATGTGGTATGGCTTATCAAAAAGAACGATGCATACCCAACAATAAAGATAAGCTACAATAATACTAATCGGGAAGATCTCTTGATACTTTGGGGGATTCATCATTCCAACAATGCAAAAGAACAGACAAATCTCTACAAAAACCCAACCACCTACATTTCAGTTGGAACATCAACTTTAAACCAGAGGTTGGCACCAAAAATAGCTACTAGATCCCAAGTAAACGGGCAACGTGGAAGAATGGACTTCTTCTGGACAATCTTAAAACCAGATGATGCAATCCATTTCGAGAGTAACGGAAATTTCATTGCTCCAGAATATGCATACAAAATTGTCAAGAAAGGGGACTCAACAGTTATGAAAAGTGGAGTGGAATATGGCCACTGCAACACCAAATGTCAAACCCCAGTAGGTGCGATAAATTCTAGTATGCCATTCCACAACATACATCCTCTCACCATTGGGGAATGTCCCAAATACGTGAAGTCAAACAAGTTGGTCCTTGCGACTGGGCTCAGAAATAGTCCTCTAAGAGAAAAGAGAAGAAAAAGAGGTCTGTTTGGGGCGATAGCAGGGTTTATAGAGGGAGGATGGCAGGGAATGGTTGATGGTTGGTATGGATACCATCATAGCAATRAGCAGGGGAGTGGGTACGCTGCGGACAAAGAATCCACCCAAAAGGCAATAGATGGAGTTACCAATAAGGTCAACTCAATCATTGACAAAATGAACACTCAATTTGAGGCAGTTGGAAGGGAGTTTAACAACTTAGAAARGAGGATAGAGAATTTGAACAAGAAAATGGAAGACGGATTCCTAGATGTCTGGACCTATAATGCTGAACTTCTAGTCCTCATGGAAAACGAGAGGACTCTAGACTTCCATGATTCAAATGTCAAGAACCTTTACGACAAAGTCAGATTACAGCTTAGGGATAATGCAAAGGAGCTGGGTAAYGGCTGTTTCGAATTCTATCACAAATGTGATAATGAATGTATGGAAAGTGTGAGAAATGGGACGTATGACTACCCTCAGTATTCAGAAGAAGCAAGATTAAAAAGAGAAGAAATAAGCGGAGTGAAATTAGAATCAGTAGGAACTTACCAGATACTGTCAATTTATTCAACAGCGGCAAGTTCCCTAGCACTGGCAATCATGATGGCTGGTCTATCTTTATGGATGTGCTCCAATGGGTCGTTACAATGCAGAATTTGCATTTAG</t>
         </is>
       </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
+      <c r="EO1" t="inlineStr">
         <is>
           <t>&gt;Flu-0402|A_NA</t>
         </is>
       </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
+      <c r="EP1" t="inlineStr">
         <is>
           <t>ATGAATCCAAATCAAAAGATAACAACCATTGGATCAATCTGTATGGTAATTGGGATAGTCAGCTTGATGCTGCAAATTGGGAACATAATCTCAATATGGGTTAGCCATTCAATCCAAACAGGGAATCAATACCAGCCTGAACCATGCAATCAAAGCATCATTACCTATGAGAACAACACCTGGGTAAATCAGACGTATGTCAACATCAGCAATACCAATTTTCTTGCTGAGCAGGCTGTTACTTCGGTAACATTAGCGGGCAATTCATCTCTTTGCCCTATTAGTGGGTGGGCAATATACAGTAAGGACAACGGTATAAGAATTGGGTCCAAGGGGAATGTGTTTGTTATAAGAGAACCGTTCATCTCATGCTCCCACTTGGAATGCAGAGCCTTTTTCCTGACCCAGGGAGCTCTGCTGAATGACAAACATTCTAATGGGACAGTTAAGGATAGAAGCCCTTATAGAACTTTGATGAGTTGTCCCGTGGGTGAGGCTCCTTCCCCGTATAATTCAAGATTTGAGTCTGTTGCTTGGTCGGCAAGTGCTTGTCATGATGGCATCAGTTGGTTGACAATCGGTATTTCTGGTCCAGACAATGGAGCTGTGGCTGTATTGAAGTACAATGGCATAATAAYGGATACTATCAAGAGTTGGAGAAACAACATTTTGAGAACTCAAGAATCTGAATGTGCTTGCGTAAATGGCTCTTGCTTCACCGTAATGACTGATGGACCAAGCAATGGGCAGGCCTCATATAAAATCTTCAAGATAGAGAAAGGGAAAGTTGTCAAGTCAGTTGAGATGAATGCCCCTAATTACCACTACGAGGAATGCTCCTGTTATCCTGATGCGGGTGATATTATGTGTGTGTGCAGGGACAATTGGCATGGCTCAAATCGGCCGTGGGTATCTTTTAATCAAAATCTGGAGTATCAAATAGGATATATATGCAGTGGGGTATTCGGGGACAATCCCCGCCCCAATGATGGAACAGGCAGTTGCAGTCCAATGCCCTCYAATGGGGCATATGGGGTAAAAGGGTTTTCATTTAAGTACGGTAATGGGGTTTGGATCGGAAGAACAAAAAGCACTAGTTCCAGAAGCGGCTTTGAGATGATTTGGGATCCGAATGGGTGGACTGAGACGGACAGTAGTTTCTCAGTGAAGCAAGACATTGTAGAAATAACTGACTGGTCAGGATATAGTGGGAGTTTTGTCCAGCATCCAGAACTGACAGGATTAGATTGCATGAGGCCTTGTTTCTGGGTTGAGCTAATCAGAGGGAGGCCCAAAGAGAACACAATTTGGACTAGCGGGAGCAGCATATCCTTTTGTGGTGTAAATAGTGACACTGTGGGTTGGTCTTGGCCAGACGGTGCTGAGTTGCCATTCACCATTGACAAGTAG</t>
         </is>
       </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
+      <c r="EQ1" t="inlineStr">
         <is>
           <t>&gt;Flu-0402|A_MP</t>
         </is>
       </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
+      <c r="ER1" t="inlineStr">
         <is>
           <t>ATGAGTCTTCTAACCGAGGTCGAAACGTACGTTCTCTCTATCGTCCCGTCGGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTTGAAGATGTCTTTGCAGGGAAGAACACCGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATCCTGTCACCTCTGACTAAGGGGATTTTGGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCTCTAAGTGGAACTGGAGACCCAAACAACATGGACAGGGCAGTCAAGTTGTACAGGAAACTAAAGAGAGAGATAACATTCCACGGTGCTAAAGAAGTTGCACTCAGTTACTCAACCGGTGCACTTGCCAGTTGTATGGGTCTCATATACAACAGGATGGGGACGGTGACCGCAGAAGTGGCATTGGGCCTAGTGTGTGCCACCTGTGAGCAGATTGCTGATTCACAGCATCGGTCTCACAGACAGATAGCTACCACCACCAACCCACTAATCAGACATGAAAACAGAATGGTTTTGGCCAGTACTACAGCTAAGGCTATGGAGCAGATGGCTGGATCGAGTGAGCAAGCAGTGGAAGCCATGGAGGTTGCTAGTCAGGCTAGGCAGATGGTGCAGGCGATGAGGACCATTGGAACTCATCCTAGCTCCAGTGCCGGTCTGAGAGATGATCTCCTTGAAAATTTGCAGGCCTACCAAAAACGGATGGGAGTGCAACTGCAGCGATTCAAGTGATCCTCTCGTTATTGCCGCAAGTATCATTGGGATCTTGCACTTGATATTGTGGATTCTTGATCGCCTTTTCTTCAAATGCGTTTATCGTCGCCTTAAATACGGTTTGAAAGGAGGGCCTTCTACGGAAGGAGTACCTGAGTCCATGAGGGAAGAGTACCGGCAGGAACAGCAGAGTGCTGTGGATGTCGACGATGGTCATTTTGTCAACATAGAGCTGGAGTAA</t>
         </is>
       </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
+      <c r="ES1" t="inlineStr">
         <is>
           <t>&gt;Flu-0402|A_NS</t>
         </is>
       </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
+      <c r="ET1" t="inlineStr">
         <is>
           <t>ATGGATTCCAACACTGTGTCAAGCTTTCAGGTAGACTGCTTTCTTTGGCATGTCCGCAAACGATTTGCAGACCAAGAACTGGGTGATGCCCCATTCCTTGACCGGCTCCGCCGAGACCAGAAGTCTCTAAGAGGAAGAGGCAGCACTCTTGGTCTGGACATCGAGACGGCCACTCGTGCTGGAAAGCAGATAGTGGAGAGGATTCTGGAGGAAGAATCCGACGAGGCACTCAAAATGACTATTGCCTCTGTGCCTGCTCCACGCTACCTAACTGACATGACTCTTGAAGAGATGTCAAGAGACTGGTTCATGCTCATGCCCAAGCAAAAAATGGCAGGCTCCCTCAGTATCAAAATGGACCAGGCGATTATGGATAAGAAAATCATACTGAAGGCAAACTTCAGTGTGATCTTCAATCGGCTGGAGACACTAATACTACTCAGAGCTTTCACTGAAGAAGGAGCAATTGTCGGCGAAATTTCACCATTGCCTTCTCTTCCAGGACATACTGATGAGGATGTCAAAAATGCAATTGGGGTCCTCATCGGAGGACTTGAATGGAATGATAACACAGTTCGAGTCTCTGAAACTTTACAGAGATTCGCTTGGAGAAGCAGTAATGAGGATGGGAGATCTCCACTCCCTCCAAAGCAGAAACGGAAAATGGAGAGAACAATTGAGTCAGAAGTTTGAAGAAATAAGGTGGCTGATTGAAGAAGTTCGACACAGACTAAAGATCACAGAAAATAGTTTTGAACAAATAACATTTATGCAAGCCTTACAACTACTGCTTGAAGTGGAGCAAGAGATAAGAACTTTCTCGTTTCAGCTTATTTAA</t>
         </is>
       </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
+      <c r="EU1" t="inlineStr">
         <is>
           <t>&gt;Flu-0403|A_MP</t>
         </is>
       </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
+      <c r="EV1" t="inlineStr">
         <is>
           <t>ATGAGTCTTCTAACCGAGGTCGAAACGTACGTTCTCTCTATCGTCCCGTCGGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTTGAAGATGTCTTTGCAGGGAAGAACACCGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATCCTGTCACCTCTGACTAAGGGGATTTTGGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCTCTAAGTGGAACTGGAGACCCAAACAACATGGACAGGGCAGTCAAGTTGTACAGGAAACTAAAGAGAGAGATAACATTCCAYGGTGCTAAAGAAGTTGCACTCAGTTACTCAACCGGTGCACTTGCCAGTTGTATGGGTCTCATATACAACAGGATGGGGACGGTGACCGCAGAAGTGGCATTGGGCCTAGTGTGTGCCACCTGTGAGCAGATTGCTGATTCACAGCATCGGTCTCACAGACAGATAGCTACCACCACCAACCCACTAATCAGACATGAAAACAGAATGGTTTTGGCCAGTACTACAGCTAAGGCTATGGAGCAGATGGCTGGATCGAGTGAGCAAGCAGTGGAAGCCATGGAGGTTGCTAGTCAGGCTAGGCAGATGGTGCAGGCGATGAGGACCATTGGAACTCATCCTAGCTCCAGTGCCGGTCTGAGAGATGATCTCCTTGAAAATTTGCAGGCCTACCAAAAACGGATGGGAGTGCAACTGCAGCGATTCAAGTGATCCTCTCGTTATTGCCGCAAGTATCATTGGGATCTTGCACTTGATATTGTGGATTCTTGATCGCCTTTTCTTCAAATGCGTTTATCGTCGCCTTAAATACGGTTTGAAAGGAGGGCCTTCTACGGAAGGAGTACCTGAGTCCATGAGGGAAGAGTACCGGCAGGAACAGCAGAGTGCTGTGGATGTYGACGATGGTCATTTTGTCAACATAGAGCTGGAGTAA</t>
         </is>
       </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
+      <c r="EW1" t="inlineStr">
         <is>
           <t>&gt;Flu-0406|A_PB2</t>
         </is>
       </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
+      <c r="EX1" t="inlineStr">
         <is>
           <t>ATGGAGAGAATAAAAGAACTAAGAGATCTAATGTCACAGTCTCGCACTCGCGAGATACTGACCAAAACCACTGTTGACCACATGGCCATAATCAAAAGGTACACATCGGGAAGGCAAGAGAAGAACCCCGCACTCAGAATGAAATGGATGATGGCAATGAAATATCCAATTACAGCAGATAATCGAATAATGGAAATGATCCCTGAGAGGAATGAACAAGGGCAAACTCTCTGGAGCAAAACAAACGATGCCGGATCAGACCGAGTGATGGTATCACCCCTGGCTGTGACATGGTGGAACAGGAACGGACCAACAACAAGTACAGTTCACTACCCAAAGGTATATAAAACTTAYTTCGAAAAAGTTGAAAGGTTGAAAAACGGGACCTTTGGCCCTGTGCACTTCAGAAACCAAGTTAAAATAAGACGGAGGGTCGATATAAACCCGGGCCATGCTGATCTCAGTGCCAAAGAGGCGCAGGATGTAATCATGGAAGTCGTCTTCCCAAATGAAGTGGGAGCAAGGATATTGACGTCGGAGTCACAACTGACGATAACAAAGGAGAAAAAGGAAGAACTCCAGGACTGCAAAATCGCTCCTCTGATGGTTGCATACATGCTAGAAAGAGAGTTGGTTCGCAAGACGAGGTTTCTCCCAGTTGCTGGTGGGACAAGCAGTGTCTACATTGAGGTGCTGCATTTGACCCAGGGGACATGCTGGGAGCAGATGTACACTCCGGGAGGAGAAGTGAGGAACGATGATGTAGACCAAAGCTTGATCATTGCTGCCAGGAATATAGTAAGAAGAGCAACAGTATCAGCAGATCCATTAGCATCTCTATTGGAGATGTGTCACAGCACACAAATTGGGGGAATAAGGATGGTGGACATCCTTCGGCAAAATCCAACAGAAGAACAAGCCGTGGATATATGCAAGGCAGCAATGGGCTTGAGGATTAGCTCATCTTTCAGCTTTGGTGGATTCACTTTTAAAAGAACAAGTGGATCGTCAGTCAAAAAAGAAGAAGAAGTGCTAACAGGCAACCTTCAAACATTGAAAATAAGAGTACATGAGGGGTATGAAGAGTTCACAATGGTTGGGAGAAGAGCAACGGCCATTCTCAGGAAAGCAACCAAAAGACTGATCCAGCTAATTGTAAGTGGGAGAGACGAGCAGTCAATTGCTGAAGCAATAATTGTGGCCATGGTATTCTCACAAGAGGACTGCATGATTAAAGCAGTTAGAGGTGACCTGAATTTTGTCAATAGGGCGAACCAGCGACTAAACCCAATGCATCAACTCTTGAGGCATTTCCAAAAGGATGCAAAGGTGCTTTTCCAAAATTGGGGAATTGAACCCATTGACAATGTGATGGGAATGATCGGGGTAATGCCCGACATGACCCCAAGTACTGAGATGTCGCTGAGGGGAATAAGAGTCAGTAAGATGGGAGTAGATGAATACTCAAGTACAGAGCGAGTAGTAGTAAGTATCGACCGGTTTTTAAGAGTTCGAGACCANNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNTAATNNGAAANTNGGAAACCGTAAAAATTCAATGGTCACAGGATCCCACAATGTTGTATAATAAGATGGAATTCGAGCCATTCCAGTCTCTAGTCCCTAAGGCAGCCAGAGGTCAATACAGTGGGTTTGTGAGAACACTATTCCAGCAAATGCGAGATGTGCTTGGAACATTTGACACTGTTCAGATAGTAAAACTCCTCCCCTTTGCTGCCGCCCCACCGGAACAAAGTAGGATGCAGTTCTCCTCCCTGACTGTGAATGTAAGAGGATCAGGAATGAGGATACTGGTAAGAGGCAATTCACCAGTGTTCAATTATAACAAGGCCACCAAGAGGCTCACAGTTCTCGGGAAAGATGCAGGTGCATTGACCGAAGATCCAGATGAAGGCACAGCTGGAGTGGAGTCTGCTGTTTTAAGAGGATTCCTCATTTTGGGCAAAGAAGACAAGAGATATGGCCCAGCATTGAGCATCAATGAGCTGAGCAATCTTGCAAAGGGAGAGAAGGCTAATGTGCTAATTGGGCAAGGAGACGTAGTGTTGGTGATGAAACGGAAACGGGACTCTAGCATACTTACTGACAGCCAGACAGCGACCAAAAGGATTCGGATGGCCATCAATTAG</t>
         </is>
       </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
+      <c r="EY1" t="inlineStr">
         <is>
           <t>&gt;Flu-0406|A_PB1</t>
         </is>
       </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
+      <c r="EZ1" t="inlineStr">
         <is>
           <t>ATGGATGTCAATCCGACTTTACTTTTCTTGAAGGTTCCAGCGCAAAATGCCATAAGCACCACATTCCCGTATACTGGAGATCCCCCATACAGCCATGGAACAGGAACAGGATATACCATGGACACAGTTAACAGAACACATCAGTATTCAGAAAAAGGGAAATGGACAACAAACTCAGAAACTGGAGCACCTCAACTCAATCCAATTGATGGACCATTGCCTGAGGACAATGAACCAAGTGGGTATGCACAAACGGACTGTGTCCTTGAAGCAATGGCTTTCCTTGAAGAGTCCCACCCAGGAATCTTTGAAAACTCGTGTCTTGAAACGATGGAAGTTGTTCAACAAACAAGAGTGGACAAGTTGACTCAAGGCCGTCAGACCTATGATTGGACGTTGAACAGGAATCAGCCGGCTGCAACTGCATTAGCTAATACTATAGAGATCTTCAGATCTAACGGCCTCACAGCCAATGAATCAGGAAGGCTAATAGATTTTCTCAGGGATGTGATGGAATCAATGGATAAGGAGGAAATGGAAATAACAACGCATTTCCAAAGGAAAAGAAGAGTGAGAGACAACATGACCAAGAAAATGGTCACACAAAGGACAATAGGAAAGAAGAAACAGAGGCTAAATAAAAAGAGCTATCTAATAAGAGCATTGACACTGAACACGATGACAAAAGAYGCCGAAAGAGGCAAATTAAAAAGAAGGGCAATTGCGACACCTGGAATGCAAATCAGAGGGTTTGTGTACTTTGTTGAAACATTAGCGAGGAGCATTTGTGATAAGCTTGAACAATCTGGACTCCCAGTTGGGGGCAATGAAAAGAAGGCTAAACTGGCAAATGTCGTGAGAAAAATGATGACCAATTCGCAGGACACAGAGCTCTCTTTCACAATCACTGGAGACAACACCAAATGGAATGAAAATCAGAACCCTAGGATGTTTCTGGCAATGATAACATATATAACAAGGAACCAACCTGAATGGTTCAGGAATGTCTTAAGCATTGCACCTATAATGTTCTCAAATAAAATGGCAAGACTAGGGAAAGGGTACATGTTCGAAAGTAAGAACATGAAGCTTCGAACACAAATACCAGCAGAAATGCTAGCAAGCATTGATATGAAGTACTTCAATGAGTCAACAAGAAAGAAAATAGAGAAGATAAGACCTCTTCTAATAGATGATACAGCCTCATTAAGCCCAGGAATGATGATGGGCATGTTCAATATGCTGAGTACAGTTTTGGGAGTTTCGATTCTAAATCTAGGACAAAGGAGGTACACCAAAACAACATACTGGTGGGACGGACTCCAATCCTCTGATGACTTTGCTCTCATAGTGAATGCTCCGAATCATGAGGGAATACAAGCAGGGGTAGACAGATTCTATAGAACCTGCAAACTGGTTGGAATCAACATGAGCAAAAAGAAGTCCTACATAAACAGGACAGGAACATTTGAATTCACAAGTTTTTTCTACCGCTATGGATTTGTAGCCAACTTCAGTATGGAGTTGCCCAGCTTTGGAGTGTCTGGGATCAATGAATCTGCAGACATGAGCATTGGAGTAACAGTGATAAAGAACAACATGATCAACAATGATCTTGGACCAGCAACAGCTCAAATGGCTCTTCAGCTATTCATCAAGGATTACAGATACACATACCGATGTCACAGAGGAGACACACAAATTCAGACAAGGAGGTCATTCGAGCTGAAGAAGTTGTGGGAACAGACCCGCTCAAAAGCAGGACTGCTGGTCTCAGATGGAGGACCAAATCTATACAATATTCGGAATCTTCACATTCCAGAAGTCTGCTTGAAATGGGAGCTAATGGACGAAGACTATCAGGGAAGGCTTTGTAATCCCCTGAATCCGTTTGTCAGCCACAAGGAAATAGAGTCTGTGAACAACGCTGTGGTGATGCCAGCTCATGGCCCGGCCAAGAGCATGGAATATGATGCTGTTGCCACCACTCACTCCTGGATACCGAAGAGGAACCGCTCCATTCTCAATACAAGCCAAAGGGGAATCCTTGAAGACGAACAGATGTATCAAAAGTGCTGCAATCTGTTCGAAAAATTCTTCCCTAGCAGTTCATACAGGAGGCCAGTTGGAATTTCCAGCATGGTGGAGGCCATGGTTTCTAGGGCCCGAATTGACGCACGAATTGACTTCGAATCTGGACGGATTAAGAAGGAGGAGTTTGCTGAGATCATGAAGATCTGTTCCACCATTGAAGAGCTCAGACGGCAGAAATAG</t>
         </is>
       </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
+      <c r="FA1" t="inlineStr">
         <is>
           <t>&gt;Flu-0406|A_PA</t>
         </is>
       </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
+      <c r="FB1" t="inlineStr">
         <is>
           <t>ATGGAAGACTTTGTGCGACAATGCTTCAATCCAATGATTGTCGAGCTTGCGGAAAAAGCAATGAAAGAATATGGGGAAGATCCGAAAATCGAGACAAACAAATTTGCCGCAATATGCACACACTTAGAAGTCTGTTTCATGTATTCGGATTTCCATTTTATTGATGAACGAGGCGAATCAATGATTGTAGAATCTGGCGATCCAAATGCATTATTGAAACACCGATTTGAGATAATCGAAGGTAGAGACAGAGCAATGGCCTGGACAGTGGTGAATAGTATCTGCAACACCACAGGGGTCGAAAAGCCCAAATTCCTCCCTGATTTGTATGACTACAAAGAGAACCGATTCATTGAAATTGGGGTAACGCGAAGGGAAGTTCACATATACTATTTAGAAAAAGCCAACAAGATAAAATCAGAGAAAACACATATTCACATATTCTCATTCACTGGAGAGGAAATGGCCACCAAGGCGGACTACTCCCTTGATGAAGAGAGCAGAGCAAGAATAAAAACCAGACTGTTCACTATAAGACAAGAAATGGCCAGTAGAGGTCTATGGGATTCCTTTCGTCAATCCGAGAGAGGCGAAGAGACAATTGAAGAAAGATTTGAAATCACAGGAACCATGCGCAGGCTTGCCGACCAAAGTCTTCCACCGAACTTCTCCAGCCTTGAAAACTTTAGAGCCTATGTGGATGGATTCGAACCGAACGGCTGCATTGAGGGCAAACTTTCTCAAATGTCAAAAGAAGTGAACGCCAGAATTGAGCCATTTCTGAAGACAACACCACGCCCTCTCAGATTACCTGATGGGCCTCCCTGTTCTCAGCGATCGAAGTTCTTGCTGATGGATGCCCTTAAGTTGAGCATCGAAGACCCTAGCCATGAGGGGGAAGGCATACCGCTGTATGATGCAATCAAATGCATGAAGACATTTTTTGGCTGGAAAGAGCCCAACATCGTAAAGCCGCATGAGAAAGGCATAAACCCTAATTACCTCCTGGCTTGGAAGCAGGTGCTGGCAGAACTTCAAGACATTGAAAATGAGGAGAAAATTCCAAAAACAAGGAACATGAAGAAAACAAGCCAATTGAAGTGGGCACTTGGTGAGAACATGGCTCCAGAAAAAGTGGACTTTGAGGACTGCAAAGATGTTAGCGATCTAAGACAGTACGACAGTGACGAACCAGAGTCTAGATCACTAGCAAGCTGGATTCAGAGTGAATTCAACAAGGCATGCGAACTGACAGATTCGAGTTGGATTGAACTTGATGAGATAGGGGAAGACGTTGCTCCAATCGAACACATTGCGAGTGTGAGGAGGAACTATTTCACAGCGGAGGTATCCCATTGCAGGGCCACTGAATACATAATGAAGGGAGTATACATAAACACAGCCCTATTGAATGCATCCTGTGCAGCCATGGATGACTTCCAATTGATTCCAATGATAAGTAAGTGCAGAACTAAAGAAGGAAGACGGAAGACAAATCTGTATGGATTCATTATAAAAGGAAGATCCCATTTGAGGAATGACACCGATGTGGTAAACTTTGTGAGCATGGAATTCTCTCTAACTGACCCAAGGCTAGAGCCACACAAATGGGAAAAGTACTGTGTTCTTGAGATAGGAGACATGCTCCTACGGACTGCAATAGGCCAAGTGTCGAGGCCCATGTTCCTGTATGTGAGAACCAATGGAACTTCCAAGATCAAAATGAAATGGGGCATGGAGATGAGGCGATGCCTTCTTCAGTCCCTTCAACAAATTGAGAGCATGATTGAGGCCGAATCTTCTGTCAAAGAGAAGGACATGTCCAAGGAATTCTTTGAAAACAAATCAGAAACATGGCCAATTGGGGAATCACCCAAAGGGGTGGAGGAAGGCTCTATTGGGAAAGTGTGCAGAACATTGCTAGCAAAGTCTGTGTTCAACAGCCTATATGCATCTCCACAACTCGAGGGGTTTTCAGCTGAATCAAGAAAATTGCTTCTCATTGTTCAGGCACTTAGGGACAACCTGGAACCTGGAACCTTCGATCTTGGGGGGCTATATGAAGCAATTGAGGAGTGCCTGATTAACGATCCCTGGGTTTTGCTTAATGCATCTTGGTTCAACTCCTTCCTCACACATGCACTGAAATAG</t>
         </is>
       </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
+      <c r="FC1" t="inlineStr">
         <is>
           <t>&gt;Flu-0406|A_HA</t>
         </is>
       </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
+      <c r="FD1" t="inlineStr">
         <is>
           <t>ATGGAGAACATAGTACTACTTCTTGCAATAGTTAGCCTTGTTAAAAGTGATCAGATTTGCATTGGTTACCATGCAAACAATTCGACAGAGCAAGTTGACACGATAATGGAAAAGAACGTCACTGTTACACATGCCCAAGACATACTGGAAAAAACACACAACGGAAAGCTCTGTGATTTAAATGGGGTGAAGCCACTGATTTTAAAGGATTGTAGTGTAGCTGGATGGCTCCTCGGAAACCCAATGTGCGACGAATTCATCAGAGTGCCGGAATGGTCATACATAGTGGAGCGGGCTAACCCAGCTAATGACCTCTGTTACCCAGGGAGCCTCAATGACTATGAAGAACTGAAACACATGTTGAGCAGAATAAATCATTTTGAGAAGATTCAGATCATTCCCAAGAGTTCCTGGCCAAATCATGAAACATCACTAGGGGTGAGCGCAGCTTGTCCATACCAGGGAGCGCCCTCCTTTTTCAGAAATGTGGTGTGGCTTATCAAAAAGAACGATGCATACCCAACAATAAAGATAAGCTACAATAATACTAATCGGGAAGATCTCTTGATACTTTGGGGGATTCATCATTCCAACAATGCAAAAGAACAGACAAATCTCTACAAAAACCCAACCACCTACATTTCAGTTGGAACATCAACTTTAAACCAGAGGTTGGCACCAAAAATAGCTACTAGATCCCAAGTAAACGGGCAACGTGGAAGAATGGACTTCTTCTGGACAATCTTAAAACCAGATGATGCAATCCATTTCGAGAGTAACGGAAATTTCATTGCTCCAGAATATGCATACAAAATTGTCAAGAAAGGGGACTCAACAGTTATGAAAAGTGGAGTGGAATATGGCCACTGCAACACCAAATGTCAAACCCCAGTAGGTGCGATAAATTCTAGTATGCCATTCCACAACATACATCCTCTCACCATCGGGGAATGTCCCAAATACGTGAAGTCAAACAAGTTGGTCCTTGCGACTGGGCTCAGAAATAGTCCTCTAAGAGAAAAGAGAAGAAAAAGAGGTCTGTTTGGGGCGATAGCAGGGTTTATAGAGGGAGGATGGCAGGGAATGGTTGATGGTTGGTATGGATACCATCATAGCAATGAGCAGGGGAGTGGGTACGCTGCGGACAAAGAATCCACCCAAAAGGCAATAGATGGAATTACCAATAAGGTCAACTCAATCATTGACAAAATGAACACTCAATTTGAGGCAGTTGGAAGGGAGTTTAACAACTTAGAAAGGAGGATAGAGAATTTGAACAAGAAAATGGAAGACGGATTCCTAGATGTCTGGACCTATAATGCTGAACTTCTAGTCCTCATGGAAAACGAGAGGACTCTAGACTTCCATGATTCAAATGTCAAGAACCTTTACGACAAAGTCAGATTACAGCTTAGGGATAATGCAAAGGAGCTGGGTAACGGCTGTTTCGAATTCTATCACAAATGTGATAATGAATGTATGGAAAGTGTGAGAAATGGGACGTATGACTACCCTCAGTATTCAGAAGAAGCAAGATTAAAAAGAGAAGAAATAAGCGGAGTGAAATTAGAATCAGTAGGAACTTACCAGATACTGTCAATTTATTCAACAGCGGCAAGTTCCCTAGCACTGGCAATCATGATGGCTGGTCTATCTTTATGGATGTGCTCCAATGGGTCGTTACAATGCAGAATTTGCATTTAG</t>
         </is>
       </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
+      <c r="FE1" t="inlineStr">
         <is>
           <t>&gt;Flu-0406|A_NP</t>
         </is>
       </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
+      <c r="FF1" t="inlineStr">
         <is>
           <t>ATGGCGTCTCAAGGCACCAAACGATCCTATGAACAAATGGAAACTGGTGGGGAACGCCAGAATGCCACTGAAATCAGAGCATCTGTTGGAAGAATGGTTGGCGGAATCGGGAGATTCTACATACAGATGTGTACTGAACTCAAACTCAGTGATTACGAAGGGAGGCTGATCCAAAACAGCATAACCATAGAAAGGATGGTTCTCTCGGCATTTGATGAGAGGAGGAACAAGTACCTGGAGGAACATCCCAGTGCCGGGAAGGATCCCAAGAAGACTGGAGGTCCAATCTACAGGAGGAGAGATGGCAAATGGGTGAGAGAGTTGATCCTCTACGACAAAGAAGAGATCAGAAGAATTTGGCGTCAAGCTAATAATGGAGAGGATGCAACTGCTGGTCTCACTCACTTGATGATTTGGCATTCCAATCTGAATGATGCCACATACCAGAGAACAAGGGCACTTGTGCGTACTGGAATGGACCCTAGAATGTGCTCTCTGATGCAAGGCTCAACCCTCCCTAGGAGATCAGGGGCTGCTGGAGCAGCAGTGAAAGGAGTTGGAACAATGGTGATGGAACTAATTCGAATGATCAAACGAGGGATCAATGATCGGAATTTCTGGAGAGGCGAAAACGGTCGGAGAACCAGGATTGCCTACGAGAGAATGTGCAACATTCTCAAGGGAAAGCTCCAAACAGCAGCACAACGGGCAATGATGGACCAAGTGAGAGAAAGCCGGAATCCTGGGAATGCTGAAATTGAAGATCTCATCTTTCTCGCACGATCTGCTCTCATCCTGAGGGGATCAGTGGCTCATAAGTCCTGTCTGCCTGCTTGCGTATATGGACTTGCTGTAGCCAGTGGATATGACTTTGAAAGAGAGGGATATTCTCTAGTCGGAATTGATCCTTTCCGTCTGCTCCAAAACAGCCAAGCCTTCAGTCTCATCAGACCGAACGAAAATCCAGCTCATAAAAGTCAGCTGGTATGGATGGCATGCCACTCTGCGGCATTTGAGGATCTGAGAGTGTCAAGCTTCATCAGAGGGACAAGAGTAGTCCCAAGAGGACAACTGTCCACCAGAGGAGTTCAGATTGCTTCAAATGAAAACATGGAGACAATGGACTCCAGTACTCTTGAACTGAGGAGCAGATATTGGGCTATAAGAACAAGAAGTGGAGGAAACACTAACCAACAGAGAGCATCTGCAGGACAAATCAGCGTACAGCCCACATTCTCTGTACAAAGAAACCTCCCATTCGAGAGAGCAACCATCATGGCAGCATTTACGGGAAACACTGAAGGCAGAACTTCAGATATGAGAACTGAGATCATAAGGATGATGGAAAATGCCAGACCTGAAGATGTGTCTTTCCAGGGGCGGGGAGTCTTCGAGCTCTCGGACGAAAAGGCAACGAACCCGATCGTGCCTTCCTTTGACATGAGTAATGAAGGATCTTATTTCTTCGGAGACAATGCAGAGGAGTATGACAATTAA</t>
         </is>
       </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
+      <c r="FG1" t="inlineStr">
         <is>
           <t>&gt;Flu-0406|A_NA</t>
         </is>
       </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
+      <c r="FH1" t="inlineStr">
         <is>
           <t>ATGAATCCAAATCAAAAGATAACAACCATTGGATCAATCTGTATGGTAATTGGGATAGTCAGCTTGATGCTGCAAATTGGGAACATAATCTCAATATGGGTTAGCCATTCAATCCAAACAGGGAATCAATACCAGCCTGAACCATGCAATCAAAGCATCATTACCTATGAGAACAACACCTGGGTAAATCAGACGTATGTCAACATCAGCAATACCAATTTTCTTGCTGAGCAAGCTGTTACTTCGGTAACATTAGCGGGCAATTCATCTCTTTGCCCTATTAGTGGGTGGGCAATATACAGTAAGGACAACGGTATAAGAATTGGGTCCAAGGGGAATGTGTTTGTTATAAGAGAACCGTTCATCTCATGCTCCCACTTGGAATGCAGAGCCTTTTTCCTGACCCAGGGAGCTCTGCTGAATGACAAACATTCTAATGGGACAGTTAAGGATAGAAGCCCTTATAGAACTTTGATGAGTTGTCCCGTGGGTGAGGCTCCTTCCCCGTATAATTCAAGATTTGAGTCTGTTGCTTGGTCGGCAAGTGCTTGTCATGATGGCATCAGTTGGTTGACAATCGGTATTTCTGGTCCAGACAATGGAGCTGTGGCTGTATTGAAGTACAATGGCATAATAACGGATACTATCAAGAGTTGGAGAAACAACATTTTAAGAACTCAAGAATCTGAATGTGCTTGCGTAAATGGCTCTTGCTTCACCGTAATGACTGATGGACCAAGCAATGGGCAGGCCTCATATAAAATCTTCAAGATAGAGAAAGGGAAAGTTGTCAAGTCAGTTGAGATGAATGCCCCTAATTACCACTACGAGGAATGCTCCTGTTATCCTGATGCGGGTGATATTATGTGTGTGTGCAGGGACAATTGGCATGGCTCAAATCGGCCGTGGGTATCTTTTAATCAAAATCTGGAGTATCAAATAGGATATATATGCAGTGGGGTTTTCGGGGACAATCCCCGCCCCAATGATGGAACAGGCAGTTGCAGTCCAATGCCCTCTAATGGGGCATATGGGGTAAAAGGGTTTTCATTTAAGTACGGTAATGGGGTTTGGATCGGAAGAACAAAAAGCACTAGTTCCAGAAGCGGCTTTGAGATGATTTGGGATCCGAATGGGTGGACTGAGACGGACAGTAGTTTCTCAGTGAAGCAAGACATTGTAGAAATAACTGACTGGTCAGGATATAGTGGGAGTTTTGTCCAGCATCCAGAACTGACAGGATTAGATTGCATGAGGCCTTGTTTCTGGGTTGAGCTAATCAGAGGGAAGCCCAAAGAGAACACAATTTGGACTAGCGGGAGCAGCATATCCTTTTGTGGTGTAAATAGTGACACTGTGGGTTGGTCTTGGCCAGACGGTGCTGAGTTGCCATTCACCATTGACAAGTAG</t>
         </is>
       </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
+      <c r="FI1" t="inlineStr">
         <is>
           <t>&gt;Flu-0406|A_MP</t>
         </is>
       </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
+      <c r="FJ1" t="inlineStr">
         <is>
           <t>ATGAGTCTTCTAACCGAGGTCGAAACGTACGTTCTCTCTATCGTCCCGTCGGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTTGAAGATGTCTTTGCAGGGAAGAACACCGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATCCTGTCACCTCTGACTAAGGGGATTTTGGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCTCTAAGTGGAACTGGAGACCCAAACAACATGGACAGGGCAGTCAAGTTGTACAGGAAACTAAAGAGAGAGATAACATTCCATGGTGCTAAAGAAGTTGCACTCAGTTACTCAACCGGTGCACTTGCCAGTTGTATGGGTCTCATATACAACAGGATGGGGACGGTGACCGCAGAAGTGGCATTGGGCCTAGTGTGTGCCACCTGTGAGCAGATTGCTGATTCACAGCATCGGTCTCACAGACAGATAGCTACCACCACCAACCCACTAATCAGACATGAAAACAGAATGGTTTTGGCCAGTACTACAGCTAAGGCTATGGAGCAGATGGCTGGATCGAGTGAGCAAGCAGTGGAAGCCATGGAGGTTGCTAGTCAGGCTAGGCAGATGGTGCAGGCGATGAGGACCATTGGAACTCATCCTAGCTCCAGTGCCGGTCTGAGAGATGATCTCCTTGAAAATTTGCAGGCCTACCAAAAACGGATGGGAGTGCAACTGCAGCGATTCAAGTGATCCTCTCGTTATTGCCGCAAGTATCATTGGGATCTTGCACTTGATATTGTGGATTCTTGATCGCCTTTTCTTCAAATGCGTTTATCGTCGCCTTAAATACGGTTTGAAAGGAGGGCCTTCTACGGAAGGAGTACCTGAGTCCATGAGGGAAGAGTACCGGCAGGAACAGCAGAGTGCTGTGGATGTTGACGATGGTCATTTTGTCAACATAGAGCTGGAGTAA</t>
         </is>
       </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
+      <c r="FK1" t="inlineStr">
         <is>
           <t>&gt;Flu-0406|A_NS</t>
         </is>
       </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
+      <c r="FL1" t="inlineStr">
         <is>
           <t>ATGGATTCCAACACTGTGTCAAGCTTTCAGGTAGACTGCTTTCTTTGGCATGTCCGCAAACGATTTGCAGACCAAGAACTGGGTGATGCCCCATTCCTTGACCGGCTCCGCCGAGACCAGAAGTCTCTAAGAGGAAGAAGCAGCACTCTTGGTCTGGACATCGAGACGGCCACTCGTGCTGGAAAGCAGATAGTGGAGAGGATTCTGGAGGAAGAATCCGACGAGGCACTCAAAATGACTATTGCCTCTGTGTCTGCTCCACGCTACCTAACTGACATGACTCTTGAAGAGATGTCAAGAGACTGGTTCATGCTCATGCCCAAGCAAAAAATGGCAGGCTCCCTCAGTATCAAAATGGACCAGGCGATTATGGATAAGAAAATCATACTGAAGGCAAACTTCAGTGTGATCTTCAATCGGCTGGAGACACTAATACTACTCAGAGCTTTCACTGAAGAAGGAGCAATTGTCGGCGAAATTTCACCATTGCCTTCTCTTCCAGGACATACTGATGAGGATGTCAAAAATGCAATTGGGGTCCTCATCGGAGGACTTGAATGGAATGATAACACAGTTCGAGTCTCTGAAACTTTACAGAGATTCGCTTGGAGAAGCAGTAATGAGGATGGGAGATCTCCACTCCCTCCAAAGCAGAAACGGAAAATGGAGAGAACAATTGAGTCAGAAGTTTGAAGAAATAAGGTGGCTGATTGRAGAAGTTCGACACAGACTAAAGATCACAGAAAATAGTTTTGAACAAATAACATTTATGCAAGCCTTACAACTACTGCTTGAAGTGGAGCAAGAGATAAGAACTTTCTCGTTTCAGCTTATTTAA</t>
         </is>
